--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -4845,54 +4845,52 @@
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1553997553</v>
+        <v>1393281432</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>0.632</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45623.53527240741</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G69" t="n">
-        <v>20.7084</v>
+        <v>5.981</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45623.57548773148</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I69" t="n">
-        <v>20.7775</v>
+        <v>5.967</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>20.7706</v>
-      </c>
-      <c r="O69" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="P69" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4903,61 +4901,59 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1554074835</v>
+        <v>1393281260</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.01</v>
+        <v>0.5612</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45623.57516572917</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G70" t="n">
-        <v>20.7426</v>
+        <v>5.812</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45623.57574133102</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I70" t="n">
-        <v>20.7764</v>
+        <v>5.81</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.26</v>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>5</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
@@ -4968,14 +4964,14 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>-1.63</v>
+        <v>0</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1555669398</v>
+        <v>1553997553</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4984,23 +4980,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45624.55073625</v>
+        <v>45623.53527240741</v>
       </c>
       <c r="G71" t="n">
-        <v>20.3273</v>
+        <v>20.7084</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45624.71914708333</v>
+        <v>45623.57548773148</v>
       </c>
       <c r="I71" t="n">
-        <v>20.4312</v>
+        <v>20.7775</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5015,13 +5011,13 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>20.1748</v>
+        <v>20.7706</v>
       </c>
       <c r="O71" t="n">
-        <v>20.4293</v>
+        <v>20.68</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -5033,22 +5029,22 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>10.17</v>
+        <v>-3.33</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>[T/P]</t>
+          <t>[S/L]</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1563562241</v>
+        <v>1393281260</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5057,41 +5053,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.02</v>
+        <v>0.555</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45631.25027201389</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G72" t="n">
-        <v>20.3099</v>
+        <v>5.812</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45631.6258153125</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I72" t="n">
-        <v>20.2391</v>
+        <v>5.801</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="O72" t="n">
-        <v>20.3672</v>
-      </c>
-      <c r="P72" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
@@ -5102,22 +5096,18 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1473693877</v>
+        <v>1393281432</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5126,35 +5116,35 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.019</v>
+        <v>0.4344</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45562.69351818287</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G73" t="n">
-        <v>700.8</v>
+        <v>5.981</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I73" t="n">
-        <v>623.8</v>
+        <v>5.968</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>14.97</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>12.28</v>
+        <v>2.59</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -5169,18 +5159,18 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-2.69</v>
+        <v>-0.01</v>
       </c>
       <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1493848938</v>
+        <v>1393281260</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5189,35 +5179,35 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45579.70088467593</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G74" t="n">
-        <v>640.3</v>
+        <v>5.812</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I74" t="n">
-        <v>623.8</v>
+        <v>5.814</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>14.96</v>
+        <v>5.81</v>
       </c>
       <c r="M74" t="n">
-        <v>13.77</v>
+        <v>5.81</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -5232,18 +5222,18 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>-1.19</v>
+        <v>0</v>
       </c>
       <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1583724019</v>
+        <v>1393281432</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5252,41 +5242,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45646.60647967592</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G75" t="n">
-        <v>20.2054</v>
+        <v>5.981</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45646.696485625</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I75" t="n">
-        <v>20.1035</v>
+        <v>5.978</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
-        <v>20.1055</v>
-      </c>
-      <c r="O75" t="n">
-        <v>20.3273</v>
-      </c>
-      <c r="P75" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
@@ -5297,18 +5285,14 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>-10.13</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1583841034</v>
+        <v>1554074835</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5317,23 +5301,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0.01</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45646.63988152778</v>
+        <v>45623.57516572917</v>
       </c>
       <c r="G76" t="n">
-        <v>20.173</v>
+        <v>20.7426</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45646.70582428241</v>
+        <v>45623.57574133102</v>
       </c>
       <c r="I76" t="n">
-        <v>20.0949</v>
+        <v>20.7764</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5347,12 +5331,8 @@
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
-        <v>20.0975</v>
-      </c>
-      <c r="O76" t="n">
-        <v>20.2542</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
         <v>5</v>
       </c>
@@ -5366,22 +5346,18 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-1.63</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1585474078</v>
+        <v>1393281260</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5390,41 +5366,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.02</v>
+        <v>0.4206</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45649.40133020833</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G77" t="n">
-        <v>20.0935</v>
+        <v>5.812</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45649.56824730324</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I77" t="n">
-        <v>20.1707</v>
+        <v>5.826</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="n">
-        <v>20</v>
-      </c>
-      <c r="O77" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="P77" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
@@ -5435,22 +5409,18 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1586033461</v>
+        <v>1393281432</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5459,41 +5429,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.01</v>
+        <v>0.4033</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45649.63114609953</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G78" t="n">
-        <v>20.1772</v>
+        <v>5.981</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45649.63200465278</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I78" t="n">
-        <v>20.1671</v>
+        <v>5.98</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>20.1687</v>
-      </c>
-      <c r="O78" t="n">
-        <v>20.2379</v>
-      </c>
-      <c r="P78" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
@@ -5504,18 +5472,14 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1587036381</v>
+        <v>1555669398</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -5531,16 +5495,16 @@
         <v>0.02</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45650.48790526621</v>
+        <v>45624.55073625</v>
       </c>
       <c r="G79" t="n">
-        <v>20.1462</v>
+        <v>20.3273</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45650.58025611111</v>
+        <v>45624.71914708333</v>
       </c>
       <c r="I79" t="n">
-        <v>20.1627</v>
+        <v>20.4312</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5555,10 +5519,10 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>20.1627</v>
+        <v>20.1748</v>
       </c>
       <c r="O79" t="n">
-        <v>20.22</v>
+        <v>20.4293</v>
       </c>
       <c r="P79" t="n">
         <v>10</v>
@@ -5573,22 +5537,22 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>1.64</v>
+        <v>10.17</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>[S/L]</t>
+          <t>[T/P]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1500272843</v>
+        <v>1393281432</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5597,35 +5561,35 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0264</v>
+        <v>0.4201</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G80" t="n">
-        <v>718.5</v>
+        <v>5.981</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45663.67045758102</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I80" t="n">
-        <v>757.79</v>
+        <v>5.98</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>18.97</v>
+        <v>2.51</v>
       </c>
       <c r="M80" t="n">
-        <v>20.01</v>
+        <v>2.51</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
@@ -5640,18 +5604,18 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1500272843</v>
+        <v>1393281432</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5660,35 +5624,35 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0021</v>
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G81" t="n">
-        <v>718.5</v>
+        <v>5.981</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45663.67059782407</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I81" t="n">
-        <v>758.27</v>
+        <v>6.186</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.51</v>
+        <v>5.98</v>
       </c>
       <c r="M81" t="n">
-        <v>1.59</v>
+        <v>6.19</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
@@ -5703,18 +5667,18 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1518147105</v>
+        <v>1563562241</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5723,19 +5687,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45597.8504690162</v>
+        <v>45631.25027201389</v>
       </c>
       <c r="G82" t="n">
-        <v>10.92</v>
+        <v>20.3099</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45667.68126778935</v>
+        <v>45631.6258153125</v>
       </c>
       <c r="I82" t="n">
-        <v>6.52</v>
+        <v>20.2391</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5747,15 +5711,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="M82" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="O82" t="n">
+        <v>20.3672</v>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
@@ -5766,18 +5732,22 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="U82" t="inlineStr"/>
+        <v>-6.99</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1551373923</v>
+        <v>1393281260</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5786,35 +5756,35 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1195</v>
+        <v>1.4632</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45621.85639895833</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G83" t="n">
-        <v>167.24</v>
+        <v>5.812</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45678.70646498843</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I83" t="n">
-        <v>198.83</v>
+        <v>6.02</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>19.99</v>
+        <v>8.5</v>
       </c>
       <c r="M83" t="n">
-        <v>23.76</v>
+        <v>8.81</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
@@ -5829,18 +5799,18 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.77</v>
+        <v>0.3</v>
       </c>
       <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1373744560</v>
+        <v>1393287040</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5849,35 +5819,35 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1248</v>
+        <v>0.2503</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45476.64586885417</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G84" t="n">
-        <v>202.58</v>
+        <v>5.811</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I84" t="n">
-        <v>172.09</v>
+        <v>6.02</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>25.28</v>
+        <v>1.45</v>
       </c>
       <c r="M84" t="n">
-        <v>21.48</v>
+        <v>1.51</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
@@ -5892,18 +5862,18 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>-3.8</v>
+        <v>0.06</v>
       </c>
       <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1450039117</v>
+        <v>1403180431</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5912,35 +5882,35 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.068</v>
+        <v>0.2773</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45544.65070009259</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G85" t="n">
-        <v>161.58</v>
+        <v>5.84</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I85" t="n">
-        <v>172.09</v>
+        <v>6.02</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>10.99</v>
+        <v>1.62</v>
       </c>
       <c r="M85" t="n">
-        <v>11.7</v>
+        <v>1.67</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
@@ -5955,18 +5925,18 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1468472119</v>
+        <v>1403180445</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5975,35 +5945,35 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45559.65212880787</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G86" t="n">
-        <v>277.82</v>
+        <v>5.836</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I86" t="n">
-        <v>336.69</v>
+        <v>6.02</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>19.98</v>
+        <v>0.05</v>
       </c>
       <c r="M86" t="n">
-        <v>24.21</v>
+        <v>0.06</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
@@ -6018,18 +5988,18 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>4.23</v>
+        <v>0.01</v>
       </c>
       <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1470564087</v>
+        <v>1393735509</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6038,35 +6008,35 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0742</v>
+        <v>0.0366</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45560.82041144676</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G87" t="n">
-        <v>269.23</v>
+        <v>67.37</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I87" t="n">
-        <v>336.69</v>
+        <v>71.16</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>19.98</v>
+        <v>2.47</v>
       </c>
       <c r="M87" t="n">
-        <v>24.98</v>
+        <v>2.6</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
@@ -6081,18 +6051,18 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>5</v>
+        <v>0.13</v>
       </c>
       <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1599434998</v>
+        <v>1395218355</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6101,35 +6071,35 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0477</v>
+        <v>0.074</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45663.73100940972</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G88" t="n">
-        <v>313.98</v>
+        <v>67.13</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I88" t="n">
-        <v>336.69</v>
+        <v>71.16</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>14.98</v>
+        <v>4.97</v>
       </c>
       <c r="M88" t="n">
-        <v>16.06</v>
+        <v>5.27</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -6144,18 +6114,18 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1495548850</v>
+        <v>1473693877</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6164,19 +6134,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.1047</v>
+        <v>0.019</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45580.70599549769</v>
+        <v>45562.69351818287</v>
       </c>
       <c r="G89" t="n">
-        <v>133.61</v>
+        <v>700.8</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I89" t="n">
-        <v>143.18</v>
+        <v>623.8</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6189,10 +6159,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>13.99</v>
+        <v>14.97</v>
       </c>
       <c r="M89" t="n">
-        <v>14.99</v>
+        <v>12.28</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
@@ -6207,18 +6177,18 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
+        <v>-2.69</v>
       </c>
       <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1517512112</v>
+        <v>1403166009</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6227,35 +6197,35 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0362</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45597.61040866898</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G90" t="n">
-        <v>132.62</v>
+        <v>68.05</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I90" t="n">
-        <v>143.18</v>
+        <v>71.16</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>2.46</v>
       </c>
       <c r="M90" t="n">
-        <v>10.8</v>
+        <v>2.58</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
@@ -6270,18 +6240,18 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.8</v>
+        <v>0.12</v>
       </c>
       <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1582735114</v>
+        <v>1403177543</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6290,35 +6260,35 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45645.90076787037</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G91" t="n">
-        <v>130.51</v>
+        <v>68.045</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I91" t="n">
-        <v>143.18</v>
+        <v>71.16</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>9.960000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="M91" t="n">
-        <v>10.92</v>
+        <v>2.62</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -6333,18 +6303,18 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.96</v>
+        <v>0.12</v>
       </c>
       <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1657658561</v>
+        <v>1403180429</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6353,41 +6323,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.02</v>
+        <v>0.0733</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45702.18774210648</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G92" t="n">
-        <v>20.4257</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45702.56168643518</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I92" t="n">
-        <v>20.3656</v>
+        <v>71.16</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
-        <v>20.3664</v>
-      </c>
-      <c r="O92" t="n">
-        <v>20.5213</v>
-      </c>
-      <c r="P92" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M92" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
@@ -6398,22 +6366,18 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1660829104</v>
+        <v>1403180445</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6422,41 +6386,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.02</v>
+        <v>0.9908</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45705.64981799768</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G93" t="n">
-        <v>20.3237</v>
+        <v>5.836</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45705.72866341435</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I93" t="n">
-        <v>20.2738</v>
+        <v>6.027</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>20.2738</v>
-      </c>
-      <c r="O93" t="n">
-        <v>20.3936</v>
-      </c>
-      <c r="P93" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M93" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
@@ -6467,22 +6429,18 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1378903852</v>
+        <v>1493848938</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6491,19 +6449,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0616</v>
+        <v>0.0213</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45579.70088467593</v>
       </c>
       <c r="G94" t="n">
-        <v>227.77</v>
+        <v>640.3</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45706.65274813658</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I94" t="n">
-        <v>243.58</v>
+        <v>623.8</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6516,10 +6474,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>14.03</v>
+        <v>14.96</v>
       </c>
       <c r="M94" t="n">
-        <v>15</v>
+        <v>13.77</v>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
@@ -6534,18 +6492,18 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.97</v>
+        <v>-1.19</v>
       </c>
       <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1378903852</v>
+        <v>1393281432</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6554,35 +6512,35 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0042</v>
+        <v>0.1102</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G95" t="n">
-        <v>227.77</v>
+        <v>5.981</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I95" t="n">
-        <v>243.45</v>
+        <v>6.176</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="M95" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
@@ -6597,18 +6555,18 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1456814919</v>
+        <v>1393301698</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6617,35 +6575,35 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0665</v>
+        <v>0.1401</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45548.6657375</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G96" t="n">
-        <v>222.94</v>
+        <v>5.99</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I96" t="n">
-        <v>243.45</v>
+        <v>6.176</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>14.83</v>
+        <v>0.84</v>
       </c>
       <c r="M96" t="n">
-        <v>16.19</v>
+        <v>0.87</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6660,18 +6618,18 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>1.36</v>
+        <v>0.03</v>
       </c>
       <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1499061783</v>
+        <v>1403180427</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6680,19 +6638,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0558</v>
+        <v>0.4203</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45582.73996877314</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G97" t="n">
-        <v>232.2</v>
+        <v>5.989</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I97" t="n">
-        <v>243.45</v>
+        <v>6.176</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6701,14 +6659,14 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>12.96</v>
+        <v>2.52</v>
       </c>
       <c r="M97" t="n">
-        <v>13.58</v>
+        <v>2.6</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -6723,14 +6681,14 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1717095547</v>
+        <v>1583724019</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -6743,19 +6701,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45736.81342114583</v>
+        <v>45646.60647967592</v>
       </c>
       <c r="G98" t="n">
-        <v>20.1198</v>
+        <v>20.2054</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45737.11337774306</v>
+        <v>45646.696485625</v>
       </c>
       <c r="I98" t="n">
-        <v>20.1348</v>
+        <v>20.1035</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6770,25 +6728,25 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>20.1349</v>
+        <v>20.1055</v>
       </c>
       <c r="O98" t="n">
-        <v>20.1623</v>
+        <v>20.3273</v>
       </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.98</v>
+        <v>-10.13</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -6799,11 +6757,11 @@
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1554741910</v>
+        <v>1583841034</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6812,19 +6770,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45623.74951100694</v>
+        <v>45646.63988152778</v>
       </c>
       <c r="G99" t="n">
-        <v>15.3</v>
+        <v>20.173</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45741.87177293981</v>
+        <v>45646.70582428241</v>
       </c>
       <c r="I99" t="n">
-        <v>20.29</v>
+        <v>20.0949</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6836,15 +6794,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L99" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="M99" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>20.0975</v>
+      </c>
+      <c r="O99" t="n">
+        <v>20.2542</v>
+      </c>
+      <c r="P99" t="n">
+        <v>5</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -6855,18 +6815,22 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U99" t="inlineStr"/>
+        <v>-3.88</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1414372592</v>
+        <v>1585474078</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6875,19 +6839,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45511.7228721412</v>
+        <v>45649.40133020833</v>
       </c>
       <c r="G100" t="n">
-        <v>455.4</v>
+        <v>20.0935</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45742.77596394676</v>
+        <v>45649.56824730324</v>
       </c>
       <c r="I100" t="n">
-        <v>547.14</v>
+        <v>20.1707</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6899,15 +6863,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="M100" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>20</v>
+      </c>
+      <c r="O100" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
@@ -6918,18 +6884,22 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U100" t="inlineStr"/>
+        <v>7.65</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1450043624</v>
+        <v>1586033461</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6938,19 +6908,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0138</v>
+        <v>0.01</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45649.63114609953</v>
       </c>
       <c r="G101" t="n">
-        <v>147.48</v>
+        <v>20.1772</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45743.76599777778</v>
+        <v>45649.63200465278</v>
       </c>
       <c r="I101" t="n">
-        <v>139.86</v>
+        <v>20.1671</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6962,15 +6932,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L101" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>20.1687</v>
+      </c>
+      <c r="O101" t="n">
+        <v>20.2379</v>
+      </c>
+      <c r="P101" t="n">
+        <v>5</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -6981,18 +6953,22 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U101" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1358151307</v>
+        <v>1587036381</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7001,19 +6977,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0124</v>
+        <v>0.02</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45460.88529037037</v>
+        <v>45650.48790526621</v>
       </c>
       <c r="G102" t="n">
-        <v>165.93</v>
+        <v>20.1462</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45743.76632650463</v>
+        <v>45650.58025611111</v>
       </c>
       <c r="I102" t="n">
-        <v>149.33</v>
+        <v>20.1627</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7025,15 +7001,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>20.1627</v>
+      </c>
+      <c r="O102" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="P102" t="n">
+        <v>10</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
@@ -7044,18 +7022,22 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="U102" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1422773288</v>
+        <v>1500272843</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7064,19 +7046,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.2</v>
+        <v>0.0264</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45518.84428505787</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G103" t="n">
-        <v>51.24</v>
+        <v>718.5</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45743.76769060185</v>
+        <v>45663.67045758102</v>
       </c>
       <c r="I103" t="n">
-        <v>58.08</v>
+        <v>757.79</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7089,10 +7071,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10.25</v>
+        <v>18.97</v>
       </c>
       <c r="M103" t="n">
-        <v>11.62</v>
+        <v>20.01</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -7107,18 +7089,18 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1631473921</v>
+        <v>1500272843</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7127,19 +7109,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.2745</v>
+        <v>0.0021</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45685.8356116088</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G104" t="n">
-        <v>40.05</v>
+        <v>718.5</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45663.67059782407</v>
       </c>
       <c r="I104" t="n">
-        <v>44.8</v>
+        <v>758.27</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7148,14 +7130,14 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>10.99</v>
+        <v>1.51</v>
       </c>
       <c r="M104" t="n">
-        <v>12.3</v>
+        <v>1.59</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -7170,18 +7152,18 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1642763333</v>
+        <v>1518147105</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MAXN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7190,19 +7172,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2459</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45692.86672944445</v>
+        <v>45597.8504690162</v>
       </c>
       <c r="G105" t="n">
-        <v>40.66</v>
+        <v>10.92</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45667.68126778935</v>
       </c>
       <c r="I105" t="n">
-        <v>44.8</v>
+        <v>6.52</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7211,14 +7193,14 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>10.92</v>
       </c>
       <c r="M105" t="n">
-        <v>11.02</v>
+        <v>6.52</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -7233,18 +7215,18 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>1.02</v>
+        <v>-4.4</v>
       </c>
       <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1666451221</v>
+        <v>1551373923</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7253,19 +7235,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1796</v>
+        <v>0.1195</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45621.85639895833</v>
       </c>
       <c r="G106" t="n">
-        <v>43</v>
+        <v>167.24</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45678.70646498843</v>
       </c>
       <c r="I106" t="n">
-        <v>44.8</v>
+        <v>198.83</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7274,14 +7256,14 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>7.72</v>
+        <v>19.99</v>
       </c>
       <c r="M106" t="n">
-        <v>8.050000000000001</v>
+        <v>23.76</v>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
@@ -7296,57 +7278,59 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>0.33</v>
+        <v>3.77</v>
       </c>
       <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1749053104</v>
+        <v>1373744560</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.01</v>
+        <v>0.1248</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45754.65117414352</v>
+        <v>45476.64586885417</v>
       </c>
       <c r="G107" t="n">
-        <v>4903.7</v>
+        <v>202.58</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45754.65218731482</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I107" t="n">
-        <v>4891.1</v>
+        <v>172.09</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="M107" t="n">
+        <v>21.48</v>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="n">
-        <v>12.26</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
@@ -7357,57 +7341,59 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>6.3</v>
+        <v>-3.8</v>
       </c>
       <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1756767326</v>
+        <v>1450039117</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.01</v>
+        <v>0.068</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45756.64805717592</v>
+        <v>45544.65070009259</v>
       </c>
       <c r="G108" t="n">
-        <v>5004.7</v>
+        <v>161.58</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45756.64937413194</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I108" t="n">
-        <v>5005.2</v>
+        <v>172.09</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11.7</v>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="n">
-        <v>12.51</v>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
@@ -7418,57 +7404,59 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>-0.25</v>
+        <v>0.71</v>
       </c>
       <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1756797155</v>
+        <v>1468472119</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.01</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45756.6510503125</v>
+        <v>45559.65212880787</v>
       </c>
       <c r="G109" t="n">
-        <v>4992.2</v>
+        <v>277.82</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45756.65185319445</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I109" t="n">
-        <v>5013.4</v>
+        <v>336.69</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M109" t="n">
+        <v>24.21</v>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
-        <v>12.48</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
@@ -7479,18 +7467,18 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>-10.6</v>
+        <v>4.23</v>
       </c>
       <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1767688540</v>
+        <v>1470564087</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7499,19 +7487,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.01</v>
+        <v>0.0742</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45761.6294487037</v>
+        <v>45560.82041144676</v>
       </c>
       <c r="G110" t="n">
-        <v>20.1226</v>
+        <v>269.23</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45761.66966099537</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I110" t="n">
-        <v>20.047</v>
+        <v>336.69</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7523,43 +7511,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="n">
-        <v>20.048</v>
-      </c>
-      <c r="O110" t="n">
-        <v>20.3404</v>
-      </c>
-      <c r="P110" t="n">
+      <c r="L110" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M110" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1768229183</v>
+        <v>1599434998</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7568,19 +7550,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.01</v>
+        <v>0.0477</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45761.71402207176</v>
+        <v>45663.73100940972</v>
       </c>
       <c r="G111" t="n">
-        <v>20.0759</v>
+        <v>313.98</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45761.77371288194</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I111" t="n">
-        <v>20.1099</v>
+        <v>336.69</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7592,17 +7574,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
-        <v>20.1099</v>
-      </c>
-      <c r="O111" t="n">
-        <v>20.2122</v>
-      </c>
-      <c r="P111" t="n">
-        <v>5</v>
-      </c>
+      <c r="L111" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M111" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
@@ -7613,22 +7593,18 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1.08</v>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1769815245</v>
+        <v>1495548850</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7637,19 +7613,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.01</v>
+        <v>0.1047</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45762.50265097222</v>
+        <v>45580.70599549769</v>
       </c>
       <c r="G112" t="n">
-        <v>20.0545</v>
+        <v>133.61</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45762.61225923611</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I112" t="n">
-        <v>19.9735</v>
+        <v>143.18</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7661,15 +7637,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="n">
-        <v>19.9742</v>
-      </c>
+      <c r="L112" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="M112" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>5</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
@@ -7680,22 +7656,18 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1666451221</v>
+        <v>1517512112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7704,19 +7676,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.0528</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45597.61040866898</v>
       </c>
       <c r="G113" t="n">
-        <v>43</v>
+        <v>132.62</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45764.85028728009</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I113" t="n">
-        <v>47.89</v>
+        <v>143.18</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7729,10 +7701,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="M113" t="n">
-        <v>2.53</v>
+        <v>10.8</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -7747,18 +7719,18 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1450043624</v>
+        <v>1582735114</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7767,23 +7739,23 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.1</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45645.90076787037</v>
       </c>
       <c r="G114" t="n">
-        <v>147.48</v>
+        <v>130.51</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45764.8517803588</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I114" t="n">
-        <v>143.22</v>
+        <v>143.18</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7792,10 +7764,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>14.75</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>14.32</v>
+        <v>10.92</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -7810,14 +7782,14 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>-0.42</v>
+        <v>0.96</v>
       </c>
       <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1777308201</v>
+        <v>1657658561</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -7830,19 +7802,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45768.12181488426</v>
+        <v>45702.18774210648</v>
       </c>
       <c r="G115" t="n">
-        <v>19.7053</v>
+        <v>20.4257</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45768.13306659722</v>
+        <v>45702.56168643518</v>
       </c>
       <c r="I115" t="n">
-        <v>19.7154</v>
+        <v>20.3656</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7856,10 +7828,14 @@
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>20.3664</v>
+      </c>
+      <c r="O115" t="n">
+        <v>20.5213</v>
+      </c>
       <c r="P115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -7871,14 +7847,18 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="U115" t="inlineStr"/>
+        <v>-5.9</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1781449563</v>
+        <v>1660829104</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -7891,19 +7871,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45769.73814164352</v>
+        <v>45705.64981799768</v>
       </c>
       <c r="G116" t="n">
-        <v>19.58</v>
+        <v>20.3237</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45769.76084202546</v>
+        <v>45705.72866341435</v>
       </c>
       <c r="I116" t="n">
-        <v>19.5255</v>
+        <v>20.2738</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7917,10 +7897,14 @@
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>20.2738</v>
+      </c>
+      <c r="O116" t="n">
+        <v>20.3936</v>
+      </c>
       <c r="P116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -7932,18 +7916,22 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="U116" t="inlineStr"/>
+        <v>-4.92</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1560258921</v>
+        <v>1378903852</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7952,19 +7940,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0.0616</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45629.37798611111</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G117" t="n">
-        <v>48.68</v>
+        <v>227.77</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45706.65274813658</v>
       </c>
       <c r="I117" t="n">
-        <v>44.15</v>
+        <v>243.58</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7977,10 +7965,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>51.41</v>
+        <v>14.03</v>
       </c>
       <c r="M117" t="n">
-        <v>49.84</v>
+        <v>15</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -7995,18 +7983,18 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>-1.57</v>
+        <v>0.97</v>
       </c>
       <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1748583646</v>
+        <v>1378903852</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8015,19 +8003,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.0042</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45754.57938657407</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G118" t="n">
-        <v>37.258</v>
+        <v>227.77</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I118" t="n">
-        <v>44.15</v>
+        <v>243.45</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8040,10 +8028,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>41.06</v>
+        <v>0.96</v>
       </c>
       <c r="M118" t="n">
-        <v>49.84</v>
+        <v>1.02</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8058,18 +8046,18 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>8.779999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1373808226</v>
+        <v>1456814919</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8078,19 +8066,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.0234</v>
+        <v>0.0665</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45476.6587916088</v>
+        <v>45548.6657375</v>
       </c>
       <c r="G119" t="n">
-        <v>459.24</v>
+        <v>222.94</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I119" t="n">
-        <v>434.71</v>
+        <v>243.45</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8103,10 +8091,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>10.75</v>
+        <v>14.83</v>
       </c>
       <c r="M119" t="n">
-        <v>10.17</v>
+        <v>16.19</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8121,18 +8109,18 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>-0.58</v>
+        <v>1.36</v>
       </c>
       <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1426782063</v>
+        <v>1499061783</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8141,23 +8129,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0372</v>
+        <v>0.0558</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45582.73996877314</v>
       </c>
       <c r="G120" t="n">
-        <v>419.46</v>
+        <v>232.2</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I120" t="n">
-        <v>434.71</v>
+        <v>243.45</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8166,10 +8154,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>15.6</v>
+        <v>12.96</v>
       </c>
       <c r="M120" t="n">
-        <v>16.17</v>
+        <v>13.58</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -8184,18 +8172,18 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1426782063</v>
+        <v>1717095547</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8204,19 +8192,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45736.81342114583</v>
       </c>
       <c r="G121" t="n">
-        <v>419.46</v>
+        <v>20.1198</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45785.65885817129</v>
+        <v>45737.11337774306</v>
       </c>
       <c r="I121" t="n">
-        <v>437.05</v>
+        <v>20.1348</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8228,37 +8216,43 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="M121" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>20.1349</v>
+      </c>
+      <c r="O121" t="n">
+        <v>20.1623</v>
+      </c>
+      <c r="P121" t="n">
+        <v>20</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U121" t="inlineStr"/>
+        <v>2.98</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1744929368</v>
+        <v>1554741910</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8267,23 +8261,23 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.0424</v>
+        <v>0.61</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45751.7450085301</v>
+        <v>45623.74951100694</v>
       </c>
       <c r="G122" t="n">
-        <v>324.48</v>
+        <v>15.3</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45785.65909077547</v>
+        <v>45741.87177293981</v>
       </c>
       <c r="I122" t="n">
-        <v>353.02</v>
+        <v>20.29</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8292,10 +8286,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>13.76</v>
+        <v>9.33</v>
       </c>
       <c r="M122" t="n">
-        <v>14.97</v>
+        <v>12.38</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -8310,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="U122" t="inlineStr"/>
     </row>
@@ -8330,7 +8324,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.0229</v>
+        <v>0.01</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>45511.7228721412</v>
@@ -8339,10 +8333,10 @@
         <v>455.4</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45742.77596394676</v>
       </c>
       <c r="I123" t="n">
-        <v>568.9299999999999</v>
+        <v>547.14</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8355,10 +8349,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>10.43</v>
+        <v>4.55</v>
       </c>
       <c r="M123" t="n">
-        <v>13.03</v>
+        <v>5.47</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -8373,18 +8367,18 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>2.6</v>
+        <v>0.92</v>
       </c>
       <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1582737192</v>
+        <v>1450043624</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8393,23 +8387,23 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.0371</v>
+        <v>0.0138</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45645.90143914352</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G124" t="n">
-        <v>524.4299999999999</v>
+        <v>147.48</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45743.76599777778</v>
       </c>
       <c r="I124" t="n">
-        <v>568.9299999999999</v>
+        <v>139.86</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8418,10 +8412,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>19.46</v>
+        <v>2.04</v>
       </c>
       <c r="M124" t="n">
-        <v>21.11</v>
+        <v>1.93</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -8436,18 +8430,18 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>1.65</v>
+        <v>-0.11</v>
       </c>
       <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1599454287</v>
+        <v>1358151307</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8456,19 +8450,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45663.73715268519</v>
+        <v>45460.88529037037</v>
       </c>
       <c r="G125" t="n">
-        <v>196.49</v>
+        <v>165.93</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45743.76632650463</v>
       </c>
       <c r="I125" t="n">
-        <v>196.89</v>
+        <v>149.33</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8481,10 +8475,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>14.99</v>
+        <v>2.06</v>
       </c>
       <c r="M125" t="n">
-        <v>15.02</v>
+        <v>1.85</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -8499,18 +8493,18 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.03</v>
+        <v>-0.21</v>
       </c>
       <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1621495599</v>
+        <v>1422773288</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8519,19 +8513,19 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45678.83206015046</v>
+        <v>45518.84428505787</v>
       </c>
       <c r="G126" t="n">
-        <v>183.39</v>
+        <v>51.24</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45743.76769060185</v>
       </c>
       <c r="I126" t="n">
-        <v>196.89</v>
+        <v>58.08</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8544,10 +8538,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>14.98</v>
+        <v>10.25</v>
       </c>
       <c r="M126" t="n">
-        <v>16.09</v>
+        <v>11.62</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
@@ -8562,18 +8556,18 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1631467534</v>
+        <v>1631473921</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8582,19 +8576,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.2745</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45685.83235356482</v>
+        <v>45685.8356116088</v>
       </c>
       <c r="G127" t="n">
-        <v>159.74</v>
+        <v>40.05</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I127" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8603,14 +8597,14 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>14.97</v>
+        <v>10.99</v>
       </c>
       <c r="M127" t="n">
-        <v>18.45</v>
+        <v>12.3</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
@@ -8625,18 +8619,18 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>3.48</v>
+        <v>1.31</v>
       </c>
       <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1666449688</v>
+        <v>1642763333</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8645,19 +8639,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.2459</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45708.67996841436</v>
+        <v>45692.86672944445</v>
       </c>
       <c r="G128" t="n">
-        <v>160.68</v>
+        <v>40.66</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I128" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8666,14 +8660,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>18.35</v>
+        <v>11.02</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
@@ -8688,18 +8682,18 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>3.37</v>
+        <v>1.02</v>
       </c>
       <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1701098878</v>
+        <v>1666451221</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8708,19 +8702,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.0051</v>
+        <v>0.1796</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G129" t="n">
-        <v>139.41</v>
+        <v>43</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I129" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8729,14 +8723,14 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.71</v>
+        <v>7.72</v>
       </c>
       <c r="M129" t="n">
-        <v>1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
@@ -8751,59 +8745,57 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>1701098878</v>
+        <v>1749053104</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45754.65117414352</v>
       </c>
       <c r="G130" t="n">
-        <v>139.41</v>
+        <v>4903.7</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45792.64655003473</v>
+        <v>45754.65218731482</v>
       </c>
       <c r="I130" t="n">
-        <v>188.02</v>
+        <v>4891.1</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="M130" t="n">
-        <v>18.8</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>12.26</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
@@ -8814,59 +8806,57 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4.86</v>
+        <v>6.3</v>
       </c>
       <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1426782063</v>
+        <v>1756767326</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.0004</v>
+        <v>0.01</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45756.64805717592</v>
       </c>
       <c r="G131" t="n">
-        <v>419.46</v>
+        <v>5004.7</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45756.64937413194</v>
       </c>
       <c r="I131" t="n">
-        <v>452.34</v>
+        <v>5005.2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0.18</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>12.51</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
@@ -8877,59 +8867,57 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>1481614059</v>
+        <v>1756797155</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.0359</v>
+        <v>0.01</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45568.77505349537</v>
+        <v>45756.6510503125</v>
       </c>
       <c r="G132" t="n">
-        <v>417.1</v>
+        <v>4992.2</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45756.65185319445</v>
       </c>
       <c r="I132" t="n">
-        <v>452.34</v>
+        <v>5013.4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="M132" t="n">
-        <v>16.24</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>12.48</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
@@ -8940,18 +8928,18 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>1.27</v>
+        <v>-10.6</v>
       </c>
       <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1517514880</v>
+        <v>1767688540</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8960,19 +8948,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.0037</v>
+        <v>0.01</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45597.6108722338</v>
+        <v>45761.6294487037</v>
       </c>
       <c r="G133" t="n">
-        <v>409.38</v>
+        <v>20.1226</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45761.66966099537</v>
       </c>
       <c r="I133" t="n">
-        <v>452.34</v>
+        <v>20.047</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8984,15 +8972,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L133" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M133" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>20.048</v>
+      </c>
+      <c r="O133" t="n">
+        <v>20.3404</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
@@ -9003,18 +8993,22 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U133" t="inlineStr"/>
+        <v>-3.77</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1393281432</v>
+        <v>1768229183</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9023,39 +9017,41 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.632</v>
+        <v>0.01</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45761.71402207176</v>
       </c>
       <c r="G134" t="n">
-        <v>5.981</v>
+        <v>20.0759</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45761.77371288194</v>
       </c>
       <c r="I134" t="n">
-        <v>5.967</v>
+        <v>20.1099</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>20.1099</v>
+      </c>
+      <c r="O134" t="n">
+        <v>20.2122</v>
+      </c>
+      <c r="P134" t="n">
+        <v>5</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
@@ -9066,18 +9062,22 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U134" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1393281260</v>
+        <v>1769815245</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9086,39 +9086,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.5612</v>
+        <v>0.01</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45762.50265097222</v>
       </c>
       <c r="G135" t="n">
-        <v>5.812</v>
+        <v>20.0545</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45762.61225923611</v>
       </c>
       <c r="I135" t="n">
-        <v>5.81</v>
+        <v>19.9735</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N135" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>19.9742</v>
+      </c>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>5</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
@@ -9129,18 +9129,22 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="inlineStr"/>
+        <v>-4.06</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1393281260</v>
+        <v>1666451221</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9149,35 +9153,35 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.555</v>
+        <v>0.0528</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G136" t="n">
-        <v>5.812</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45764.85028728009</v>
       </c>
       <c r="I136" t="n">
-        <v>5.801</v>
+        <v>47.89</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.23</v>
+        <v>2.27</v>
       </c>
       <c r="M136" t="n">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -9192,18 +9196,18 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>-0.01</v>
+        <v>0.25</v>
       </c>
       <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1393281432</v>
+        <v>1450043624</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9212,35 +9216,35 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.4344</v>
+        <v>0.1</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G137" t="n">
-        <v>5.981</v>
+        <v>147.48</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45764.8517803588</v>
       </c>
       <c r="I137" t="n">
-        <v>5.968</v>
+        <v>143.22</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.6</v>
+        <v>14.75</v>
       </c>
       <c r="M137" t="n">
-        <v>2.59</v>
+        <v>14.32</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -9255,18 +9259,18 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>-0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1393281260</v>
+        <v>1777308201</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9275,39 +9279,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45768.12181488426</v>
       </c>
       <c r="G138" t="n">
-        <v>5.812</v>
+        <v>19.7053</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45768.13306659722</v>
       </c>
       <c r="I138" t="n">
-        <v>5.814</v>
+        <v>19.7154</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="M138" t="n">
-        <v>5.81</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>5</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
@@ -9318,18 +9320,18 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1393281432</v>
+        <v>1781449563</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9338,39 +9340,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45769.73814164352</v>
       </c>
       <c r="G139" t="n">
-        <v>5.981</v>
+        <v>19.58</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45769.76084202546</v>
       </c>
       <c r="I139" t="n">
-        <v>5.978</v>
+        <v>19.5255</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M139" t="n">
-        <v>5.98</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>5</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
@@ -9381,18 +9381,18 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>-2.79</v>
       </c>
       <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1393281260</v>
+        <v>1560258921</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9401,35 +9401,35 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.4206</v>
+        <v>1</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45629.37798611111</v>
       </c>
       <c r="G140" t="n">
-        <v>5.812</v>
+        <v>48.68</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I140" t="n">
-        <v>5.826</v>
+        <v>44.15</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.44</v>
+        <v>51.41</v>
       </c>
       <c r="M140" t="n">
-        <v>2.45</v>
+        <v>49.84</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -9444,18 +9444,18 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0.01</v>
+        <v>-1.57</v>
       </c>
       <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1393281432</v>
+        <v>1748583646</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9464,35 +9464,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.4033</v>
+        <v>1</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45754.57938657407</v>
       </c>
       <c r="G141" t="n">
-        <v>5.981</v>
+        <v>37.258</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I141" t="n">
-        <v>5.98</v>
+        <v>44.15</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.41</v>
+        <v>41.06</v>
       </c>
       <c r="M141" t="n">
-        <v>2.41</v>
+        <v>49.84</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -9507,18 +9507,18 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1393281432</v>
+        <v>1373808226</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9527,35 +9527,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.4201</v>
+        <v>0.0234</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45476.6587916088</v>
       </c>
       <c r="G142" t="n">
-        <v>5.981</v>
+        <v>459.24</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I142" t="n">
-        <v>5.98</v>
+        <v>434.71</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.51</v>
+        <v>10.75</v>
       </c>
       <c r="M142" t="n">
-        <v>2.51</v>
+        <v>10.17</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -9570,18 +9570,18 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1393281432</v>
+        <v>1426782063</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9590,35 +9590,35 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.0372</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G143" t="n">
-        <v>5.981</v>
+        <v>419.46</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I143" t="n">
-        <v>6.186</v>
+        <v>434.71</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>5.98</v>
+        <v>15.6</v>
       </c>
       <c r="M143" t="n">
-        <v>6.19</v>
+        <v>16.17</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -9633,18 +9633,18 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>1393281260</v>
+        <v>1426782063</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9653,35 +9653,35 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1.4632</v>
+        <v>0.01</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G144" t="n">
-        <v>5.812</v>
+        <v>419.46</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45785.65885817129</v>
       </c>
       <c r="I144" t="n">
-        <v>6.02</v>
+        <v>437.05</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>8.5</v>
+        <v>4.19</v>
       </c>
       <c r="M144" t="n">
-        <v>8.81</v>
+        <v>4.37</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -9696,18 +9696,18 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>1393287040</v>
+        <v>1744929368</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9716,19 +9716,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.2503</v>
+        <v>0.0424</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45751.7450085301</v>
       </c>
       <c r="G145" t="n">
-        <v>5.811</v>
+        <v>324.48</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45785.65909077547</v>
       </c>
       <c r="I145" t="n">
-        <v>6.02</v>
+        <v>353.02</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -9737,14 +9737,14 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.45</v>
+        <v>13.76</v>
       </c>
       <c r="M145" t="n">
-        <v>1.51</v>
+        <v>14.97</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
@@ -9759,18 +9759,18 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0.06</v>
+        <v>1.21</v>
       </c>
       <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>1403180431</v>
+        <v>1414372592</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9779,35 +9779,35 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.2773</v>
+        <v>0.0229</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45511.7228721412</v>
       </c>
       <c r="G146" t="n">
-        <v>5.84</v>
+        <v>455.4</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I146" t="n">
-        <v>6.02</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.62</v>
+        <v>10.43</v>
       </c>
       <c r="M146" t="n">
-        <v>1.67</v>
+        <v>13.03</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
@@ -9822,18 +9822,18 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>0.05</v>
+        <v>2.6</v>
       </c>
       <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>1403180445</v>
+        <v>1582737192</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9842,35 +9842,35 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.0092</v>
+        <v>0.0371</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45645.90143914352</v>
       </c>
       <c r="G147" t="n">
-        <v>5.836</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I147" t="n">
-        <v>6.02</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0.05</v>
+        <v>19.46</v>
       </c>
       <c r="M147" t="n">
-        <v>0.06</v>
+        <v>21.11</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -9885,18 +9885,18 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>0.01</v>
+        <v>1.65</v>
       </c>
       <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>1393735509</v>
+        <v>1599454287</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9905,35 +9905,35 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.0366</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45663.73715268519</v>
       </c>
       <c r="G148" t="n">
-        <v>67.37</v>
+        <v>196.49</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I148" t="n">
-        <v>71.16</v>
+        <v>196.89</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.47</v>
+        <v>14.99</v>
       </c>
       <c r="M148" t="n">
-        <v>2.6</v>
+        <v>15.02</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
@@ -9948,18 +9948,18 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>1395218355</v>
+        <v>1621495599</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9968,35 +9968,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.074</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45678.83206015046</v>
       </c>
       <c r="G149" t="n">
-        <v>67.13</v>
+        <v>183.39</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I149" t="n">
-        <v>71.16</v>
+        <v>196.89</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>4.97</v>
+        <v>14.98</v>
       </c>
       <c r="M149" t="n">
-        <v>5.27</v>
+        <v>16.09</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
@@ -10011,18 +10011,18 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>0.3</v>
+        <v>1.11</v>
       </c>
       <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>1403166009</v>
+        <v>1631467534</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10031,35 +10031,35 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.0362</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45685.83235356482</v>
       </c>
       <c r="G150" t="n">
-        <v>68.05</v>
+        <v>159.74</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I150" t="n">
-        <v>71.16</v>
+        <v>196.89</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.46</v>
+        <v>14.97</v>
       </c>
       <c r="M150" t="n">
-        <v>2.58</v>
+        <v>18.45</v>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
@@ -10074,18 +10074,18 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.12</v>
+        <v>3.48</v>
       </c>
       <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1403177543</v>
+        <v>1666449688</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10094,35 +10094,35 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.0368</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45708.67996841436</v>
       </c>
       <c r="G151" t="n">
-        <v>68.045</v>
+        <v>160.68</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I151" t="n">
-        <v>71.16</v>
+        <v>196.89</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.5</v>
+        <v>14.98</v>
       </c>
       <c r="M151" t="n">
-        <v>2.62</v>
+        <v>18.35</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -10137,18 +10137,18 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>0.12</v>
+        <v>3.37</v>
       </c>
       <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1403180429</v>
+        <v>1701098878</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -10157,35 +10157,35 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.0733</v>
+        <v>0.0051</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45727.87167579861</v>
       </c>
       <c r="G152" t="n">
-        <v>68.01000000000001</v>
+        <v>139.41</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I152" t="n">
-        <v>71.16</v>
+        <v>196.89</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4.99</v>
+        <v>0.71</v>
       </c>
       <c r="M152" t="n">
-        <v>5.22</v>
+        <v>1</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -10200,18 +10200,18 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>1403180445</v>
+        <v>1701098878</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -10220,35 +10220,35 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9908</v>
+        <v>0.1</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45727.87167579861</v>
       </c>
       <c r="G153" t="n">
-        <v>5.836</v>
+        <v>139.41</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45792.64655003473</v>
       </c>
       <c r="I153" t="n">
-        <v>6.027</v>
+        <v>188.02</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>5.78</v>
+        <v>13.94</v>
       </c>
       <c r="M153" t="n">
-        <v>5.97</v>
+        <v>18.8</v>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
@@ -10263,18 +10263,18 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>0.18</v>
+        <v>4.86</v>
       </c>
       <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>1393281432</v>
+        <v>1426782063</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -10283,35 +10283,35 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.1102</v>
+        <v>0.0004</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G154" t="n">
-        <v>5.981</v>
+        <v>419.46</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I154" t="n">
-        <v>6.176</v>
+        <v>452.34</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0.66</v>
+        <v>0.17</v>
       </c>
       <c r="M154" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -10326,18 +10326,18 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1393301698</v>
+        <v>1481614059</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -10346,35 +10346,35 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.1401</v>
+        <v>0.0359</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45568.77505349537</v>
       </c>
       <c r="G155" t="n">
-        <v>5.99</v>
+        <v>417.1</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I155" t="n">
-        <v>6.176</v>
+        <v>452.34</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0.84</v>
+        <v>14.97</v>
       </c>
       <c r="M155" t="n">
-        <v>0.87</v>
+        <v>16.24</v>
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -10389,18 +10389,18 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>0.03</v>
+        <v>1.27</v>
       </c>
       <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1403180427</v>
+        <v>1517514880</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -10409,35 +10409,35 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.4203</v>
+        <v>0.0037</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45597.6108722338</v>
       </c>
       <c r="G156" t="n">
-        <v>5.989</v>
+        <v>409.38</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I156" t="n">
-        <v>6.176</v>
+        <v>452.34</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.52</v>
+        <v>1.51</v>
       </c>
       <c r="M156" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
@@ -10452,7 +10452,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="U156" t="inlineStr"/>
     </row>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -1505,11 +1505,11 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1375856858</v>
+        <v>1393281432</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1518,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1052</v>
+        <v>0.632</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G17" t="n">
-        <v>188.48</v>
+        <v>5.981</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I17" t="n">
-        <v>189.21</v>
+        <v>5.967</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>19.83</v>
+        <v>3.78</v>
       </c>
       <c r="M17" t="n">
-        <v>19.9</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1357595824</v>
+        <v>1375856858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.1052</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G18" t="n">
-        <v>22.89</v>
+        <v>188.48</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I18" t="n">
-        <v>18.62</v>
+        <v>189.21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>22.89</v>
+        <v>19.83</v>
       </c>
       <c r="M18" t="n">
-        <v>18.62</v>
+        <v>19.9</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.27</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1375967973</v>
+        <v>1393281260</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1644,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0014</v>
+        <v>0.5612</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>5.812</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I19" t="n">
-        <v>182.97</v>
+        <v>5.81</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.26</v>
+        <v>3.26</v>
       </c>
       <c r="M19" t="n">
-        <v>0.26</v>
+        <v>3.26</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1694,11 +1694,11 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1377834040</v>
+        <v>1357595824</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,19 +1707,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1077</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G20" t="n">
-        <v>186.7</v>
+        <v>22.89</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I20" t="n">
-        <v>182.97</v>
+        <v>18.62</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>20.11</v>
+        <v>22.89</v>
       </c>
       <c r="M20" t="n">
-        <v>19.71</v>
+        <v>18.62</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1750,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.39</v>
+        <v>-4.27</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1377407433</v>
+        <v>1393281260</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1770,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0771</v>
+        <v>0.555</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G21" t="n">
-        <v>129.48</v>
+        <v>5.812</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I21" t="n">
-        <v>130.75</v>
+        <v>5.801</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.98</v>
+        <v>3.23</v>
       </c>
       <c r="M21" t="n">
-        <v>10.08</v>
+        <v>3.22</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1813,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1377407433</v>
+        <v>1393281432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1833,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0001</v>
+        <v>0.4344</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G22" t="n">
-        <v>129.48</v>
+        <v>5.981</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I22" t="n">
-        <v>131.24</v>
+        <v>5.968</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01</v>
+        <v>2.59</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1876,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1377834040</v>
+        <v>1393281260</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,35 +1896,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0011</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G23" t="n">
-        <v>186.7</v>
+        <v>5.812</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I23" t="n">
-        <v>184.46</v>
+        <v>5.814</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.21</v>
+        <v>5.81</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2</v>
+        <v>5.81</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1939,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1362491459</v>
+        <v>1393281432</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,35 +1959,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.228</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G24" t="n">
-        <v>88.67</v>
+        <v>5.981</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I24" t="n">
-        <v>87.81</v>
+        <v>5.978</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.22</v>
+        <v>5.98</v>
       </c>
       <c r="M24" t="n">
-        <v>20.02</v>
+        <v>5.98</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1362491459</v>
+        <v>1393281260</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0001</v>
+        <v>0.4206</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G25" t="n">
-        <v>88.67</v>
+        <v>5.812</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I25" t="n">
-        <v>87.81999999999999</v>
+        <v>5.826</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.01</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01</v>
+        <v>2.45</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2065,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1375856858</v>
+        <v>1393281432</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,35 +2085,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0026</v>
+        <v>0.4033</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G26" t="n">
-        <v>188.48</v>
+        <v>5.981</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I26" t="n">
-        <v>190.3</v>
+        <v>5.98</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>2.41</v>
       </c>
       <c r="M26" t="n">
-        <v>0.49</v>
+        <v>2.41</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1377584836</v>
+        <v>1393281432</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,35 +2148,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4828</v>
+        <v>0.4201</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G27" t="n">
-        <v>41.87</v>
+        <v>5.981</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I27" t="n">
-        <v>42.35</v>
+        <v>5.98</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.21</v>
+        <v>2.51</v>
       </c>
       <c r="M27" t="n">
-        <v>20.45</v>
+        <v>2.51</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1377584836</v>
+        <v>1375967973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0013</v>
+        <v>0.0014</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G28" t="n">
-        <v>41.87</v>
+        <v>183</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I28" t="n">
-        <v>42.35</v>
+        <v>182.97</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1350885655</v>
+        <v>1393281432</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,35 +2274,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0234</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G29" t="n">
-        <v>427.17</v>
+        <v>5.981</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I29" t="n">
-        <v>458.18</v>
+        <v>6.186</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>5.98</v>
       </c>
       <c r="M29" t="n">
-        <v>10.72</v>
+        <v>6.19</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2317,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.72</v>
+        <v>0.21</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1414374074</v>
+        <v>1393281260</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,35 +2337,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0481</v>
+        <v>1.4632</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G30" t="n">
-        <v>311.85</v>
+        <v>5.812</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I30" t="n">
-        <v>308</v>
+        <v>6.02</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="M30" t="n">
-        <v>14.81</v>
+        <v>8.81</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.19</v>
+        <v>0.3</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1414372067</v>
+        <v>1393287040</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,23 +2400,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0575</v>
+        <v>0.2503</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G31" t="n">
-        <v>260.8</v>
+        <v>5.811</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I31" t="n">
-        <v>290.19</v>
+        <v>6.02</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>16.69</v>
+        <v>1.51</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>0.06</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1377764546</v>
+        <v>1403180431</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,35 +2463,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.2773</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G32" t="n">
-        <v>244.47</v>
+        <v>5.84</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I32" t="n">
-        <v>196.86</v>
+        <v>6.02</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>19.02</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>15.32</v>
+        <v>1.67</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-3.7</v>
+        <v>0.05</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1377764546</v>
+        <v>1403180445</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0051</v>
+        <v>0.0092</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G33" t="n">
-        <v>244.47</v>
+        <v>5.836</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I33" t="n">
-        <v>196.91</v>
+        <v>6.02</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>0.05</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1380259753</v>
+        <v>1377834040</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.131</v>
+        <v>0.1077</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G34" t="n">
-        <v>190.71</v>
+        <v>186.7</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I34" t="n">
-        <v>161.87</v>
+        <v>182.97</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>24.98</v>
+        <v>20.11</v>
       </c>
       <c r="M34" t="n">
-        <v>21.2</v>
+        <v>19.71</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,39 +2632,39 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-3.78</v>
+        <v>-0.39</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1509051251</v>
+        <v>1377407433</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.0771</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G35" t="n">
-        <v>19.8731</v>
+        <v>129.48</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I35" t="n">
-        <v>19.8835</v>
+        <v>130.75</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2676,13 +2676,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10.08</v>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2693,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1.05</v>
+        <v>0.09</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1508055372</v>
+        <v>1393735509</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2713,37 +2715,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.02</v>
+        <v>0.0366</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G36" t="n">
-        <v>19.8369</v>
+        <v>67.37</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I36" t="n">
-        <v>19.8761</v>
+        <v>71.16</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.6</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -2754,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.94</v>
+        <v>0.13</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1512925323</v>
+        <v>1395218355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2774,102 +2778,102 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>0.074</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G37" t="n">
-        <v>20.0663</v>
+        <v>67.13</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I37" t="n">
-        <v>20.1405</v>
+        <v>71.16</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.27</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>5</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.68</v>
+        <v>0.3</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1514707570</v>
+        <v>1403166009</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01</v>
+        <v>0.0362</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45595.88186449074</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G38" t="n">
-        <v>20.1597</v>
+        <v>68.05</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45595.94583810185</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I38" t="n">
-        <v>20.1911</v>
+        <v>71.16</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="O38" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2880,61 +2884,59 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1516787001</v>
+        <v>1403177543</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01</v>
+        <v>0.0368</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G39" t="n">
-        <v>2748.04</v>
+        <v>68.045</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I39" t="n">
-        <v>2747.79</v>
+        <v>71.16</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.62</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -2945,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1516790032</v>
+        <v>1403180429</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2965,37 +2967,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.01</v>
+        <v>0.0733</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45597.13541888889</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G40" t="n">
-        <v>2747.23</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45597.13874358797</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I40" t="n">
-        <v>2747.25</v>
+        <v>71.16</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M40" t="n">
+        <v>5.22</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -3006,57 +3010,59 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1516793905</v>
+        <v>1403180445</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.01</v>
+        <v>0.9908</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45597.14024802083</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G41" t="n">
-        <v>2747.11</v>
+        <v>5.836</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45597.14548700232</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I41" t="n">
-        <v>2747.77</v>
+        <v>6.027</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.97</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -3067,18 +3073,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.66</v>
+        <v>0.18</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1516796610</v>
+        <v>1393281432</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3087,37 +3093,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>0.1102</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45597.14556364583</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G42" t="n">
-        <v>2748.12</v>
+        <v>5.981</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45597.14936810185</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I42" t="n">
-        <v>2746.29</v>
+        <v>6.176</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.68</v>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -3128,57 +3136,59 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>-1.83</v>
+        <v>0.02</v>
       </c>
       <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1516798655</v>
+        <v>1393301698</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>0.1401</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45597.14949375</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G43" t="n">
-        <v>2746.13</v>
+        <v>5.99</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45597.15075293981</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I43" t="n">
-        <v>2747.4</v>
+        <v>6.176</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.87</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>13.73</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -3189,18 +3199,18 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.27</v>
+        <v>0.03</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1516805560</v>
+        <v>1403180427</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3209,37 +3219,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>0.4203</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45597.16385188657</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G44" t="n">
-        <v>2748.03</v>
+        <v>5.989</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45597.16756914352</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I44" t="n">
-        <v>2748.36</v>
+        <v>6.176</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.6</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -3250,18 +3262,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1516814771</v>
+        <v>1377407433</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3270,37 +3282,39 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>45481.65801625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>129.48</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45482.91500505787</v>
+      </c>
+      <c r="I45" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>0.01</v>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>45597.18416002315</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2749.48</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>45597.18971934028</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2749.54</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0.01</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>13.75</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -3311,18 +3325,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1516838270</v>
+        <v>1377834040</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3331,19 +3345,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.01</v>
+        <v>0.0011</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45597.23811159722</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G46" t="n">
-        <v>2751.84</v>
+        <v>186.7</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45597.56254815972</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I46" t="n">
-        <v>2756.23</v>
+        <v>184.46</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3355,15 +3369,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>2754.07</v>
-      </c>
-      <c r="P46" t="n">
-        <v>13.76</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -3374,22 +3388,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1515520253</v>
+        <v>1362491459</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3398,19 +3408,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0.228</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G47" t="n">
-        <v>20.0901</v>
+        <v>88.67</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I47" t="n">
-        <v>20.0775</v>
+        <v>87.81</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3422,35 +3432,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="M47" t="n">
+        <v>20.02</v>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>5</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1517450167</v>
+        <v>1362491459</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3459,37 +3471,39 @@
         </is>
       </c>
       <c r="E48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>45464.66139070602</v>
+      </c>
+      <c r="G48" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>45483.77897271991</v>
+      </c>
+      <c r="I48" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>0.01</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>45597.59638905092</v>
-      </c>
-      <c r="G48" t="n">
-        <v>19.9771</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>45597.73077270833</v>
-      </c>
-      <c r="I48" t="n">
-        <v>20.0775</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0.01</v>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>5</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3500,39 +3514,39 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1517930572</v>
+        <v>1375856858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>0.0026</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G49" t="n">
-        <v>20.078</v>
+        <v>188.48</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I49" t="n">
-        <v>20.082</v>
+        <v>190.3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3544,13 +3558,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.49</v>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>5</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -3561,18 +3577,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1517879253</v>
+        <v>1377584836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3581,19 +3597,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0.4828</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G50" t="n">
-        <v>20.08</v>
+        <v>41.87</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I50" t="n">
-        <v>19.63</v>
+        <v>42.35</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3602,44 +3618,40 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop-out</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="M50" t="n">
+        <v>20.45</v>
+      </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="P50" t="n">
-        <v>12.05</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1379227659</v>
+        <v>1377584836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3648,19 +3660,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1521</v>
+        <v>0.0013</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G51" t="n">
-        <v>131.38</v>
+        <v>41.87</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I51" t="n">
-        <v>148.18</v>
+        <v>42.35</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3673,10 +3685,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>19.98</v>
+        <v>0.05</v>
       </c>
       <c r="M51" t="n">
-        <v>22.54</v>
+        <v>0.06</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3691,18 +3703,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.56</v>
+        <v>0.01</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1527051962</v>
+        <v>1350885655</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3711,19 +3723,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.01</v>
+        <v>0.0234</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45604.13145401621</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G52" t="n">
-        <v>19.8302</v>
+        <v>427.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45604.56280116898</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I52" t="n">
-        <v>19.9681</v>
+        <v>458.18</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3735,17 +3747,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="O52" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P52" t="n">
-        <v>5</v>
-      </c>
+      <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
@@ -3756,22 +3766,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1527744522</v>
+        <v>1414374074</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3780,19 +3786,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.01</v>
+        <v>0.0481</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45604.55607921296</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G53" t="n">
-        <v>19.9784</v>
+        <v>311.85</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45604.57083508102</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I53" t="n">
-        <v>19.9497</v>
+        <v>308</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3804,17 +3810,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="O53" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P53" t="n">
-        <v>5</v>
-      </c>
+      <c r="L53" t="n">
+        <v>15</v>
+      </c>
+      <c r="M53" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
@@ -3825,22 +3829,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.19</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1528126100</v>
+        <v>1414372067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,19 +3849,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>0.0575</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45604.66918148148</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G54" t="n">
-        <v>20.0428</v>
+        <v>260.8</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45604.71914307871</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I54" t="n">
-        <v>20.0988</v>
+        <v>290.19</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3873,17 +3873,15 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>20.0988</v>
-      </c>
-      <c r="O54" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P54" t="n">
-        <v>5</v>
-      </c>
+      <c r="L54" t="n">
+        <v>15</v>
+      </c>
+      <c r="M54" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
@@ -3894,47 +3892,43 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1528325630</v>
+        <v>1377764546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45604.72032700232</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G55" t="n">
-        <v>20.0912</v>
+        <v>244.47</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45604.72263849537</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I55" t="n">
-        <v>20.1101</v>
+        <v>196.86</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3942,17 +3936,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="O55" t="n">
-        <v>20.0219</v>
-      </c>
-      <c r="P55" t="n">
-        <v>5</v>
-      </c>
+      <c r="L55" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="M55" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
@@ -3963,22 +3955,18 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-3.7</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1531224336</v>
+        <v>1377764546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3987,19 +3975,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>0.0051</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45608.2460031713</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G56" t="n">
-        <v>153.589</v>
+        <v>244.47</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45608.25044886574</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I56" t="n">
-        <v>153.468</v>
+        <v>196.91</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4011,17 +3999,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>153.47</v>
-      </c>
-      <c r="O56" t="n">
-        <v>153.619</v>
-      </c>
-      <c r="P56" t="n">
-        <v>5</v>
-      </c>
+      <c r="L56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
@@ -4032,43 +4018,39 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.25</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1531227124</v>
+        <v>1380259753</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.131</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45608.25015417824</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G57" t="n">
-        <v>153.483</v>
+        <v>190.71</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45608.25207638889</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I57" t="n">
-        <v>153.458</v>
+        <v>161.87</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4080,15 +4062,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>153.458</v>
-      </c>
+      <c r="L57" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="M57" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>5</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
@@ -4099,22 +4081,18 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-3.78</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1531230129</v>
+        <v>1509051251</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4123,19 +4101,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45608.2544440162</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G58" t="n">
-        <v>153.445</v>
+        <v>19.8731</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45608.25666561343</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I58" t="n">
-        <v>153.502</v>
+        <v>19.8835</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4149,14 +4127,10 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>153.502</v>
-      </c>
-      <c r="O58" t="n">
-        <v>153.395</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4168,18 +4142,14 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-1.05</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1531192665</v>
+        <v>1508055372</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4195,16 +4165,16 @@
         <v>0.02</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45608.19828637732</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G59" t="n">
-        <v>20.412</v>
+        <v>19.8369</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45608.34380275463</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I59" t="n">
-        <v>20.4421</v>
+        <v>19.8761</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4218,12 +4188,8 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>20.4429</v>
-      </c>
-      <c r="O59" t="n">
-        <v>20.5326</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
         <v>10</v>
       </c>
@@ -4237,18 +4203,14 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>3.94</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1531349564</v>
+        <v>1512925323</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4257,23 +4219,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45608.34449649305</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G60" t="n">
-        <v>20.4344</v>
+        <v>20.0663</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45608.34490908564</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I60" t="n">
-        <v>20.4507</v>
+        <v>20.1405</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4296,20 +4258,20 @@
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.8</v>
+        <v>3.68</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1531351286</v>
+        <v>1514707570</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4318,23 +4280,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45608.34571399305</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G61" t="n">
-        <v>20.4554</v>
+        <v>20.1597</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45608.35180353009</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I61" t="n">
-        <v>20.45</v>
+        <v>20.1911</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4349,10 +4311,10 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>20.4381</v>
+        <v>20.19</v>
       </c>
       <c r="O61" t="n">
-        <v>20.47</v>
+        <v>20.12</v>
       </c>
       <c r="P61" t="n">
         <v>5</v>
@@ -4367,39 +4329,43 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1531358421</v>
+        <v>1516787001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45608.3501140162</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G62" t="n">
-        <v>20.4503</v>
+        <v>2748.04</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45608.35479755787</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I62" t="n">
-        <v>20.4382</v>
+        <v>2747.79</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4413,14 +4379,10 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>20.4388</v>
-      </c>
-      <c r="O62" t="n">
-        <v>20.4767</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>13.74</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4432,22 +4394,18 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1532703059</v>
+        <v>1516790032</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4456,19 +4414,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45608.75711524305</v>
+        <v>45597.13541888889</v>
       </c>
       <c r="G63" t="n">
-        <v>20.6261</v>
+        <v>2747.23</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45608.76530484953</v>
+        <v>45597.13874358797</v>
       </c>
       <c r="I63" t="n">
-        <v>20.6299</v>
+        <v>2747.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4482,14 +4440,10 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>20.5745</v>
-      </c>
-      <c r="O63" t="n">
-        <v>20.6364</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>10</v>
+        <v>13.74</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4501,39 +4455,39 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.37</v>
+        <v>0.02</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1532729622</v>
+        <v>1516793905</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>0.01</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45608.76652064815</v>
+        <v>45597.14024802083</v>
       </c>
       <c r="G64" t="n">
-        <v>154.853</v>
+        <v>2747.11</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45608.76796081018</v>
+        <v>45597.14548700232</v>
       </c>
       <c r="I64" t="n">
-        <v>154.873</v>
+        <v>2747.77</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4550,7 +4504,7 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>5</v>
+        <v>13.74</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4562,18 +4516,18 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0.13</v>
+        <v>-0.66</v>
       </c>
       <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1533930062</v>
+        <v>1516796610</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4585,16 +4539,16 @@
         <v>0.01</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45609.61569380787</v>
+        <v>45597.14556364583</v>
       </c>
       <c r="G65" t="n">
-        <v>20.507</v>
+        <v>2748.12</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45609.63889303241</v>
+        <v>45597.14936810185</v>
       </c>
       <c r="I65" t="n">
-        <v>20.5531</v>
+        <v>2746.29</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4608,14 +4562,10 @@
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>20.431</v>
-      </c>
-      <c r="O65" t="n">
-        <v>20.5528</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>13.74</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -4627,43 +4577,39 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>-1.83</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1536772518</v>
+        <v>1516798655</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45610.86999649306</v>
+        <v>45597.14949375</v>
       </c>
       <c r="G66" t="n">
-        <v>20.4311</v>
+        <v>2746.13</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45610.88084664352</v>
+        <v>45597.15075293981</v>
       </c>
       <c r="I66" t="n">
-        <v>20.4923</v>
+        <v>2747.4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4677,14 +4623,10 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>20.4941</v>
-      </c>
-      <c r="O66" t="n">
-        <v>20.5653</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>13.73</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -4696,22 +4638,18 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-1.27</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1540892910</v>
+        <v>1516805560</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4720,19 +4658,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45614.83689460648</v>
+        <v>45597.16385188657</v>
       </c>
       <c r="G67" t="n">
-        <v>20.2371</v>
+        <v>2748.03</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45615.43822850694</v>
+        <v>45597.16756914352</v>
       </c>
       <c r="I67" t="n">
-        <v>20.3181</v>
+        <v>2748.36</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4746,41 +4684,33 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="O67" t="n">
-        <v>20.3179</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>13.74</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1541930457</v>
+        <v>1516814771</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4789,19 +4719,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45615.56159975695</v>
+        <v>45597.18416002315</v>
       </c>
       <c r="G68" t="n">
-        <v>20.2629</v>
+        <v>2749.48</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45615.58509630787</v>
+        <v>45597.18971934028</v>
       </c>
       <c r="I68" t="n">
-        <v>20.2887</v>
+        <v>2749.54</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4815,14 +4745,10 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>20.2059</v>
-      </c>
-      <c r="O68" t="n">
-        <v>20.2856</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>13.75</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4834,22 +4760,18 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1393281432</v>
+        <v>1516838270</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4858,39 +4780,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.632</v>
+        <v>0.01</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.23811159722</v>
       </c>
       <c r="G69" t="n">
-        <v>5.981</v>
+        <v>2751.84</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45597.56254815972</v>
       </c>
       <c r="I69" t="n">
-        <v>5.967</v>
+        <v>2756.23</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="M69" t="n">
-        <v>3.77</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>2754.07</v>
+      </c>
+      <c r="P69" t="n">
+        <v>13.76</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4901,18 +4823,22 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U69" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1393281260</v>
+        <v>1515520253</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4921,57 +4847,55 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.5612</v>
+        <v>0.01</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G70" t="n">
-        <v>5.812</v>
+        <v>20.0901</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I70" t="n">
-        <v>5.81</v>
+        <v>20.0775</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M70" t="n">
-        <v>3.26</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1553997553</v>
+        <v>1517450167</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4980,23 +4904,23 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>0.01</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45623.53527240741</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G71" t="n">
-        <v>20.7084</v>
+        <v>19.9771</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45623.57548773148</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I71" t="n">
-        <v>20.7775</v>
+        <v>20.0775</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5010,12 +4934,8 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
-        <v>20.7706</v>
-      </c>
-      <c r="O71" t="n">
-        <v>20.68</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>5</v>
       </c>
@@ -5029,63 +4949,57 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1393281260</v>
+        <v>1517930572</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.555</v>
+        <v>0.01</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G72" t="n">
-        <v>5.812</v>
+        <v>20.078</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I72" t="n">
-        <v>5.801</v>
+        <v>20.082</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="M72" t="n">
-        <v>3.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>5</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
@@ -5096,18 +5010,18 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>-0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1393281432</v>
+        <v>1517879253</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5116,61 +5030,65 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.4344</v>
+        <v>0.01</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G73" t="n">
-        <v>5.981</v>
+        <v>20.08</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I73" t="n">
-        <v>5.968</v>
+        <v>19.63</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M73" t="n">
-        <v>2.59</v>
-      </c>
+          <t>stop-out</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="P73" t="n">
+        <v>12.05</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U73" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1393281260</v>
+        <v>1379227659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5179,35 +5097,35 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.1521</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G74" t="n">
-        <v>5.812</v>
+        <v>131.38</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I74" t="n">
-        <v>5.814</v>
+        <v>148.18</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>5.81</v>
+        <v>19.98</v>
       </c>
       <c r="M74" t="n">
-        <v>5.81</v>
+        <v>22.54</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -5222,18 +5140,18 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1393281432</v>
+        <v>1527051962</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5242,39 +5160,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45604.13145401621</v>
       </c>
       <c r="G75" t="n">
-        <v>5.981</v>
+        <v>19.8302</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45604.56280116898</v>
       </c>
       <c r="I75" t="n">
-        <v>5.978</v>
+        <v>19.9681</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M75" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="O75" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P75" t="n">
+        <v>5</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
@@ -5285,14 +5205,18 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1554074835</v>
+        <v>1527744522</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5301,23 +5225,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0.01</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45623.57516572917</v>
+        <v>45604.55607921296</v>
       </c>
       <c r="G76" t="n">
-        <v>20.7426</v>
+        <v>19.9784</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45623.57574133102</v>
+        <v>45604.57083508102</v>
       </c>
       <c r="I76" t="n">
-        <v>20.7764</v>
+        <v>19.9497</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5331,8 +5255,12 @@
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="O76" t="n">
+        <v>20.2</v>
+      </c>
       <c r="P76" t="n">
         <v>5</v>
       </c>
@@ -5346,18 +5274,22 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="U76" t="inlineStr"/>
+        <v>-1.44</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1393281260</v>
+        <v>1528126100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5366,39 +5298,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.4206</v>
+        <v>0.01</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45604.66918148148</v>
       </c>
       <c r="G77" t="n">
-        <v>5.812</v>
+        <v>20.0428</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45604.71914307871</v>
       </c>
       <c r="I77" t="n">
-        <v>5.826</v>
+        <v>20.0988</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="M77" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="n">
+        <v>20.0988</v>
+      </c>
+      <c r="O77" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P77" t="n">
+        <v>5</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
@@ -5409,39 +5343,43 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U77" t="inlineStr"/>
+        <v>2.79</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1393281432</v>
+        <v>1528325630</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.4033</v>
+        <v>0.01</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45604.72032700232</v>
       </c>
       <c r="G78" t="n">
-        <v>5.981</v>
+        <v>20.0912</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45604.72263849537</v>
       </c>
       <c r="I78" t="n">
-        <v>5.98</v>
+        <v>20.1101</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5450,18 +5388,20 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="M78" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="O78" t="n">
+        <v>20.0219</v>
+      </c>
+      <c r="P78" t="n">
+        <v>5</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
@@ -5472,18 +5412,22 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="inlineStr"/>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1555669398</v>
+        <v>1531224336</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5492,19 +5436,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45624.55073625</v>
+        <v>45608.2460031713</v>
       </c>
       <c r="G79" t="n">
-        <v>20.3273</v>
+        <v>153.589</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45624.71914708333</v>
+        <v>45608.25044886574</v>
       </c>
       <c r="I79" t="n">
-        <v>20.4312</v>
+        <v>153.468</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5519,13 +5463,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>20.1748</v>
+        <v>153.47</v>
       </c>
       <c r="O79" t="n">
-        <v>20.4293</v>
+        <v>153.619</v>
       </c>
       <c r="P79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5537,63 +5481,63 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>10.17</v>
+        <v>-0.79</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>[T/P]</t>
+          <t>[S/L]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1393281432</v>
+        <v>1531227124</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.4201</v>
+        <v>0.01</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45608.25015417824</v>
       </c>
       <c r="G80" t="n">
-        <v>5.981</v>
+        <v>153.483</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45608.25207638889</v>
       </c>
       <c r="I80" t="n">
-        <v>5.98</v>
+        <v>153.458</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="M80" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>153.458</v>
+      </c>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>5</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
@@ -5604,59 +5548,65 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1393281432</v>
+        <v>1531230129</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45608.2544440162</v>
       </c>
       <c r="G81" t="n">
-        <v>5.981</v>
+        <v>153.445</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45608.25666561343</v>
       </c>
       <c r="I81" t="n">
-        <v>6.186</v>
+        <v>153.502</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M81" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>153.502</v>
+      </c>
+      <c r="O81" t="n">
+        <v>153.395</v>
+      </c>
+      <c r="P81" t="n">
+        <v>5</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
@@ -5667,14 +5617,18 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="U81" t="inlineStr"/>
+        <v>-0.37</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1563562241</v>
+        <v>1531192665</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -5690,16 +5644,16 @@
         <v>0.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45631.25027201389</v>
+        <v>45608.19828637732</v>
       </c>
       <c r="G82" t="n">
-        <v>20.3099</v>
+        <v>20.412</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45631.6258153125</v>
+        <v>45608.34380275463</v>
       </c>
       <c r="I82" t="n">
-        <v>20.2391</v>
+        <v>20.4421</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5714,10 +5668,10 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>20.24</v>
+        <v>20.4429</v>
       </c>
       <c r="O82" t="n">
-        <v>20.3672</v>
+        <v>20.5326</v>
       </c>
       <c r="P82" t="n">
         <v>10</v>
@@ -5732,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>-6.99</v>
+        <v>2.94</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -5743,52 +5697,50 @@
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1393281260</v>
+        <v>1531349564</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.4632</v>
+        <v>0.01</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45608.34449649305</v>
       </c>
       <c r="G83" t="n">
-        <v>5.812</v>
+        <v>20.4344</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45608.34490908564</v>
       </c>
       <c r="I83" t="n">
-        <v>6.02</v>
+        <v>20.4507</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M83" t="n">
-        <v>8.81</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
@@ -5799,18 +5751,18 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1393287040</v>
+        <v>1531351286</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5819,39 +5771,41 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.2503</v>
+        <v>0.01</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45608.34571399305</v>
       </c>
       <c r="G84" t="n">
-        <v>5.811</v>
+        <v>20.4554</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45608.35180353009</v>
       </c>
       <c r="I84" t="n">
-        <v>6.02</v>
+        <v>20.45</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>20.4381</v>
+      </c>
+      <c r="O84" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="P84" t="n">
+        <v>5</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
@@ -5862,18 +5816,18 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1403180431</v>
+        <v>1531358421</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5882,39 +5836,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.2773</v>
+        <v>0.02</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45608.3501140162</v>
       </c>
       <c r="G85" t="n">
-        <v>5.84</v>
+        <v>20.4503</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45608.35479755787</v>
       </c>
       <c r="I85" t="n">
-        <v>6.02</v>
+        <v>20.4382</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L85" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>20.4388</v>
+      </c>
+      <c r="O85" t="n">
+        <v>20.4767</v>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
@@ -5925,18 +5881,22 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="U85" t="inlineStr"/>
+        <v>-1.18</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1403180445</v>
+        <v>1532703059</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5945,39 +5905,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0092</v>
+        <v>0.02</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45608.75711524305</v>
       </c>
       <c r="G86" t="n">
-        <v>5.836</v>
+        <v>20.6261</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45608.76530484953</v>
       </c>
       <c r="I86" t="n">
-        <v>6.02</v>
+        <v>20.6299</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>20.5745</v>
+      </c>
+      <c r="O86" t="n">
+        <v>20.6364</v>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
@@ -5988,18 +5950,18 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1393735509</v>
+        <v>1532729622</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6008,39 +5970,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0366</v>
+        <v>0.01</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45608.76652064815</v>
       </c>
       <c r="G87" t="n">
-        <v>67.37</v>
+        <v>154.853</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45608.76796081018</v>
       </c>
       <c r="I87" t="n">
-        <v>71.16</v>
+        <v>154.873</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L87" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>5</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
@@ -6058,11 +6018,11 @@
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1395218355</v>
+        <v>1533930062</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6071,39 +6031,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.074</v>
+        <v>0.01</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45609.61569380787</v>
       </c>
       <c r="G88" t="n">
-        <v>67.13</v>
+        <v>20.507</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45609.63889303241</v>
       </c>
       <c r="I88" t="n">
-        <v>71.16</v>
+        <v>20.5531</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L88" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M88" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>20.431</v>
+      </c>
+      <c r="O88" t="n">
+        <v>20.5528</v>
+      </c>
+      <c r="P88" t="n">
+        <v>5</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
@@ -6114,18 +6076,22 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U88" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1473693877</v>
+        <v>1536772518</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6134,19 +6100,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45562.69351818287</v>
+        <v>45610.86999649306</v>
       </c>
       <c r="G89" t="n">
-        <v>700.8</v>
+        <v>20.4311</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45610.88084664352</v>
       </c>
       <c r="I89" t="n">
-        <v>623.8</v>
+        <v>20.4923</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6158,15 +6124,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L89" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="M89" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>20.4941</v>
+      </c>
+      <c r="O89" t="n">
+        <v>20.5653</v>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
@@ -6177,18 +6145,22 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="U89" t="inlineStr"/>
+        <v>5.97</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1403166009</v>
+        <v>1540892910</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6197,61 +6169,67 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0362</v>
+        <v>0.02</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45614.83689460648</v>
       </c>
       <c r="G90" t="n">
-        <v>68.05</v>
+        <v>20.2371</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45615.43822850694</v>
       </c>
       <c r="I90" t="n">
-        <v>71.16</v>
+        <v>20.3181</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L90" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="O90" t="n">
+        <v>20.3179</v>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U90" t="inlineStr"/>
+        <v>7.97</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1403177543</v>
+        <v>1541930457</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6260,39 +6238,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0368</v>
+        <v>0.02</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45615.56159975695</v>
       </c>
       <c r="G91" t="n">
-        <v>68.045</v>
+        <v>20.2629</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45615.58509630787</v>
       </c>
       <c r="I91" t="n">
-        <v>71.16</v>
+        <v>20.2887</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>20.2059</v>
+      </c>
+      <c r="O91" t="n">
+        <v>20.2856</v>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -6303,59 +6283,65 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U91" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1403180429</v>
+        <v>1553997553</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0733</v>
+        <v>0.01</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45623.53527240741</v>
       </c>
       <c r="G92" t="n">
-        <v>68.01000000000001</v>
+        <v>20.7084</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45623.57548773148</v>
       </c>
       <c r="I92" t="n">
-        <v>71.16</v>
+        <v>20.7775</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L92" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M92" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>20.7706</v>
+      </c>
+      <c r="O92" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="P92" t="n">
+        <v>5</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
@@ -6366,59 +6352,61 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="U92" t="inlineStr"/>
+        <v>-3.33</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1403180445</v>
+        <v>1554074835</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9908</v>
+        <v>0.01</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45623.57516572917</v>
       </c>
       <c r="G93" t="n">
-        <v>5.836</v>
+        <v>20.7426</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45623.57574133102</v>
       </c>
       <c r="I93" t="n">
-        <v>6.027</v>
+        <v>20.7764</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M93" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>5</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
@@ -6429,18 +6417,18 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0.18</v>
+        <v>-1.63</v>
       </c>
       <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1493848938</v>
+        <v>1555669398</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6449,19 +6437,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0213</v>
+        <v>0.02</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45579.70088467593</v>
+        <v>45624.55073625</v>
       </c>
       <c r="G94" t="n">
-        <v>640.3</v>
+        <v>20.3273</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45624.71914708333</v>
       </c>
       <c r="I94" t="n">
-        <v>623.8</v>
+        <v>20.4312</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6473,15 +6461,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L94" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="M94" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>20.1748</v>
+      </c>
+      <c r="O94" t="n">
+        <v>20.4293</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -6492,18 +6482,22 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="U94" t="inlineStr"/>
+        <v>10.17</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1393281432</v>
+        <v>1563562241</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6512,39 +6506,41 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.1102</v>
+        <v>0.02</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45631.25027201389</v>
       </c>
       <c r="G95" t="n">
-        <v>5.981</v>
+        <v>20.3099</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45631.6258153125</v>
       </c>
       <c r="I95" t="n">
-        <v>6.176</v>
+        <v>20.2391</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="O95" t="n">
+        <v>20.3672</v>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -6555,18 +6551,22 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U95" t="inlineStr"/>
+        <v>-6.99</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1393301698</v>
+        <v>1473693877</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6575,35 +6575,35 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1401</v>
+        <v>0.019</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45562.69351818287</v>
       </c>
       <c r="G96" t="n">
-        <v>5.99</v>
+        <v>700.8</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I96" t="n">
-        <v>6.176</v>
+        <v>623.8</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.84</v>
+        <v>14.97</v>
       </c>
       <c r="M96" t="n">
-        <v>0.87</v>
+        <v>12.28</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6618,18 +6618,18 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>0.03</v>
+        <v>-2.69</v>
       </c>
       <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1403180427</v>
+        <v>1493848938</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6638,35 +6638,35 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.4203</v>
+        <v>0.0213</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45579.70088467593</v>
       </c>
       <c r="G97" t="n">
-        <v>5.989</v>
+        <v>640.3</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I97" t="n">
-        <v>6.176</v>
+        <v>623.8</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.52</v>
+        <v>14.96</v>
       </c>
       <c r="M97" t="n">
-        <v>2.6</v>
+        <v>13.77</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0.08</v>
+        <v>-1.19</v>
       </c>
       <c r="U97" t="inlineStr"/>
     </row>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -1505,11 +1505,11 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1393281432</v>
+        <v>1375856858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1518,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.632</v>
+        <v>0.1052</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G17" t="n">
-        <v>5.981</v>
+        <v>188.48</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I17" t="n">
-        <v>5.967</v>
+        <v>189.21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.78</v>
+        <v>19.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>19.9</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1375856858</v>
+        <v>1357595824</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1052</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G18" t="n">
-        <v>188.48</v>
+        <v>22.89</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I18" t="n">
-        <v>189.21</v>
+        <v>18.62</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>19.83</v>
+        <v>22.89</v>
       </c>
       <c r="M18" t="n">
-        <v>19.9</v>
+        <v>18.62</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.07000000000000001</v>
+        <v>-4.27</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1393281260</v>
+        <v>1375967973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1644,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5612</v>
+        <v>0.0014</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G19" t="n">
-        <v>5.812</v>
+        <v>183</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I19" t="n">
-        <v>5.81</v>
+        <v>182.97</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.26</v>
+        <v>0.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.26</v>
+        <v>0.26</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1694,11 +1694,11 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1357595824</v>
+        <v>1377834040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,19 +1707,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.1077</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G20" t="n">
-        <v>22.89</v>
+        <v>186.7</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I20" t="n">
-        <v>18.62</v>
+        <v>182.97</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22.89</v>
+        <v>20.11</v>
       </c>
       <c r="M20" t="n">
-        <v>18.62</v>
+        <v>19.71</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1750,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.27</v>
+        <v>-0.39</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1393281260</v>
+        <v>1377407433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1770,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.555</v>
+        <v>0.0771</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G21" t="n">
-        <v>5.812</v>
+        <v>129.48</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I21" t="n">
-        <v>5.801</v>
+        <v>130.75</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.23</v>
+        <v>9.98</v>
       </c>
       <c r="M21" t="n">
-        <v>3.22</v>
+        <v>10.08</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1813,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1393281432</v>
+        <v>1377407433</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1833,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4344</v>
+        <v>0.0001</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G22" t="n">
-        <v>5.981</v>
+        <v>129.48</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45482.91500505787</v>
       </c>
       <c r="I22" t="n">
-        <v>5.968</v>
+        <v>131.24</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>0.01</v>
       </c>
       <c r="M22" t="n">
-        <v>2.59</v>
+        <v>0.01</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1876,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1393281260</v>
+        <v>1377834040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,35 +1896,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G23" t="n">
-        <v>5.812</v>
+        <v>186.7</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I23" t="n">
-        <v>5.814</v>
+        <v>184.46</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.81</v>
+        <v>0.21</v>
       </c>
       <c r="M23" t="n">
-        <v>5.81</v>
+        <v>0.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1939,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1393281432</v>
+        <v>1362491459</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,35 +1959,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.228</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G24" t="n">
-        <v>5.981</v>
+        <v>88.67</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I24" t="n">
-        <v>5.978</v>
+        <v>87.81</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.98</v>
+        <v>20.22</v>
       </c>
       <c r="M24" t="n">
-        <v>5.98</v>
+        <v>20.02</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1393281260</v>
+        <v>1362491459</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4206</v>
+        <v>0.0001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G25" t="n">
-        <v>5.812</v>
+        <v>88.67</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45483.77897271991</v>
       </c>
       <c r="I25" t="n">
-        <v>5.826</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>0.01</v>
       </c>
       <c r="M25" t="n">
-        <v>2.45</v>
+        <v>0.01</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2065,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1393281432</v>
+        <v>1375856858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,35 +2085,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4033</v>
+        <v>0.0026</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G26" t="n">
-        <v>5.981</v>
+        <v>188.48</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I26" t="n">
-        <v>5.98</v>
+        <v>190.3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.41</v>
+        <v>0.49</v>
       </c>
       <c r="M26" t="n">
-        <v>2.41</v>
+        <v>0.49</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2135,11 +2135,11 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1393281432</v>
+        <v>1377584836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,35 +2148,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4201</v>
+        <v>0.4828</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G27" t="n">
-        <v>5.981</v>
+        <v>41.87</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I27" t="n">
-        <v>5.98</v>
+        <v>42.35</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.51</v>
+        <v>20.21</v>
       </c>
       <c r="M27" t="n">
-        <v>2.51</v>
+        <v>20.45</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1375967973</v>
+        <v>1377584836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0014</v>
+        <v>0.0013</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G28" t="n">
-        <v>183</v>
+        <v>41.87</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I28" t="n">
-        <v>182.97</v>
+        <v>42.35</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="M28" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1393281432</v>
+        <v>1350885655</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,35 +2274,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.0234</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G29" t="n">
-        <v>5.981</v>
+        <v>427.17</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I29" t="n">
-        <v>6.186</v>
+        <v>458.18</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.98</v>
+        <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>6.19</v>
+        <v>10.72</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2317,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1393281260</v>
+        <v>1414374074</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,35 +2337,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.4632</v>
+        <v>0.0481</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G30" t="n">
-        <v>5.812</v>
+        <v>311.85</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I30" t="n">
-        <v>6.02</v>
+        <v>308</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>8.81</v>
+        <v>14.81</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1393287040</v>
+        <v>1414372067</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,35 +2400,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.2503</v>
+        <v>0.0575</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G31" t="n">
-        <v>5.811</v>
+        <v>260.8</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I31" t="n">
-        <v>6.02</v>
+        <v>290.19</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>1.51</v>
+        <v>16.69</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.06</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1403180431</v>
+        <v>1377764546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,35 +2463,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2773</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G32" t="n">
-        <v>5.84</v>
+        <v>244.47</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I32" t="n">
-        <v>6.02</v>
+        <v>196.86</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>19.02</v>
       </c>
       <c r="M32" t="n">
-        <v>1.67</v>
+        <v>15.32</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.05</v>
+        <v>-3.7</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1403180445</v>
+        <v>1377764546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0092</v>
+        <v>0.0051</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G33" t="n">
-        <v>5.836</v>
+        <v>244.47</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I33" t="n">
-        <v>6.02</v>
+        <v>196.91</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.05</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1377834040</v>
+        <v>1380259753</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1077</v>
+        <v>0.131</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G34" t="n">
-        <v>186.7</v>
+        <v>190.71</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I34" t="n">
-        <v>182.97</v>
+        <v>161.87</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>20.11</v>
+        <v>24.98</v>
       </c>
       <c r="M34" t="n">
-        <v>19.71</v>
+        <v>21.2</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,39 +2632,39 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.39</v>
+        <v>-3.78</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1377407433</v>
+        <v>1509051251</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0771</v>
+        <v>0.02</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G35" t="n">
-        <v>129.48</v>
+        <v>19.8731</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I35" t="n">
-        <v>130.75</v>
+        <v>19.8835</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2676,15 +2676,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="M35" t="n">
-        <v>10.08</v>
-      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2695,18 +2693,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.09</v>
+        <v>-1.05</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1393735509</v>
+        <v>1508055372</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2715,39 +2713,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0366</v>
+        <v>0.02</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G36" t="n">
-        <v>67.37</v>
+        <v>19.8369</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I36" t="n">
-        <v>71.16</v>
+        <v>19.8761</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -2758,18 +2754,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.13</v>
+        <v>3.94</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1395218355</v>
+        <v>1512925323</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2778,102 +2774,102 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.074</v>
+        <v>0.01</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G37" t="n">
-        <v>67.13</v>
+        <v>20.0663</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I37" t="n">
-        <v>71.16</v>
+        <v>20.1405</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M37" t="n">
-        <v>5.27</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>5</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.3</v>
+        <v>3.68</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1403166009</v>
+        <v>1514707570</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0362</v>
+        <v>0.01</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G38" t="n">
-        <v>68.05</v>
+        <v>20.1597</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I38" t="n">
-        <v>71.16</v>
+        <v>20.1911</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O38" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2884,59 +2880,61 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U38" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1403177543</v>
+        <v>1516787001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0368</v>
+        <v>0.01</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G39" t="n">
-        <v>68.045</v>
+        <v>2748.04</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I39" t="n">
-        <v>71.16</v>
+        <v>2747.79</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.62</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -2947,18 +2945,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1403180429</v>
+        <v>1516790032</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2967,39 +2965,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0733</v>
+        <v>0.01</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45597.13541888889</v>
       </c>
       <c r="G40" t="n">
-        <v>68.01000000000001</v>
+        <v>2747.23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.13874358797</v>
       </c>
       <c r="I40" t="n">
-        <v>71.16</v>
+        <v>2747.25</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M40" t="n">
-        <v>5.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -3010,59 +3006,57 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1403180445</v>
+        <v>1516793905</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9908</v>
+        <v>0.01</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45597.14024802083</v>
       </c>
       <c r="G41" t="n">
-        <v>5.836</v>
+        <v>2747.11</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45597.14548700232</v>
       </c>
       <c r="I41" t="n">
-        <v>6.027</v>
+        <v>2747.77</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -3073,18 +3067,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.18</v>
+        <v>-0.66</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1393281432</v>
+        <v>1516796610</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3093,39 +3087,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.1102</v>
+        <v>0.01</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.14556364583</v>
       </c>
       <c r="G42" t="n">
-        <v>5.981</v>
+        <v>2748.12</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45597.14936810185</v>
       </c>
       <c r="I42" t="n">
-        <v>6.176</v>
+        <v>2746.29</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.68</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -3136,59 +3128,57 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0.02</v>
+        <v>-1.83</v>
       </c>
       <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1393301698</v>
+        <v>1516798655</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.1401</v>
+        <v>0.01</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45597.14949375</v>
       </c>
       <c r="G43" t="n">
-        <v>5.99</v>
+        <v>2746.13</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45597.15075293981</v>
       </c>
       <c r="I43" t="n">
-        <v>6.176</v>
+        <v>2747.4</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.87</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>13.73</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -3199,18 +3189,18 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.03</v>
+        <v>-1.27</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1403180427</v>
+        <v>1516805560</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3219,39 +3209,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.4203</v>
+        <v>0.01</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45597.16385188657</v>
       </c>
       <c r="G44" t="n">
-        <v>5.989</v>
+        <v>2748.03</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45597.16756914352</v>
       </c>
       <c r="I44" t="n">
-        <v>6.176</v>
+        <v>2748.36</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -3262,18 +3250,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1377407433</v>
+        <v>1516814771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3282,19 +3270,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0001</v>
+        <v>0.01</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45597.18416002315</v>
       </c>
       <c r="G45" t="n">
-        <v>129.48</v>
+        <v>2749.48</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45597.18971934028</v>
       </c>
       <c r="I45" t="n">
-        <v>131.24</v>
+        <v>2749.54</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3306,15 +3294,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>13.75</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -3325,18 +3311,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1377834040</v>
+        <v>1516838270</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3345,19 +3331,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0011</v>
+        <v>0.01</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45597.23811159722</v>
       </c>
       <c r="G46" t="n">
-        <v>186.7</v>
+        <v>2751.84</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45597.56254815972</v>
       </c>
       <c r="I46" t="n">
-        <v>184.46</v>
+        <v>2756.23</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3369,15 +3355,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>2754.07</v>
+      </c>
+      <c r="P46" t="n">
+        <v>13.76</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -3388,18 +3374,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U46" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1362491459</v>
+        <v>1515520253</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3408,19 +3398,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.228</v>
+        <v>0.01</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G47" t="n">
-        <v>88.67</v>
+        <v>20.0901</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I47" t="n">
-        <v>87.81</v>
+        <v>20.0775</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3432,37 +3422,35 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="M47" t="n">
-        <v>20.02</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>5</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.2</v>
+        <v>-0.63</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1362491459</v>
+        <v>1517450167</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3471,19 +3459,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0001</v>
+        <v>0.01</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G48" t="n">
-        <v>88.67</v>
+        <v>19.9771</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I48" t="n">
-        <v>87.81999999999999</v>
+        <v>20.0775</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3495,15 +3483,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>5</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3514,39 +3500,39 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1375856858</v>
+        <v>1517930572</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0026</v>
+        <v>0.01</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G49" t="n">
-        <v>188.48</v>
+        <v>20.078</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I49" t="n">
-        <v>190.3</v>
+        <v>20.082</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3558,15 +3544,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.49</v>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>5</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -3577,18 +3561,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1377584836</v>
+        <v>1517879253</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3597,19 +3581,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.4828</v>
+        <v>0.01</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G50" t="n">
-        <v>41.87</v>
+        <v>20.08</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I50" t="n">
-        <v>42.35</v>
+        <v>19.63</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3618,40 +3602,44 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="M50" t="n">
-        <v>20.45</v>
-      </c>
+          <t>stop-out</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="P50" t="n">
+        <v>12.05</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="U50" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1377584836</v>
+        <v>1379227659</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3660,19 +3648,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0013</v>
+        <v>0.1521</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G51" t="n">
-        <v>41.87</v>
+        <v>131.38</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I51" t="n">
-        <v>42.35</v>
+        <v>148.18</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3685,10 +3673,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.05</v>
+        <v>19.98</v>
       </c>
       <c r="M51" t="n">
-        <v>0.06</v>
+        <v>22.54</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3703,18 +3691,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.01</v>
+        <v>2.56</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1350885655</v>
+        <v>1527051962</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3723,19 +3711,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0234</v>
+        <v>0.01</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45604.13145401621</v>
       </c>
       <c r="G52" t="n">
-        <v>427.17</v>
+        <v>19.8302</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45604.56280116898</v>
       </c>
       <c r="I52" t="n">
-        <v>458.18</v>
+        <v>19.9681</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3747,15 +3735,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>10</v>
-      </c>
-      <c r="M52" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="O52" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P52" t="n">
+        <v>5</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
@@ -3766,18 +3756,22 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1414374074</v>
+        <v>1527744522</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3786,19 +3780,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0481</v>
+        <v>0.01</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45604.55607921296</v>
       </c>
       <c r="G53" t="n">
-        <v>311.85</v>
+        <v>19.9784</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45604.57083508102</v>
       </c>
       <c r="I53" t="n">
-        <v>308</v>
+        <v>19.9497</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3810,15 +3804,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>15</v>
-      </c>
-      <c r="M53" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="O53" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
@@ -3829,18 +3825,22 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
+        <v>-1.44</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1414372067</v>
+        <v>1528126100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,19 +3849,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0575</v>
+        <v>0.01</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45604.66918148148</v>
       </c>
       <c r="G54" t="n">
-        <v>260.8</v>
+        <v>20.0428</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45604.71914307871</v>
       </c>
       <c r="I54" t="n">
-        <v>290.19</v>
+        <v>20.0988</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3873,15 +3873,17 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>15</v>
-      </c>
-      <c r="M54" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>20.0988</v>
+      </c>
+      <c r="O54" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>5</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
@@ -3892,43 +3894,47 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
+        <v>2.79</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1377764546</v>
+        <v>1528325630</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45604.72032700232</v>
       </c>
       <c r="G55" t="n">
-        <v>244.47</v>
+        <v>20.0912</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45604.72263849537</v>
       </c>
       <c r="I55" t="n">
-        <v>196.86</v>
+        <v>20.1101</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3936,15 +3942,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L55" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="M55" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="O55" t="n">
+        <v>20.0219</v>
+      </c>
+      <c r="P55" t="n">
+        <v>5</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
@@ -3955,18 +3963,22 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1377764546</v>
+        <v>1531224336</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3975,19 +3987,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0051</v>
+        <v>0.01</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45608.2460031713</v>
       </c>
       <c r="G56" t="n">
-        <v>244.47</v>
+        <v>153.589</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45608.25044886574</v>
       </c>
       <c r="I56" t="n">
-        <v>196.91</v>
+        <v>153.468</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3999,15 +4011,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>153.47</v>
+      </c>
+      <c r="O56" t="n">
+        <v>153.619</v>
+      </c>
+      <c r="P56" t="n">
+        <v>5</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
@@ -4018,39 +4032,43 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
+        <v>-0.79</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1380259753</v>
+        <v>1531227124</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.131</v>
+        <v>0.01</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45608.25015417824</v>
       </c>
       <c r="G57" t="n">
-        <v>190.71</v>
+        <v>153.483</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45608.25207638889</v>
       </c>
       <c r="I57" t="n">
-        <v>161.87</v>
+        <v>153.458</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4062,15 +4080,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="M57" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>153.458</v>
+      </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>5</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
@@ -4081,18 +4099,22 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="U57" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1509051251</v>
+        <v>1531230129</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4101,19 +4123,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45608.2544440162</v>
       </c>
       <c r="G58" t="n">
-        <v>19.8731</v>
+        <v>153.445</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45608.25666561343</v>
       </c>
       <c r="I58" t="n">
-        <v>19.8835</v>
+        <v>153.502</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4127,10 +4149,14 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>153.502</v>
+      </c>
+      <c r="O58" t="n">
+        <v>153.395</v>
+      </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4142,14 +4168,18 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="U58" t="inlineStr"/>
+        <v>-0.37</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1508055372</v>
+        <v>1531192665</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4165,16 +4195,16 @@
         <v>0.02</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45608.19828637732</v>
       </c>
       <c r="G59" t="n">
-        <v>19.8369</v>
+        <v>20.412</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45608.34380275463</v>
       </c>
       <c r="I59" t="n">
-        <v>19.8761</v>
+        <v>20.4421</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4188,8 +4218,12 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>20.4429</v>
+      </c>
+      <c r="O59" t="n">
+        <v>20.5326</v>
+      </c>
       <c r="P59" t="n">
         <v>10</v>
       </c>
@@ -4203,14 +4237,18 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
+        <v>2.94</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1512925323</v>
+        <v>1531349564</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4219,23 +4257,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45608.34449649305</v>
       </c>
       <c r="G60" t="n">
-        <v>20.0663</v>
+        <v>20.4344</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45608.34490908564</v>
       </c>
       <c r="I60" t="n">
-        <v>20.1405</v>
+        <v>20.4507</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4258,20 +4296,20 @@
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3.68</v>
+        <v>-0.8</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1514707570</v>
+        <v>1531351286</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4280,23 +4318,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45595.88186449074</v>
+        <v>45608.34571399305</v>
       </c>
       <c r="G61" t="n">
-        <v>20.1597</v>
+        <v>20.4554</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45595.94583810185</v>
+        <v>45608.35180353009</v>
       </c>
       <c r="I61" t="n">
-        <v>20.1911</v>
+        <v>20.45</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4311,10 +4349,10 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>20.19</v>
+        <v>20.4381</v>
       </c>
       <c r="O61" t="n">
-        <v>20.12</v>
+        <v>20.47</v>
       </c>
       <c r="P61" t="n">
         <v>5</v>
@@ -4329,43 +4367,39 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.26</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1516787001</v>
+        <v>1531358421</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45608.3501140162</v>
       </c>
       <c r="G62" t="n">
-        <v>2748.04</v>
+        <v>20.4503</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45608.35479755787</v>
       </c>
       <c r="I62" t="n">
-        <v>2747.79</v>
+        <v>20.4382</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4379,10 +4413,14 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>20.4388</v>
+      </c>
+      <c r="O62" t="n">
+        <v>20.4767</v>
+      </c>
       <c r="P62" t="n">
-        <v>13.74</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -4394,18 +4432,22 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>-1.18</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1516790032</v>
+        <v>1532703059</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4414,19 +4456,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45597.13541888889</v>
+        <v>45608.75711524305</v>
       </c>
       <c r="G63" t="n">
-        <v>2747.23</v>
+        <v>20.6261</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45597.13874358797</v>
+        <v>45608.76530484953</v>
       </c>
       <c r="I63" t="n">
-        <v>2747.25</v>
+        <v>20.6299</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4440,10 +4482,14 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>20.5745</v>
+      </c>
+      <c r="O63" t="n">
+        <v>20.6364</v>
+      </c>
       <c r="P63" t="n">
-        <v>13.74</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -4455,39 +4501,39 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1516793905</v>
+        <v>1532729622</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>0.01</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45597.14024802083</v>
+        <v>45608.76652064815</v>
       </c>
       <c r="G64" t="n">
-        <v>2747.11</v>
+        <v>154.853</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45597.14548700232</v>
+        <v>45608.76796081018</v>
       </c>
       <c r="I64" t="n">
-        <v>2747.77</v>
+        <v>154.873</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4504,7 +4550,7 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>13.74</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4516,18 +4562,18 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>-0.66</v>
+        <v>0.13</v>
       </c>
       <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1516796610</v>
+        <v>1533930062</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4539,16 +4585,16 @@
         <v>0.01</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45597.14556364583</v>
+        <v>45609.61569380787</v>
       </c>
       <c r="G65" t="n">
-        <v>2748.12</v>
+        <v>20.507</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45597.14936810185</v>
+        <v>45609.63889303241</v>
       </c>
       <c r="I65" t="n">
-        <v>2746.29</v>
+        <v>20.5531</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4562,10 +4608,14 @@
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>20.431</v>
+      </c>
+      <c r="O65" t="n">
+        <v>20.5528</v>
+      </c>
       <c r="P65" t="n">
-        <v>13.74</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -4577,39 +4627,43 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="U65" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1516798655</v>
+        <v>1536772518</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45597.14949375</v>
+        <v>45610.86999649306</v>
       </c>
       <c r="G66" t="n">
-        <v>2746.13</v>
+        <v>20.4311</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45597.15075293981</v>
+        <v>45610.88084664352</v>
       </c>
       <c r="I66" t="n">
-        <v>2747.4</v>
+        <v>20.4923</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4623,10 +4677,14 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>20.4941</v>
+      </c>
+      <c r="O66" t="n">
+        <v>20.5653</v>
+      </c>
       <c r="P66" t="n">
-        <v>13.73</v>
+        <v>10</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -4638,18 +4696,22 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="U66" t="inlineStr"/>
+        <v>5.97</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1516805560</v>
+        <v>1540892910</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4658,19 +4720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45597.16385188657</v>
+        <v>45614.83689460648</v>
       </c>
       <c r="G67" t="n">
-        <v>2748.03</v>
+        <v>20.2371</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45597.16756914352</v>
+        <v>45615.43822850694</v>
       </c>
       <c r="I67" t="n">
-        <v>2748.36</v>
+        <v>20.3181</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4684,33 +4746,41 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="O67" t="n">
+        <v>20.3179</v>
+      </c>
       <c r="P67" t="n">
-        <v>13.74</v>
+        <v>10</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="U67" t="inlineStr"/>
+        <v>7.97</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1516814771</v>
+        <v>1541930457</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4719,19 +4789,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45597.18416002315</v>
+        <v>45615.56159975695</v>
       </c>
       <c r="G68" t="n">
-        <v>2749.48</v>
+        <v>20.2629</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45597.18971934028</v>
+        <v>45615.58509630787</v>
       </c>
       <c r="I68" t="n">
-        <v>2749.54</v>
+        <v>20.2887</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4745,10 +4815,14 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>20.2059</v>
+      </c>
+      <c r="O68" t="n">
+        <v>20.2856</v>
+      </c>
       <c r="P68" t="n">
-        <v>13.75</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4760,39 +4834,43 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U68" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1516838270</v>
+        <v>1553997553</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>0.01</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45597.23811159722</v>
+        <v>45623.53527240741</v>
       </c>
       <c r="G69" t="n">
-        <v>2751.84</v>
+        <v>20.7084</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45597.56254815972</v>
+        <v>45623.57548773148</v>
       </c>
       <c r="I69" t="n">
-        <v>2756.23</v>
+        <v>20.7775</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4806,12 +4884,14 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>20.7706</v>
+      </c>
       <c r="O69" t="n">
-        <v>2754.07</v>
+        <v>20.68</v>
       </c>
       <c r="P69" t="n">
-        <v>13.76</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -4823,18 +4903,18 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>4.39</v>
+        <v>-3.33</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>[T/P]</t>
+          <t>[S/L]</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1515520253</v>
+        <v>1554074835</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4843,23 +4923,23 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>0.01</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45623.57516572917</v>
       </c>
       <c r="G70" t="n">
-        <v>20.0901</v>
+        <v>20.7426</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45623.57574133102</v>
       </c>
       <c r="I70" t="n">
-        <v>20.0775</v>
+        <v>20.7764</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4882,20 +4962,20 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>-0.63</v>
+        <v>-1.63</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1517450167</v>
+        <v>1555669398</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4908,19 +4988,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45597.59638905092</v>
+        <v>45624.55073625</v>
       </c>
       <c r="G71" t="n">
-        <v>19.9771</v>
+        <v>20.3273</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45597.73077270833</v>
+        <v>45624.71914708333</v>
       </c>
       <c r="I71" t="n">
-        <v>20.0775</v>
+        <v>20.4312</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4934,10 +5014,14 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>20.1748</v>
+      </c>
+      <c r="O71" t="n">
+        <v>20.4293</v>
+      </c>
       <c r="P71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -4949,14 +5033,18 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>5</v>
-      </c>
-      <c r="U71" t="inlineStr"/>
+        <v>10.17</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1517930572</v>
+        <v>1563562241</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4965,23 +5053,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45631.25027201389</v>
       </c>
       <c r="G72" t="n">
-        <v>20.078</v>
+        <v>20.3099</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45631.6258153125</v>
       </c>
       <c r="I72" t="n">
-        <v>20.082</v>
+        <v>20.2391</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4995,10 +5083,14 @@
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="N72" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20.3672</v>
+      </c>
       <c r="P72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -5010,18 +5102,22 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="U72" t="inlineStr"/>
+        <v>-6.99</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1517879253</v>
+        <v>1473693877</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5030,19 +5126,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45562.69351818287</v>
       </c>
       <c r="G73" t="n">
-        <v>20.08</v>
+        <v>700.8</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I73" t="n">
-        <v>19.63</v>
+        <v>623.8</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5051,44 +5147,40 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>stop-out</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M73" t="n">
+        <v>12.28</v>
+      </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="P73" t="n">
-        <v>12.05</v>
-      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+        <v>-2.69</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1379227659</v>
+        <v>1493848938</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5097,19 +5189,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.1521</v>
+        <v>0.0213</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45579.70088467593</v>
       </c>
       <c r="G74" t="n">
-        <v>131.38</v>
+        <v>640.3</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I74" t="n">
-        <v>148.18</v>
+        <v>623.8</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5122,10 +5214,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>19.98</v>
+        <v>14.96</v>
       </c>
       <c r="M74" t="n">
-        <v>22.54</v>
+        <v>13.77</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -5140,14 +5232,14 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>2.56</v>
+        <v>-1.19</v>
       </c>
       <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1527051962</v>
+        <v>1583724019</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5160,19 +5252,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45604.13145401621</v>
+        <v>45646.60647967592</v>
       </c>
       <c r="G75" t="n">
-        <v>19.8302</v>
+        <v>20.2054</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45604.56280116898</v>
+        <v>45646.696485625</v>
       </c>
       <c r="I75" t="n">
-        <v>19.9681</v>
+        <v>20.1035</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5187,13 +5279,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>19.97</v>
+        <v>20.1055</v>
       </c>
       <c r="O75" t="n">
-        <v>20.12</v>
+        <v>20.3273</v>
       </c>
       <c r="P75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -5205,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>6.9</v>
+        <v>-10.13</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -5216,7 +5308,7 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1527744522</v>
+        <v>1583841034</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5232,16 +5324,16 @@
         <v>0.01</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45604.55607921296</v>
+        <v>45646.63988152778</v>
       </c>
       <c r="G76" t="n">
-        <v>19.9784</v>
+        <v>20.173</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45604.57083508102</v>
+        <v>45646.70582428241</v>
       </c>
       <c r="I76" t="n">
-        <v>19.9497</v>
+        <v>20.0949</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5256,10 +5348,10 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>19.95</v>
+        <v>20.0975</v>
       </c>
       <c r="O76" t="n">
-        <v>20.2</v>
+        <v>20.2542</v>
       </c>
       <c r="P76" t="n">
         <v>5</v>
@@ -5274,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-1.44</v>
+        <v>-3.88</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -5285,7 +5377,7 @@
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1528126100</v>
+        <v>1585474078</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -5298,19 +5390,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45604.66918148148</v>
+        <v>45649.40133020833</v>
       </c>
       <c r="G77" t="n">
-        <v>20.0428</v>
+        <v>20.0935</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45604.71914307871</v>
+        <v>45649.56824730324</v>
       </c>
       <c r="I77" t="n">
-        <v>20.0988</v>
+        <v>20.1707</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5319,19 +5411,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>20.0988</v>
+        <v>20</v>
       </c>
       <c r="O77" t="n">
-        <v>20.2</v>
+        <v>20.17</v>
       </c>
       <c r="P77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -5343,18 +5435,18 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2.79</v>
+        <v>7.65</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>[S/L]</t>
+          <t>[T/P]</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1528325630</v>
+        <v>1586033461</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -5363,27 +5455,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>0.01</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45604.72032700232</v>
+        <v>45649.63114609953</v>
       </c>
       <c r="G78" t="n">
-        <v>20.0912</v>
+        <v>20.1772</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45604.72263849537</v>
+        <v>45649.63200465278</v>
       </c>
       <c r="I78" t="n">
-        <v>20.1101</v>
+        <v>20.1671</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5394,10 +5486,10 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>20.11</v>
+        <v>20.1687</v>
       </c>
       <c r="O78" t="n">
-        <v>20.0219</v>
+        <v>20.2379</v>
       </c>
       <c r="P78" t="n">
         <v>5</v>
@@ -5412,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -5423,11 +5515,11 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1531224336</v>
+        <v>1587036381</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5436,19 +5528,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45608.2460031713</v>
+        <v>45650.48790526621</v>
       </c>
       <c r="G79" t="n">
-        <v>153.589</v>
+        <v>20.1462</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45608.25044886574</v>
+        <v>45650.58025611111</v>
       </c>
       <c r="I79" t="n">
-        <v>153.468</v>
+        <v>20.1627</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5463,13 +5555,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>153.47</v>
+        <v>20.1627</v>
       </c>
       <c r="O79" t="n">
-        <v>153.619</v>
+        <v>20.22</v>
       </c>
       <c r="P79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5481,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>-0.79</v>
+        <v>1.64</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -5492,32 +5584,32 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1531227124</v>
+        <v>1500272843</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.01</v>
+        <v>0.0264</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45608.25015417824</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G80" t="n">
-        <v>153.483</v>
+        <v>718.5</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45608.25207638889</v>
+        <v>45663.67045758102</v>
       </c>
       <c r="I80" t="n">
-        <v>153.458</v>
+        <v>757.79</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5529,15 +5621,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
-        <v>153.458</v>
-      </c>
+      <c r="L80" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="M80" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="n">
-        <v>5</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
@@ -5548,43 +5640,39 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1.04</v>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1531230129</v>
+        <v>1500272843</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.01</v>
+        <v>0.0021</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45608.2544440162</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G81" t="n">
-        <v>153.445</v>
+        <v>718.5</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45608.25666561343</v>
+        <v>45663.67059782407</v>
       </c>
       <c r="I81" t="n">
-        <v>153.502</v>
+        <v>758.27</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5596,17 +5684,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
-        <v>153.502</v>
-      </c>
-      <c r="O81" t="n">
-        <v>153.395</v>
-      </c>
-      <c r="P81" t="n">
-        <v>5</v>
-      </c>
+      <c r="L81" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
@@ -5617,22 +5703,18 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1531192665</v>
+        <v>1518147105</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MAXN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5641,19 +5723,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45608.19828637732</v>
+        <v>45597.8504690162</v>
       </c>
       <c r="G82" t="n">
-        <v>20.412</v>
+        <v>10.92</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45608.34380275463</v>
+        <v>45667.68126778935</v>
       </c>
       <c r="I82" t="n">
-        <v>20.4421</v>
+        <v>6.52</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5665,17 +5747,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="n">
-        <v>20.4429</v>
-      </c>
-      <c r="O82" t="n">
-        <v>20.5326</v>
-      </c>
-      <c r="P82" t="n">
-        <v>10</v>
-      </c>
+      <c r="L82" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="M82" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
@@ -5686,43 +5766,39 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-4.4</v>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1531349564</v>
+        <v>1551373923</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.01</v>
+        <v>0.1195</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45608.34449649305</v>
+        <v>45621.85639895833</v>
       </c>
       <c r="G83" t="n">
-        <v>20.4344</v>
+        <v>167.24</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45608.34490908564</v>
+        <v>45678.70646498843</v>
       </c>
       <c r="I83" t="n">
-        <v>20.4507</v>
+        <v>198.83</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5734,13 +5810,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M83" t="n">
+        <v>23.76</v>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="n">
-        <v>5</v>
-      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
@@ -5751,18 +5829,18 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>-0.8</v>
+        <v>3.77</v>
       </c>
       <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1531351286</v>
+        <v>1373744560</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5771,19 +5849,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.01</v>
+        <v>0.1248</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45608.34571399305</v>
+        <v>45476.64586885417</v>
       </c>
       <c r="G84" t="n">
-        <v>20.4554</v>
+        <v>202.58</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45608.35180353009</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I84" t="n">
-        <v>20.45</v>
+        <v>172.09</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5795,17 +5873,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="n">
-        <v>20.4381</v>
-      </c>
-      <c r="O84" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="P84" t="n">
-        <v>5</v>
-      </c>
+      <c r="L84" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="M84" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
@@ -5816,18 +5892,18 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>-0.26</v>
+        <v>-3.8</v>
       </c>
       <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1531358421</v>
+        <v>1450039117</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5836,19 +5912,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.02</v>
+        <v>0.068</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45608.3501140162</v>
+        <v>45544.65070009259</v>
       </c>
       <c r="G85" t="n">
-        <v>20.4503</v>
+        <v>161.58</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45608.35479755787</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I85" t="n">
-        <v>20.4382</v>
+        <v>172.09</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5860,17 +5936,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="n">
-        <v>20.4388</v>
-      </c>
-      <c r="O85" t="n">
-        <v>20.4767</v>
-      </c>
-      <c r="P85" t="n">
-        <v>10</v>
-      </c>
+      <c r="L85" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M85" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
@@ -5881,22 +5955,18 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.71</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1532703059</v>
+        <v>1468472119</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5905,19 +5975,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.02</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45608.75711524305</v>
+        <v>45559.65212880787</v>
       </c>
       <c r="G86" t="n">
-        <v>20.6261</v>
+        <v>277.82</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45608.76530484953</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I86" t="n">
-        <v>20.6299</v>
+        <v>336.69</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5929,17 +5999,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="n">
-        <v>20.5745</v>
-      </c>
-      <c r="O86" t="n">
-        <v>20.6364</v>
-      </c>
-      <c r="P86" t="n">
-        <v>10</v>
-      </c>
+      <c r="L86" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M86" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
@@ -5950,18 +6018,18 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0.37</v>
+        <v>4.23</v>
       </c>
       <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1532729622</v>
+        <v>1470564087</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5970,19 +6038,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.01</v>
+        <v>0.0742</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45608.76652064815</v>
+        <v>45560.82041144676</v>
       </c>
       <c r="G87" t="n">
-        <v>154.853</v>
+        <v>269.23</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45608.76796081018</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I87" t="n">
-        <v>154.873</v>
+        <v>336.69</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -5994,35 +6062,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M87" t="n">
+        <v>24.98</v>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="n">
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>5</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0.13</v>
       </c>
       <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1533930062</v>
+        <v>1599434998</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6031,19 +6101,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.01</v>
+        <v>0.0477</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45609.61569380787</v>
+        <v>45663.73100940972</v>
       </c>
       <c r="G88" t="n">
-        <v>20.507</v>
+        <v>313.98</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45609.63889303241</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I88" t="n">
-        <v>20.5531</v>
+        <v>336.69</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6055,17 +6125,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="n">
-        <v>20.431</v>
-      </c>
-      <c r="O88" t="n">
-        <v>20.5528</v>
-      </c>
-      <c r="P88" t="n">
-        <v>5</v>
-      </c>
+      <c r="L88" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M88" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
@@ -6076,22 +6144,18 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>1.08</v>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1536772518</v>
+        <v>1495548850</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6100,19 +6164,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.02</v>
+        <v>0.1047</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45610.86999649306</v>
+        <v>45580.70599549769</v>
       </c>
       <c r="G89" t="n">
-        <v>20.4311</v>
+        <v>133.61</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45610.88084664352</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I89" t="n">
-        <v>20.4923</v>
+        <v>143.18</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6124,17 +6188,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="n">
-        <v>20.4941</v>
-      </c>
-      <c r="O89" t="n">
-        <v>20.5653</v>
-      </c>
-      <c r="P89" t="n">
-        <v>10</v>
-      </c>
+      <c r="L89" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="M89" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
@@ -6145,22 +6207,18 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1540892910</v>
+        <v>1517512112</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6169,19 +6227,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.02</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45614.83689460648</v>
+        <v>45597.61040866898</v>
       </c>
       <c r="G90" t="n">
-        <v>20.2371</v>
+        <v>132.62</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45615.43822850694</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I90" t="n">
-        <v>20.3181</v>
+        <v>143.18</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6193,43 +6251,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="O90" t="n">
-        <v>20.3179</v>
-      </c>
-      <c r="P90" t="n">
+      <c r="L90" t="n">
         <v>10</v>
       </c>
+      <c r="M90" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1541930457</v>
+        <v>1582735114</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6238,23 +6290,23 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.02</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45615.56159975695</v>
+        <v>45645.90076787037</v>
       </c>
       <c r="G91" t="n">
-        <v>20.2629</v>
+        <v>130.51</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45615.58509630787</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I91" t="n">
-        <v>20.2887</v>
+        <v>143.18</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6262,17 +6314,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
-        <v>20.2059</v>
-      </c>
-      <c r="O91" t="n">
-        <v>20.2856</v>
-      </c>
-      <c r="P91" t="n">
-        <v>10</v>
-      </c>
+      <c r="L91" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="M91" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -6283,18 +6333,14 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.96</v>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1553997553</v>
+        <v>1657658561</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -6303,23 +6349,23 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45623.53527240741</v>
+        <v>45702.18774210648</v>
       </c>
       <c r="G92" t="n">
-        <v>20.7084</v>
+        <v>20.4257</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45623.57548773148</v>
+        <v>45702.56168643518</v>
       </c>
       <c r="I92" t="n">
-        <v>20.7775</v>
+        <v>20.3656</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6334,13 +6380,13 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>20.7706</v>
+        <v>20.3664</v>
       </c>
       <c r="O92" t="n">
-        <v>20.68</v>
+        <v>20.5213</v>
       </c>
       <c r="P92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -6352,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-3.33</v>
+        <v>-5.9</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -6363,7 +6409,7 @@
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1554074835</v>
+        <v>1660829104</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -6372,23 +6418,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45623.57516572917</v>
+        <v>45705.64981799768</v>
       </c>
       <c r="G93" t="n">
-        <v>20.7426</v>
+        <v>20.3237</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45623.57574133102</v>
+        <v>45705.72866341435</v>
       </c>
       <c r="I93" t="n">
-        <v>20.7764</v>
+        <v>20.2738</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6402,10 +6448,14 @@
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>20.2738</v>
+      </c>
+      <c r="O93" t="n">
+        <v>20.3936</v>
+      </c>
       <c r="P93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -6417,18 +6467,22 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>-1.63</v>
-      </c>
-      <c r="U93" t="inlineStr"/>
+        <v>-4.92</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1555669398</v>
+        <v>1378903852</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6437,19 +6491,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.02</v>
+        <v>0.0616</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45624.55073625</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G94" t="n">
-        <v>20.3273</v>
+        <v>227.77</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45624.71914708333</v>
+        <v>45706.65274813658</v>
       </c>
       <c r="I94" t="n">
-        <v>20.4312</v>
+        <v>243.58</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6461,17 +6515,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="n">
-        <v>20.1748</v>
-      </c>
-      <c r="O94" t="n">
-        <v>20.4293</v>
-      </c>
-      <c r="P94" t="n">
-        <v>10</v>
-      </c>
+      <c r="L94" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="M94" t="n">
+        <v>15</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -6482,22 +6534,18 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1563562241</v>
+        <v>1378903852</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6506,19 +6554,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.02</v>
+        <v>0.0042</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45631.25027201389</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G95" t="n">
-        <v>20.3099</v>
+        <v>227.77</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45631.6258153125</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I95" t="n">
-        <v>20.2391</v>
+        <v>243.45</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6530,17 +6578,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="O95" t="n">
-        <v>20.3672</v>
-      </c>
-      <c r="P95" t="n">
-        <v>10</v>
-      </c>
+      <c r="L95" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -6551,22 +6597,18 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1473693877</v>
+        <v>1456814919</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6575,19 +6617,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.019</v>
+        <v>0.0665</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45562.69351818287</v>
+        <v>45548.6657375</v>
       </c>
       <c r="G96" t="n">
-        <v>700.8</v>
+        <v>222.94</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I96" t="n">
-        <v>623.8</v>
+        <v>243.45</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6600,10 +6642,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>14.97</v>
+        <v>14.83</v>
       </c>
       <c r="M96" t="n">
-        <v>12.28</v>
+        <v>16.19</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6618,18 +6660,18 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>-2.69</v>
+        <v>1.36</v>
       </c>
       <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1493848938</v>
+        <v>1499061783</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6638,23 +6680,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0213</v>
+        <v>0.0558</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45579.70088467593</v>
+        <v>45582.73996877314</v>
       </c>
       <c r="G97" t="n">
-        <v>640.3</v>
+        <v>232.2</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I97" t="n">
-        <v>623.8</v>
+        <v>243.45</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6663,10 +6705,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>14.96</v>
+        <v>12.96</v>
       </c>
       <c r="M97" t="n">
-        <v>13.77</v>
+        <v>13.58</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -6681,14 +6723,14 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>-1.19</v>
+        <v>0.62</v>
       </c>
       <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1583724019</v>
+        <v>1717095547</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -6701,19 +6743,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45646.60647967592</v>
+        <v>45736.81342114583</v>
       </c>
       <c r="G98" t="n">
-        <v>20.2054</v>
+        <v>20.1198</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45646.696485625</v>
+        <v>45737.11337774306</v>
       </c>
       <c r="I98" t="n">
-        <v>20.1035</v>
+        <v>20.1348</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6728,25 +6770,25 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>20.1055</v>
+        <v>20.1349</v>
       </c>
       <c r="O98" t="n">
-        <v>20.3273</v>
+        <v>20.1623</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>-10.13</v>
+        <v>2.98</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -6757,11 +6799,11 @@
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1583841034</v>
+        <v>1554741910</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6770,19 +6812,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45646.63988152778</v>
+        <v>45623.74951100694</v>
       </c>
       <c r="G99" t="n">
-        <v>20.173</v>
+        <v>15.3</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45646.70582428241</v>
+        <v>45741.87177293981</v>
       </c>
       <c r="I99" t="n">
-        <v>20.0949</v>
+        <v>20.29</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6794,17 +6836,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
-        <v>20.0975</v>
-      </c>
-      <c r="O99" t="n">
-        <v>20.2542</v>
-      </c>
-      <c r="P99" t="n">
-        <v>5</v>
-      </c>
+      <c r="L99" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="M99" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -6815,22 +6855,18 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>3.05</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1585474078</v>
+        <v>1414372592</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6839,19 +6875,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45649.40133020833</v>
+        <v>45511.7228721412</v>
       </c>
       <c r="G100" t="n">
-        <v>20.0935</v>
+        <v>455.4</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45649.56824730324</v>
+        <v>45742.77596394676</v>
       </c>
       <c r="I100" t="n">
-        <v>20.1707</v>
+        <v>547.14</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6863,17 +6899,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="n">
-        <v>20</v>
-      </c>
-      <c r="O100" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="P100" t="n">
-        <v>10</v>
-      </c>
+      <c r="L100" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M100" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
@@ -6884,22 +6918,18 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1586033461</v>
+        <v>1450043624</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6908,19 +6938,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.01</v>
+        <v>0.0138</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45649.63114609953</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G101" t="n">
-        <v>20.1772</v>
+        <v>147.48</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45649.63200465278</v>
+        <v>45743.76599777778</v>
       </c>
       <c r="I101" t="n">
-        <v>20.1671</v>
+        <v>139.86</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6932,17 +6962,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
-        <v>20.1687</v>
-      </c>
-      <c r="O101" t="n">
-        <v>20.2379</v>
-      </c>
-      <c r="P101" t="n">
-        <v>5</v>
-      </c>
+      <c r="L101" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -6953,22 +6981,18 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.11</v>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1587036381</v>
+        <v>1358151307</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6977,19 +7001,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.02</v>
+        <v>0.0124</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45650.48790526621</v>
+        <v>45460.88529037037</v>
       </c>
       <c r="G102" t="n">
-        <v>20.1462</v>
+        <v>165.93</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45650.58025611111</v>
+        <v>45743.76632650463</v>
       </c>
       <c r="I102" t="n">
-        <v>20.1627</v>
+        <v>149.33</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7001,17 +7025,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="n">
-        <v>20.1627</v>
-      </c>
-      <c r="O102" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="P102" t="n">
-        <v>10</v>
-      </c>
+      <c r="L102" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
@@ -7022,22 +7044,18 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.21</v>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1500272843</v>
+        <v>1422773288</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7046,19 +7064,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.0264</v>
+        <v>0.2</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45518.84428505787</v>
       </c>
       <c r="G103" t="n">
-        <v>718.5</v>
+        <v>51.24</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45663.67045758102</v>
+        <v>45743.76769060185</v>
       </c>
       <c r="I103" t="n">
-        <v>757.79</v>
+        <v>58.08</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7071,10 +7089,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>18.97</v>
+        <v>10.25</v>
       </c>
       <c r="M103" t="n">
-        <v>20.01</v>
+        <v>11.62</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -7089,18 +7107,18 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1500272843</v>
+        <v>1631473921</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7109,19 +7127,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.0021</v>
+        <v>0.2745</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45685.8356116088</v>
       </c>
       <c r="G104" t="n">
-        <v>718.5</v>
+        <v>40.05</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45663.67059782407</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I104" t="n">
-        <v>758.27</v>
+        <v>44.8</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7130,14 +7148,14 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.51</v>
+        <v>10.99</v>
       </c>
       <c r="M104" t="n">
-        <v>1.59</v>
+        <v>12.3</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -7152,18 +7170,18 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0.08</v>
+        <v>1.31</v>
       </c>
       <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1518147105</v>
+        <v>1642763333</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7172,19 +7190,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0.2459</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45597.8504690162</v>
+        <v>45692.86672944445</v>
       </c>
       <c r="G105" t="n">
-        <v>10.92</v>
+        <v>40.66</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45667.68126778935</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I105" t="n">
-        <v>6.52</v>
+        <v>44.8</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7193,14 +7211,14 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10.92</v>
+        <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>6.52</v>
+        <v>11.02</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -7215,18 +7233,18 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>-4.4</v>
+        <v>1.02</v>
       </c>
       <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1551373923</v>
+        <v>1666451221</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7235,19 +7253,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1195</v>
+        <v>0.1796</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45621.85639895833</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G106" t="n">
-        <v>167.24</v>
+        <v>43</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45678.70646498843</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I106" t="n">
-        <v>198.83</v>
+        <v>44.8</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7256,14 +7274,14 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>19.99</v>
+        <v>7.72</v>
       </c>
       <c r="M106" t="n">
-        <v>23.76</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
@@ -7278,59 +7296,57 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>3.77</v>
+        <v>0.33</v>
       </c>
       <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1373744560</v>
+        <v>1749053104</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.1248</v>
+        <v>0.01</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45476.64586885417</v>
+        <v>45754.65117414352</v>
       </c>
       <c r="G107" t="n">
-        <v>202.58</v>
+        <v>4903.7</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45754.65218731482</v>
       </c>
       <c r="I107" t="n">
-        <v>172.09</v>
+        <v>4891.1</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="M107" t="n">
-        <v>21.48</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
+      <c r="P107" t="n">
+        <v>12.26</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
@@ -7341,59 +7357,57 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>-3.8</v>
+        <v>6.3</v>
       </c>
       <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1450039117</v>
+        <v>1756767326</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.068</v>
+        <v>0.01</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45544.65070009259</v>
+        <v>45756.64805717592</v>
       </c>
       <c r="G108" t="n">
-        <v>161.58</v>
+        <v>5004.7</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45756.64937413194</v>
       </c>
       <c r="I108" t="n">
-        <v>172.09</v>
+        <v>5005.2</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="M108" t="n">
-        <v>11.7</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>12.51</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
@@ -7404,59 +7418,57 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>0.71</v>
+        <v>-0.25</v>
       </c>
       <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1468472119</v>
+        <v>1756797155</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45559.65212880787</v>
+        <v>45756.6510503125</v>
       </c>
       <c r="G109" t="n">
-        <v>277.82</v>
+        <v>4992.2</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45756.65185319445</v>
       </c>
       <c r="I109" t="n">
-        <v>336.69</v>
+        <v>5013.4</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M109" t="n">
-        <v>24.21</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
+      <c r="P109" t="n">
+        <v>12.48</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
@@ -7467,18 +7479,18 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>4.23</v>
+        <v>-10.6</v>
       </c>
       <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1470564087</v>
+        <v>1767688540</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7487,19 +7499,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.0742</v>
+        <v>0.01</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45560.82041144676</v>
+        <v>45761.6294487037</v>
       </c>
       <c r="G110" t="n">
-        <v>269.23</v>
+        <v>20.1226</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45761.66966099537</v>
       </c>
       <c r="I110" t="n">
-        <v>336.69</v>
+        <v>20.047</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7511,15 +7523,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L110" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M110" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>20.048</v>
+      </c>
+      <c r="O110" t="n">
+        <v>20.3404</v>
+      </c>
+      <c r="P110" t="n">
+        <v>5</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
@@ -7530,18 +7544,22 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>5</v>
-      </c>
-      <c r="U110" t="inlineStr"/>
+        <v>-3.77</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1599434998</v>
+        <v>1768229183</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7550,19 +7568,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.0477</v>
+        <v>0.01</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45663.73100940972</v>
+        <v>45761.71402207176</v>
       </c>
       <c r="G111" t="n">
-        <v>313.98</v>
+        <v>20.0759</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45761.77371288194</v>
       </c>
       <c r="I111" t="n">
-        <v>336.69</v>
+        <v>20.1099</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7574,15 +7592,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L111" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="M111" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>20.1099</v>
+      </c>
+      <c r="O111" t="n">
+        <v>20.2122</v>
+      </c>
+      <c r="P111" t="n">
+        <v>5</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
@@ -7593,18 +7613,22 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U111" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1495548850</v>
+        <v>1769815245</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7613,19 +7637,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.1047</v>
+        <v>0.01</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45580.70599549769</v>
+        <v>45762.50265097222</v>
       </c>
       <c r="G112" t="n">
-        <v>133.61</v>
+        <v>20.0545</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45762.61225923611</v>
       </c>
       <c r="I112" t="n">
-        <v>143.18</v>
+        <v>19.9735</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7637,15 +7661,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L112" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="M112" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="N112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>19.9742</v>
+      </c>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>5</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
@@ -7656,18 +7680,22 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" t="inlineStr"/>
+        <v>-4.06</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1517512112</v>
+        <v>1666451221</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7676,19 +7704,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45597.61040866898</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G113" t="n">
-        <v>132.62</v>
+        <v>43</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45764.85028728009</v>
       </c>
       <c r="I113" t="n">
-        <v>143.18</v>
+        <v>47.89</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7701,10 +7729,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>10</v>
+        <v>2.27</v>
       </c>
       <c r="M113" t="n">
-        <v>10.8</v>
+        <v>2.53</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -7719,18 +7747,18 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1582735114</v>
+        <v>1450043624</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7739,23 +7767,23 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45645.90076787037</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G114" t="n">
-        <v>130.51</v>
+        <v>147.48</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45764.8517803588</v>
       </c>
       <c r="I114" t="n">
-        <v>143.18</v>
+        <v>143.22</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7764,10 +7792,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>9.960000000000001</v>
+        <v>14.75</v>
       </c>
       <c r="M114" t="n">
-        <v>10.92</v>
+        <v>14.32</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -7782,14 +7810,14 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>0.96</v>
+        <v>-0.42</v>
       </c>
       <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1657658561</v>
+        <v>1777308201</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -7802,19 +7830,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45702.18774210648</v>
+        <v>45768.12181488426</v>
       </c>
       <c r="G115" t="n">
-        <v>20.4257</v>
+        <v>19.7053</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45702.56168643518</v>
+        <v>45768.13306659722</v>
       </c>
       <c r="I115" t="n">
-        <v>20.3656</v>
+        <v>19.7154</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7828,14 +7856,10 @@
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="n">
-        <v>20.3664</v>
-      </c>
-      <c r="O115" t="n">
-        <v>20.5213</v>
-      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -7847,18 +7871,14 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.51</v>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1660829104</v>
+        <v>1781449563</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -7871,19 +7891,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45705.64981799768</v>
+        <v>45769.73814164352</v>
       </c>
       <c r="G116" t="n">
-        <v>20.3237</v>
+        <v>19.58</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45705.72866341435</v>
+        <v>45769.76084202546</v>
       </c>
       <c r="I116" t="n">
-        <v>20.2738</v>
+        <v>19.5255</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7897,14 +7917,10 @@
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="n">
-        <v>20.2738</v>
-      </c>
-      <c r="O116" t="n">
-        <v>20.3936</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -7916,22 +7932,18 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-2.79</v>
+      </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1378903852</v>
+        <v>1560258921</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7940,19 +7952,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.0616</v>
+        <v>1</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45629.37798611111</v>
       </c>
       <c r="G117" t="n">
-        <v>227.77</v>
+        <v>48.68</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45706.65274813658</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I117" t="n">
-        <v>243.58</v>
+        <v>44.15</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7965,10 +7977,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>14.03</v>
+        <v>51.41</v>
       </c>
       <c r="M117" t="n">
-        <v>15</v>
+        <v>49.84</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -7983,18 +7995,18 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>0.97</v>
+        <v>-1.57</v>
       </c>
       <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1378903852</v>
+        <v>1748583646</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8003,19 +8015,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.0042</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45754.57938657407</v>
       </c>
       <c r="G118" t="n">
-        <v>227.77</v>
+        <v>37.258</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I118" t="n">
-        <v>243.45</v>
+        <v>44.15</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8028,10 +8040,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0.96</v>
+        <v>41.06</v>
       </c>
       <c r="M118" t="n">
-        <v>1.02</v>
+        <v>49.84</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8046,18 +8058,18 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>0.06</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1456814919</v>
+        <v>1373808226</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8066,19 +8078,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.0665</v>
+        <v>0.0234</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45548.6657375</v>
+        <v>45476.6587916088</v>
       </c>
       <c r="G119" t="n">
-        <v>222.94</v>
+        <v>459.24</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I119" t="n">
-        <v>243.45</v>
+        <v>434.71</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8091,10 +8103,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>14.83</v>
+        <v>10.75</v>
       </c>
       <c r="M119" t="n">
-        <v>16.19</v>
+        <v>10.17</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8109,18 +8121,18 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>1.36</v>
+        <v>-0.58</v>
       </c>
       <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1499061783</v>
+        <v>1426782063</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8129,23 +8141,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0558</v>
+        <v>0.0372</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45582.73996877314</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G120" t="n">
-        <v>232.2</v>
+        <v>419.46</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I120" t="n">
-        <v>243.45</v>
+        <v>434.71</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8154,10 +8166,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>12.96</v>
+        <v>15.6</v>
       </c>
       <c r="M120" t="n">
-        <v>13.58</v>
+        <v>16.17</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -8172,18 +8184,18 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1717095547</v>
+        <v>1426782063</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8192,19 +8204,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45736.81342114583</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G121" t="n">
-        <v>20.1198</v>
+        <v>419.46</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45737.11337774306</v>
+        <v>45785.65885817129</v>
       </c>
       <c r="I121" t="n">
-        <v>20.1348</v>
+        <v>437.05</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8216,43 +8228,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
-        <v>20.1349</v>
-      </c>
-      <c r="O121" t="n">
-        <v>20.1623</v>
-      </c>
-      <c r="P121" t="n">
-        <v>20</v>
-      </c>
+      <c r="L121" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1554741910</v>
+        <v>1744929368</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8261,23 +8267,23 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.61</v>
+        <v>0.0424</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45623.74951100694</v>
+        <v>45751.7450085301</v>
       </c>
       <c r="G122" t="n">
-        <v>15.3</v>
+        <v>324.48</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45741.87177293981</v>
+        <v>45785.65909077547</v>
       </c>
       <c r="I122" t="n">
-        <v>20.29</v>
+        <v>353.02</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8286,10 +8292,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>9.33</v>
+        <v>13.76</v>
       </c>
       <c r="M122" t="n">
-        <v>12.38</v>
+        <v>14.97</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -8304,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="U122" t="inlineStr"/>
     </row>
@@ -8324,7 +8330,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.01</v>
+        <v>0.0229</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>45511.7228721412</v>
@@ -8333,10 +8339,10 @@
         <v>455.4</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45742.77596394676</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I123" t="n">
-        <v>547.14</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8349,10 +8355,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>4.55</v>
+        <v>10.43</v>
       </c>
       <c r="M123" t="n">
-        <v>5.47</v>
+        <v>13.03</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -8367,18 +8373,18 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>0.92</v>
+        <v>2.6</v>
       </c>
       <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1450043624</v>
+        <v>1582737192</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8387,23 +8393,23 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.0138</v>
+        <v>0.0371</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45645.90143914352</v>
       </c>
       <c r="G124" t="n">
-        <v>147.48</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45743.76599777778</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I124" t="n">
-        <v>139.86</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8412,10 +8418,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.04</v>
+        <v>19.46</v>
       </c>
       <c r="M124" t="n">
-        <v>1.93</v>
+        <v>21.11</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -8430,18 +8436,18 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>-0.11</v>
+        <v>1.65</v>
       </c>
       <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1358151307</v>
+        <v>1599454287</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8450,19 +8456,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.0124</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45460.88529037037</v>
+        <v>45663.73715268519</v>
       </c>
       <c r="G125" t="n">
-        <v>165.93</v>
+        <v>196.49</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45743.76632650463</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I125" t="n">
-        <v>149.33</v>
+        <v>196.89</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8475,10 +8481,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.06</v>
+        <v>14.99</v>
       </c>
       <c r="M125" t="n">
-        <v>1.85</v>
+        <v>15.02</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -8493,18 +8499,18 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>-0.21</v>
+        <v>0.03</v>
       </c>
       <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1422773288</v>
+        <v>1621495599</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8513,19 +8519,19 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.2</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45518.84428505787</v>
+        <v>45678.83206015046</v>
       </c>
       <c r="G126" t="n">
-        <v>51.24</v>
+        <v>183.39</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45743.76769060185</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I126" t="n">
-        <v>58.08</v>
+        <v>196.89</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8538,10 +8544,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>10.25</v>
+        <v>14.98</v>
       </c>
       <c r="M126" t="n">
-        <v>11.62</v>
+        <v>16.09</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
@@ -8556,18 +8562,18 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1631473921</v>
+        <v>1631467534</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8576,19 +8582,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.2745</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45685.8356116088</v>
+        <v>45685.83235356482</v>
       </c>
       <c r="G127" t="n">
-        <v>40.05</v>
+        <v>159.74</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I127" t="n">
-        <v>44.8</v>
+        <v>196.89</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8597,14 +8603,14 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>10.99</v>
+        <v>14.97</v>
       </c>
       <c r="M127" t="n">
-        <v>12.3</v>
+        <v>18.45</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
@@ -8619,18 +8625,18 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>1.31</v>
+        <v>3.48</v>
       </c>
       <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1642763333</v>
+        <v>1666449688</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8639,19 +8645,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.2459</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45692.86672944445</v>
+        <v>45708.67996841436</v>
       </c>
       <c r="G128" t="n">
-        <v>40.66</v>
+        <v>160.68</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I128" t="n">
-        <v>44.8</v>
+        <v>196.89</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8660,14 +8666,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>10</v>
+        <v>14.98</v>
       </c>
       <c r="M128" t="n">
-        <v>11.02</v>
+        <v>18.35</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
@@ -8682,18 +8688,18 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>1.02</v>
+        <v>3.37</v>
       </c>
       <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1666451221</v>
+        <v>1701098878</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8702,19 +8708,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.1796</v>
+        <v>0.0051</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45727.87167579861</v>
       </c>
       <c r="G129" t="n">
-        <v>43</v>
+        <v>139.41</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I129" t="n">
-        <v>44.8</v>
+        <v>196.89</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8723,14 +8729,14 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>7.72</v>
+        <v>0.71</v>
       </c>
       <c r="M129" t="n">
-        <v>8.050000000000001</v>
+        <v>1</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
@@ -8745,57 +8751,59 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>1749053104</v>
+        <v>1701098878</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45754.65117414352</v>
+        <v>45727.87167579861</v>
       </c>
       <c r="G130" t="n">
-        <v>4903.7</v>
+        <v>139.41</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45754.65218731482</v>
+        <v>45792.64655003473</v>
       </c>
       <c r="I130" t="n">
-        <v>4891.1</v>
+        <v>188.02</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="M130" t="n">
+        <v>18.8</v>
+      </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="n">
-        <v>12.26</v>
-      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
@@ -8806,57 +8814,59 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>6.3</v>
+        <v>4.86</v>
       </c>
       <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1756767326</v>
+        <v>1426782063</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.01</v>
+        <v>0.0004</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45756.64805717592</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G131" t="n">
-        <v>5004.7</v>
+        <v>419.46</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>45756.64937413194</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I131" t="n">
-        <v>5005.2</v>
+        <v>452.34</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.18</v>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="n">
-        <v>12.51</v>
-      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
@@ -8867,57 +8877,59 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>1756797155</v>
+        <v>1481614059</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.01</v>
+        <v>0.0359</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45756.6510503125</v>
+        <v>45568.77505349537</v>
       </c>
       <c r="G132" t="n">
-        <v>4992.2</v>
+        <v>417.1</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45756.65185319445</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I132" t="n">
-        <v>5013.4</v>
+        <v>452.34</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M132" t="n">
+        <v>16.24</v>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="n">
-        <v>12.48</v>
-      </c>
+      <c r="P132" t="inlineStr"/>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
@@ -8928,18 +8940,18 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>-10.6</v>
+        <v>1.27</v>
       </c>
       <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1767688540</v>
+        <v>1517514880</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8948,19 +8960,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.01</v>
+        <v>0.0037</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45761.6294487037</v>
+        <v>45597.6108722338</v>
       </c>
       <c r="G133" t="n">
-        <v>20.1226</v>
+        <v>409.38</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45761.66966099537</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I133" t="n">
-        <v>20.047</v>
+        <v>452.34</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8972,17 +8984,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
-        <v>20.048</v>
-      </c>
-      <c r="O133" t="n">
-        <v>20.3404</v>
-      </c>
-      <c r="P133" t="n">
-        <v>5</v>
-      </c>
+      <c r="L133" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
@@ -8993,22 +9003,18 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1768229183</v>
+        <v>1393281432</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9017,41 +9023,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.01</v>
+        <v>0.632</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45761.71402207176</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G134" t="n">
-        <v>20.0759</v>
+        <v>5.981</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45761.77371288194</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I134" t="n">
-        <v>20.1099</v>
+        <v>5.967</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="n">
-        <v>20.1099</v>
-      </c>
-      <c r="O134" t="n">
-        <v>20.2122</v>
-      </c>
-      <c r="P134" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
@@ -9062,22 +9066,18 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1769815245</v>
+        <v>1393281260</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9086,39 +9086,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.01</v>
+        <v>0.5612</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45762.50265097222</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G135" t="n">
-        <v>20.0545</v>
+        <v>5.812</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>45762.61225923611</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I135" t="n">
-        <v>19.9735</v>
+        <v>5.81</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="n">
-        <v>19.9742</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="n">
-        <v>5</v>
-      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
@@ -9129,22 +9129,18 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1666451221</v>
+        <v>1393281260</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9153,35 +9149,35 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.0528</v>
+        <v>0.555</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G136" t="n">
-        <v>43</v>
+        <v>5.812</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45764.85028728009</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I136" t="n">
-        <v>47.89</v>
+        <v>5.801</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.27</v>
+        <v>3.23</v>
       </c>
       <c r="M136" t="n">
-        <v>2.53</v>
+        <v>3.22</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -9196,18 +9192,18 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1450043624</v>
+        <v>1393281432</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9216,35 +9212,35 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.1</v>
+        <v>0.4344</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G137" t="n">
-        <v>147.48</v>
+        <v>5.981</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>45764.8517803588</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I137" t="n">
-        <v>143.22</v>
+        <v>5.968</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>14.75</v>
+        <v>2.6</v>
       </c>
       <c r="M137" t="n">
-        <v>14.32</v>
+        <v>2.59</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -9259,18 +9255,18 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>-0.42</v>
+        <v>-0.01</v>
       </c>
       <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1777308201</v>
+        <v>1393281260</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9279,37 +9275,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45768.12181488426</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G138" t="n">
-        <v>19.7053</v>
+        <v>5.812</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45768.13306659722</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I138" t="n">
-        <v>19.7154</v>
+        <v>5.814</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="M138" t="n">
+        <v>5.81</v>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
-        <v>5</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
@@ -9320,18 +9318,18 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1781449563</v>
+        <v>1393281432</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9340,37 +9338,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45769.73814164352</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G139" t="n">
-        <v>19.58</v>
+        <v>5.981</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45769.76084202546</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I139" t="n">
-        <v>19.5255</v>
+        <v>5.978</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M139" t="n">
+        <v>5.98</v>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="n">
-        <v>5</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
@@ -9381,18 +9381,18 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>-2.79</v>
+        <v>0</v>
       </c>
       <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1560258921</v>
+        <v>1393281260</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9401,35 +9401,35 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>0.4206</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45629.37798611111</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G140" t="n">
-        <v>48.68</v>
+        <v>5.812</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I140" t="n">
-        <v>44.15</v>
+        <v>5.826</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51.41</v>
+        <v>2.44</v>
       </c>
       <c r="M140" t="n">
-        <v>49.84</v>
+        <v>2.45</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -9444,18 +9444,18 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>-1.57</v>
+        <v>0.01</v>
       </c>
       <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1748583646</v>
+        <v>1393281432</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9464,35 +9464,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0.4033</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45754.57938657407</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G141" t="n">
-        <v>37.258</v>
+        <v>5.981</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I141" t="n">
-        <v>44.15</v>
+        <v>5.98</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>41.06</v>
+        <v>2.41</v>
       </c>
       <c r="M141" t="n">
-        <v>49.84</v>
+        <v>2.41</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -9507,18 +9507,18 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>8.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1373808226</v>
+        <v>1393281432</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9527,35 +9527,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.0234</v>
+        <v>0.4201</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45476.6587916088</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G142" t="n">
-        <v>459.24</v>
+        <v>5.981</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I142" t="n">
-        <v>434.71</v>
+        <v>5.98</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>10.75</v>
+        <v>2.51</v>
       </c>
       <c r="M142" t="n">
-        <v>10.17</v>
+        <v>2.51</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -9570,18 +9570,18 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1426782063</v>
+        <v>1393281432</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9590,35 +9590,35 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.0372</v>
+        <v>1</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G143" t="n">
-        <v>419.46</v>
+        <v>5.981</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I143" t="n">
-        <v>434.71</v>
+        <v>6.186</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>15.6</v>
+        <v>5.98</v>
       </c>
       <c r="M143" t="n">
-        <v>16.17</v>
+        <v>6.19</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -9633,18 +9633,18 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>1426782063</v>
+        <v>1393281260</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9653,35 +9653,35 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.01</v>
+        <v>1.4632</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G144" t="n">
-        <v>419.46</v>
+        <v>5.812</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45785.65885817129</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I144" t="n">
-        <v>437.05</v>
+        <v>6.02</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>4.19</v>
+        <v>8.5</v>
       </c>
       <c r="M144" t="n">
-        <v>4.37</v>
+        <v>8.81</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -9696,18 +9696,18 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>1744929368</v>
+        <v>1393287040</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9716,19 +9716,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.0424</v>
+        <v>0.2503</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45751.7450085301</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G145" t="n">
-        <v>324.48</v>
+        <v>5.811</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45785.65909077547</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I145" t="n">
-        <v>353.02</v>
+        <v>6.02</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -9737,14 +9737,14 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>13.76</v>
+        <v>1.45</v>
       </c>
       <c r="M145" t="n">
-        <v>14.97</v>
+        <v>1.51</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
@@ -9759,18 +9759,18 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>1.21</v>
+        <v>0.06</v>
       </c>
       <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>1414372592</v>
+        <v>1403180431</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9779,35 +9779,35 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.0229</v>
+        <v>0.2773</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45511.7228721412</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G146" t="n">
-        <v>455.4</v>
+        <v>5.84</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I146" t="n">
-        <v>568.9299999999999</v>
+        <v>6.02</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>10.43</v>
+        <v>1.62</v>
       </c>
       <c r="M146" t="n">
-        <v>13.03</v>
+        <v>1.67</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
@@ -9822,18 +9822,18 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>2.6</v>
+        <v>0.05</v>
       </c>
       <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>1582737192</v>
+        <v>1403180445</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9842,35 +9842,35 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.0371</v>
+        <v>0.0092</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45645.90143914352</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G147" t="n">
-        <v>524.4299999999999</v>
+        <v>5.836</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I147" t="n">
-        <v>568.9299999999999</v>
+        <v>6.02</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>19.46</v>
+        <v>0.05</v>
       </c>
       <c r="M147" t="n">
-        <v>21.11</v>
+        <v>0.06</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -9885,18 +9885,18 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>1.65</v>
+        <v>0.01</v>
       </c>
       <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>1599454287</v>
+        <v>1393735509</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9905,35 +9905,35 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0366</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45663.73715268519</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G148" t="n">
-        <v>196.49</v>
+        <v>67.37</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I148" t="n">
-        <v>196.89</v>
+        <v>71.16</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>14.99</v>
+        <v>2.47</v>
       </c>
       <c r="M148" t="n">
-        <v>15.02</v>
+        <v>2.6</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
@@ -9948,18 +9948,18 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>1621495599</v>
+        <v>1395218355</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9968,35 +9968,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45678.83206015046</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G149" t="n">
-        <v>183.39</v>
+        <v>67.13</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I149" t="n">
-        <v>196.89</v>
+        <v>71.16</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>14.98</v>
+        <v>4.97</v>
       </c>
       <c r="M149" t="n">
-        <v>16.09</v>
+        <v>5.27</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
@@ -10011,18 +10011,18 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>1.11</v>
+        <v>0.3</v>
       </c>
       <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>1631467534</v>
+        <v>1403166009</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10031,35 +10031,35 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0362</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45685.83235356482</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G150" t="n">
-        <v>159.74</v>
+        <v>68.05</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I150" t="n">
-        <v>196.89</v>
+        <v>71.16</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>14.97</v>
+        <v>2.46</v>
       </c>
       <c r="M150" t="n">
-        <v>18.45</v>
+        <v>2.58</v>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
@@ -10074,18 +10074,18 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>3.48</v>
+        <v>0.12</v>
       </c>
       <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1666449688</v>
+        <v>1403177543</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10094,35 +10094,35 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45708.67996841436</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G151" t="n">
-        <v>160.68</v>
+        <v>68.045</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I151" t="n">
-        <v>196.89</v>
+        <v>71.16</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>14.98</v>
+        <v>2.5</v>
       </c>
       <c r="M151" t="n">
-        <v>18.35</v>
+        <v>2.62</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -10137,18 +10137,18 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>3.37</v>
+        <v>0.12</v>
       </c>
       <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1701098878</v>
+        <v>1403180429</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -10157,35 +10157,35 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.0051</v>
+        <v>0.0733</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G152" t="n">
-        <v>139.41</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I152" t="n">
-        <v>196.89</v>
+        <v>71.16</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0.71</v>
+        <v>4.99</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>5.22</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -10200,18 +10200,18 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>1701098878</v>
+        <v>1403180445</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -10220,35 +10220,35 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.1</v>
+        <v>0.9908</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G153" t="n">
-        <v>139.41</v>
+        <v>5.836</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>45792.64655003473</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I153" t="n">
-        <v>188.02</v>
+        <v>6.027</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>13.94</v>
+        <v>5.78</v>
       </c>
       <c r="M153" t="n">
-        <v>18.8</v>
+        <v>5.97</v>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
@@ -10263,18 +10263,18 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>4.86</v>
+        <v>0.18</v>
       </c>
       <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>1426782063</v>
+        <v>1393281432</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -10283,35 +10283,35 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.0004</v>
+        <v>0.1102</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G154" t="n">
-        <v>419.46</v>
+        <v>5.981</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I154" t="n">
-        <v>452.34</v>
+        <v>6.176</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0.17</v>
+        <v>0.66</v>
       </c>
       <c r="M154" t="n">
-        <v>0.18</v>
+        <v>0.68</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -10326,18 +10326,18 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1481614059</v>
+        <v>1393301698</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -10346,35 +10346,35 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.0359</v>
+        <v>0.1401</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45568.77505349537</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G155" t="n">
-        <v>417.1</v>
+        <v>5.99</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I155" t="n">
-        <v>452.34</v>
+        <v>6.176</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>14.97</v>
+        <v>0.84</v>
       </c>
       <c r="M155" t="n">
-        <v>16.24</v>
+        <v>0.87</v>
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -10389,18 +10389,18 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>1.27</v>
+        <v>0.03</v>
       </c>
       <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1517514880</v>
+        <v>1403180427</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -10409,35 +10409,35 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.0037</v>
+        <v>0.4203</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45597.6108722338</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G156" t="n">
-        <v>409.38</v>
+        <v>5.989</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I156" t="n">
-        <v>452.34</v>
+        <v>6.176</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="M156" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
@@ -10452,7 +10452,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="U156" t="inlineStr"/>
     </row>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U157"/>
+  <dimension ref="A1:U170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9010,11 +9010,11 @@
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1393281432</v>
+        <v>1381375440</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9023,35 +9023,35 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.632</v>
+        <v>0.1057</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45484.67118305556</v>
       </c>
       <c r="G134" t="n">
-        <v>5.981</v>
+        <v>189.11</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I134" t="n">
-        <v>5.967</v>
+        <v>212.35</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.78</v>
+        <v>19.99</v>
       </c>
       <c r="M134" t="n">
-        <v>3.77</v>
+        <v>22.45</v>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
@@ -9066,18 +9066,18 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>-0.01</v>
+        <v>2.46</v>
       </c>
       <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1393281260</v>
+        <v>1511085920</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9086,35 +9086,35 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.5612</v>
+        <v>0.0761</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45593.7262772338</v>
       </c>
       <c r="G135" t="n">
-        <v>5.812</v>
+        <v>196.9</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I135" t="n">
-        <v>5.81</v>
+        <v>212.35</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.26</v>
+        <v>14.98</v>
       </c>
       <c r="M135" t="n">
-        <v>3.26</v>
+        <v>16.16</v>
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
@@ -9129,18 +9129,18 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1393281260</v>
+        <v>1532661507</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9149,35 +9149,35 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.555</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45608.74251091435</v>
       </c>
       <c r="G136" t="n">
-        <v>5.812</v>
+        <v>190.67</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I136" t="n">
-        <v>5.801</v>
+        <v>212.35</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.23</v>
+        <v>12.98</v>
       </c>
       <c r="M136" t="n">
-        <v>3.22</v>
+        <v>14.46</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -9192,18 +9192,18 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>-0.01</v>
+        <v>1.48</v>
       </c>
       <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1393281432</v>
+        <v>1554742887</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9212,35 +9212,35 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.4344</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45623.74993096065</v>
       </c>
       <c r="G137" t="n">
-        <v>5.981</v>
+        <v>178.48</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I137" t="n">
-        <v>5.968</v>
+        <v>212.35</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.6</v>
+        <v>14.99</v>
       </c>
       <c r="M137" t="n">
-        <v>2.59</v>
+        <v>17.84</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -9255,18 +9255,18 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>-0.01</v>
+        <v>2.85</v>
       </c>
       <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1393281260</v>
+        <v>1582708979</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9275,35 +9275,35 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45645.88746972222</v>
       </c>
       <c r="G138" t="n">
-        <v>5.812</v>
+        <v>195.11</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I138" t="n">
-        <v>5.814</v>
+        <v>212.35</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>5.81</v>
+        <v>15</v>
       </c>
       <c r="M138" t="n">
-        <v>5.81</v>
+        <v>16.33</v>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
@@ -9318,18 +9318,18 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1393281432</v>
+        <v>1680991980</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9338,35 +9338,35 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0.0892</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45716.85566212963</v>
       </c>
       <c r="G139" t="n">
-        <v>5.981</v>
+        <v>178.67</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I139" t="n">
-        <v>5.978</v>
+        <v>212.35</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>5.98</v>
+        <v>15.94</v>
       </c>
       <c r="M139" t="n">
-        <v>5.98</v>
+        <v>18.94</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
@@ -9381,18 +9381,18 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1393281260</v>
+        <v>1517514880</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9401,35 +9401,35 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.4206</v>
+        <v>0.0231</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45597.6108722338</v>
       </c>
       <c r="G140" t="n">
-        <v>5.812</v>
+        <v>409.38</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45818.9064246875</v>
       </c>
       <c r="I140" t="n">
-        <v>5.826</v>
+        <v>470.07</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M140" t="n">
-        <v>2.45</v>
+        <v>10.86</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -9444,18 +9444,18 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0.01</v>
+        <v>1.4</v>
       </c>
       <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1393281432</v>
+        <v>1648737122</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9464,35 +9464,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.4033</v>
+        <v>0.0169</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45695.8561993287</v>
       </c>
       <c r="G141" t="n">
-        <v>5.981</v>
+        <v>408.33</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45818.9064246875</v>
       </c>
       <c r="I141" t="n">
-        <v>5.98</v>
+        <v>470.07</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.41</v>
+        <v>6.9</v>
       </c>
       <c r="M141" t="n">
-        <v>2.41</v>
+        <v>7.94</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -9507,18 +9507,18 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1393281432</v>
+        <v>1648740228</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9527,35 +9527,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.4201</v>
+        <v>0.0538</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45695.85792373843</v>
       </c>
       <c r="G142" t="n">
-        <v>5.981</v>
+        <v>185.82</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45818.90659450232</v>
       </c>
       <c r="I142" t="n">
-        <v>5.98</v>
+        <v>178.54</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.51</v>
+        <v>10</v>
       </c>
       <c r="M142" t="n">
-        <v>2.51</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -9570,18 +9570,18 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1393281432</v>
+        <v>1712850989</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9590,35 +9590,35 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45734.85576756945</v>
       </c>
       <c r="G143" t="n">
-        <v>5.981</v>
+        <v>160.64</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45818.90659450232</v>
       </c>
       <c r="I143" t="n">
-        <v>6.186</v>
+        <v>178.54</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>5.98</v>
+        <v>15.45</v>
       </c>
       <c r="M143" t="n">
-        <v>6.19</v>
+        <v>17.18</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -9633,18 +9633,18 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0.21</v>
+        <v>1.73</v>
       </c>
       <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>1393281260</v>
+        <v>1666457581</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9653,35 +9653,35 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1.4632</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45708.68135143518</v>
       </c>
       <c r="G144" t="n">
-        <v>5.812</v>
+        <v>38.23</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I144" t="n">
-        <v>6.02</v>
+        <v>38.6</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>8.5</v>
+        <v>19.98</v>
       </c>
       <c r="M144" t="n">
-        <v>8.81</v>
+        <v>20.18</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -9696,18 +9696,18 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>1393287040</v>
+        <v>1825032378</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9716,35 +9716,35 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.2503</v>
+        <v>0.2894</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45792.76093159722</v>
       </c>
       <c r="G145" t="n">
-        <v>5.811</v>
+        <v>34.55</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I145" t="n">
-        <v>6.02</v>
+        <v>38.6</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.45</v>
+        <v>10</v>
       </c>
       <c r="M145" t="n">
-        <v>1.51</v>
+        <v>11.17</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
@@ -9759,18 +9759,18 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0.06</v>
+        <v>1.17</v>
       </c>
       <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>1403180431</v>
+        <v>1830410729</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9779,35 +9779,35 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.2773</v>
+        <v>0.1879</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45796.82476541667</v>
       </c>
       <c r="G146" t="n">
-        <v>5.84</v>
+        <v>33.66</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I146" t="n">
-        <v>6.02</v>
+        <v>38.6</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.62</v>
+        <v>6.32</v>
       </c>
       <c r="M146" t="n">
-        <v>1.67</v>
+        <v>7.25</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
@@ -9822,18 +9822,18 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>0.05</v>
+        <v>0.92</v>
       </c>
       <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>1403180445</v>
+        <v>1393281432</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.0092</v>
+        <v>0.632</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G147" t="n">
-        <v>5.836</v>
+        <v>5.981</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I147" t="n">
-        <v>6.02</v>
+        <v>5.967</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0.05</v>
+        <v>3.78</v>
       </c>
       <c r="M147" t="n">
-        <v>0.06</v>
+        <v>3.77</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -9885,18 +9885,18 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>1393735509</v>
+        <v>1393281260</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9905,19 +9905,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.0366</v>
+        <v>0.5612</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G148" t="n">
-        <v>67.37</v>
+        <v>5.812</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I148" t="n">
-        <v>71.16</v>
+        <v>5.81</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.47</v>
+        <v>3.26</v>
       </c>
       <c r="M148" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
@@ -9948,18 +9948,18 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>1395218355</v>
+        <v>1393281260</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9968,19 +9968,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.074</v>
+        <v>0.555</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G149" t="n">
-        <v>67.13</v>
+        <v>5.812</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I149" t="n">
-        <v>71.16</v>
+        <v>5.801</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -9993,10 +9993,10 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>4.97</v>
+        <v>3.23</v>
       </c>
       <c r="M149" t="n">
-        <v>5.27</v>
+        <v>3.22</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
@@ -10011,18 +10011,18 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>0.3</v>
+        <v>-0.01</v>
       </c>
       <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>1403166009</v>
+        <v>1393281432</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10031,19 +10031,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.0362</v>
+        <v>0.4344</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G150" t="n">
-        <v>68.05</v>
+        <v>5.981</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I150" t="n">
-        <v>71.16</v>
+        <v>5.968</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="M150" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
@@ -10074,18 +10074,18 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1403177543</v>
+        <v>1393281260</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10094,19 +10094,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.0368</v>
+        <v>1</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G151" t="n">
-        <v>68.045</v>
+        <v>5.812</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I151" t="n">
-        <v>71.16</v>
+        <v>5.814</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.5</v>
+        <v>5.81</v>
       </c>
       <c r="M151" t="n">
-        <v>2.62</v>
+        <v>5.81</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -10137,18 +10137,18 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1403180429</v>
+        <v>1393281432</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -10157,19 +10157,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.0733</v>
+        <v>1</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G152" t="n">
-        <v>68.01000000000001</v>
+        <v>5.981</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I152" t="n">
-        <v>71.16</v>
+        <v>5.978</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4.99</v>
+        <v>5.98</v>
       </c>
       <c r="M152" t="n">
-        <v>5.22</v>
+        <v>5.98</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -10200,14 +10200,14 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>1403180445</v>
+        <v>1393281260</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -10220,19 +10220,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9908</v>
+        <v>0.4206</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G153" t="n">
-        <v>5.836</v>
+        <v>5.812</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I153" t="n">
-        <v>6.027</v>
+        <v>5.826</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>5.78</v>
+        <v>2.44</v>
       </c>
       <c r="M153" t="n">
-        <v>5.97</v>
+        <v>2.45</v>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="U153" t="inlineStr"/>
     </row>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.1102</v>
+        <v>0.4033</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>45496.37566553241</v>
@@ -10292,10 +10292,10 @@
         <v>5.981</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I154" t="n">
-        <v>6.176</v>
+        <v>5.98</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0.66</v>
+        <v>2.41</v>
       </c>
       <c r="M154" t="n">
-        <v>0.68</v>
+        <v>2.41</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -10326,14 +10326,14 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1393301698</v>
+        <v>1393281432</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -10346,19 +10346,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.1401</v>
+        <v>0.4201</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G155" t="n">
-        <v>5.99</v>
+        <v>5.981</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I155" t="n">
-        <v>6.176</v>
+        <v>5.98</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0.84</v>
+        <v>2.51</v>
       </c>
       <c r="M155" t="n">
-        <v>0.87</v>
+        <v>2.51</v>
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -10389,14 +10389,14 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1403180427</v>
+        <v>1393281432</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -10409,19 +10409,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.4203</v>
+        <v>1</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G156" t="n">
-        <v>5.989</v>
+        <v>5.981</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I156" t="n">
-        <v>6.176</v>
+        <v>6.186</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -10434,10 +10434,10 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.52</v>
+        <v>5.98</v>
       </c>
       <c r="M156" t="n">
-        <v>2.6</v>
+        <v>6.19</v>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
@@ -10452,28 +10452,56 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>1393281260</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1.4632</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>45496.37564016203</v>
+      </c>
+      <c r="G157" t="n">
+        <v>5.812</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>45726.37526289352</v>
+      </c>
+      <c r="I157" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M157" t="n">
+        <v>8.81</v>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
@@ -10481,15 +10509,806 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>1393287040</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>45496.37755140047</v>
+      </c>
+      <c r="G158" t="n">
+        <v>5.811</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>45726.37526289352</v>
+      </c>
+      <c r="I158" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>1403180431</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>45504.64299350695</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>45726.37526289352</v>
+      </c>
+      <c r="I159" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>1403180445</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>45504.64300175926</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5.836</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>45726.37526289352</v>
+      </c>
+      <c r="I160" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>1393735509</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>45496.61777673611</v>
+      </c>
+      <c r="G161" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>45726.37603653935</v>
+      </c>
+      <c r="I161" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>1395218355</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>45497.65423574074</v>
+      </c>
+      <c r="G162" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>45726.37603653935</v>
+      </c>
+      <c r="I162" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>1403166009</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>45504.63556387732</v>
+      </c>
+      <c r="G163" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>45726.37603653935</v>
+      </c>
+      <c r="I163" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>1403177543</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>45504.64158137731</v>
+      </c>
+      <c r="G164" t="n">
+        <v>68.045</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>45726.37603653935</v>
+      </c>
+      <c r="I164" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>1403180429</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>45504.6429933912</v>
+      </c>
+      <c r="G165" t="n">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>45726.37603653935</v>
+      </c>
+      <c r="I165" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M165" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>1403180445</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>45504.64300175926</v>
+      </c>
+      <c r="G166" t="n">
+        <v>5.836</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>45726.43231427083</v>
+      </c>
+      <c r="I166" t="n">
+        <v>6.027</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M166" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>1393281432</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FLOA.L</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>45496.37566553241</v>
+      </c>
+      <c r="G167" t="n">
+        <v>5.981</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>45727.38638285879</v>
+      </c>
+      <c r="I167" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>1393301698</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FLOA.L</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>45496.37886077546</v>
+      </c>
+      <c r="G168" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>45727.38638285879</v>
+      </c>
+      <c r="I168" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>1403180427</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FLOA.L</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>45504.64299328704</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5.989</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>45727.38638285879</v>
+      </c>
+      <c r="I169" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M169" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="U157" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="U170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U170"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3385,11 +3385,11 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1515520253</v>
+        <v>1393281432</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3398,59 +3398,61 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0.632</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G47" t="n">
-        <v>20.0901</v>
+        <v>5.981</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I47" t="n">
-        <v>20.0775</v>
+        <v>5.967</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.77</v>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>5</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.63</v>
+        <v>-0.01</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1517450167</v>
+        <v>1393281260</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3459,37 +3461,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>0.5612</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45597.59638905092</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9771</v>
+        <v>5.812</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45597.73077270833</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I48" t="n">
-        <v>20.0775</v>
+        <v>5.81</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.26</v>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>5</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3500,57 +3504,59 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1517930572</v>
+        <v>1393281260</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>0.555</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G49" t="n">
-        <v>20.078</v>
+        <v>5.812</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I49" t="n">
-        <v>20.082</v>
+        <v>5.801</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.22</v>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>5</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -3561,18 +3567,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1517879253</v>
+        <v>1515520253</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3584,16 +3590,16 @@
         <v>0.01</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G50" t="n">
-        <v>20.08</v>
+        <v>20.0901</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I50" t="n">
-        <v>19.63</v>
+        <v>20.0775</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3602,44 +3608,38 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop-out</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>20.92</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>12.05</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
         <v>-0.63</v>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1379227659</v>
+        <v>1393281432</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3648,35 +3648,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1521</v>
+        <v>0.4344</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G51" t="n">
-        <v>131.38</v>
+        <v>5.981</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I51" t="n">
-        <v>148.18</v>
+        <v>5.968</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>19.98</v>
+        <v>2.6</v>
       </c>
       <c r="M51" t="n">
-        <v>22.54</v>
+        <v>2.59</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3691,18 +3691,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.56</v>
+        <v>-0.01</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1527051962</v>
+        <v>1393281260</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3711,41 +3711,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45604.13145401621</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G52" t="n">
-        <v>19.8302</v>
+        <v>5.812</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45604.56280116898</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I52" t="n">
-        <v>19.9681</v>
+        <v>5.814</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="O52" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P52" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="M52" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
@@ -3756,22 +3754,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1527744522</v>
+        <v>1393281432</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3780,41 +3774,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45604.55607921296</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G53" t="n">
-        <v>19.9784</v>
+        <v>5.981</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45604.57083508102</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I53" t="n">
-        <v>19.9497</v>
+        <v>5.978</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="O53" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P53" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
@@ -3825,22 +3817,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1528126100</v>
+        <v>1393281260</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,88 +3837,82 @@
         </is>
       </c>
       <c r="E54" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>45496.37564016203</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5.812</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>45504.63556305556</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5.826</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.01</v>
       </c>
-      <c r="F54" s="2" t="n">
-        <v>45604.66918148148</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20.0428</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>45604.71914307871</v>
-      </c>
-      <c r="I54" t="n">
-        <v>20.0988</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>20.0988</v>
-      </c>
-      <c r="O54" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1528325630</v>
+        <v>1393281432</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0.4033</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45604.72032700232</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G55" t="n">
-        <v>20.0912</v>
+        <v>5.981</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45604.72263849537</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I55" t="n">
-        <v>20.1101</v>
+        <v>5.98</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3939,20 +3921,18 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="O55" t="n">
-        <v>20.0219</v>
-      </c>
-      <c r="P55" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
@@ -3963,22 +3943,18 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1531224336</v>
+        <v>1517450167</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3990,16 +3966,16 @@
         <v>0.01</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45608.2460031713</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G56" t="n">
-        <v>153.589</v>
+        <v>19.9771</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45608.25044886574</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I56" t="n">
-        <v>153.468</v>
+        <v>20.0775</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4013,12 +3989,8 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>153.47</v>
-      </c>
-      <c r="O56" t="n">
-        <v>153.619</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
         <v>5</v>
       </c>
@@ -4032,63 +4004,59 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1531227124</v>
+        <v>1393281432</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.4201</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45608.25015417824</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G57" t="n">
-        <v>153.483</v>
+        <v>5.981</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45608.25207638889</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I57" t="n">
-        <v>153.458</v>
+        <v>5.98</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>153.458</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>5</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
@@ -4099,22 +4067,18 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1531230129</v>
+        <v>1517930572</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4126,16 +4090,16 @@
         <v>0.01</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45608.2544440162</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G58" t="n">
-        <v>153.445</v>
+        <v>20.078</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45608.25666561343</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I58" t="n">
-        <v>153.502</v>
+        <v>20.082</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4149,12 +4113,8 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>153.502</v>
-      </c>
-      <c r="O58" t="n">
-        <v>153.395</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
         <v>5</v>
       </c>
@@ -4168,22 +4128,18 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.2</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1531192665</v>
+        <v>1393281432</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4192,41 +4148,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45608.19828637732</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G59" t="n">
-        <v>20.412</v>
+        <v>5.981</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45608.34380275463</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I59" t="n">
-        <v>20.4421</v>
+        <v>6.186</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>20.4429</v>
-      </c>
-      <c r="O59" t="n">
-        <v>20.5326</v>
-      </c>
-      <c r="P59" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M59" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
@@ -4237,43 +4191,39 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1531349564</v>
+        <v>1517879253</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45608.34449649305</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G60" t="n">
-        <v>20.4344</v>
+        <v>20.08</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45608.34490908564</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I60" t="n">
-        <v>20.4507</v>
+        <v>19.63</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4282,38 +4232,44 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>stop-out</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>20.92</v>
+      </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>12.05</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="U60" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1531351286</v>
+        <v>1393281260</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4322,41 +4278,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>1.4632</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45608.34571399305</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G61" t="n">
-        <v>20.4554</v>
+        <v>5.812</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45608.35180353009</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I61" t="n">
-        <v>20.45</v>
+        <v>6.02</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>20.4381</v>
-      </c>
-      <c r="O61" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="P61" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
@@ -4367,18 +4321,18 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.26</v>
+        <v>0.3</v>
       </c>
       <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1531358421</v>
+        <v>1393287040</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4387,41 +4341,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.2503</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45608.3501140162</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G62" t="n">
-        <v>20.4503</v>
+        <v>5.811</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45608.35479755787</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I62" t="n">
-        <v>20.4382</v>
+        <v>6.02</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>20.4388</v>
-      </c>
-      <c r="O62" t="n">
-        <v>20.4767</v>
-      </c>
-      <c r="P62" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4432,22 +4384,18 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1532703059</v>
+        <v>1403180431</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4456,41 +4404,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.02</v>
+        <v>0.2773</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45608.75711524305</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G63" t="n">
-        <v>20.6261</v>
+        <v>5.84</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45608.76530484953</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I63" t="n">
-        <v>20.6299</v>
+        <v>6.02</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>20.5745</v>
-      </c>
-      <c r="O63" t="n">
-        <v>20.6364</v>
-      </c>
-      <c r="P63" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
@@ -4501,18 +4447,18 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1532729622</v>
+        <v>1403180445</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4521,37 +4467,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.01</v>
+        <v>0.0092</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45608.76652064815</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G64" t="n">
-        <v>154.853</v>
+        <v>5.836</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45608.76796081018</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I64" t="n">
-        <v>154.873</v>
+        <v>6.02</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.06</v>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>5</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -4562,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1533930062</v>
+        <v>1379227659</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4582,19 +4530,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.01</v>
+        <v>0.1521</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45609.61569380787</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G65" t="n">
-        <v>20.507</v>
+        <v>131.38</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45609.63889303241</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I65" t="n">
-        <v>20.5531</v>
+        <v>148.18</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4606,17 +4554,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>20.431</v>
-      </c>
-      <c r="O65" t="n">
-        <v>20.5528</v>
-      </c>
-      <c r="P65" t="n">
-        <v>5</v>
-      </c>
+      <c r="L65" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M65" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
@@ -4627,22 +4573,18 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>2.56</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1536772518</v>
+        <v>1393735509</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4651,41 +4593,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.02</v>
+        <v>0.0366</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45610.86999649306</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G66" t="n">
-        <v>20.4311</v>
+        <v>67.37</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45610.88084664352</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I66" t="n">
-        <v>20.4923</v>
+        <v>71.16</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>20.4941</v>
-      </c>
-      <c r="O66" t="n">
-        <v>20.5653</v>
-      </c>
-      <c r="P66" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -4696,22 +4636,18 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1540892910</v>
+        <v>1395218355</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4720,67 +4656,61 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.02</v>
+        <v>0.074</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45614.83689460648</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G67" t="n">
-        <v>20.2371</v>
+        <v>67.13</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45615.43822850694</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I67" t="n">
-        <v>20.3181</v>
+        <v>71.16</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="O67" t="n">
-        <v>20.3179</v>
-      </c>
-      <c r="P67" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M67" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1541930457</v>
+        <v>1403166009</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4789,41 +4719,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.02</v>
+        <v>0.0362</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45615.56159975695</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G68" t="n">
-        <v>20.2629</v>
+        <v>68.05</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45615.58509630787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I68" t="n">
-        <v>20.2887</v>
+        <v>71.16</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>20.2059</v>
-      </c>
-      <c r="O68" t="n">
-        <v>20.2856</v>
-      </c>
-      <c r="P68" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -4834,65 +4762,59 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1553997553</v>
+        <v>1403177543</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>0.0368</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45623.53527240741</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G69" t="n">
-        <v>20.7084</v>
+        <v>68.045</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45623.57548773148</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I69" t="n">
-        <v>20.7775</v>
+        <v>71.16</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>20.7706</v>
-      </c>
-      <c r="O69" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="P69" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4903,61 +4825,59 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1554074835</v>
+        <v>1403180429</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.01</v>
+        <v>0.0733</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45623.57516572917</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G70" t="n">
-        <v>20.7426</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45623.57574133102</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I70" t="n">
-        <v>20.7764</v>
+        <v>71.16</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5.22</v>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>5</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
@@ -4968,18 +4888,18 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>-1.63</v>
+        <v>0.23</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1555669398</v>
+        <v>1403180445</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4988,41 +4908,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.02</v>
+        <v>0.9908</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45624.55073625</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G71" t="n">
-        <v>20.3273</v>
+        <v>5.836</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45624.71914708333</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I71" t="n">
-        <v>20.4312</v>
+        <v>6.027</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
-        <v>20.1748</v>
-      </c>
-      <c r="O71" t="n">
-        <v>20.4293</v>
-      </c>
-      <c r="P71" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
@@ -5033,18 +4951,14 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1563562241</v>
+        <v>1527051962</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5057,19 +4971,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45631.25027201389</v>
+        <v>45604.13145401621</v>
       </c>
       <c r="G72" t="n">
-        <v>20.3099</v>
+        <v>19.8302</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45631.6258153125</v>
+        <v>45604.56280116898</v>
       </c>
       <c r="I72" t="n">
-        <v>20.2391</v>
+        <v>19.9681</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5084,13 +4998,13 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>20.24</v>
+        <v>19.97</v>
       </c>
       <c r="O72" t="n">
-        <v>20.3672</v>
+        <v>20.12</v>
       </c>
       <c r="P72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -5102,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>-6.99</v>
+        <v>6.9</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -5113,11 +5027,11 @@
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1473693877</v>
+        <v>1393281432</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5126,35 +5040,35 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.019</v>
+        <v>0.1102</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45562.69351818287</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G73" t="n">
-        <v>700.8</v>
+        <v>5.981</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I73" t="n">
-        <v>623.8</v>
+        <v>6.176</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>14.97</v>
+        <v>0.66</v>
       </c>
       <c r="M73" t="n">
-        <v>12.28</v>
+        <v>0.68</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -5169,18 +5083,18 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-2.69</v>
+        <v>0.02</v>
       </c>
       <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1493848938</v>
+        <v>1527744522</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5189,19 +5103,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0213</v>
+        <v>0.01</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45579.70088467593</v>
+        <v>45604.55607921296</v>
       </c>
       <c r="G74" t="n">
-        <v>640.3</v>
+        <v>19.9784</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45604.57083508102</v>
       </c>
       <c r="I74" t="n">
-        <v>623.8</v>
+        <v>19.9497</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5213,15 +5127,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="M74" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="O74" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
@@ -5232,18 +5148,22 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="U74" t="inlineStr"/>
+        <v>-1.44</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1583724019</v>
+        <v>1393301698</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5252,41 +5172,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.02</v>
+        <v>0.1401</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45646.60647967592</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G75" t="n">
-        <v>20.2054</v>
+        <v>5.99</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45646.696485625</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I75" t="n">
-        <v>20.1035</v>
+        <v>6.176</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
-        <v>20.1055</v>
-      </c>
-      <c r="O75" t="n">
-        <v>20.3273</v>
-      </c>
-      <c r="P75" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
@@ -5297,22 +5215,18 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>-10.13</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1583841034</v>
+        <v>1403180427</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5321,41 +5235,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.01</v>
+        <v>0.4203</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45646.63988152778</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G76" t="n">
-        <v>20.173</v>
+        <v>5.989</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45646.70582428241</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I76" t="n">
-        <v>20.0949</v>
+        <v>6.176</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
-        <v>20.0975</v>
-      </c>
-      <c r="O76" t="n">
-        <v>20.2542</v>
-      </c>
-      <c r="P76" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
@@ -5366,18 +5278,14 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-3.88</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1585474078</v>
+        <v>1528126100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -5390,19 +5298,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45649.40133020833</v>
+        <v>45604.66918148148</v>
       </c>
       <c r="G77" t="n">
-        <v>20.0935</v>
+        <v>20.0428</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45649.56824730324</v>
+        <v>45604.71914307871</v>
       </c>
       <c r="I77" t="n">
-        <v>20.1707</v>
+        <v>20.0988</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5411,19 +5319,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>20</v>
+        <v>20.0988</v>
       </c>
       <c r="O77" t="n">
-        <v>20.17</v>
+        <v>20.2</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -5435,18 +5343,18 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>7.65</v>
+        <v>2.79</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>[T/P]</t>
+          <t>[S/L]</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1586033461</v>
+        <v>1528325630</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -5455,27 +5363,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>0.01</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45649.63114609953</v>
+        <v>45604.72032700232</v>
       </c>
       <c r="G78" t="n">
-        <v>20.1772</v>
+        <v>20.0912</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45649.63200465278</v>
+        <v>45604.72263849537</v>
       </c>
       <c r="I78" t="n">
-        <v>20.1671</v>
+        <v>20.1101</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5486,10 +5394,10 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>20.1687</v>
+        <v>20.11</v>
       </c>
       <c r="O78" t="n">
-        <v>20.2379</v>
+        <v>20.0219</v>
       </c>
       <c r="P78" t="n">
         <v>5</v>
@@ -5504,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -5515,11 +5423,11 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1587036381</v>
+        <v>1531224336</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5528,19 +5436,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45650.48790526621</v>
+        <v>45608.2460031713</v>
       </c>
       <c r="G79" t="n">
-        <v>20.1462</v>
+        <v>153.589</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45650.58025611111</v>
+        <v>45608.25044886574</v>
       </c>
       <c r="I79" t="n">
-        <v>20.1627</v>
+        <v>153.468</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5555,13 +5463,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>20.1627</v>
+        <v>153.47</v>
       </c>
       <c r="O79" t="n">
-        <v>20.22</v>
+        <v>153.619</v>
       </c>
       <c r="P79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5573,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>1.64</v>
+        <v>-0.79</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -5584,32 +5492,32 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1500272843</v>
+        <v>1531227124</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0264</v>
+        <v>0.01</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45608.25015417824</v>
       </c>
       <c r="G80" t="n">
-        <v>718.5</v>
+        <v>153.483</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45663.67045758102</v>
+        <v>45608.25207638889</v>
       </c>
       <c r="I80" t="n">
-        <v>757.79</v>
+        <v>153.458</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5621,15 +5529,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="M80" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>153.458</v>
+      </c>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>5</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
@@ -5640,39 +5548,43 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="U80" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1500272843</v>
+        <v>1531230129</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0021</v>
+        <v>0.01</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45608.2544440162</v>
       </c>
       <c r="G81" t="n">
-        <v>718.5</v>
+        <v>153.445</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45663.67059782407</v>
+        <v>45608.25666561343</v>
       </c>
       <c r="I81" t="n">
-        <v>758.27</v>
+        <v>153.502</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5684,15 +5596,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>153.502</v>
+      </c>
+      <c r="O81" t="n">
+        <v>153.395</v>
+      </c>
+      <c r="P81" t="n">
+        <v>5</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
@@ -5703,18 +5617,22 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U81" t="inlineStr"/>
+        <v>-0.37</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1518147105</v>
+        <v>1531192665</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5723,19 +5641,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45597.8504690162</v>
+        <v>45608.19828637732</v>
       </c>
       <c r="G82" t="n">
-        <v>10.92</v>
+        <v>20.412</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45667.68126778935</v>
+        <v>45608.34380275463</v>
       </c>
       <c r="I82" t="n">
-        <v>6.52</v>
+        <v>20.4421</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5747,15 +5665,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="M82" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>20.4429</v>
+      </c>
+      <c r="O82" t="n">
+        <v>20.5326</v>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
@@ -5766,39 +5686,43 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="U82" t="inlineStr"/>
+        <v>2.94</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1551373923</v>
+        <v>1531349564</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1195</v>
+        <v>0.01</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45621.85639895833</v>
+        <v>45608.34449649305</v>
       </c>
       <c r="G83" t="n">
-        <v>167.24</v>
+        <v>20.4344</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45678.70646498843</v>
+        <v>45608.34490908564</v>
       </c>
       <c r="I83" t="n">
-        <v>198.83</v>
+        <v>20.4507</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5810,15 +5734,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="M83" t="n">
-        <v>23.76</v>
-      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
@@ -5829,18 +5751,18 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.77</v>
+        <v>-0.8</v>
       </c>
       <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1373744560</v>
+        <v>1531351286</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5849,19 +5771,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1248</v>
+        <v>0.01</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45476.64586885417</v>
+        <v>45608.34571399305</v>
       </c>
       <c r="G84" t="n">
-        <v>202.58</v>
+        <v>20.4554</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45608.35180353009</v>
       </c>
       <c r="I84" t="n">
-        <v>172.09</v>
+        <v>20.45</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5873,15 +5795,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="M84" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>20.4381</v>
+      </c>
+      <c r="O84" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="P84" t="n">
+        <v>5</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
@@ -5892,18 +5816,18 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>-3.8</v>
+        <v>-0.26</v>
       </c>
       <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1450039117</v>
+        <v>1531358421</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5912,19 +5836,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.068</v>
+        <v>0.02</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45544.65070009259</v>
+        <v>45608.3501140162</v>
       </c>
       <c r="G85" t="n">
-        <v>161.58</v>
+        <v>20.4503</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45608.35479755787</v>
       </c>
       <c r="I85" t="n">
-        <v>172.09</v>
+        <v>20.4382</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5936,15 +5860,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="M85" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>20.4388</v>
+      </c>
+      <c r="O85" t="n">
+        <v>20.4767</v>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
@@ -5955,18 +5881,22 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="U85" t="inlineStr"/>
+        <v>-1.18</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1468472119</v>
+        <v>1532703059</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5975,19 +5905,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45559.65212880787</v>
+        <v>45608.75711524305</v>
       </c>
       <c r="G86" t="n">
-        <v>277.82</v>
+        <v>20.6261</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45608.76530484953</v>
       </c>
       <c r="I86" t="n">
-        <v>336.69</v>
+        <v>20.6299</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5999,15 +5929,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L86" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M86" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>20.5745</v>
+      </c>
+      <c r="O86" t="n">
+        <v>20.6364</v>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
@@ -6018,18 +5950,18 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>4.23</v>
+        <v>0.37</v>
       </c>
       <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1470564087</v>
+        <v>1532729622</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6038,19 +5970,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0742</v>
+        <v>0.01</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45560.82041144676</v>
+        <v>45608.76652064815</v>
       </c>
       <c r="G87" t="n">
-        <v>269.23</v>
+        <v>154.853</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45608.76796081018</v>
       </c>
       <c r="I87" t="n">
-        <v>336.69</v>
+        <v>154.873</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6062,15 +5994,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M87" t="n">
-        <v>24.98</v>
-      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>5</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
@@ -6081,18 +6011,18 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>5</v>
+        <v>0.13</v>
       </c>
       <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1599434998</v>
+        <v>1533930062</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6101,19 +6031,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0477</v>
+        <v>0.01</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45663.73100940972</v>
+        <v>45609.61569380787</v>
       </c>
       <c r="G88" t="n">
-        <v>313.98</v>
+        <v>20.507</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45609.63889303241</v>
       </c>
       <c r="I88" t="n">
-        <v>336.69</v>
+        <v>20.5531</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6125,15 +6055,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L88" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="M88" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>20.431</v>
+      </c>
+      <c r="O88" t="n">
+        <v>20.5528</v>
+      </c>
+      <c r="P88" t="n">
+        <v>5</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
@@ -6144,18 +6076,22 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U88" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1495548850</v>
+        <v>1536772518</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6164,19 +6100,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.1047</v>
+        <v>0.02</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45580.70599549769</v>
+        <v>45610.86999649306</v>
       </c>
       <c r="G89" t="n">
-        <v>133.61</v>
+        <v>20.4311</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45610.88084664352</v>
       </c>
       <c r="I89" t="n">
-        <v>143.18</v>
+        <v>20.4923</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6188,15 +6124,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L89" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="M89" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>20.4941</v>
+      </c>
+      <c r="O89" t="n">
+        <v>20.5653</v>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
@@ -6207,18 +6145,22 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="inlineStr"/>
+        <v>5.97</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1517512112</v>
+        <v>1540892910</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6227,19 +6169,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45597.61040866898</v>
+        <v>45614.83689460648</v>
       </c>
       <c r="G90" t="n">
-        <v>132.62</v>
+        <v>20.2371</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45615.43822850694</v>
       </c>
       <c r="I90" t="n">
-        <v>143.18</v>
+        <v>20.3181</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6251,37 +6193,43 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="O90" t="n">
+        <v>20.3179</v>
+      </c>
+      <c r="P90" t="n">
         <v>10</v>
       </c>
-      <c r="M90" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U90" t="inlineStr"/>
+        <v>7.97</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1582735114</v>
+        <v>1541930457</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6290,23 +6238,23 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45645.90076787037</v>
+        <v>45615.56159975695</v>
       </c>
       <c r="G91" t="n">
-        <v>130.51</v>
+        <v>20.2629</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45615.58509630787</v>
       </c>
       <c r="I91" t="n">
-        <v>143.18</v>
+        <v>20.2887</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6314,15 +6262,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L91" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="M91" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>20.2059</v>
+      </c>
+      <c r="O91" t="n">
+        <v>20.2856</v>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -6333,14 +6283,18 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="U91" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1657658561</v>
+        <v>1553997553</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -6349,23 +6303,23 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45702.18774210648</v>
+        <v>45623.53527240741</v>
       </c>
       <c r="G92" t="n">
-        <v>20.4257</v>
+        <v>20.7084</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45702.56168643518</v>
+        <v>45623.57548773148</v>
       </c>
       <c r="I92" t="n">
-        <v>20.3656</v>
+        <v>20.7775</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6380,13 +6334,13 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>20.3664</v>
+        <v>20.7706</v>
       </c>
       <c r="O92" t="n">
-        <v>20.5213</v>
+        <v>20.68</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -6398,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-5.9</v>
+        <v>-3.33</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -6409,7 +6363,7 @@
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1660829104</v>
+        <v>1554074835</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -6418,23 +6372,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45705.64981799768</v>
+        <v>45623.57516572917</v>
       </c>
       <c r="G93" t="n">
-        <v>20.3237</v>
+        <v>20.7426</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45705.72866341435</v>
+        <v>45623.57574133102</v>
       </c>
       <c r="I93" t="n">
-        <v>20.2738</v>
+        <v>20.7764</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6448,14 +6402,10 @@
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>20.2738</v>
-      </c>
-      <c r="O93" t="n">
-        <v>20.3936</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -6467,22 +6417,18 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-1.63</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1378903852</v>
+        <v>1555669398</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6491,19 +6437,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0616</v>
+        <v>0.02</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45624.55073625</v>
       </c>
       <c r="G94" t="n">
-        <v>227.77</v>
+        <v>20.3273</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45706.65274813658</v>
+        <v>45624.71914708333</v>
       </c>
       <c r="I94" t="n">
-        <v>243.58</v>
+        <v>20.4312</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6515,15 +6461,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L94" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="M94" t="n">
-        <v>15</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>20.1748</v>
+      </c>
+      <c r="O94" t="n">
+        <v>20.4293</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -6534,18 +6482,22 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="U94" t="inlineStr"/>
+        <v>10.17</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1378903852</v>
+        <v>1563562241</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6554,19 +6506,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0042</v>
+        <v>0.02</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45631.25027201389</v>
       </c>
       <c r="G95" t="n">
-        <v>227.77</v>
+        <v>20.3099</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45631.6258153125</v>
       </c>
       <c r="I95" t="n">
-        <v>243.45</v>
+        <v>20.2391</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6578,15 +6530,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="O95" t="n">
+        <v>20.3672</v>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -6597,18 +6551,22 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U95" t="inlineStr"/>
+        <v>-6.99</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1456814919</v>
+        <v>1473693877</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6617,19 +6575,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0665</v>
+        <v>0.019</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45548.6657375</v>
+        <v>45562.69351818287</v>
       </c>
       <c r="G96" t="n">
-        <v>222.94</v>
+        <v>700.8</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I96" t="n">
-        <v>243.45</v>
+        <v>623.8</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6642,10 +6600,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>14.83</v>
+        <v>14.97</v>
       </c>
       <c r="M96" t="n">
-        <v>16.19</v>
+        <v>12.28</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6660,18 +6618,18 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>1.36</v>
+        <v>-2.69</v>
       </c>
       <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1499061783</v>
+        <v>1493848938</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6680,23 +6638,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0558</v>
+        <v>0.0213</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45582.73996877314</v>
+        <v>45579.70088467593</v>
       </c>
       <c r="G97" t="n">
-        <v>232.2</v>
+        <v>640.3</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I97" t="n">
-        <v>243.45</v>
+        <v>623.8</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6705,10 +6663,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>12.96</v>
+        <v>14.96</v>
       </c>
       <c r="M97" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -6723,14 +6681,14 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0.62</v>
+        <v>-1.19</v>
       </c>
       <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1717095547</v>
+        <v>1583724019</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -6743,19 +6701,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45736.81342114583</v>
+        <v>45646.60647967592</v>
       </c>
       <c r="G98" t="n">
-        <v>20.1198</v>
+        <v>20.2054</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45737.11337774306</v>
+        <v>45646.696485625</v>
       </c>
       <c r="I98" t="n">
-        <v>20.1348</v>
+        <v>20.1035</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6770,25 +6728,25 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>20.1349</v>
+        <v>20.1055</v>
       </c>
       <c r="O98" t="n">
-        <v>20.1623</v>
+        <v>20.3273</v>
       </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.98</v>
+        <v>-10.13</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -6799,11 +6757,11 @@
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1554741910</v>
+        <v>1583841034</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6812,19 +6770,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45623.74951100694</v>
+        <v>45646.63988152778</v>
       </c>
       <c r="G99" t="n">
-        <v>15.3</v>
+        <v>20.173</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45741.87177293981</v>
+        <v>45646.70582428241</v>
       </c>
       <c r="I99" t="n">
-        <v>20.29</v>
+        <v>20.0949</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6836,15 +6794,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L99" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="M99" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>20.0975</v>
+      </c>
+      <c r="O99" t="n">
+        <v>20.2542</v>
+      </c>
+      <c r="P99" t="n">
+        <v>5</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -6855,18 +6815,22 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U99" t="inlineStr"/>
+        <v>-3.88</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1414372592</v>
+        <v>1585474078</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6875,19 +6839,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45511.7228721412</v>
+        <v>45649.40133020833</v>
       </c>
       <c r="G100" t="n">
-        <v>455.4</v>
+        <v>20.0935</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45742.77596394676</v>
+        <v>45649.56824730324</v>
       </c>
       <c r="I100" t="n">
-        <v>547.14</v>
+        <v>20.1707</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6899,15 +6863,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="M100" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>20</v>
+      </c>
+      <c r="O100" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
@@ -6918,18 +6884,22 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U100" t="inlineStr"/>
+        <v>7.65</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1450043624</v>
+        <v>1586033461</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6938,19 +6908,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0138</v>
+        <v>0.01</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45649.63114609953</v>
       </c>
       <c r="G101" t="n">
-        <v>147.48</v>
+        <v>20.1772</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45743.76599777778</v>
+        <v>45649.63200465278</v>
       </c>
       <c r="I101" t="n">
-        <v>139.86</v>
+        <v>20.1671</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6962,15 +6932,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L101" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>20.1687</v>
+      </c>
+      <c r="O101" t="n">
+        <v>20.2379</v>
+      </c>
+      <c r="P101" t="n">
+        <v>5</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -6981,18 +6953,22 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U101" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1358151307</v>
+        <v>1587036381</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7001,19 +6977,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0124</v>
+        <v>0.02</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45460.88529037037</v>
+        <v>45650.48790526621</v>
       </c>
       <c r="G102" t="n">
-        <v>165.93</v>
+        <v>20.1462</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45743.76632650463</v>
+        <v>45650.58025611111</v>
       </c>
       <c r="I102" t="n">
-        <v>149.33</v>
+        <v>20.1627</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7025,15 +7001,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>20.1627</v>
+      </c>
+      <c r="O102" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="P102" t="n">
+        <v>10</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
@@ -7044,18 +7022,22 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="U102" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1422773288</v>
+        <v>1500272843</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7064,19 +7046,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.2</v>
+        <v>0.0264</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45518.84428505787</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G103" t="n">
-        <v>51.24</v>
+        <v>718.5</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45743.76769060185</v>
+        <v>45663.67045758102</v>
       </c>
       <c r="I103" t="n">
-        <v>58.08</v>
+        <v>757.79</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7089,10 +7071,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10.25</v>
+        <v>18.97</v>
       </c>
       <c r="M103" t="n">
-        <v>11.62</v>
+        <v>20.01</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -7107,18 +7089,18 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1631473921</v>
+        <v>1500272843</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7127,19 +7109,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.2745</v>
+        <v>0.0021</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45685.8356116088</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G104" t="n">
-        <v>40.05</v>
+        <v>718.5</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45663.67059782407</v>
       </c>
       <c r="I104" t="n">
-        <v>44.8</v>
+        <v>758.27</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7148,14 +7130,14 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>10.99</v>
+        <v>1.51</v>
       </c>
       <c r="M104" t="n">
-        <v>12.3</v>
+        <v>1.59</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -7170,18 +7152,18 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1642763333</v>
+        <v>1518147105</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MAXN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7190,19 +7172,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2459</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45692.86672944445</v>
+        <v>45597.8504690162</v>
       </c>
       <c r="G105" t="n">
-        <v>40.66</v>
+        <v>10.92</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45667.68126778935</v>
       </c>
       <c r="I105" t="n">
-        <v>44.8</v>
+        <v>6.52</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7211,14 +7193,14 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>10.92</v>
       </c>
       <c r="M105" t="n">
-        <v>11.02</v>
+        <v>6.52</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -7233,18 +7215,18 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>1.02</v>
+        <v>-4.4</v>
       </c>
       <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1666451221</v>
+        <v>1551373923</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7253,19 +7235,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1796</v>
+        <v>0.1195</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45621.85639895833</v>
       </c>
       <c r="G106" t="n">
-        <v>43</v>
+        <v>167.24</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45678.70646498843</v>
       </c>
       <c r="I106" t="n">
-        <v>44.8</v>
+        <v>198.83</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7274,14 +7256,14 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>7.72</v>
+        <v>19.99</v>
       </c>
       <c r="M106" t="n">
-        <v>8.050000000000001</v>
+        <v>23.76</v>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
@@ -7296,57 +7278,59 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>0.33</v>
+        <v>3.77</v>
       </c>
       <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1749053104</v>
+        <v>1373744560</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.01</v>
+        <v>0.1248</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45754.65117414352</v>
+        <v>45476.64586885417</v>
       </c>
       <c r="G107" t="n">
-        <v>4903.7</v>
+        <v>202.58</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45754.65218731482</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I107" t="n">
-        <v>4891.1</v>
+        <v>172.09</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="M107" t="n">
+        <v>21.48</v>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="n">
-        <v>12.26</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
@@ -7357,57 +7341,59 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>6.3</v>
+        <v>-3.8</v>
       </c>
       <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1756767326</v>
+        <v>1450039117</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.01</v>
+        <v>0.068</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45756.64805717592</v>
+        <v>45544.65070009259</v>
       </c>
       <c r="G108" t="n">
-        <v>5004.7</v>
+        <v>161.58</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45756.64937413194</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I108" t="n">
-        <v>5005.2</v>
+        <v>172.09</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11.7</v>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="n">
-        <v>12.51</v>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
@@ -7418,57 +7404,59 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>-0.25</v>
+        <v>0.71</v>
       </c>
       <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1756797155</v>
+        <v>1468472119</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.01</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45756.6510503125</v>
+        <v>45559.65212880787</v>
       </c>
       <c r="G109" t="n">
-        <v>4992.2</v>
+        <v>277.82</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45756.65185319445</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I109" t="n">
-        <v>5013.4</v>
+        <v>336.69</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M109" t="n">
+        <v>24.21</v>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
-        <v>12.48</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
@@ -7479,18 +7467,18 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>-10.6</v>
+        <v>4.23</v>
       </c>
       <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1767688540</v>
+        <v>1470564087</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7499,19 +7487,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.01</v>
+        <v>0.0742</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45761.6294487037</v>
+        <v>45560.82041144676</v>
       </c>
       <c r="G110" t="n">
-        <v>20.1226</v>
+        <v>269.23</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45761.66966099537</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I110" t="n">
-        <v>20.047</v>
+        <v>336.69</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7523,43 +7511,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="n">
-        <v>20.048</v>
-      </c>
-      <c r="O110" t="n">
-        <v>20.3404</v>
-      </c>
-      <c r="P110" t="n">
+      <c r="L110" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M110" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1768229183</v>
+        <v>1599434998</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7568,19 +7550,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.01</v>
+        <v>0.0477</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45761.71402207176</v>
+        <v>45663.73100940972</v>
       </c>
       <c r="G111" t="n">
-        <v>20.0759</v>
+        <v>313.98</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45761.77371288194</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I111" t="n">
-        <v>20.1099</v>
+        <v>336.69</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7592,17 +7574,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
-        <v>20.1099</v>
-      </c>
-      <c r="O111" t="n">
-        <v>20.2122</v>
-      </c>
-      <c r="P111" t="n">
-        <v>5</v>
-      </c>
+      <c r="L111" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M111" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
@@ -7613,22 +7593,18 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1.08</v>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1769815245</v>
+        <v>1495548850</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7637,19 +7613,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.01</v>
+        <v>0.1047</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45762.50265097222</v>
+        <v>45580.70599549769</v>
       </c>
       <c r="G112" t="n">
-        <v>20.0545</v>
+        <v>133.61</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45762.61225923611</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I112" t="n">
-        <v>19.9735</v>
+        <v>143.18</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7661,15 +7637,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="n">
-        <v>19.9742</v>
-      </c>
+      <c r="L112" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="M112" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>5</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
@@ -7680,22 +7656,18 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1666451221</v>
+        <v>1517512112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7704,19 +7676,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.0528</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45597.61040866898</v>
       </c>
       <c r="G113" t="n">
-        <v>43</v>
+        <v>132.62</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45764.85028728009</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I113" t="n">
-        <v>47.89</v>
+        <v>143.18</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7729,10 +7701,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="M113" t="n">
-        <v>2.53</v>
+        <v>10.8</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -7747,18 +7719,18 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1450043624</v>
+        <v>1582735114</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7767,23 +7739,23 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.1</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45645.90076787037</v>
       </c>
       <c r="G114" t="n">
-        <v>147.48</v>
+        <v>130.51</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45764.8517803588</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I114" t="n">
-        <v>143.22</v>
+        <v>143.18</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7792,10 +7764,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>14.75</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>14.32</v>
+        <v>10.92</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -7810,14 +7782,14 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>-0.42</v>
+        <v>0.96</v>
       </c>
       <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1777308201</v>
+        <v>1657658561</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -7830,19 +7802,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45768.12181488426</v>
+        <v>45702.18774210648</v>
       </c>
       <c r="G115" t="n">
-        <v>19.7053</v>
+        <v>20.4257</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45768.13306659722</v>
+        <v>45702.56168643518</v>
       </c>
       <c r="I115" t="n">
-        <v>19.7154</v>
+        <v>20.3656</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7856,10 +7828,14 @@
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>20.3664</v>
+      </c>
+      <c r="O115" t="n">
+        <v>20.5213</v>
+      </c>
       <c r="P115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -7871,14 +7847,18 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="U115" t="inlineStr"/>
+        <v>-5.9</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1781449563</v>
+        <v>1660829104</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -7891,19 +7871,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45769.73814164352</v>
+        <v>45705.64981799768</v>
       </c>
       <c r="G116" t="n">
-        <v>19.58</v>
+        <v>20.3237</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45769.76084202546</v>
+        <v>45705.72866341435</v>
       </c>
       <c r="I116" t="n">
-        <v>19.5255</v>
+        <v>20.2738</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7917,10 +7897,14 @@
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>20.2738</v>
+      </c>
+      <c r="O116" t="n">
+        <v>20.3936</v>
+      </c>
       <c r="P116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -7932,18 +7916,22 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="U116" t="inlineStr"/>
+        <v>-4.92</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1560258921</v>
+        <v>1378903852</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7952,19 +7940,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0.0616</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45629.37798611111</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G117" t="n">
-        <v>48.68</v>
+        <v>227.77</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45706.65274813658</v>
       </c>
       <c r="I117" t="n">
-        <v>44.15</v>
+        <v>243.58</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7977,10 +7965,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>51.41</v>
+        <v>14.03</v>
       </c>
       <c r="M117" t="n">
-        <v>49.84</v>
+        <v>15</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -7995,18 +7983,18 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>-1.57</v>
+        <v>0.97</v>
       </c>
       <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1748583646</v>
+        <v>1378903852</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8015,19 +8003,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.0042</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45754.57938657407</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G118" t="n">
-        <v>37.258</v>
+        <v>227.77</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I118" t="n">
-        <v>44.15</v>
+        <v>243.45</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8040,10 +8028,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>41.06</v>
+        <v>0.96</v>
       </c>
       <c r="M118" t="n">
-        <v>49.84</v>
+        <v>1.02</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8058,18 +8046,18 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>8.779999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1373808226</v>
+        <v>1456814919</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8078,19 +8066,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.0234</v>
+        <v>0.0665</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45476.6587916088</v>
+        <v>45548.6657375</v>
       </c>
       <c r="G119" t="n">
-        <v>459.24</v>
+        <v>222.94</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I119" t="n">
-        <v>434.71</v>
+        <v>243.45</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8103,10 +8091,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>10.75</v>
+        <v>14.83</v>
       </c>
       <c r="M119" t="n">
-        <v>10.17</v>
+        <v>16.19</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8121,18 +8109,18 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>-0.58</v>
+        <v>1.36</v>
       </c>
       <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1426782063</v>
+        <v>1499061783</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8141,23 +8129,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0372</v>
+        <v>0.0558</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45582.73996877314</v>
       </c>
       <c r="G120" t="n">
-        <v>419.46</v>
+        <v>232.2</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I120" t="n">
-        <v>434.71</v>
+        <v>243.45</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8166,10 +8154,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>15.6</v>
+        <v>12.96</v>
       </c>
       <c r="M120" t="n">
-        <v>16.17</v>
+        <v>13.58</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -8184,18 +8172,18 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1426782063</v>
+        <v>1717095547</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8204,19 +8192,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45736.81342114583</v>
       </c>
       <c r="G121" t="n">
-        <v>419.46</v>
+        <v>20.1198</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45785.65885817129</v>
+        <v>45737.11337774306</v>
       </c>
       <c r="I121" t="n">
-        <v>437.05</v>
+        <v>20.1348</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8228,37 +8216,43 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="M121" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>20.1349</v>
+      </c>
+      <c r="O121" t="n">
+        <v>20.1623</v>
+      </c>
+      <c r="P121" t="n">
+        <v>20</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U121" t="inlineStr"/>
+        <v>2.98</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1744929368</v>
+        <v>1554741910</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8267,23 +8261,23 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.0424</v>
+        <v>0.61</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45751.7450085301</v>
+        <v>45623.74951100694</v>
       </c>
       <c r="G122" t="n">
-        <v>324.48</v>
+        <v>15.3</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45785.65909077547</v>
+        <v>45741.87177293981</v>
       </c>
       <c r="I122" t="n">
-        <v>353.02</v>
+        <v>20.29</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8292,10 +8286,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>13.76</v>
+        <v>9.33</v>
       </c>
       <c r="M122" t="n">
-        <v>14.97</v>
+        <v>12.38</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -8310,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="U122" t="inlineStr"/>
     </row>
@@ -8330,7 +8324,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.0229</v>
+        <v>0.01</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>45511.7228721412</v>
@@ -8339,10 +8333,10 @@
         <v>455.4</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45742.77596394676</v>
       </c>
       <c r="I123" t="n">
-        <v>568.9299999999999</v>
+        <v>547.14</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8355,10 +8349,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>10.43</v>
+        <v>4.55</v>
       </c>
       <c r="M123" t="n">
-        <v>13.03</v>
+        <v>5.47</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -8373,18 +8367,18 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>2.6</v>
+        <v>0.92</v>
       </c>
       <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1582737192</v>
+        <v>1450043624</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8393,23 +8387,23 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.0371</v>
+        <v>0.0138</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45645.90143914352</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G124" t="n">
-        <v>524.4299999999999</v>
+        <v>147.48</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45785.66047934028</v>
+        <v>45743.76599777778</v>
       </c>
       <c r="I124" t="n">
-        <v>568.9299999999999</v>
+        <v>139.86</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8418,10 +8412,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>19.46</v>
+        <v>2.04</v>
       </c>
       <c r="M124" t="n">
-        <v>21.11</v>
+        <v>1.93</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -8436,18 +8430,18 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>1.65</v>
+        <v>-0.11</v>
       </c>
       <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1599454287</v>
+        <v>1358151307</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8456,19 +8450,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45663.73715268519</v>
+        <v>45460.88529037037</v>
       </c>
       <c r="G125" t="n">
-        <v>196.49</v>
+        <v>165.93</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45743.76632650463</v>
       </c>
       <c r="I125" t="n">
-        <v>196.89</v>
+        <v>149.33</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8481,10 +8475,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>14.99</v>
+        <v>2.06</v>
       </c>
       <c r="M125" t="n">
-        <v>15.02</v>
+        <v>1.85</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -8499,18 +8493,18 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>0.03</v>
+        <v>-0.21</v>
       </c>
       <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1621495599</v>
+        <v>1422773288</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8519,19 +8513,19 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45678.83206015046</v>
+        <v>45518.84428505787</v>
       </c>
       <c r="G126" t="n">
-        <v>183.39</v>
+        <v>51.24</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45743.76769060185</v>
       </c>
       <c r="I126" t="n">
-        <v>196.89</v>
+        <v>58.08</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8544,10 +8538,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>14.98</v>
+        <v>10.25</v>
       </c>
       <c r="M126" t="n">
-        <v>16.09</v>
+        <v>11.62</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
@@ -8562,18 +8556,18 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1631467534</v>
+        <v>1631473921</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8582,19 +8576,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.2745</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45685.83235356482</v>
+        <v>45685.8356116088</v>
       </c>
       <c r="G127" t="n">
-        <v>159.74</v>
+        <v>40.05</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I127" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8603,14 +8597,14 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>14.97</v>
+        <v>10.99</v>
       </c>
       <c r="M127" t="n">
-        <v>18.45</v>
+        <v>12.3</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
@@ -8625,18 +8619,18 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>3.48</v>
+        <v>1.31</v>
       </c>
       <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1666449688</v>
+        <v>1642763333</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8645,19 +8639,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.2459</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45708.67996841436</v>
+        <v>45692.86672944445</v>
       </c>
       <c r="G128" t="n">
-        <v>160.68</v>
+        <v>40.66</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I128" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8666,14 +8660,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>18.35</v>
+        <v>11.02</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
@@ -8688,18 +8682,18 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>3.37</v>
+        <v>1.02</v>
       </c>
       <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1701098878</v>
+        <v>1666451221</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8708,19 +8702,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.0051</v>
+        <v>0.1796</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G129" t="n">
-        <v>139.41</v>
+        <v>43</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45791.64976413194</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I129" t="n">
-        <v>196.89</v>
+        <v>44.8</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8729,14 +8723,14 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0.71</v>
+        <v>7.72</v>
       </c>
       <c r="M129" t="n">
-        <v>1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
@@ -8751,59 +8745,57 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>1701098878</v>
+        <v>1749053104</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45727.87167579861</v>
+        <v>45754.65117414352</v>
       </c>
       <c r="G130" t="n">
-        <v>139.41</v>
+        <v>4903.7</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45792.64655003473</v>
+        <v>45754.65218731482</v>
       </c>
       <c r="I130" t="n">
-        <v>188.02</v>
+        <v>4891.1</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="M130" t="n">
-        <v>18.8</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>12.26</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
@@ -8814,59 +8806,57 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4.86</v>
+        <v>6.3</v>
       </c>
       <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1426782063</v>
+        <v>1756767326</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.0004</v>
+        <v>0.01</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45756.64805717592</v>
       </c>
       <c r="G131" t="n">
-        <v>419.46</v>
+        <v>5004.7</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45756.64937413194</v>
       </c>
       <c r="I131" t="n">
-        <v>452.34</v>
+        <v>5005.2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0.18</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>12.51</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
@@ -8877,59 +8867,57 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>1481614059</v>
+        <v>1756797155</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.0359</v>
+        <v>0.01</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45568.77505349537</v>
+        <v>45756.6510503125</v>
       </c>
       <c r="G132" t="n">
-        <v>417.1</v>
+        <v>4992.2</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45756.65185319445</v>
       </c>
       <c r="I132" t="n">
-        <v>452.34</v>
+        <v>5013.4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="M132" t="n">
-        <v>16.24</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>12.48</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
@@ -8940,18 +8928,18 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>1.27</v>
+        <v>-10.6</v>
       </c>
       <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1517514880</v>
+        <v>1767688540</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8960,19 +8948,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.0037</v>
+        <v>0.01</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45597.6108722338</v>
+        <v>45761.6294487037</v>
       </c>
       <c r="G133" t="n">
-        <v>409.38</v>
+        <v>20.1226</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45792.64781748843</v>
+        <v>45761.66966099537</v>
       </c>
       <c r="I133" t="n">
-        <v>452.34</v>
+        <v>20.047</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8984,15 +8972,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L133" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M133" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>20.048</v>
+      </c>
+      <c r="O133" t="n">
+        <v>20.3404</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
@@ -9003,18 +8993,22 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U133" t="inlineStr"/>
+        <v>-3.77</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1381375440</v>
+        <v>1768229183</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9023,19 +9017,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.1057</v>
+        <v>0.01</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45484.67118305556</v>
+        <v>45761.71402207176</v>
       </c>
       <c r="G134" t="n">
-        <v>189.11</v>
+        <v>20.0759</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45761.77371288194</v>
       </c>
       <c r="I134" t="n">
-        <v>212.35</v>
+        <v>20.1099</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9047,15 +9041,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L134" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="M134" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>20.1099</v>
+      </c>
+      <c r="O134" t="n">
+        <v>20.2122</v>
+      </c>
+      <c r="P134" t="n">
+        <v>5</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
@@ -9066,18 +9062,22 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U134" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1511085920</v>
+        <v>1769815245</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9086,19 +9086,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.0761</v>
+        <v>0.01</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45593.7262772338</v>
+        <v>45762.50265097222</v>
       </c>
       <c r="G135" t="n">
-        <v>196.9</v>
+        <v>20.0545</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45762.61225923611</v>
       </c>
       <c r="I135" t="n">
-        <v>212.35</v>
+        <v>19.9735</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9110,15 +9110,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L135" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="M135" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="N135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>19.9742</v>
+      </c>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>5</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
@@ -9129,18 +9129,22 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U135" t="inlineStr"/>
+        <v>-4.06</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1532661507</v>
+        <v>1666451221</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9149,19 +9153,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45608.74251091435</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G136" t="n">
-        <v>190.67</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45764.85028728009</v>
       </c>
       <c r="I136" t="n">
-        <v>212.35</v>
+        <v>47.89</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9174,10 +9178,10 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>12.98</v>
+        <v>2.27</v>
       </c>
       <c r="M136" t="n">
-        <v>14.46</v>
+        <v>2.53</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -9192,18 +9196,18 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>1.48</v>
+        <v>0.25</v>
       </c>
       <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1554742887</v>
+        <v>1450043624</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9212,19 +9216,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45623.74993096065</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G137" t="n">
-        <v>178.48</v>
+        <v>147.48</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45764.8517803588</v>
       </c>
       <c r="I137" t="n">
-        <v>212.35</v>
+        <v>143.22</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -9237,10 +9241,10 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>14.99</v>
+        <v>14.75</v>
       </c>
       <c r="M137" t="n">
-        <v>17.84</v>
+        <v>14.32</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -9255,18 +9259,18 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>2.85</v>
+        <v>-0.42</v>
       </c>
       <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1582708979</v>
+        <v>1777308201</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9275,23 +9279,23 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.0769</v>
+        <v>0.01</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45645.88746972222</v>
+        <v>45768.12181488426</v>
       </c>
       <c r="G138" t="n">
-        <v>195.11</v>
+        <v>19.7053</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45768.13306659722</v>
       </c>
       <c r="I138" t="n">
-        <v>212.35</v>
+        <v>19.7154</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9299,15 +9303,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L138" t="n">
-        <v>15</v>
-      </c>
-      <c r="M138" t="n">
-        <v>16.33</v>
-      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>5</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
@@ -9318,18 +9320,18 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>1.33</v>
+        <v>0.51</v>
       </c>
       <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1680991980</v>
+        <v>1781449563</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9338,19 +9340,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.0892</v>
+        <v>0.01</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45716.85566212963</v>
+        <v>45769.73814164352</v>
       </c>
       <c r="G139" t="n">
-        <v>178.67</v>
+        <v>19.58</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45818.80060692129</v>
+        <v>45769.76084202546</v>
       </c>
       <c r="I139" t="n">
-        <v>212.35</v>
+        <v>19.5255</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9362,15 +9364,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L139" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="M139" t="n">
-        <v>18.94</v>
-      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>5</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
@@ -9381,18 +9381,18 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>3</v>
+        <v>-2.79</v>
       </c>
       <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1517514880</v>
+        <v>1560258921</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9401,19 +9401,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.0231</v>
+        <v>1</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45597.6108722338</v>
+        <v>45629.37798611111</v>
       </c>
       <c r="G140" t="n">
-        <v>409.38</v>
+        <v>48.68</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45818.9064246875</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I140" t="n">
-        <v>470.07</v>
+        <v>44.15</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>9.460000000000001</v>
+        <v>51.41</v>
       </c>
       <c r="M140" t="n">
-        <v>10.86</v>
+        <v>49.84</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -9444,18 +9444,18 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>1.4</v>
+        <v>-1.57</v>
       </c>
       <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1648737122</v>
+        <v>1748583646</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9464,19 +9464,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.0169</v>
+        <v>1</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45695.8561993287</v>
+        <v>45754.57938657407</v>
       </c>
       <c r="G141" t="n">
-        <v>408.33</v>
+        <v>37.258</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45818.9064246875</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I141" t="n">
-        <v>470.07</v>
+        <v>44.15</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>6.9</v>
+        <v>41.06</v>
       </c>
       <c r="M141" t="n">
-        <v>7.94</v>
+        <v>49.84</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -9507,18 +9507,18 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>1.04</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1648740228</v>
+        <v>1373808226</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9527,19 +9527,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.0538</v>
+        <v>0.0234</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45695.85792373843</v>
+        <v>45476.6587916088</v>
       </c>
       <c r="G142" t="n">
-        <v>185.82</v>
+        <v>459.24</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>45818.90659450232</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I142" t="n">
-        <v>178.54</v>
+        <v>434.71</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="M142" t="n">
-        <v>9.609999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -9570,18 +9570,18 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>-0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1712850989</v>
+        <v>1426782063</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9590,19 +9590,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0372</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45734.85576756945</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G143" t="n">
-        <v>160.64</v>
+        <v>419.46</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45818.90659450232</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I143" t="n">
-        <v>178.54</v>
+        <v>434.71</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>15.45</v>
+        <v>15.6</v>
       </c>
       <c r="M143" t="n">
-        <v>17.18</v>
+        <v>16.17</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -9633,18 +9633,18 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>1.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>1666457581</v>
+        <v>1426782063</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9653,19 +9653,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45708.68135143518</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G144" t="n">
-        <v>38.23</v>
+        <v>419.46</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45825.89271061343</v>
+        <v>45785.65885817129</v>
       </c>
       <c r="I144" t="n">
-        <v>38.6</v>
+        <v>437.05</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>19.98</v>
+        <v>4.19</v>
       </c>
       <c r="M144" t="n">
-        <v>20.18</v>
+        <v>4.37</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -9696,18 +9696,18 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>1825032378</v>
+        <v>1744929368</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9716,23 +9716,23 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.2894</v>
+        <v>0.0424</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45792.76093159722</v>
+        <v>45751.7450085301</v>
       </c>
       <c r="G145" t="n">
-        <v>34.55</v>
+        <v>324.48</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>45825.89271061343</v>
+        <v>45785.65909077547</v>
       </c>
       <c r="I145" t="n">
-        <v>38.6</v>
+        <v>353.02</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>10</v>
+        <v>13.76</v>
       </c>
       <c r="M145" t="n">
-        <v>11.17</v>
+        <v>14.97</v>
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
@@ -9759,18 +9759,18 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>1830410729</v>
+        <v>1414372592</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9779,19 +9779,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.1879</v>
+        <v>0.0229</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45796.82476541667</v>
+        <v>45511.7228721412</v>
       </c>
       <c r="G146" t="n">
-        <v>33.66</v>
+        <v>455.4</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>45825.89271061343</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I146" t="n">
-        <v>38.6</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>6.32</v>
+        <v>10.43</v>
       </c>
       <c r="M146" t="n">
-        <v>7.25</v>
+        <v>13.03</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
@@ -9822,18 +9822,18 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>0.92</v>
+        <v>2.6</v>
       </c>
       <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>1393281432</v>
+        <v>1582737192</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9842,35 +9842,35 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.632</v>
+        <v>0.0371</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45645.90143914352</v>
       </c>
       <c r="G147" t="n">
-        <v>5.981</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45785.66047934028</v>
       </c>
       <c r="I147" t="n">
-        <v>5.967</v>
+        <v>568.9299999999999</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.78</v>
+        <v>19.46</v>
       </c>
       <c r="M147" t="n">
-        <v>3.77</v>
+        <v>21.11</v>
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
@@ -9885,18 +9885,18 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>-0.01</v>
+        <v>1.65</v>
       </c>
       <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>1393281260</v>
+        <v>1599454287</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9905,35 +9905,35 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.5612</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45663.73715268519</v>
       </c>
       <c r="G148" t="n">
-        <v>5.812</v>
+        <v>196.49</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I148" t="n">
-        <v>5.81</v>
+        <v>196.89</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.26</v>
+        <v>14.99</v>
       </c>
       <c r="M148" t="n">
-        <v>3.26</v>
+        <v>15.02</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
@@ -9948,18 +9948,18 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>1393281260</v>
+        <v>1621495599</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9968,35 +9968,35 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.555</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45678.83206015046</v>
       </c>
       <c r="G149" t="n">
-        <v>5.812</v>
+        <v>183.39</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I149" t="n">
-        <v>5.801</v>
+        <v>196.89</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.23</v>
+        <v>14.98</v>
       </c>
       <c r="M149" t="n">
-        <v>3.22</v>
+        <v>16.09</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
@@ -10011,18 +10011,18 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>-0.01</v>
+        <v>1.11</v>
       </c>
       <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>1393281432</v>
+        <v>1631467534</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10031,35 +10031,35 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.4344</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45685.83235356482</v>
       </c>
       <c r="G150" t="n">
-        <v>5.981</v>
+        <v>159.74</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I150" t="n">
-        <v>5.968</v>
+        <v>196.89</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.6</v>
+        <v>14.97</v>
       </c>
       <c r="M150" t="n">
-        <v>2.59</v>
+        <v>18.45</v>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
@@ -10074,18 +10074,18 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>-0.01</v>
+        <v>3.48</v>
       </c>
       <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1393281260</v>
+        <v>1666449688</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10094,35 +10094,35 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45708.67996841436</v>
       </c>
       <c r="G151" t="n">
-        <v>5.812</v>
+        <v>160.68</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45791.64976413194</v>
       </c>
       <c r="I151" t="n">
-        <v>5.814</v>
+        <v>196.89</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>5.81</v>
+        <v>14.98</v>
       </c>
       <c r="M151" t="n">
-        <v>5.81</v>
+        <v>18.35</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -10137,18 +10137,18 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1393281432</v>
+        <v>1701098878</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -10157,35 +10157,35 @@
         </is>
       </c>
       <c r="E152" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>45727.87167579861</v>
+      </c>
+      <c r="G152" t="n">
+        <v>139.41</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>45791.64976413194</v>
+      </c>
+      <c r="I152" t="n">
+        <v>196.89</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M152" t="n">
         <v>1</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>45496.37566553241</v>
-      </c>
-      <c r="G152" t="n">
-        <v>5.981</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>45497.65424459491</v>
-      </c>
-      <c r="I152" t="n">
-        <v>5.978</v>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L152" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M152" t="n">
-        <v>5.98</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -10200,18 +10200,18 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>1393281260</v>
+        <v>1701098878</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -10220,35 +10220,35 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.4206</v>
+        <v>0.1</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45727.87167579861</v>
       </c>
       <c r="G153" t="n">
-        <v>5.812</v>
+        <v>139.41</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45792.64655003473</v>
       </c>
       <c r="I153" t="n">
-        <v>5.826</v>
+        <v>188.02</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.44</v>
+        <v>13.94</v>
       </c>
       <c r="M153" t="n">
-        <v>2.45</v>
+        <v>18.8</v>
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
@@ -10263,18 +10263,18 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>0.01</v>
+        <v>4.86</v>
       </c>
       <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>1393281432</v>
+        <v>1426782063</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -10283,35 +10283,35 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.4033</v>
+        <v>0.0004</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G154" t="n">
-        <v>5.981</v>
+        <v>419.46</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I154" t="n">
-        <v>5.98</v>
+        <v>452.34</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.41</v>
+        <v>0.17</v>
       </c>
       <c r="M154" t="n">
-        <v>2.41</v>
+        <v>0.18</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -10326,18 +10326,18 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1393281432</v>
+        <v>1481614059</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -10346,35 +10346,35 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.4201</v>
+        <v>0.0359</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45568.77505349537</v>
       </c>
       <c r="G155" t="n">
-        <v>5.981</v>
+        <v>417.1</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I155" t="n">
-        <v>5.98</v>
+        <v>452.34</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.51</v>
+        <v>14.97</v>
       </c>
       <c r="M155" t="n">
-        <v>2.51</v>
+        <v>16.24</v>
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -10389,18 +10389,18 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1393281432</v>
+        <v>1517514880</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -10409,35 +10409,35 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.0037</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.6108722338</v>
       </c>
       <c r="G156" t="n">
-        <v>5.981</v>
+        <v>409.38</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45792.64781748843</v>
       </c>
       <c r="I156" t="n">
-        <v>6.186</v>
+        <v>452.34</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>5.98</v>
+        <v>1.51</v>
       </c>
       <c r="M156" t="n">
-        <v>6.19</v>
+        <v>1.67</v>
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
@@ -10452,18 +10452,18 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="n">
-        <v>1393281260</v>
+        <v>1381375440</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -10472,35 +10472,35 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1.4632</v>
+        <v>0.1057</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45484.67118305556</v>
       </c>
       <c r="G157" t="n">
-        <v>5.812</v>
+        <v>189.11</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I157" t="n">
-        <v>6.02</v>
+        <v>212.35</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>8.5</v>
+        <v>19.99</v>
       </c>
       <c r="M157" t="n">
-        <v>8.81</v>
+        <v>22.45</v>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
@@ -10515,18 +10515,18 @@
         <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>0.3</v>
+        <v>2.46</v>
       </c>
       <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="n">
-        <v>1393287040</v>
+        <v>1511085920</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10535,35 +10535,35 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.2503</v>
+        <v>0.0761</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45593.7262772338</v>
       </c>
       <c r="G158" t="n">
-        <v>5.811</v>
+        <v>196.9</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I158" t="n">
-        <v>6.02</v>
+        <v>212.35</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.45</v>
+        <v>14.98</v>
       </c>
       <c r="M158" t="n">
-        <v>1.51</v>
+        <v>16.16</v>
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
@@ -10578,18 +10578,18 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>0.06</v>
+        <v>1.18</v>
       </c>
       <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="n">
-        <v>1403180431</v>
+        <v>1532661507</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10598,35 +10598,35 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.2773</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45608.74251091435</v>
       </c>
       <c r="G159" t="n">
-        <v>5.84</v>
+        <v>190.67</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I159" t="n">
-        <v>6.02</v>
+        <v>212.35</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.62</v>
+        <v>12.98</v>
       </c>
       <c r="M159" t="n">
-        <v>1.67</v>
+        <v>14.46</v>
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
@@ -10641,18 +10641,18 @@
         <v>0</v>
       </c>
       <c r="T159" t="n">
-        <v>0.05</v>
+        <v>1.48</v>
       </c>
       <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="n">
-        <v>1403180445</v>
+        <v>1554742887</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10661,35 +10661,35 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.0092</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45623.74993096065</v>
       </c>
       <c r="G160" t="n">
-        <v>5.836</v>
+        <v>178.48</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I160" t="n">
-        <v>6.02</v>
+        <v>212.35</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0.05</v>
+        <v>14.99</v>
       </c>
       <c r="M160" t="n">
-        <v>0.06</v>
+        <v>17.84</v>
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
@@ -10704,18 +10704,18 @@
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>0.01</v>
+        <v>2.85</v>
       </c>
       <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="n">
-        <v>1393735509</v>
+        <v>1582708979</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10724,35 +10724,35 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.0366</v>
+        <v>0.0769</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45645.88746972222</v>
       </c>
       <c r="G161" t="n">
-        <v>67.37</v>
+        <v>195.11</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I161" t="n">
-        <v>71.16</v>
+        <v>212.35</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.47</v>
+        <v>15</v>
       </c>
       <c r="M161" t="n">
-        <v>2.6</v>
+        <v>16.33</v>
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
@@ -10767,18 +10767,18 @@
         <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>0.13</v>
+        <v>1.33</v>
       </c>
       <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="n">
-        <v>1395218355</v>
+        <v>1680991980</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10787,35 +10787,35 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.074</v>
+        <v>0.0892</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45716.85566212963</v>
       </c>
       <c r="G162" t="n">
-        <v>67.13</v>
+        <v>178.67</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45818.80060692129</v>
       </c>
       <c r="I162" t="n">
-        <v>71.16</v>
+        <v>212.35</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>4.97</v>
+        <v>15.94</v>
       </c>
       <c r="M162" t="n">
-        <v>5.27</v>
+        <v>18.94</v>
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
@@ -10830,18 +10830,18 @@
         <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="n">
-        <v>1403166009</v>
+        <v>1517514880</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10850,35 +10850,35 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.0362</v>
+        <v>0.0231</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45597.6108722338</v>
       </c>
       <c r="G163" t="n">
-        <v>68.05</v>
+        <v>409.38</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45818.9064246875</v>
       </c>
       <c r="I163" t="n">
-        <v>71.16</v>
+        <v>470.07</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.46</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M163" t="n">
-        <v>2.58</v>
+        <v>10.86</v>
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
@@ -10893,18 +10893,18 @@
         <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>0.12</v>
+        <v>1.4</v>
       </c>
       <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="n">
-        <v>1403177543</v>
+        <v>1648737122</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10913,35 +10913,35 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.0368</v>
+        <v>0.0169</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45695.8561993287</v>
       </c>
       <c r="G164" t="n">
-        <v>68.045</v>
+        <v>408.33</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45818.9064246875</v>
       </c>
       <c r="I164" t="n">
-        <v>71.16</v>
+        <v>470.07</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="M164" t="n">
-        <v>2.62</v>
+        <v>7.94</v>
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
@@ -10956,18 +10956,18 @@
         <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>0.12</v>
+        <v>1.04</v>
       </c>
       <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="n">
-        <v>1403180429</v>
+        <v>1648740228</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10976,35 +10976,35 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.0733</v>
+        <v>0.0538</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45695.85792373843</v>
       </c>
       <c r="G165" t="n">
-        <v>68.01000000000001</v>
+        <v>185.82</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45818.90659450232</v>
       </c>
       <c r="I165" t="n">
-        <v>71.16</v>
+        <v>178.54</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>4.99</v>
+        <v>10</v>
       </c>
       <c r="M165" t="n">
-        <v>5.22</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
@@ -11019,18 +11019,18 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>0.23</v>
+        <v>-0.39</v>
       </c>
       <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="n">
-        <v>1403180445</v>
+        <v>1712850989</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -11039,35 +11039,35 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.9908</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45734.85576756945</v>
       </c>
       <c r="G166" t="n">
-        <v>5.836</v>
+        <v>160.64</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45818.90659450232</v>
       </c>
       <c r="I166" t="n">
-        <v>6.027</v>
+        <v>178.54</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>5.78</v>
+        <v>15.45</v>
       </c>
       <c r="M166" t="n">
-        <v>5.97</v>
+        <v>17.18</v>
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
@@ -11082,18 +11082,18 @@
         <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>0.18</v>
+        <v>1.73</v>
       </c>
       <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="n">
-        <v>1393281432</v>
+        <v>1666457581</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -11102,35 +11102,35 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.1102</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45708.68135143518</v>
       </c>
       <c r="G167" t="n">
-        <v>5.981</v>
+        <v>38.23</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I167" t="n">
-        <v>6.176</v>
+        <v>38.6</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0.66</v>
+        <v>19.98</v>
       </c>
       <c r="M167" t="n">
-        <v>0.68</v>
+        <v>20.18</v>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
@@ -11145,18 +11145,18 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="n">
-        <v>1393301698</v>
+        <v>1825032378</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -11165,35 +11165,35 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.1401</v>
+        <v>0.2894</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45792.76093159722</v>
       </c>
       <c r="G168" t="n">
-        <v>5.99</v>
+        <v>34.55</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I168" t="n">
-        <v>6.176</v>
+        <v>38.6</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0.84</v>
+        <v>10</v>
       </c>
       <c r="M168" t="n">
-        <v>0.87</v>
+        <v>11.17</v>
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
@@ -11208,18 +11208,18 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>0.03</v>
+        <v>1.17</v>
       </c>
       <c r="U168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="n">
-        <v>1403180427</v>
+        <v>1830410729</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -11228,35 +11228,35 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.4203</v>
+        <v>0.1879</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45796.82476541667</v>
       </c>
       <c r="G169" t="n">
-        <v>5.989</v>
+        <v>33.66</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45825.89271061343</v>
       </c>
       <c r="I169" t="n">
-        <v>6.176</v>
+        <v>38.6</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.52</v>
+        <v>6.32</v>
       </c>
       <c r="M169" t="n">
-        <v>2.6</v>
+        <v>7.25</v>
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
@@ -11271,28 +11271,56 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
       <c r="U169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>1648737122</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>45695.8561993287</v>
+      </c>
+      <c r="G170" t="n">
+        <v>408.33</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>45828.65828179398</v>
+      </c>
+      <c r="I170" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M170" t="n">
+        <v>4.34</v>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
@@ -11300,15 +11328,365 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>1635194724</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>45687.85271719907</v>
+      </c>
+      <c r="G171" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>45831.65008516204</v>
+      </c>
+      <c r="I171" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="M171" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>1635194724</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>45687.85271719907</v>
+      </c>
+      <c r="G172" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>45831.65009055556</v>
+      </c>
+      <c r="I172" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>1727564345</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>45743.76175253472</v>
+      </c>
+      <c r="G173" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>45831.65009055556</v>
+      </c>
+      <c r="I173" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>10</v>
+      </c>
+      <c r="M173" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>1825032062</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>45792.7608031713</v>
+      </c>
+      <c r="G174" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>45831.65009055556</v>
+      </c>
+      <c r="I174" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>10</v>
+      </c>
+      <c r="M174" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>1845431561</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>45805.66210747686</v>
+      </c>
+      <c r="G175" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>45831.65009055556</v>
+      </c>
+      <c r="I175" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M175" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="U170" t="inlineStr"/>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="U176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U176"/>
+  <dimension ref="A1:U191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,11 +609,11 @@
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1342063955</v>
+        <v>1393281432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -622,35 +622,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4139</v>
+        <v>0.632</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45446.37534833333</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G3" t="n">
-        <v>33.545</v>
+        <v>5.981</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45453.66360037037</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I3" t="n">
-        <v>32.605</v>
+        <v>5.967</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>15.15</v>
+        <v>3.78</v>
       </c>
       <c r="M3" t="n">
-        <v>14.42</v>
+        <v>3.77</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -665,18 +665,18 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.73</v>
+        <v>-0.01</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1350877137</v>
+        <v>1393281260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -685,41 +685,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.5612</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45453.90555224537</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G4" t="n">
-        <v>38900</v>
+        <v>5.812</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45453.90972410879</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I4" t="n">
-        <v>38869</v>
+        <v>5.81</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pending(t/p|s/l)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>38874</v>
-      </c>
-      <c r="O4" t="n">
-        <v>38933</v>
-      </c>
-      <c r="P4" t="n">
-        <v>9.73</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -730,22 +728,18 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1357581812</v>
+        <v>1393281260</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -754,35 +748,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.123</v>
+        <v>0.555</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45460.64587106481</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>5.812</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45460.73847521991</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I5" t="n">
-        <v>165.24</v>
+        <v>5.801</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>3.23</v>
       </c>
       <c r="M5" t="n">
-        <v>20.32</v>
+        <v>3.22</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -797,18 +791,18 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1343394966</v>
+        <v>1393281432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -817,35 +811,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.4344</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45446.90410443287</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G6" t="n">
-        <v>13.37</v>
+        <v>5.981</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45460.88503490741</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I6" t="n">
-        <v>12.62</v>
+        <v>5.968</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>13.37</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>12.62</v>
+        <v>2.59</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -860,18 +854,18 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.75</v>
+        <v>-0.01</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1349530190</v>
+        <v>1393281260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -880,35 +874,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G7" t="n">
-        <v>118.42</v>
+        <v>5.812</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45464.64586856482</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I7" t="n">
-        <v>126.75</v>
+        <v>5.814</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14.21</v>
+        <v>5.81</v>
       </c>
       <c r="M7" t="n">
-        <v>15.21</v>
+        <v>5.81</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -923,22 +917,18 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1343379129</v>
+        <v>1393281432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -947,35 +937,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0975</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45446.89366082176</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G8" t="n">
-        <v>205.08</v>
+        <v>5.981</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45464.6458686574</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I8" t="n">
-        <v>211.24</v>
+        <v>5.978</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>5.98</v>
       </c>
       <c r="M8" t="n">
-        <v>20.6</v>
+        <v>5.98</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -990,18 +980,18 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1349530190</v>
+        <v>1393281260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1010,35 +1000,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.051</v>
+        <v>0.4206</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G9" t="n">
-        <v>118.42</v>
+        <v>5.812</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45464.64586949074</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I9" t="n">
-        <v>126.76</v>
+        <v>5.826</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.04</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>6.46</v>
+        <v>2.45</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1053,22 +1043,18 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1357737013</v>
+        <v>1393281432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1077,35 +1063,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0115</v>
+        <v>0.4033</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45460.68557657408</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G10" t="n">
-        <v>1797.13</v>
+        <v>5.981</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45464.65982668981</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I10" t="n">
-        <v>1686.26</v>
+        <v>5.98</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>20.67</v>
+        <v>2.41</v>
       </c>
       <c r="M10" t="n">
-        <v>19.39</v>
+        <v>2.41</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1120,18 +1106,18 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1362492338</v>
+        <v>1393281432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1140,35 +1126,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2806</v>
+        <v>0.4201</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45464.66150739583</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G11" t="n">
-        <v>71.61</v>
+        <v>5.981</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45464.66725368056</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I11" t="n">
-        <v>70.95999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>20.09</v>
+        <v>2.51</v>
       </c>
       <c r="M11" t="n">
-        <v>19.91</v>
+        <v>2.51</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1183,18 +1169,18 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1342641165</v>
+        <v>1393281432</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,35 +1189,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1322</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45446.64586891203</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G12" t="n">
-        <v>155.59</v>
+        <v>5.981</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45478.65186430555</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I12" t="n">
-        <v>183.6</v>
+        <v>6.186</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>20.57</v>
+        <v>5.98</v>
       </c>
       <c r="M12" t="n">
-        <v>24.27</v>
+        <v>6.19</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1246,18 +1232,18 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>0.21</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1347626622</v>
+        <v>1393281260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1266,35 +1252,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1488</v>
+        <v>1.4632</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G13" t="n">
-        <v>67.2</v>
+        <v>5.812</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I13" t="n">
-        <v>69.65000000000001</v>
+        <v>6.02</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="M13" t="n">
-        <v>10.36</v>
+        <v>8.81</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1309,18 +1295,18 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1362562387</v>
+        <v>1393287040</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1329,35 +1315,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.202</v>
+        <v>0.2503</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G14" t="n">
-        <v>100.78</v>
+        <v>5.811</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I14" t="n">
-        <v>100.83</v>
+        <v>6.02</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>20.36</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>20.37</v>
+        <v>1.51</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1372,18 +1358,18 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1362488938</v>
+        <v>1403180431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1392,35 +1378,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2742</v>
+        <v>0.2773</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G15" t="n">
-        <v>72.93000000000001</v>
+        <v>5.84</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I15" t="n">
-        <v>72.29000000000001</v>
+        <v>6.02</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>19.82</v>
+        <v>1.67</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1435,18 +1421,18 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.18</v>
+        <v>0.05</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1375967973</v>
+        <v>1403180445</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1455,35 +1441,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.109</v>
+        <v>0.0092</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>5.836</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I16" t="n">
-        <v>186.5</v>
+        <v>6.02</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>19.95</v>
+        <v>0.05</v>
       </c>
       <c r="M16" t="n">
-        <v>20.33</v>
+        <v>0.06</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1498,18 +1484,18 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1375856858</v>
+        <v>1393735509</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1504,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1052</v>
+        <v>0.0366</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G17" t="n">
-        <v>188.48</v>
+        <v>67.37</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I17" t="n">
-        <v>189.21</v>
+        <v>71.16</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>19.83</v>
+        <v>2.47</v>
       </c>
       <c r="M17" t="n">
-        <v>19.9</v>
+        <v>2.6</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1547,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1357595824</v>
+        <v>1395218355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1581,35 +1567,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.074</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G18" t="n">
-        <v>22.89</v>
+        <v>67.13</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I18" t="n">
-        <v>18.62</v>
+        <v>71.16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>22.89</v>
+        <v>4.97</v>
       </c>
       <c r="M18" t="n">
-        <v>18.62</v>
+        <v>5.27</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1610,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.27</v>
+        <v>0.3</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1375967973</v>
+        <v>1403166009</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1630,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0014</v>
+        <v>0.0362</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>68.05</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I19" t="n">
-        <v>182.97</v>
+        <v>71.16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.26</v>
+        <v>2.46</v>
       </c>
       <c r="M19" t="n">
-        <v>0.26</v>
+        <v>2.58</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1687,18 +1673,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1377834040</v>
+        <v>1403177543</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,35 +1693,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1077</v>
+        <v>0.0368</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G20" t="n">
-        <v>186.7</v>
+        <v>68.045</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I20" t="n">
-        <v>182.97</v>
+        <v>71.16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>20.11</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.71</v>
+        <v>2.62</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1736,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.39</v>
+        <v>0.12</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1377407433</v>
+        <v>1403180429</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1756,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0771</v>
+        <v>0.0733</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G21" t="n">
-        <v>129.48</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I21" t="n">
-        <v>130.75</v>
+        <v>71.16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.98</v>
+        <v>4.99</v>
       </c>
       <c r="M21" t="n">
-        <v>10.08</v>
+        <v>5.22</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1799,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1377407433</v>
+        <v>1403180445</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1819,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0001</v>
+        <v>0.9908</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G22" t="n">
-        <v>129.48</v>
+        <v>5.836</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I22" t="n">
-        <v>131.24</v>
+        <v>6.027</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>5.78</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01</v>
+        <v>5.97</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1862,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1377834040</v>
+        <v>1393281432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,35 +1882,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0011</v>
+        <v>0.1102</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G23" t="n">
-        <v>186.7</v>
+        <v>5.981</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I23" t="n">
-        <v>184.46</v>
+        <v>6.176</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1925,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1362491459</v>
+        <v>1393301698</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,35 +1945,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.228</v>
+        <v>0.1401</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G24" t="n">
-        <v>88.67</v>
+        <v>5.99</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I24" t="n">
-        <v>87.81</v>
+        <v>6.176</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.22</v>
+        <v>0.84</v>
       </c>
       <c r="M24" t="n">
-        <v>20.02</v>
+        <v>0.87</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +1988,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2</v>
+        <v>0.03</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1362491459</v>
+        <v>1403180427</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2008,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0001</v>
+        <v>0.4203</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G25" t="n">
-        <v>88.67</v>
+        <v>5.989</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I25" t="n">
-        <v>87.81999999999999</v>
+        <v>6.176</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.01</v>
+        <v>2.52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01</v>
+        <v>2.6</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2051,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1375856858</v>
+        <v>1342063955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,19 +2071,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0026</v>
+        <v>0.4139</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45446.37534833333</v>
       </c>
       <c r="G26" t="n">
-        <v>188.48</v>
+        <v>33.545</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45453.66360037037</v>
       </c>
       <c r="I26" t="n">
-        <v>190.3</v>
+        <v>32.605</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2110,10 +2096,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>15.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0.49</v>
+        <v>14.42</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2128,18 +2114,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1377584836</v>
+        <v>1350877137</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>US30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,19 +2134,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4828</v>
+        <v>0.01</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45453.90555224537</v>
       </c>
       <c r="G27" t="n">
-        <v>41.87</v>
+        <v>38900</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45453.90972410879</v>
       </c>
       <c r="I27" t="n">
-        <v>42.35</v>
+        <v>38869</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2169,18 +2155,20 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="M27" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>pending(t/p|s/l)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>38874</v>
+      </c>
+      <c r="O27" t="n">
+        <v>38933</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9.73</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -2191,18 +2179,22 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="U27" t="inlineStr"/>
+        <v>-1.55</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1377584836</v>
+        <v>1357581812</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,19 +2203,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0013</v>
+        <v>0.123</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45460.64587106481</v>
       </c>
       <c r="G28" t="n">
-        <v>41.87</v>
+        <v>1.65</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45460.73847521991</v>
       </c>
       <c r="I28" t="n">
-        <v>42.35</v>
+        <v>165.24</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2232,14 +2224,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>20.32</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2246,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1350885655</v>
+        <v>1343394966</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,19 +2266,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0234</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45446.90410443287</v>
       </c>
       <c r="G29" t="n">
-        <v>427.17</v>
+        <v>13.37</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45460.88503490741</v>
       </c>
       <c r="I29" t="n">
-        <v>458.18</v>
+        <v>12.62</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2299,10 +2291,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>13.37</v>
       </c>
       <c r="M29" t="n">
-        <v>10.72</v>
+        <v>12.62</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2309,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1414374074</v>
+        <v>1349530190</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,23 +2329,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0481</v>
+        <v>0.12</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G30" t="n">
-        <v>311.85</v>
+        <v>118.42</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45464.64586856482</v>
       </c>
       <c r="I30" t="n">
-        <v>308</v>
+        <v>126.75</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2362,10 +2354,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>14.21</v>
       </c>
       <c r="M30" t="n">
-        <v>14.81</v>
+        <v>15.21</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2372,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1414372067</v>
+        <v>1343379129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,19 +2396,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0575</v>
+        <v>0.0975</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45446.89366082176</v>
       </c>
       <c r="G31" t="n">
-        <v>260.8</v>
+        <v>205.08</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45464.6458686574</v>
       </c>
       <c r="I31" t="n">
-        <v>290.19</v>
+        <v>211.24</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2421,14 +2417,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M31" t="n">
-        <v>16.69</v>
+        <v>20.6</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2439,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>0.6</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1377764546</v>
+        <v>1349530190</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,23 +2459,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G32" t="n">
-        <v>244.47</v>
+        <v>118.42</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45464.64586949074</v>
       </c>
       <c r="I32" t="n">
-        <v>196.86</v>
+        <v>126.76</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2488,10 +2484,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>19.02</v>
+        <v>6.04</v>
       </c>
       <c r="M32" t="n">
-        <v>15.32</v>
+        <v>6.46</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2502,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>0.42</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1377764546</v>
+        <v>1357737013</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,19 +2526,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0051</v>
+        <v>0.0115</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45460.68557657408</v>
       </c>
       <c r="G33" t="n">
-        <v>244.47</v>
+        <v>1797.13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45464.65982668981</v>
       </c>
       <c r="I33" t="n">
-        <v>196.91</v>
+        <v>1686.26</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>20.67</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>19.39</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.25</v>
+        <v>-1.28</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1380259753</v>
+        <v>1362492338</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.131</v>
+        <v>0.2806</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45464.66150739583</v>
       </c>
       <c r="G34" t="n">
-        <v>190.71</v>
+        <v>71.61</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45464.66725368056</v>
       </c>
       <c r="I34" t="n">
-        <v>161.87</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>24.98</v>
+        <v>20.09</v>
       </c>
       <c r="M34" t="n">
-        <v>21.2</v>
+        <v>19.91</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,39 +2632,39 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-3.78</v>
+        <v>-0.18</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1509051251</v>
+        <v>1342641165</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.1322</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45446.64586891203</v>
       </c>
       <c r="G35" t="n">
-        <v>19.8731</v>
+        <v>155.59</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45478.65186430555</v>
       </c>
       <c r="I35" t="n">
-        <v>19.8835</v>
+        <v>183.6</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2676,13 +2676,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="M35" t="n">
+        <v>24.27</v>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2693,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1.05</v>
+        <v>3.7</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1508055372</v>
+        <v>1347626622</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2713,19 +2715,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.02</v>
+        <v>0.1488</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G36" t="n">
-        <v>19.8369</v>
+        <v>67.2</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I36" t="n">
-        <v>19.8761</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2737,13 +2739,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.36</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -2754,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.94</v>
+        <v>0.36</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1512925323</v>
+        <v>1362562387</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2774,19 +2778,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>0.202</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G37" t="n">
-        <v>20.0663</v>
+        <v>100.78</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I37" t="n">
-        <v>20.1405</v>
+        <v>100.83</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2798,56 +2802,58 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20.37</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>5</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.68</v>
+        <v>0.01</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1514707570</v>
+        <v>1362488938</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01</v>
+        <v>0.2742</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45595.88186449074</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G38" t="n">
-        <v>20.1597</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45595.94583810185</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I38" t="n">
-        <v>20.1911</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2859,17 +2865,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="O38" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>5</v>
-      </c>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2880,43 +2884,39 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.18</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1516787001</v>
+        <v>1375967973</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01</v>
+        <v>0.109</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G39" t="n">
-        <v>2748.04</v>
+        <v>183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I39" t="n">
-        <v>2747.79</v>
+        <v>186.5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2928,13 +2928,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20.33</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -2945,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1516790032</v>
+        <v>1375856858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2965,19 +2967,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.01</v>
+        <v>0.1052</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45597.13541888889</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G40" t="n">
-        <v>2747.23</v>
+        <v>188.48</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45597.13874358797</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I40" t="n">
-        <v>2747.25</v>
+        <v>189.21</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2989,13 +2991,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="M40" t="n">
+        <v>19.9</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -3006,39 +3010,39 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1516793905</v>
+        <v>1357595824</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45597.14024802083</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G41" t="n">
-        <v>2747.11</v>
+        <v>22.89</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45597.14548700232</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I41" t="n">
-        <v>2747.77</v>
+        <v>18.62</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3050,13 +3054,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="M41" t="n">
+        <v>18.62</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -3067,18 +3073,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.66</v>
+        <v>-4.27</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1516796610</v>
+        <v>1375967973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3087,19 +3093,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>0.0014</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45597.14556364583</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G42" t="n">
-        <v>2748.12</v>
+        <v>183</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45597.14936810185</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I42" t="n">
-        <v>2746.29</v>
+        <v>182.97</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3111,13 +3117,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.26</v>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -3128,39 +3136,39 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1516798655</v>
+        <v>1377834040</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>0.1077</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45597.14949375</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G43" t="n">
-        <v>2746.13</v>
+        <v>186.7</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45597.15075293981</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I43" t="n">
-        <v>2747.4</v>
+        <v>182.97</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3172,13 +3180,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="M43" t="n">
+        <v>19.71</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>13.73</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -3189,18 +3199,18 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.27</v>
+        <v>-0.39</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1516805560</v>
+        <v>1377407433</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3209,19 +3219,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>0.0771</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45597.16385188657</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G44" t="n">
-        <v>2748.03</v>
+        <v>129.48</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45597.16756914352</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I44" t="n">
-        <v>2748.36</v>
+        <v>130.75</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3233,13 +3243,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10.08</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -3250,18 +3262,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1516814771</v>
+        <v>1377407433</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3270,37 +3282,39 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>45481.65801625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>129.48</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45482.91500505787</v>
+      </c>
+      <c r="I45" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>0.01</v>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>45597.18416002315</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2749.48</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>45597.18971934028</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2749.54</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0.01</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>13.75</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -3311,18 +3325,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1516838270</v>
+        <v>1377834040</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3331,19 +3345,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.01</v>
+        <v>0.0011</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45597.23811159722</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G46" t="n">
-        <v>2751.84</v>
+        <v>186.7</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45597.56254815972</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I46" t="n">
-        <v>2756.23</v>
+        <v>184.46</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3355,15 +3369,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>2754.07</v>
-      </c>
-      <c r="P46" t="n">
-        <v>13.76</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -3374,22 +3388,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1393281432</v>
+        <v>1362491459</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3398,35 +3408,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.632</v>
+        <v>0.228</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G47" t="n">
-        <v>5.981</v>
+        <v>88.67</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I47" t="n">
-        <v>5.967</v>
+        <v>87.81</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.78</v>
+        <v>20.22</v>
       </c>
       <c r="M47" t="n">
-        <v>3.77</v>
+        <v>20.02</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3441,18 +3451,18 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1393281260</v>
+        <v>1362491459</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3461,35 +3471,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5612</v>
+        <v>0.0001</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G48" t="n">
-        <v>5.812</v>
+        <v>88.67</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45483.77897271991</v>
       </c>
       <c r="I48" t="n">
-        <v>5.81</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.26</v>
+        <v>0.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.26</v>
+        <v>0.01</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -3511,11 +3521,11 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1393281260</v>
+        <v>1375856858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3524,35 +3534,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.555</v>
+        <v>0.0026</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G49" t="n">
-        <v>5.812</v>
+        <v>188.48</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I49" t="n">
-        <v>5.801</v>
+        <v>190.3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.23</v>
+        <v>0.49</v>
       </c>
       <c r="M49" t="n">
-        <v>3.22</v>
+        <v>0.49</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3567,18 +3577,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1515520253</v>
+        <v>1377584836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3587,19 +3597,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0.4828</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G50" t="n">
-        <v>20.0901</v>
+        <v>41.87</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I50" t="n">
-        <v>20.0775</v>
+        <v>42.35</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3611,35 +3621,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="M50" t="n">
+        <v>20.45</v>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>5</v>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.63</v>
+        <v>0.23</v>
       </c>
       <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1393281432</v>
+        <v>1377584836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3648,35 +3660,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.4344</v>
+        <v>0.0013</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G51" t="n">
-        <v>5.981</v>
+        <v>41.87</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I51" t="n">
-        <v>5.968</v>
+        <v>42.35</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.6</v>
+        <v>0.05</v>
       </c>
       <c r="M51" t="n">
-        <v>2.59</v>
+        <v>0.06</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3691,18 +3703,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1393281260</v>
+        <v>1350885655</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3711,35 +3723,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0.0234</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G52" t="n">
-        <v>5.812</v>
+        <v>427.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I52" t="n">
-        <v>5.814</v>
+        <v>458.18</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>5.81</v>
+        <v>10</v>
       </c>
       <c r="M52" t="n">
-        <v>5.81</v>
+        <v>10.72</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -3754,18 +3766,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1393281432</v>
+        <v>1414374074</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3774,35 +3786,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0.0481</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G53" t="n">
-        <v>5.981</v>
+        <v>311.85</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I53" t="n">
-        <v>5.978</v>
+        <v>308</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5.98</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>5.98</v>
+        <v>14.81</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -3817,18 +3829,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1393281260</v>
+        <v>1414372067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3837,35 +3849,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4206</v>
+        <v>0.0575</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G54" t="n">
-        <v>5.812</v>
+        <v>260.8</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I54" t="n">
-        <v>5.826</v>
+        <v>290.19</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L54" t="n">
-        <v>2.44</v>
+        <v>15</v>
       </c>
       <c r="M54" t="n">
-        <v>2.45</v>
+        <v>16.69</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3880,18 +3892,18 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.01</v>
+        <v>1.69</v>
       </c>
       <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1393281432</v>
+        <v>1377764546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3900,35 +3912,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.4033</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G55" t="n">
-        <v>5.981</v>
+        <v>244.47</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I55" t="n">
-        <v>5.98</v>
+        <v>196.86</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.41</v>
+        <v>19.02</v>
       </c>
       <c r="M55" t="n">
-        <v>2.41</v>
+        <v>15.32</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -3943,18 +3955,18 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1517450167</v>
+        <v>1377764546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3963,19 +3975,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>0.0051</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45597.59638905092</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G56" t="n">
-        <v>19.9771</v>
+        <v>244.47</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45597.73077270833</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I56" t="n">
-        <v>20.0775</v>
+        <v>196.91</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3987,13 +3999,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="n">
-        <v>5</v>
-      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
@@ -4004,18 +4018,18 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>-0.25</v>
       </c>
       <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1393281432</v>
+        <v>1380259753</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4024,35 +4038,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.4201</v>
+        <v>0.131</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G57" t="n">
-        <v>5.981</v>
+        <v>190.71</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I57" t="n">
-        <v>5.98</v>
+        <v>161.87</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.51</v>
+        <v>24.98</v>
       </c>
       <c r="M57" t="n">
-        <v>2.51</v>
+        <v>21.2</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -4067,14 +4081,14 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1517930572</v>
+        <v>1509051251</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4087,19 +4101,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G58" t="n">
-        <v>20.078</v>
+        <v>19.8731</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I58" t="n">
-        <v>20.082</v>
+        <v>19.8835</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4116,7 +4130,7 @@
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4128,18 +4142,18 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.2</v>
+        <v>-1.05</v>
       </c>
       <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1393281432</v>
+        <v>1508055372</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4148,39 +4162,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G59" t="n">
-        <v>5.981</v>
+        <v>19.8369</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I59" t="n">
-        <v>6.186</v>
+        <v>19.8761</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.19</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
@@ -4191,18 +4203,18 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.21</v>
+        <v>3.94</v>
       </c>
       <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1517879253</v>
+        <v>1512925323</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4214,16 +4226,16 @@
         <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G60" t="n">
-        <v>20.08</v>
+        <v>20.0663</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I60" t="n">
-        <v>19.63</v>
+        <v>20.1405</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4232,85 +4244,81 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop-out</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
-        <v>20.92</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>12.05</v>
+        <v>5</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.63</v>
+        <v>-0.22</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+        <v>3.68</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1393281260</v>
+        <v>1514707570</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.4632</v>
+        <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G61" t="n">
-        <v>5.812</v>
+        <v>20.1597</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I61" t="n">
-        <v>6.02</v>
+        <v>20.1911</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M61" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O61" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P61" t="n">
+        <v>5</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
@@ -4321,59 +4329,61 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1393287040</v>
+        <v>1516787001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2503</v>
+        <v>0.01</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G62" t="n">
-        <v>5.811</v>
+        <v>2748.04</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I62" t="n">
-        <v>6.02</v>
+        <v>2747.79</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1.51</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4384,18 +4394,18 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1403180431</v>
+        <v>1516790032</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4404,39 +4414,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2773</v>
+        <v>0.01</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45597.13541888889</v>
       </c>
       <c r="G63" t="n">
-        <v>5.84</v>
+        <v>2747.23</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45597.13874358797</v>
       </c>
       <c r="I63" t="n">
-        <v>6.02</v>
+        <v>2747.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1.67</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
@@ -4447,59 +4455,57 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1403180445</v>
+        <v>1516793905</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0092</v>
+        <v>0.01</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45597.14024802083</v>
       </c>
       <c r="G64" t="n">
-        <v>5.836</v>
+        <v>2747.11</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45597.14548700232</v>
       </c>
       <c r="I64" t="n">
-        <v>6.02</v>
+        <v>2747.77</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.06</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -4510,18 +4516,18 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0.01</v>
+        <v>-0.66</v>
       </c>
       <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1379227659</v>
+        <v>1516796610</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4530,19 +4536,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45597.14556364583</v>
       </c>
       <c r="G65" t="n">
-        <v>131.38</v>
+        <v>2748.12</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45597.14936810185</v>
       </c>
       <c r="I65" t="n">
-        <v>148.18</v>
+        <v>2746.29</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4554,15 +4560,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M65" t="n">
-        <v>22.54</v>
-      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
@@ -4573,59 +4577,57 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.56</v>
+        <v>-1.83</v>
       </c>
       <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1393735509</v>
+        <v>1516798655</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0366</v>
+        <v>0.01</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45597.14949375</v>
       </c>
       <c r="G66" t="n">
-        <v>67.37</v>
+        <v>2746.13</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.15075293981</v>
       </c>
       <c r="I66" t="n">
-        <v>71.16</v>
+        <v>2747.4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M66" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>13.73</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -4636,18 +4638,18 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0.13</v>
+        <v>-1.27</v>
       </c>
       <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1395218355</v>
+        <v>1516805560</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4656,39 +4658,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.074</v>
+        <v>0.01</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45597.16385188657</v>
       </c>
       <c r="G67" t="n">
-        <v>67.13</v>
+        <v>2748.03</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.16756914352</v>
       </c>
       <c r="I67" t="n">
-        <v>71.16</v>
+        <v>2748.36</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M67" t="n">
-        <v>5.27</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
@@ -4699,18 +4699,18 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1403166009</v>
+        <v>1516814771</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4719,39 +4719,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0362</v>
+        <v>0.01</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45597.18416002315</v>
       </c>
       <c r="G68" t="n">
-        <v>68.05</v>
+        <v>2749.48</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.18971934028</v>
       </c>
       <c r="I68" t="n">
-        <v>71.16</v>
+        <v>2749.54</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M68" t="n">
-        <v>2.58</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>13.75</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -4762,18 +4760,18 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1403177543</v>
+        <v>1516838270</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4782,39 +4780,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.0368</v>
+        <v>0.01</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45597.23811159722</v>
       </c>
       <c r="G69" t="n">
-        <v>68.045</v>
+        <v>2751.84</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.56254815972</v>
       </c>
       <c r="I69" t="n">
-        <v>71.16</v>
+        <v>2756.23</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M69" t="n">
-        <v>2.62</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>2754.07</v>
+      </c>
+      <c r="P69" t="n">
+        <v>13.76</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4825,18 +4823,22 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U69" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1403180429</v>
+        <v>1515520253</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4845,61 +4847,59 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0733</v>
+        <v>0.01</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G70" t="n">
-        <v>68.01000000000001</v>
+        <v>20.0901</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I70" t="n">
-        <v>71.16</v>
+        <v>20.0775</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M70" t="n">
-        <v>5.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0.23</v>
+        <v>-0.63</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1403180445</v>
+        <v>1517450167</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4908,39 +4908,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9908</v>
+        <v>0.01</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G71" t="n">
-        <v>5.836</v>
+        <v>19.9771</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I71" t="n">
-        <v>6.027</v>
+        <v>20.0775</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M71" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>5</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
@@ -4951,14 +4949,14 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1527051962</v>
+        <v>1517930572</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4967,23 +4965,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>0.01</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45604.13145401621</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G72" t="n">
-        <v>19.8302</v>
+        <v>20.078</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45604.56280116898</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I72" t="n">
-        <v>19.9681</v>
+        <v>20.082</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4997,12 +4995,8 @@
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="O72" t="n">
-        <v>20.12</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>5</v>
       </c>
@@ -5016,22 +5010,18 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.2</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1393281432</v>
+        <v>1517879253</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5040,61 +5030,65 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.1102</v>
+        <v>0.01</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G73" t="n">
-        <v>5.981</v>
+        <v>20.08</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I73" t="n">
-        <v>6.176</v>
+        <v>19.63</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.68</v>
-      </c>
+          <t>stop-out</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="P73" t="n">
+        <v>12.05</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U73" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1527744522</v>
+        <v>1379227659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5103,19 +5097,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.01</v>
+        <v>0.1521</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45604.55607921296</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G74" t="n">
-        <v>19.9784</v>
+        <v>131.38</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45604.57083508102</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I74" t="n">
-        <v>19.9497</v>
+        <v>148.18</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5127,17 +5121,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="O74" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P74" t="n">
-        <v>5</v>
-      </c>
+      <c r="L74" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M74" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
@@ -5148,22 +5140,18 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>2.56</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1393301698</v>
+        <v>1527051962</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5172,39 +5160,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.1401</v>
+        <v>0.01</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45604.13145401621</v>
       </c>
       <c r="G75" t="n">
-        <v>5.99</v>
+        <v>19.8302</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45604.56280116898</v>
       </c>
       <c r="I75" t="n">
-        <v>6.176</v>
+        <v>19.9681</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="O75" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P75" t="n">
+        <v>5</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
@@ -5215,18 +5205,22 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U75" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1403180427</v>
+        <v>1527744522</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5235,39 +5229,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.4203</v>
+        <v>0.01</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45604.55607921296</v>
       </c>
       <c r="G76" t="n">
-        <v>5.989</v>
+        <v>19.9784</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45604.57083508102</v>
       </c>
       <c r="I76" t="n">
-        <v>6.176</v>
+        <v>19.9497</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="O76" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P76" t="n">
+        <v>5</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
@@ -5278,9 +5274,13 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U76" t="inlineStr"/>
+        <v>-1.44</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -11655,22 +11655,50 @@
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>1582737192</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>45645.90143914352</v>
+      </c>
+      <c r="G176" t="n">
+        <v>524.4299999999999</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>45833.64891153935</v>
+      </c>
+      <c r="I176" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>xStation Mobile Android</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
@@ -11678,15 +11706,932 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>1599435465</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>45663.7311559375</v>
+      </c>
+      <c r="G177" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>45833.64891153935</v>
+      </c>
+      <c r="I177" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="M177" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="n">
+        <v>1606697510</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>45667.68664710648</v>
+      </c>
+      <c r="G178" t="n">
+        <v>507.68</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>45833.64891153935</v>
+      </c>
+      <c r="I178" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M178" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>1885700231</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>45828.65147913194</v>
+      </c>
+      <c r="G179" t="n">
+        <v>534.86</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>45833.64891153935</v>
+      </c>
+      <c r="I179" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M179" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="n">
+        <v>1680991980</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>45716.85566212963</v>
+      </c>
+      <c r="G180" t="n">
+        <v>178.67</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>45834.65445795139</v>
+      </c>
+      <c r="I180" t="n">
+        <v>223.73</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="M180" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>1378901781</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BOTZ.L</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>45482.71294290509</v>
+      </c>
+      <c r="G181" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>45841.69192508102</v>
+      </c>
+      <c r="I181" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="M181" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="U181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="n">
+        <v>1533882988</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BOTZ.L</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>45609.60769533565</v>
+      </c>
+      <c r="G182" t="n">
+        <v>21.905</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>45841.69192508102</v>
+      </c>
+      <c r="I182" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="M182" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="U182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="n">
+        <v>1583696868</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BOTZ.L</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>45646.60053962963</v>
+      </c>
+      <c r="G183" t="n">
+        <v>20.645</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>45841.69192508102</v>
+      </c>
+      <c r="I183" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="M183" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="U183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="n">
+        <v>1381417257</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BATT.AS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>45484.67877002315</v>
+      </c>
+      <c r="G184" t="n">
+        <v>16.374</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>45841.69225577547</v>
+      </c>
+      <c r="I184" t="n">
+        <v>16.116</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M184" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="n">
+        <v>1594315903</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BATT.AS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>45659.42644487268</v>
+      </c>
+      <c r="G185" t="n">
+        <v>16.425</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>45841.69225577547</v>
+      </c>
+      <c r="I185" t="n">
+        <v>16.116</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="M185" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="n">
+        <v>1680991980</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>45716.85566212963</v>
+      </c>
+      <c r="G186" t="n">
+        <v>178.67</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>45853.66093041666</v>
+      </c>
+      <c r="I186" t="n">
+        <v>234.22</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="M186" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>1701100481</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>45727.8721437037</v>
+      </c>
+      <c r="G187" t="n">
+        <v>171.67</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>45853.66093041666</v>
+      </c>
+      <c r="I187" t="n">
+        <v>234.22</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="n">
+        <v>1701100481</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>45727.8721437037</v>
+      </c>
+      <c r="G188" t="n">
+        <v>171.67</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>45853.66136265046</v>
+      </c>
+      <c r="I188" t="n">
+        <v>234.42</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M188" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="n">
+        <v>1701100481</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>45727.8721437037</v>
+      </c>
+      <c r="G189" t="n">
+        <v>171.67</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>45855.64709616898</v>
+      </c>
+      <c r="I189" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="M189" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="U189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="n">
+        <v>1729617775</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>45744.71339717592</v>
+      </c>
+      <c r="G190" t="n">
+        <v>165.35</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>45855.64709616898</v>
+      </c>
+      <c r="I190" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M190" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S176" t="n">
-        <v>0</v>
-      </c>
-      <c r="T176" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="U176" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>76.51000000000001</v>
+      </c>
+      <c r="U191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U219"/>
+  <dimension ref="A1:U231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3196,11 +3196,11 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1516805560</v>
+        <v>1393281432</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3209,37 +3209,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.01</v>
+        <v>0.632</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45597.16385188657</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G44" t="n">
-        <v>2748.03</v>
+        <v>5.981</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45597.16756914352</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I44" t="n">
-        <v>2748.36</v>
+        <v>5.967</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.77</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -3250,14 +3252,14 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1516814771</v>
+        <v>1516805560</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3273,16 +3275,16 @@
         <v>0.01</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45597.18416002315</v>
+        <v>45597.16385188657</v>
       </c>
       <c r="G45" t="n">
-        <v>2749.48</v>
+        <v>2748.03</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45597.18971934028</v>
+        <v>45597.16756914352</v>
       </c>
       <c r="I45" t="n">
-        <v>2749.54</v>
+        <v>2748.36</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3299,7 +3301,7 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>13.75</v>
+        <v>13.74</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3311,18 +3313,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1516838270</v>
+        <v>1393281260</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3331,39 +3333,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.01</v>
+        <v>0.5612</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45597.23811159722</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G46" t="n">
-        <v>2751.84</v>
+        <v>5.812</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45597.56254815972</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I46" t="n">
-        <v>2756.23</v>
+        <v>5.81</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.26</v>
+      </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
-        <v>2754.07</v>
-      </c>
-      <c r="P46" t="n">
-        <v>13.76</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -3374,22 +3376,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1515520253</v>
+        <v>1516814771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3401,16 +3399,16 @@
         <v>0.01</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45597.18416002315</v>
       </c>
       <c r="G47" t="n">
-        <v>20.0901</v>
+        <v>2749.48</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45597.18971934028</v>
       </c>
       <c r="I47" t="n">
-        <v>20.0775</v>
+        <v>2749.54</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3427,30 +3425,30 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>13.75</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.63</v>
+        <v>0.06</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1517450167</v>
+        <v>1393281260</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3459,37 +3457,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>0.555</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45597.59638905092</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G48" t="n">
-        <v>19.9771</v>
+        <v>5.812</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45597.73077270833</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I48" t="n">
-        <v>20.0775</v>
+        <v>5.801</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.22</v>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>5</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3500,57 +3500,59 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>-0.01</v>
       </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1517930572</v>
+        <v>1393281432</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>0.4344</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G49" t="n">
-        <v>20.078</v>
+        <v>5.981</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I49" t="n">
-        <v>20.082</v>
+        <v>5.968</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.59</v>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>5</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
@@ -3561,18 +3563,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1517879253</v>
+        <v>1393281260</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3581,65 +3583,61 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G50" t="n">
-        <v>20.08</v>
+        <v>5.812</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I50" t="n">
-        <v>19.63</v>
+        <v>5.814</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop-out</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5.81</v>
+      </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="P50" t="n">
-        <v>12.05</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1379227659</v>
+        <v>1393281432</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3648,35 +3646,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1521</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G51" t="n">
-        <v>131.38</v>
+        <v>5.981</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I51" t="n">
-        <v>148.18</v>
+        <v>5.978</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>19.98</v>
+        <v>5.98</v>
       </c>
       <c r="M51" t="n">
-        <v>22.54</v>
+        <v>5.98</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3691,18 +3689,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1527051962</v>
+        <v>1516838270</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3714,16 +3712,16 @@
         <v>0.01</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45604.13145401621</v>
+        <v>45597.23811159722</v>
       </c>
       <c r="G52" t="n">
-        <v>19.8302</v>
+        <v>2751.84</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45604.56280116898</v>
+        <v>45597.56254815972</v>
       </c>
       <c r="I52" t="n">
-        <v>19.9681</v>
+        <v>2756.23</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3737,14 +3735,12 @@
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>19.97</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>20.12</v>
+        <v>2754.07</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>13.76</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -3756,22 +3752,22 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>6.9</v>
+        <v>4.39</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>[S/L]</t>
+          <t>[T/P]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1527744522</v>
+        <v>1393281260</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3780,67 +3776,61 @@
         </is>
       </c>
       <c r="E53" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>45496.37564016203</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.812</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>45504.63556305556</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5.826</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
         <v>0.01</v>
       </c>
-      <c r="F53" s="2" t="n">
-        <v>45604.55607921296</v>
-      </c>
-      <c r="G53" t="n">
-        <v>19.9784</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>45604.57083508102</v>
-      </c>
-      <c r="I53" t="n">
-        <v>19.9497</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="O53" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P53" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1528126100</v>
+        <v>1393281432</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,23 +3839,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>0.4033</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45604.66918148148</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G54" t="n">
-        <v>20.0428</v>
+        <v>5.981</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45604.71914307871</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I54" t="n">
-        <v>20.0988</v>
+        <v>5.98</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3873,17 +3863,15 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>20.0988</v>
-      </c>
-      <c r="O54" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P54" t="n">
-        <v>5</v>
-      </c>
+      <c r="L54" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
@@ -3894,18 +3882,14 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1528325630</v>
+        <v>1515520253</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3914,27 +3898,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>0.01</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45604.72032700232</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G55" t="n">
-        <v>20.0912</v>
+        <v>20.0901</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45604.72263849537</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I55" t="n">
-        <v>20.1101</v>
+        <v>20.0775</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3944,12 +3928,8 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="O55" t="n">
-        <v>20.0219</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>5</v>
       </c>
@@ -3957,28 +3937,24 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.63</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1531224336</v>
+        <v>1393281432</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3987,41 +3963,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>0.4201</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45608.2460031713</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G56" t="n">
-        <v>153.589</v>
+        <v>5.981</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45608.25044886574</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I56" t="n">
-        <v>153.468</v>
+        <v>5.98</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>153.47</v>
-      </c>
-      <c r="O56" t="n">
-        <v>153.619</v>
-      </c>
-      <c r="P56" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
@@ -4032,63 +4006,59 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1531227124</v>
+        <v>1393281432</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45608.25015417824</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G57" t="n">
-        <v>153.483</v>
+        <v>5.981</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45608.25207638889</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I57" t="n">
-        <v>153.458</v>
+        <v>6.186</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>153.458</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>5</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
@@ -4099,43 +4069,39 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1531230129</v>
+        <v>1517450167</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>0.01</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45608.2544440162</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G58" t="n">
-        <v>153.445</v>
+        <v>19.9771</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45608.25666561343</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I58" t="n">
-        <v>153.502</v>
+        <v>20.0775</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4149,12 +4115,8 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>153.502</v>
-      </c>
-      <c r="O58" t="n">
-        <v>153.395</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
         <v>5</v>
       </c>
@@ -4168,22 +4130,18 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1531192665</v>
+        <v>1393281260</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4192,41 +4150,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>1.4632</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45608.19828637732</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G59" t="n">
-        <v>20.412</v>
+        <v>5.812</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45608.34380275463</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I59" t="n">
-        <v>20.4421</v>
+        <v>6.02</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>20.4429</v>
-      </c>
-      <c r="O59" t="n">
-        <v>20.5326</v>
-      </c>
-      <c r="P59" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
@@ -4237,61 +4193,59 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1531349564</v>
+        <v>1393287040</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.2503</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45608.34449649305</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G60" t="n">
-        <v>20.4344</v>
+        <v>5.811</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45608.34490908564</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I60" t="n">
-        <v>20.4507</v>
+        <v>6.02</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.51</v>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>5</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
@@ -4302,14 +4256,14 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>-0.8</v>
+        <v>0.06</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1531351286</v>
+        <v>1517930572</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4318,23 +4272,23 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45608.34571399305</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G61" t="n">
-        <v>20.4554</v>
+        <v>20.078</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45608.35180353009</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I61" t="n">
-        <v>20.45</v>
+        <v>20.082</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4348,12 +4302,8 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>20.4381</v>
-      </c>
-      <c r="O61" t="n">
-        <v>20.47</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
         <v>5</v>
       </c>
@@ -4367,18 +4317,18 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1531358421</v>
+        <v>1403180431</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4387,41 +4337,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.2773</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45608.3501140162</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G62" t="n">
-        <v>20.4503</v>
+        <v>5.84</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45608.35479755787</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I62" t="n">
-        <v>20.4382</v>
+        <v>6.02</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>20.4388</v>
-      </c>
-      <c r="O62" t="n">
-        <v>20.4767</v>
-      </c>
-      <c r="P62" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4432,22 +4380,18 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1532703059</v>
+        <v>1403180445</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4456,41 +4400,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.02</v>
+        <v>0.0092</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45608.75711524305</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G63" t="n">
-        <v>20.6261</v>
+        <v>5.836</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45608.76530484953</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I63" t="n">
-        <v>20.6299</v>
+        <v>6.02</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>20.5745</v>
-      </c>
-      <c r="O63" t="n">
-        <v>20.6364</v>
-      </c>
-      <c r="P63" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
@@ -4501,18 +4443,18 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.37</v>
+        <v>0.01</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1532729622</v>
+        <v>1393735509</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4521,37 +4463,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.01</v>
+        <v>0.0366</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45608.76652064815</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G64" t="n">
-        <v>154.853</v>
+        <v>67.37</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45608.76796081018</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I64" t="n">
-        <v>154.873</v>
+        <v>71.16</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.6</v>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>5</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -4569,11 +4513,11 @@
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1533930062</v>
+        <v>1395218355</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4582,41 +4526,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.01</v>
+        <v>0.074</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45609.61569380787</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G65" t="n">
-        <v>20.507</v>
+        <v>67.13</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45609.63889303241</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I65" t="n">
-        <v>20.5531</v>
+        <v>71.16</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>20.431</v>
-      </c>
-      <c r="O65" t="n">
-        <v>20.5528</v>
-      </c>
-      <c r="P65" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="M65" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
@@ -4627,22 +4569,18 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1536772518</v>
+        <v>1517879253</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4651,19 +4589,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45610.86999649306</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G66" t="n">
-        <v>20.4311</v>
+        <v>20.08</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45610.88084664352</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I66" t="n">
-        <v>20.4923</v>
+        <v>19.63</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4672,46 +4610,44 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>stop-out</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>20.4941</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>20.5653</v>
+        <v>20.92</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>12.05</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>5.97</v>
+        <v>-18</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>[S/L]</t>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1540892910</v>
+        <v>1403166009</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4720,67 +4656,61 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.02</v>
+        <v>0.0362</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45614.83689460648</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G67" t="n">
-        <v>20.2371</v>
+        <v>68.05</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45615.43822850694</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I67" t="n">
-        <v>20.3181</v>
+        <v>71.16</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="O67" t="n">
-        <v>20.3179</v>
-      </c>
-      <c r="P67" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1541930457</v>
+        <v>1403177543</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4789,41 +4719,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.02</v>
+        <v>0.0368</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45615.56159975695</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G68" t="n">
-        <v>20.2629</v>
+        <v>68.045</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45615.58509630787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I68" t="n">
-        <v>20.2887</v>
+        <v>71.16</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>20.2059</v>
-      </c>
-      <c r="O68" t="n">
-        <v>20.2856</v>
-      </c>
-      <c r="P68" t="n">
-        <v>10</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -4834,65 +4762,59 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1553997553</v>
+        <v>1403180429</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>0.0733</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45623.53527240741</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G69" t="n">
-        <v>20.7084</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45623.57548773148</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I69" t="n">
-        <v>20.7775</v>
+        <v>71.16</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>20.7706</v>
-      </c>
-      <c r="O69" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="P69" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4903,61 +4825,59 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1554074835</v>
+        <v>1403180445</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.01</v>
+        <v>0.9908</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45623.57516572917</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G70" t="n">
-        <v>20.7426</v>
+        <v>5.836</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45623.57574133102</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I70" t="n">
-        <v>20.7764</v>
+        <v>6.027</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5.97</v>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>5</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
@@ -4968,18 +4888,18 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>-1.63</v>
+        <v>0.18</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1555669398</v>
+        <v>1379227659</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4988,19 +4908,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.02</v>
+        <v>0.1521</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45624.55073625</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G71" t="n">
-        <v>20.3273</v>
+        <v>131.38</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45624.71914708333</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I71" t="n">
-        <v>20.4312</v>
+        <v>148.18</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5012,17 +4932,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="n">
-        <v>20.1748</v>
-      </c>
-      <c r="O71" t="n">
-        <v>20.4293</v>
-      </c>
-      <c r="P71" t="n">
-        <v>10</v>
-      </c>
+      <c r="L71" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M71" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
@@ -5033,22 +4951,18 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>2.56</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1563562241</v>
+        <v>1393281432</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5057,67 +4971,61 @@
         </is>
       </c>
       <c r="E72" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>45496.37566553241</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5.981</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>45727.38638285879</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.02</v>
       </c>
-      <c r="F72" s="2" t="n">
-        <v>45631.25027201389</v>
-      </c>
-      <c r="G72" t="n">
-        <v>20.3099</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>45631.6258153125</v>
-      </c>
-      <c r="I72" t="n">
-        <v>20.2391</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="O72" t="n">
-        <v>20.3672</v>
-      </c>
-      <c r="P72" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1473693877</v>
+        <v>1393301698</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5126,35 +5034,35 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.019</v>
+        <v>0.1401</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45562.69351818287</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G73" t="n">
-        <v>700.8</v>
+        <v>5.99</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I73" t="n">
-        <v>623.8</v>
+        <v>6.176</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>14.97</v>
+        <v>0.84</v>
       </c>
       <c r="M73" t="n">
-        <v>12.28</v>
+        <v>0.87</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
@@ -5169,18 +5077,18 @@
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-2.69</v>
+        <v>0.03</v>
       </c>
       <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1493848938</v>
+        <v>1403180427</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5189,35 +5097,35 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0213</v>
+        <v>0.4203</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45579.70088467593</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G74" t="n">
-        <v>640.3</v>
+        <v>5.989</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45646.60573655093</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I74" t="n">
-        <v>623.8</v>
+        <v>6.176</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>14.96</v>
+        <v>2.52</v>
       </c>
       <c r="M74" t="n">
-        <v>13.77</v>
+        <v>2.6</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -5232,14 +5140,14 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>-1.19</v>
+        <v>0.08</v>
       </c>
       <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1583724019</v>
+        <v>1527051962</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5252,19 +5160,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45646.60647967592</v>
+        <v>45604.13145401621</v>
       </c>
       <c r="G75" t="n">
-        <v>20.2054</v>
+        <v>19.8302</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45646.696485625</v>
+        <v>45604.56280116898</v>
       </c>
       <c r="I75" t="n">
-        <v>20.1035</v>
+        <v>19.9681</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5279,13 +5187,13 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>20.1055</v>
+        <v>19.97</v>
       </c>
       <c r="O75" t="n">
-        <v>20.3273</v>
+        <v>20.12</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -5297,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>-10.13</v>
+        <v>6.9</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -5308,7 +5216,7 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1583841034</v>
+        <v>1527744522</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5324,16 +5232,16 @@
         <v>0.01</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45646.63988152778</v>
+        <v>45604.55607921296</v>
       </c>
       <c r="G76" t="n">
-        <v>20.173</v>
+        <v>19.9784</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45646.70582428241</v>
+        <v>45604.57083508102</v>
       </c>
       <c r="I76" t="n">
-        <v>20.0949</v>
+        <v>19.9497</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5348,10 +5256,10 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
-        <v>20.0975</v>
+        <v>19.95</v>
       </c>
       <c r="O76" t="n">
-        <v>20.2542</v>
+        <v>20.2</v>
       </c>
       <c r="P76" t="n">
         <v>5</v>
@@ -5366,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>-3.88</v>
+        <v>-1.44</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -5377,7 +5285,7 @@
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1585474078</v>
+        <v>1528126100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -5390,19 +5298,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45649.40133020833</v>
+        <v>45604.66918148148</v>
       </c>
       <c r="G77" t="n">
-        <v>20.0935</v>
+        <v>20.0428</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45649.56824730324</v>
+        <v>45604.71914307871</v>
       </c>
       <c r="I77" t="n">
-        <v>20.1707</v>
+        <v>20.0988</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5411,19 +5319,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>20</v>
+        <v>20.0988</v>
       </c>
       <c r="O77" t="n">
-        <v>20.17</v>
+        <v>20.2</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -5435,18 +5343,18 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>7.65</v>
+        <v>2.79</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>[T/P]</t>
+          <t>[S/L]</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1586033461</v>
+        <v>1528325630</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -5455,27 +5363,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>0.01</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45649.63114609953</v>
+        <v>45604.72032700232</v>
       </c>
       <c r="G78" t="n">
-        <v>20.1772</v>
+        <v>20.0912</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45649.63200465278</v>
+        <v>45604.72263849537</v>
       </c>
       <c r="I78" t="n">
-        <v>20.1671</v>
+        <v>20.1101</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5486,10 +5394,10 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
-        <v>20.1687</v>
+        <v>20.11</v>
       </c>
       <c r="O78" t="n">
-        <v>20.2379</v>
+        <v>20.0219</v>
       </c>
       <c r="P78" t="n">
         <v>5</v>
@@ -5504,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -5515,11 +5423,11 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1587036381</v>
+        <v>1531224336</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5528,19 +5436,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45650.48790526621</v>
+        <v>45608.2460031713</v>
       </c>
       <c r="G79" t="n">
-        <v>20.1462</v>
+        <v>153.589</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45650.58025611111</v>
+        <v>45608.25044886574</v>
       </c>
       <c r="I79" t="n">
-        <v>20.1627</v>
+        <v>153.468</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5555,13 +5463,13 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>20.1627</v>
+        <v>153.47</v>
       </c>
       <c r="O79" t="n">
-        <v>20.22</v>
+        <v>153.619</v>
       </c>
       <c r="P79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5573,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>1.64</v>
+        <v>-0.79</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -5584,32 +5492,32 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1500272843</v>
+        <v>1531227124</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0264</v>
+        <v>0.01</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45608.25015417824</v>
       </c>
       <c r="G80" t="n">
-        <v>718.5</v>
+        <v>153.483</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45663.67045758102</v>
+        <v>45608.25207638889</v>
       </c>
       <c r="I80" t="n">
-        <v>757.79</v>
+        <v>153.458</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5621,15 +5529,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="M80" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>153.458</v>
+      </c>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>5</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
@@ -5640,39 +5548,43 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="U80" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1500272843</v>
+        <v>1531230129</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0021</v>
+        <v>0.01</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45583.64588594907</v>
+        <v>45608.2544440162</v>
       </c>
       <c r="G81" t="n">
-        <v>718.5</v>
+        <v>153.445</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45663.67059782407</v>
+        <v>45608.25666561343</v>
       </c>
       <c r="I81" t="n">
-        <v>758.27</v>
+        <v>153.502</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5684,15 +5596,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="n">
+        <v>153.502</v>
+      </c>
+      <c r="O81" t="n">
+        <v>153.395</v>
+      </c>
+      <c r="P81" t="n">
+        <v>5</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
@@ -5703,18 +5617,22 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="U81" t="inlineStr"/>
+        <v>-0.37</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1518147105</v>
+        <v>1531192665</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5723,19 +5641,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45597.8504690162</v>
+        <v>45608.19828637732</v>
       </c>
       <c r="G82" t="n">
-        <v>10.92</v>
+        <v>20.412</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45667.68126778935</v>
+        <v>45608.34380275463</v>
       </c>
       <c r="I82" t="n">
-        <v>6.52</v>
+        <v>20.4421</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5747,15 +5665,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="M82" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="n">
+        <v>20.4429</v>
+      </c>
+      <c r="O82" t="n">
+        <v>20.5326</v>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
@@ -5766,39 +5686,43 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="U82" t="inlineStr"/>
+        <v>2.94</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1551373923</v>
+        <v>1531349564</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1195</v>
+        <v>0.01</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45621.85639895833</v>
+        <v>45608.34449649305</v>
       </c>
       <c r="G83" t="n">
-        <v>167.24</v>
+        <v>20.4344</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45678.70646498843</v>
+        <v>45608.34490908564</v>
       </c>
       <c r="I83" t="n">
-        <v>198.83</v>
+        <v>20.4507</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5810,15 +5734,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="M83" t="n">
-        <v>23.76</v>
-      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
@@ -5829,18 +5751,18 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.77</v>
+        <v>-0.8</v>
       </c>
       <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1373744560</v>
+        <v>1531351286</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5849,19 +5771,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1248</v>
+        <v>0.01</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45476.64586885417</v>
+        <v>45608.34571399305</v>
       </c>
       <c r="G84" t="n">
-        <v>202.58</v>
+        <v>20.4554</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45608.35180353009</v>
       </c>
       <c r="I84" t="n">
-        <v>172.09</v>
+        <v>20.45</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5873,15 +5795,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="M84" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="n">
+        <v>20.4381</v>
+      </c>
+      <c r="O84" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="P84" t="n">
+        <v>5</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
@@ -5892,18 +5816,18 @@
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>-3.8</v>
+        <v>-0.26</v>
       </c>
       <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1450039117</v>
+        <v>1531358421</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5912,19 +5836,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.068</v>
+        <v>0.02</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45544.65070009259</v>
+        <v>45608.3501140162</v>
       </c>
       <c r="G85" t="n">
-        <v>161.58</v>
+        <v>20.4503</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45680.72583917824</v>
+        <v>45608.35479755787</v>
       </c>
       <c r="I85" t="n">
-        <v>172.09</v>
+        <v>20.4382</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5936,15 +5860,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="M85" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>20.4388</v>
+      </c>
+      <c r="O85" t="n">
+        <v>20.4767</v>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
@@ -5955,18 +5881,22 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="U85" t="inlineStr"/>
+        <v>-1.18</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1468472119</v>
+        <v>1532703059</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5975,19 +5905,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45559.65212880787</v>
+        <v>45608.75711524305</v>
       </c>
       <c r="G86" t="n">
-        <v>277.82</v>
+        <v>20.6261</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45608.76530484953</v>
       </c>
       <c r="I86" t="n">
-        <v>336.69</v>
+        <v>20.6299</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -5999,15 +5929,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L86" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M86" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="n">
+        <v>20.5745</v>
+      </c>
+      <c r="O86" t="n">
+        <v>20.6364</v>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
@@ -6018,18 +5950,18 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>4.23</v>
+        <v>0.37</v>
       </c>
       <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1470564087</v>
+        <v>1532729622</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>JPY=X</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6038,19 +5970,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0742</v>
+        <v>0.01</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45560.82041144676</v>
+        <v>45608.76652064815</v>
       </c>
       <c r="G87" t="n">
-        <v>269.23</v>
+        <v>154.853</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45608.76796081018</v>
       </c>
       <c r="I87" t="n">
-        <v>336.69</v>
+        <v>154.873</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6062,15 +5994,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M87" t="n">
-        <v>24.98</v>
-      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>5</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
@@ -6081,18 +6011,18 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>5</v>
+        <v>0.13</v>
       </c>
       <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1599434998</v>
+        <v>1533930062</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6101,19 +6031,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0477</v>
+        <v>0.01</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45663.73100940972</v>
+        <v>45609.61569380787</v>
       </c>
       <c r="G88" t="n">
-        <v>313.98</v>
+        <v>20.507</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45685.83792359954</v>
+        <v>45609.63889303241</v>
       </c>
       <c r="I88" t="n">
-        <v>336.69</v>
+        <v>20.5531</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6125,15 +6055,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L88" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="M88" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>20.431</v>
+      </c>
+      <c r="O88" t="n">
+        <v>20.5528</v>
+      </c>
+      <c r="P88" t="n">
+        <v>5</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
@@ -6144,18 +6076,22 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="U88" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1495548850</v>
+        <v>1536772518</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6164,19 +6100,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.1047</v>
+        <v>0.02</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45580.70599549769</v>
+        <v>45610.86999649306</v>
       </c>
       <c r="G89" t="n">
-        <v>133.61</v>
+        <v>20.4311</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45610.88084664352</v>
       </c>
       <c r="I89" t="n">
-        <v>143.18</v>
+        <v>20.4923</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6188,15 +6124,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L89" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="M89" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>20.4941</v>
+      </c>
+      <c r="O89" t="n">
+        <v>20.5653</v>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
@@ -6207,18 +6145,22 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="inlineStr"/>
+        <v>5.97</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1517512112</v>
+        <v>1540892910</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6227,19 +6169,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45597.61040866898</v>
+        <v>45614.83689460648</v>
       </c>
       <c r="G90" t="n">
-        <v>132.62</v>
+        <v>20.2371</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45615.43822850694</v>
       </c>
       <c r="I90" t="n">
-        <v>143.18</v>
+        <v>20.3181</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6251,37 +6193,43 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="O90" t="n">
+        <v>20.3179</v>
+      </c>
+      <c r="P90" t="n">
         <v>10</v>
       </c>
-      <c r="M90" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U90" t="inlineStr"/>
+        <v>7.97</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1582735114</v>
+        <v>1541930457</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6290,23 +6238,23 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45645.90076787037</v>
+        <v>45615.56159975695</v>
       </c>
       <c r="G91" t="n">
-        <v>130.51</v>
+        <v>20.2629</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45695.85266428241</v>
+        <v>45615.58509630787</v>
       </c>
       <c r="I91" t="n">
-        <v>143.18</v>
+        <v>20.2887</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xStation Mobile Android</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6314,15 +6262,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L91" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="M91" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>20.2059</v>
+      </c>
+      <c r="O91" t="n">
+        <v>20.2856</v>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -6333,14 +6283,18 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="U91" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1657658561</v>
+        <v>1553997553</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -6349,23 +6303,23 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45702.18774210648</v>
+        <v>45623.53527240741</v>
       </c>
       <c r="G92" t="n">
-        <v>20.4257</v>
+        <v>20.7084</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45702.56168643518</v>
+        <v>45623.57548773148</v>
       </c>
       <c r="I92" t="n">
-        <v>20.3656</v>
+        <v>20.7775</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6380,13 +6334,13 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
-        <v>20.3664</v>
+        <v>20.7706</v>
       </c>
       <c r="O92" t="n">
-        <v>20.5213</v>
+        <v>20.68</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -6398,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>-5.9</v>
+        <v>-3.33</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -6409,7 +6363,7 @@
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1660829104</v>
+        <v>1554074835</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -6418,23 +6372,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45705.64981799768</v>
+        <v>45623.57516572917</v>
       </c>
       <c r="G93" t="n">
-        <v>20.3237</v>
+        <v>20.7426</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45705.72866341435</v>
+        <v>45623.57574133102</v>
       </c>
       <c r="I93" t="n">
-        <v>20.2738</v>
+        <v>20.7764</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6448,14 +6402,10 @@
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>20.2738</v>
-      </c>
-      <c r="O93" t="n">
-        <v>20.3936</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -6467,22 +6417,18 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-1.63</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1378903852</v>
+        <v>1555669398</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6491,19 +6437,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0616</v>
+        <v>0.02</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45624.55073625</v>
       </c>
       <c r="G94" t="n">
-        <v>227.77</v>
+        <v>20.3273</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>45706.65274813658</v>
+        <v>45624.71914708333</v>
       </c>
       <c r="I94" t="n">
-        <v>243.58</v>
+        <v>20.4312</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6515,15 +6461,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L94" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="M94" t="n">
-        <v>15</v>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>20.1748</v>
+      </c>
+      <c r="O94" t="n">
+        <v>20.4293</v>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -6534,18 +6482,22 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="U94" t="inlineStr"/>
+        <v>10.17</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1378903852</v>
+        <v>1563562241</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6554,19 +6506,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0042</v>
+        <v>0.02</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45482.71372086806</v>
+        <v>45631.25027201389</v>
       </c>
       <c r="G95" t="n">
-        <v>227.77</v>
+        <v>20.3099</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45631.6258153125</v>
       </c>
       <c r="I95" t="n">
-        <v>243.45</v>
+        <v>20.2391</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6578,15 +6530,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="O95" t="n">
+        <v>20.3672</v>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -6597,18 +6551,22 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="U95" t="inlineStr"/>
+        <v>-6.99</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1456814919</v>
+        <v>1473693877</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6617,19 +6575,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0665</v>
+        <v>0.019</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45548.6657375</v>
+        <v>45562.69351818287</v>
       </c>
       <c r="G96" t="n">
-        <v>222.94</v>
+        <v>700.8</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I96" t="n">
-        <v>243.45</v>
+        <v>623.8</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6642,10 +6600,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>14.83</v>
+        <v>14.97</v>
       </c>
       <c r="M96" t="n">
-        <v>16.19</v>
+        <v>12.28</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6660,18 +6618,18 @@
         <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>1.36</v>
+        <v>-2.69</v>
       </c>
       <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1499061783</v>
+        <v>1493848938</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MC.PA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6680,23 +6638,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0558</v>
+        <v>0.0213</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45582.73996877314</v>
+        <v>45579.70088467593</v>
       </c>
       <c r="G97" t="n">
-        <v>232.2</v>
+        <v>640.3</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45706.65290153935</v>
+        <v>45646.60573655093</v>
       </c>
       <c r="I97" t="n">
-        <v>243.45</v>
+        <v>623.8</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6705,10 +6663,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>12.96</v>
+        <v>14.96</v>
       </c>
       <c r="M97" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
@@ -6723,14 +6681,14 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0.62</v>
+        <v>-1.19</v>
       </c>
       <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1717095547</v>
+        <v>1583724019</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -6743,19 +6701,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45736.81342114583</v>
+        <v>45646.60647967592</v>
       </c>
       <c r="G98" t="n">
-        <v>20.1198</v>
+        <v>20.2054</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45737.11337774306</v>
+        <v>45646.696485625</v>
       </c>
       <c r="I98" t="n">
-        <v>20.1348</v>
+        <v>20.1035</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6770,25 +6728,25 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>20.1349</v>
+        <v>20.1055</v>
       </c>
       <c r="O98" t="n">
-        <v>20.1623</v>
+        <v>20.3273</v>
       </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.98</v>
+        <v>-10.13</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -6799,11 +6757,11 @@
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1554741910</v>
+        <v>1583841034</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6812,19 +6770,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45623.74951100694</v>
+        <v>45646.63988152778</v>
       </c>
       <c r="G99" t="n">
-        <v>15.3</v>
+        <v>20.173</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45741.87177293981</v>
+        <v>45646.70582428241</v>
       </c>
       <c r="I99" t="n">
-        <v>20.29</v>
+        <v>20.0949</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6836,15 +6794,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L99" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="M99" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>20.0975</v>
+      </c>
+      <c r="O99" t="n">
+        <v>20.2542</v>
+      </c>
+      <c r="P99" t="n">
+        <v>5</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -6855,18 +6815,22 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U99" t="inlineStr"/>
+        <v>-3.88</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1414372592</v>
+        <v>1585474078</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6875,19 +6839,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45511.7228721412</v>
+        <v>45649.40133020833</v>
       </c>
       <c r="G100" t="n">
-        <v>455.4</v>
+        <v>20.0935</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>45742.77596394676</v>
+        <v>45649.56824730324</v>
       </c>
       <c r="I100" t="n">
-        <v>547.14</v>
+        <v>20.1707</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6899,15 +6863,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="M100" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>20</v>
+      </c>
+      <c r="O100" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
@@ -6918,18 +6884,22 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U100" t="inlineStr"/>
+        <v>7.65</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1450043624</v>
+        <v>1586033461</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6938,19 +6908,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0138</v>
+        <v>0.01</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45649.63114609953</v>
       </c>
       <c r="G101" t="n">
-        <v>147.48</v>
+        <v>20.1772</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45743.76599777778</v>
+        <v>45649.63200465278</v>
       </c>
       <c r="I101" t="n">
-        <v>139.86</v>
+        <v>20.1671</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6962,15 +6932,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L101" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>20.1687</v>
+      </c>
+      <c r="O101" t="n">
+        <v>20.2379</v>
+      </c>
+      <c r="P101" t="n">
+        <v>5</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -6981,18 +6953,22 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U101" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1358151307</v>
+        <v>1587036381</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7001,19 +6977,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0124</v>
+        <v>0.02</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45460.88529037037</v>
+        <v>45650.48790526621</v>
       </c>
       <c r="G102" t="n">
-        <v>165.93</v>
+        <v>20.1462</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45743.76632650463</v>
+        <v>45650.58025611111</v>
       </c>
       <c r="I102" t="n">
-        <v>149.33</v>
+        <v>20.1627</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7025,15 +7001,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>20.1627</v>
+      </c>
+      <c r="O102" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="P102" t="n">
+        <v>10</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
@@ -7044,18 +7022,22 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="U102" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1422773288</v>
+        <v>1500272843</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7064,19 +7046,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.2</v>
+        <v>0.0264</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45518.84428505787</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G103" t="n">
-        <v>51.24</v>
+        <v>718.5</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45743.76769060185</v>
+        <v>45663.67045758102</v>
       </c>
       <c r="I103" t="n">
-        <v>58.08</v>
+        <v>757.79</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7089,10 +7071,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>10.25</v>
+        <v>18.97</v>
       </c>
       <c r="M103" t="n">
-        <v>11.62</v>
+        <v>20.01</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -7107,18 +7089,18 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1631473921</v>
+        <v>1500272843</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7127,19 +7109,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.2745</v>
+        <v>0.0021</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45685.8356116088</v>
+        <v>45583.64588594907</v>
       </c>
       <c r="G104" t="n">
-        <v>40.05</v>
+        <v>718.5</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45663.67059782407</v>
       </c>
       <c r="I104" t="n">
-        <v>44.8</v>
+        <v>758.27</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7148,14 +7130,14 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>10.99</v>
+        <v>1.51</v>
       </c>
       <c r="M104" t="n">
-        <v>12.3</v>
+        <v>1.59</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -7170,18 +7152,18 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>1.31</v>
+        <v>0.08</v>
       </c>
       <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1642763333</v>
+        <v>1518147105</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MAXN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7190,19 +7172,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2459</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45692.86672944445</v>
+        <v>45597.8504690162</v>
       </c>
       <c r="G105" t="n">
-        <v>40.66</v>
+        <v>10.92</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45667.68126778935</v>
       </c>
       <c r="I105" t="n">
-        <v>44.8</v>
+        <v>6.52</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7211,14 +7193,14 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>10.92</v>
       </c>
       <c r="M105" t="n">
-        <v>11.02</v>
+        <v>6.52</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
@@ -7233,18 +7215,18 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>1.02</v>
+        <v>-4.4</v>
       </c>
       <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1666451221</v>
+        <v>1551373923</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7253,19 +7235,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.1796</v>
+        <v>0.1195</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45621.85639895833</v>
       </c>
       <c r="G106" t="n">
-        <v>43</v>
+        <v>167.24</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45754.64763142361</v>
+        <v>45678.70646498843</v>
       </c>
       <c r="I106" t="n">
-        <v>44.8</v>
+        <v>198.83</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7274,14 +7256,14 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>7.72</v>
+        <v>19.99</v>
       </c>
       <c r="M106" t="n">
-        <v>8.050000000000001</v>
+        <v>23.76</v>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
@@ -7296,57 +7278,59 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>0.33</v>
+        <v>3.77</v>
       </c>
       <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1749053104</v>
+        <v>1373744560</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.01</v>
+        <v>0.1248</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45754.65117414352</v>
+        <v>45476.64586885417</v>
       </c>
       <c r="G107" t="n">
-        <v>4903.7</v>
+        <v>202.58</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45754.65218731482</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I107" t="n">
-        <v>4891.1</v>
+        <v>172.09</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="M107" t="n">
+        <v>21.48</v>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="n">
-        <v>12.26</v>
-      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
@@ -7357,57 +7341,59 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>6.3</v>
+        <v>-3.8</v>
       </c>
       <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1756767326</v>
+        <v>1450039117</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.01</v>
+        <v>0.068</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45756.64805717592</v>
+        <v>45544.65070009259</v>
       </c>
       <c r="G108" t="n">
-        <v>5004.7</v>
+        <v>161.58</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45756.64937413194</v>
+        <v>45680.72583917824</v>
       </c>
       <c r="I108" t="n">
-        <v>5005.2</v>
+        <v>172.09</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11.7</v>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="n">
-        <v>12.51</v>
-      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
@@ -7418,57 +7404,59 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>-0.25</v>
+        <v>0.71</v>
       </c>
       <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1756797155</v>
+        <v>1468472119</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.01</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45756.6510503125</v>
+        <v>45559.65212880787</v>
       </c>
       <c r="G109" t="n">
-        <v>4992.2</v>
+        <v>277.82</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45756.65185319445</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I109" t="n">
-        <v>5013.4</v>
+        <v>336.69</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M109" t="n">
+        <v>24.21</v>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="n">
-        <v>12.48</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
@@ -7479,18 +7467,18 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>-10.6</v>
+        <v>4.23</v>
       </c>
       <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1767688540</v>
+        <v>1470564087</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7499,19 +7487,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.01</v>
+        <v>0.0742</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45761.6294487037</v>
+        <v>45560.82041144676</v>
       </c>
       <c r="G110" t="n">
-        <v>20.1226</v>
+        <v>269.23</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>45761.66966099537</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I110" t="n">
-        <v>20.047</v>
+        <v>336.69</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7523,43 +7511,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="n">
-        <v>20.048</v>
-      </c>
-      <c r="O110" t="n">
-        <v>20.3404</v>
-      </c>
-      <c r="P110" t="n">
+      <c r="L110" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="M110" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1768229183</v>
+        <v>1599434998</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7568,19 +7550,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.01</v>
+        <v>0.0477</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45761.71402207176</v>
+        <v>45663.73100940972</v>
       </c>
       <c r="G111" t="n">
-        <v>20.0759</v>
+        <v>313.98</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45761.77371288194</v>
+        <v>45685.83792359954</v>
       </c>
       <c r="I111" t="n">
-        <v>20.1099</v>
+        <v>336.69</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7592,17 +7574,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="n">
-        <v>20.1099</v>
-      </c>
-      <c r="O111" t="n">
-        <v>20.2122</v>
-      </c>
-      <c r="P111" t="n">
-        <v>5</v>
-      </c>
+      <c r="L111" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M111" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
@@ -7613,22 +7593,18 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1.08</v>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1769815245</v>
+        <v>1495548850</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7637,19 +7613,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.01</v>
+        <v>0.1047</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45762.50265097222</v>
+        <v>45580.70599549769</v>
       </c>
       <c r="G112" t="n">
-        <v>20.0545</v>
+        <v>133.61</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45762.61225923611</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I112" t="n">
-        <v>19.9735</v>
+        <v>143.18</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7661,15 +7637,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="n">
-        <v>19.9742</v>
-      </c>
+      <c r="L112" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="M112" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>5</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
@@ -7680,22 +7656,18 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1666451221</v>
+        <v>1517512112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7704,19 +7676,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.0528</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45708.68022618056</v>
+        <v>45597.61040866898</v>
       </c>
       <c r="G113" t="n">
-        <v>43</v>
+        <v>132.62</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45764.85028728009</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I113" t="n">
-        <v>47.89</v>
+        <v>143.18</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7729,10 +7701,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="M113" t="n">
-        <v>2.53</v>
+        <v>10.8</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -7747,18 +7719,18 @@
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1393281432</v>
+        <v>1582735114</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7767,35 +7739,35 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.632</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45645.90076787037</v>
       </c>
       <c r="G114" t="n">
-        <v>5.981</v>
+        <v>130.51</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45695.85266428241</v>
       </c>
       <c r="I114" t="n">
-        <v>5.967</v>
+        <v>143.18</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile Android</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.78</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>3.77</v>
+        <v>10.92</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -7810,18 +7782,18 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>-0.01</v>
+        <v>0.96</v>
       </c>
       <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1450043624</v>
+        <v>1657658561</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7830,19 +7802,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45544.65163506944</v>
+        <v>45702.18774210648</v>
       </c>
       <c r="G115" t="n">
-        <v>147.48</v>
+        <v>20.4257</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45764.8517803588</v>
+        <v>45702.56168643518</v>
       </c>
       <c r="I115" t="n">
-        <v>143.22</v>
+        <v>20.3656</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7854,15 +7826,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="M115" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>20.3664</v>
+      </c>
+      <c r="O115" t="n">
+        <v>20.5213</v>
+      </c>
+      <c r="P115" t="n">
+        <v>10</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
@@ -7873,18 +7847,22 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="U115" t="inlineStr"/>
+        <v>-5.9</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1393281260</v>
+        <v>1660829104</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7893,39 +7871,41 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.5612</v>
+        <v>0.02</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45705.64981799768</v>
       </c>
       <c r="G116" t="n">
-        <v>5.812</v>
+        <v>20.3237</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45705.72866341435</v>
       </c>
       <c r="I116" t="n">
-        <v>5.81</v>
+        <v>20.2738</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>20.2738</v>
+      </c>
+      <c r="O116" t="n">
+        <v>20.3936</v>
+      </c>
+      <c r="P116" t="n">
+        <v>10</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
@@ -7936,18 +7916,22 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="inlineStr"/>
+        <v>-4.92</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1777308201</v>
+        <v>1378903852</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7956,19 +7940,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.01</v>
+        <v>0.0616</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45768.12181488426</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G117" t="n">
-        <v>19.7053</v>
+        <v>227.77</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45768.13306659722</v>
+        <v>45706.65274813658</v>
       </c>
       <c r="I117" t="n">
-        <v>19.7154</v>
+        <v>243.58</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -7980,13 +7964,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="M117" t="n">
+        <v>15</v>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="n">
-        <v>5</v>
-      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
@@ -7997,18 +7983,18 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1393281260</v>
+        <v>1378903852</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8017,35 +8003,35 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.555</v>
+        <v>0.0042</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45482.71372086806</v>
       </c>
       <c r="G118" t="n">
-        <v>5.812</v>
+        <v>227.77</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I118" t="n">
-        <v>5.801</v>
+        <v>243.45</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.23</v>
+        <v>0.96</v>
       </c>
       <c r="M118" t="n">
-        <v>3.22</v>
+        <v>1.02</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -8060,18 +8046,18 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1393281432</v>
+        <v>1456814919</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8080,35 +8066,35 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.4344</v>
+        <v>0.0665</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45548.6657375</v>
       </c>
       <c r="G119" t="n">
-        <v>5.981</v>
+        <v>222.94</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I119" t="n">
-        <v>5.968</v>
+        <v>243.45</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.6</v>
+        <v>14.83</v>
       </c>
       <c r="M119" t="n">
-        <v>2.59</v>
+        <v>16.19</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -8123,18 +8109,18 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>-0.01</v>
+        <v>1.36</v>
       </c>
       <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1393281260</v>
+        <v>1499061783</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8143,19 +8129,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0.0558</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45582.73996877314</v>
       </c>
       <c r="G120" t="n">
-        <v>5.812</v>
+        <v>232.2</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45706.65290153935</v>
       </c>
       <c r="I120" t="n">
-        <v>5.814</v>
+        <v>243.45</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8164,14 +8150,14 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>5.81</v>
+        <v>12.96</v>
       </c>
       <c r="M120" t="n">
-        <v>5.81</v>
+        <v>13.58</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -8186,18 +8172,18 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1393281432</v>
+        <v>1717095547</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8206,61 +8192,67 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45736.81342114583</v>
       </c>
       <c r="G121" t="n">
-        <v>5.981</v>
+        <v>20.1198</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45737.11337774306</v>
       </c>
       <c r="I121" t="n">
-        <v>5.978</v>
+        <v>20.1348</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L121" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="M121" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>20.1349</v>
+      </c>
+      <c r="O121" t="n">
+        <v>20.1623</v>
+      </c>
+      <c r="P121" t="n">
+        <v>20</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="inlineStr"/>
+        <v>2.98</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1781449563</v>
+        <v>1554741910</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8269,19 +8261,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45769.73814164352</v>
+        <v>45623.74951100694</v>
       </c>
       <c r="G122" t="n">
-        <v>19.58</v>
+        <v>15.3</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45769.76084202546</v>
+        <v>45741.87177293981</v>
       </c>
       <c r="I122" t="n">
-        <v>19.5255</v>
+        <v>20.29</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8293,13 +8285,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="M122" t="n">
+        <v>12.38</v>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>5</v>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
@@ -8310,18 +8304,18 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>-2.79</v>
+        <v>3.05</v>
       </c>
       <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1393281260</v>
+        <v>1414372592</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8330,35 +8324,35 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.4206</v>
+        <v>0.01</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45511.7228721412</v>
       </c>
       <c r="G123" t="n">
-        <v>5.812</v>
+        <v>455.4</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45742.77596394676</v>
       </c>
       <c r="I123" t="n">
-        <v>5.826</v>
+        <v>547.14</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.44</v>
+        <v>4.55</v>
       </c>
       <c r="M123" t="n">
-        <v>2.45</v>
+        <v>5.47</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -8373,18 +8367,18 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>0.01</v>
+        <v>0.92</v>
       </c>
       <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1393281432</v>
+        <v>1450043624</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8393,35 +8387,35 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.4033</v>
+        <v>0.0138</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G124" t="n">
-        <v>5.981</v>
+        <v>147.48</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45743.76599777778</v>
       </c>
       <c r="I124" t="n">
-        <v>5.98</v>
+        <v>139.86</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="M124" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -8436,18 +8430,18 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1560258921</v>
+        <v>1358151307</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8456,19 +8450,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>0.0124</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45629.37798611111</v>
+        <v>45460.88529037037</v>
       </c>
       <c r="G125" t="n">
-        <v>48.68</v>
+        <v>165.93</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45743.76632650463</v>
       </c>
       <c r="I125" t="n">
-        <v>44.15</v>
+        <v>149.33</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8481,10 +8475,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>51.41</v>
+        <v>2.06</v>
       </c>
       <c r="M125" t="n">
-        <v>49.84</v>
+        <v>1.85</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -8499,18 +8493,18 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>-1.57</v>
+        <v>-0.21</v>
       </c>
       <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1393281432</v>
+        <v>1422773288</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8519,35 +8513,35 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.4201</v>
+        <v>0.2</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45518.84428505787</v>
       </c>
       <c r="G126" t="n">
-        <v>5.981</v>
+        <v>51.24</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45743.76769060185</v>
       </c>
       <c r="I126" t="n">
-        <v>5.98</v>
+        <v>58.08</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.51</v>
+        <v>10.25</v>
       </c>
       <c r="M126" t="n">
-        <v>2.51</v>
+        <v>11.62</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
@@ -8562,18 +8556,18 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1393281432</v>
+        <v>1631473921</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8582,35 +8576,35 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0.2745</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45685.8356116088</v>
       </c>
       <c r="G127" t="n">
-        <v>5.981</v>
+        <v>40.05</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I127" t="n">
-        <v>6.186</v>
+        <v>44.8</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L127" t="n">
-        <v>5.98</v>
+        <v>10.99</v>
       </c>
       <c r="M127" t="n">
-        <v>6.19</v>
+        <v>12.3</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
@@ -8625,18 +8619,18 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>0.21</v>
+        <v>1.31</v>
       </c>
       <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1748583646</v>
+        <v>1642763333</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8645,19 +8639,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0.2459</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45754.57938657407</v>
+        <v>45692.86672944445</v>
       </c>
       <c r="G128" t="n">
-        <v>37.258</v>
+        <v>40.66</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45782.67688657407</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I128" t="n">
-        <v>44.15</v>
+        <v>44.8</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8666,14 +8660,14 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>41.06</v>
+        <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>49.84</v>
+        <v>11.02</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
@@ -8688,18 +8682,18 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>8.779999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1393281260</v>
+        <v>1666451221</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8708,35 +8702,35 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1.4632</v>
+        <v>0.1796</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G129" t="n">
-        <v>5.812</v>
+        <v>43</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45754.64763142361</v>
       </c>
       <c r="I129" t="n">
-        <v>6.02</v>
+        <v>44.8</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L129" t="n">
-        <v>8.5</v>
+        <v>7.72</v>
       </c>
       <c r="M129" t="n">
-        <v>8.81</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
@@ -8751,39 +8745,39 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>1393287040</v>
+        <v>1749053104</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.2503</v>
+        <v>0.01</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45754.65117414352</v>
       </c>
       <c r="G130" t="n">
-        <v>5.811</v>
+        <v>4903.7</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45754.65218731482</v>
       </c>
       <c r="I130" t="n">
-        <v>6.02</v>
+        <v>4891.1</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -8795,15 +8789,13 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L130" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M130" t="n">
-        <v>1.51</v>
-      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>12.26</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
@@ -8814,39 +8806,39 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>0.06</v>
+        <v>6.3</v>
       </c>
       <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1403180431</v>
+        <v>1756767326</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.2773</v>
+        <v>0.01</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45756.64805717592</v>
       </c>
       <c r="G131" t="n">
-        <v>5.84</v>
+        <v>5004.7</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45756.64937413194</v>
       </c>
       <c r="I131" t="n">
-        <v>6.02</v>
+        <v>5005.2</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8858,15 +8850,13 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L131" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M131" t="n">
-        <v>1.67</v>
-      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>12.51</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
@@ -8877,39 +8867,39 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0.05</v>
+        <v>-0.25</v>
       </c>
       <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>1403180445</v>
+        <v>1756797155</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.0092</v>
+        <v>0.01</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45756.6510503125</v>
       </c>
       <c r="G132" t="n">
-        <v>5.836</v>
+        <v>4992.2</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45756.65185319445</v>
       </c>
       <c r="I132" t="n">
-        <v>6.02</v>
+        <v>5013.4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8921,15 +8911,13 @@
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="L132" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>12.48</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
@@ -8940,18 +8928,18 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>0.01</v>
+        <v>-10.6</v>
       </c>
       <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1373808226</v>
+        <v>1767688540</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8960,19 +8948,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.0234</v>
+        <v>0.01</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45476.6587916088</v>
+        <v>45761.6294487037</v>
       </c>
       <c r="G133" t="n">
-        <v>459.24</v>
+        <v>20.1226</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45761.66966099537</v>
       </c>
       <c r="I133" t="n">
-        <v>434.71</v>
+        <v>20.047</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -8984,15 +8972,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L133" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="M133" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>20.048</v>
+      </c>
+      <c r="O133" t="n">
+        <v>20.3404</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
@@ -9003,18 +8993,22 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="U133" t="inlineStr"/>
+        <v>-3.77</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1393735509</v>
+        <v>1768229183</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9023,39 +9017,41 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.0366</v>
+        <v>0.01</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45761.71402207176</v>
       </c>
       <c r="G134" t="n">
-        <v>67.37</v>
+        <v>20.0759</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45761.77371288194</v>
       </c>
       <c r="I134" t="n">
-        <v>71.16</v>
+        <v>20.1099</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M134" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>20.1099</v>
+      </c>
+      <c r="O134" t="n">
+        <v>20.2122</v>
+      </c>
+      <c r="P134" t="n">
+        <v>5</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
@@ -9066,18 +9062,22 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="U134" t="inlineStr"/>
+        <v>1.69</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1395218355</v>
+        <v>1769815245</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9086,39 +9086,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.074</v>
+        <v>0.01</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45762.50265097222</v>
       </c>
       <c r="G135" t="n">
-        <v>67.13</v>
+        <v>20.0545</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45762.61225923611</v>
       </c>
       <c r="I135" t="n">
-        <v>71.16</v>
+        <v>19.9735</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M135" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="N135" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>19.9742</v>
+      </c>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>5</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
@@ -9129,18 +9129,22 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U135" t="inlineStr"/>
+        <v>-4.06</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1403166009</v>
+        <v>1666451221</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9149,35 +9153,35 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.0362</v>
+        <v>0.0528</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45708.68022618056</v>
       </c>
       <c r="G136" t="n">
-        <v>68.05</v>
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45764.85028728009</v>
       </c>
       <c r="I136" t="n">
-        <v>71.16</v>
+        <v>47.89</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="M136" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -9192,18 +9196,18 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1403177543</v>
+        <v>1450043624</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9212,35 +9216,35 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.0368</v>
+        <v>0.1</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45544.65163506944</v>
       </c>
       <c r="G137" t="n">
-        <v>68.045</v>
+        <v>147.48</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45764.8517803588</v>
       </c>
       <c r="I137" t="n">
-        <v>71.16</v>
+        <v>143.22</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.5</v>
+        <v>14.75</v>
       </c>
       <c r="M137" t="n">
-        <v>2.62</v>
+        <v>14.32</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -9255,18 +9259,18 @@
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>0.12</v>
+        <v>-0.42</v>
       </c>
       <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1403180429</v>
+        <v>1777308201</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9275,39 +9279,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.0733</v>
+        <v>0.01</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45768.12181488426</v>
       </c>
       <c r="G138" t="n">
-        <v>68.01000000000001</v>
+        <v>19.7053</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45768.13306659722</v>
       </c>
       <c r="I138" t="n">
-        <v>71.16</v>
+        <v>19.7154</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L138" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M138" t="n">
-        <v>5.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>5</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
@@ -9318,18 +9320,18 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1403180445</v>
+        <v>1781449563</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9338,39 +9340,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9908</v>
+        <v>0.01</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45769.73814164352</v>
       </c>
       <c r="G139" t="n">
-        <v>5.836</v>
+        <v>19.58</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45769.76084202546</v>
       </c>
       <c r="I139" t="n">
-        <v>6.027</v>
+        <v>19.5255</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M139" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>5</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
@@ -9381,18 +9381,18 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0.18</v>
+        <v>-2.79</v>
       </c>
       <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1426782063</v>
+        <v>1560258921</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9401,19 +9401,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.0372</v>
+        <v>1</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45523.66633670139</v>
+        <v>45629.37798611111</v>
       </c>
       <c r="G140" t="n">
-        <v>419.46</v>
+        <v>48.68</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45784.77664918981</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I140" t="n">
-        <v>434.71</v>
+        <v>44.15</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>15.6</v>
+        <v>51.41</v>
       </c>
       <c r="M140" t="n">
-        <v>16.17</v>
+        <v>49.84</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -9444,18 +9444,18 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.57</v>
       </c>
       <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1393281432</v>
+        <v>1748583646</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9464,35 +9464,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.1102</v>
+        <v>1</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45754.57938657407</v>
       </c>
       <c r="G141" t="n">
-        <v>5.981</v>
+        <v>37.258</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45782.67688657407</v>
       </c>
       <c r="I141" t="n">
-        <v>6.176</v>
+        <v>44.15</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0.66</v>
+        <v>41.06</v>
       </c>
       <c r="M141" t="n">
-        <v>0.68</v>
+        <v>49.84</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -9507,18 +9507,18 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0.02</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1393301698</v>
+        <v>1373808226</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9527,35 +9527,35 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.1401</v>
+        <v>0.0234</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45476.6587916088</v>
       </c>
       <c r="G142" t="n">
-        <v>5.99</v>
+        <v>459.24</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I142" t="n">
-        <v>6.176</v>
+        <v>434.71</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0.84</v>
+        <v>10.75</v>
       </c>
       <c r="M142" t="n">
-        <v>0.87</v>
+        <v>10.17</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -9570,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>0.03</v>
+        <v>-0.58</v>
       </c>
       <c r="U142" t="inlineStr"/>
     </row>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.01</v>
+        <v>0.0372</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>45523.66633670139</v>
@@ -9599,10 +9599,10 @@
         <v>419.46</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>45785.65885817129</v>
+        <v>45784.77664918981</v>
       </c>
       <c r="I143" t="n">
-        <v>437.05</v>
+        <v>434.71</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4.19</v>
+        <v>15.6</v>
       </c>
       <c r="M143" t="n">
-        <v>4.37</v>
+        <v>16.17</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -9633,18 +9633,18 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>1403180427</v>
+        <v>1426782063</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9653,35 +9653,35 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.4203</v>
+        <v>0.01</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45523.66633670139</v>
       </c>
       <c r="G144" t="n">
-        <v>5.989</v>
+        <v>419.46</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45785.65885817129</v>
       </c>
       <c r="I144" t="n">
-        <v>6.176</v>
+        <v>437.05</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.52</v>
+        <v>4.19</v>
       </c>
       <c r="M144" t="n">
-        <v>2.6</v>
+        <v>4.37</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -9696,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="U144" t="inlineStr"/>
     </row>
@@ -14364,22 +14364,50 @@
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
+      <c r="B219" t="n">
+        <v>1811432805</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>45785.66143194444</v>
+      </c>
+      <c r="G219" t="n">
+        <v>128.46</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>45887.64704395834</v>
+      </c>
+      <c r="I219" t="n">
+        <v>215.19</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>6</v>
+      </c>
+      <c r="M219" t="n">
+        <v>10.05</v>
+      </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
@@ -14387,15 +14415,743 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0</v>
+      </c>
+      <c r="T219" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="n">
+        <v>1843469729</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>45804.66615434028</v>
+      </c>
+      <c r="G220" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>45887.64704395834</v>
+      </c>
+      <c r="I220" t="n">
+        <v>215.19</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="M220" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="n">
+        <v>1845431561</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>45805.66210747686</v>
+      </c>
+      <c r="G221" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>45897.72358047454</v>
+      </c>
+      <c r="I221" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="n">
+        <v>1932757037</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>45859.74017818287</v>
+      </c>
+      <c r="G222" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>45897.72358047454</v>
+      </c>
+      <c r="I222" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M222" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="n">
+        <v>1955448954</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>45873.6472281713</v>
+      </c>
+      <c r="G223" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>45897.72358047454</v>
+      </c>
+      <c r="I223" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M223" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="n">
+        <v>1970057305</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>45881.70511153936</v>
+      </c>
+      <c r="G224" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>45897.72358047454</v>
+      </c>
+      <c r="I224" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="M224" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="n">
+        <v>1566610015</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>45632.87667065972</v>
+      </c>
+      <c r="G225" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>45898.65353149306</v>
+      </c>
+      <c r="I225" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="M225" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="n">
+        <v>1566610015</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>45632.87667065972</v>
+      </c>
+      <c r="G226" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>45898.65353875</v>
+      </c>
+      <c r="I226" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M226" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="n">
+        <v>1582714896</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>45645.89066243055</v>
+      </c>
+      <c r="G227" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>45898.65353875</v>
+      </c>
+      <c r="I227" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>xStation Mobile Android</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M227" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="n">
+        <v>0</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="n">
+        <v>1599449649</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>45663.73562508102</v>
+      </c>
+      <c r="G228" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>45898.65353875</v>
+      </c>
+      <c r="I228" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M228" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="U228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="n">
+        <v>1867461578</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>BAP</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>45818.90835054398</v>
+      </c>
+      <c r="G229" t="n">
+        <v>216.54</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>45902.65487939815</v>
+      </c>
+      <c r="I229" t="n">
+        <v>255.13</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="M229" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0</v>
+      </c>
+      <c r="T229" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="U229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>1712850989</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>45734.85576756945</v>
+      </c>
+      <c r="G230" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>45910.86976126157</v>
+      </c>
+      <c r="I230" t="n">
+        <v>239.3</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M230" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S219" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" t="n">
-        <v>124.35</v>
-      </c>
-      <c r="U219" t="inlineStr"/>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>142.91</v>
+      </c>
+      <c r="U231" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -542,11 +542,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1345716305</v>
+        <v>1393281432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,35 +555,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0171</v>
+        <v>0.632</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45448.6458705787</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G2" t="n">
-        <v>1184.19</v>
+        <v>5.981</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45452.49530114583</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I2" t="n">
-        <v>1184.19</v>
+        <v>5.967</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>20.25</v>
+        <v>3.78</v>
       </c>
       <c r="M2" t="n">
-        <v>20.25</v>
+        <v>3.77</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -598,22 +598,18 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>STC Transfer Out</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1342063955</v>
+        <v>1393281260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -622,35 +618,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4139</v>
+        <v>0.5612</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45446.37534833333</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G3" t="n">
-        <v>33.545</v>
+        <v>5.812</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45453.66360037037</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I3" t="n">
-        <v>32.605</v>
+        <v>5.81</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>15.15</v>
+        <v>3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>14.42</v>
+        <v>3.26</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -665,18 +661,18 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1350877137</v>
+        <v>1393281260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -685,41 +681,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.555</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45453.90555224537</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G4" t="n">
-        <v>38900</v>
+        <v>5.812</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45453.90972410879</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I4" t="n">
-        <v>38869</v>
+        <v>5.801</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>pending(t/p|s/l)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>38874</v>
-      </c>
-      <c r="O4" t="n">
-        <v>38933</v>
-      </c>
-      <c r="P4" t="n">
-        <v>9.73</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -730,22 +724,18 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1357581812</v>
+        <v>1393281432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -754,35 +744,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.123</v>
+        <v>0.4344</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45460.64587106481</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>5.981</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45460.73847521991</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I5" t="n">
-        <v>165.24</v>
+        <v>5.968</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>20.32</v>
+        <v>2.59</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -797,18 +787,18 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1343394966</v>
+        <v>1393281260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -820,32 +810,32 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45446.90410443287</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G6" t="n">
-        <v>13.37</v>
+        <v>5.812</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45460.88503490741</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I6" t="n">
-        <v>12.62</v>
+        <v>5.814</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>13.37</v>
+        <v>5.81</v>
       </c>
       <c r="M6" t="n">
-        <v>12.62</v>
+        <v>5.81</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -860,18 +850,18 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1349530190</v>
+        <v>1393281432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -880,35 +870,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G7" t="n">
-        <v>118.42</v>
+        <v>5.981</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45464.64586856482</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I7" t="n">
-        <v>126.75</v>
+        <v>5.978</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14.21</v>
+        <v>5.98</v>
       </c>
       <c r="M7" t="n">
-        <v>15.21</v>
+        <v>5.98</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -923,22 +913,18 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1343379129</v>
+        <v>1393281260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -947,35 +933,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0975</v>
+        <v>0.4206</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45446.89366082176</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G8" t="n">
-        <v>205.08</v>
+        <v>5.812</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45464.6458686574</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I8" t="n">
-        <v>211.24</v>
+        <v>5.826</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>2.44</v>
       </c>
       <c r="M8" t="n">
-        <v>20.6</v>
+        <v>2.45</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -990,14 +976,14 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6</v>
+        <v>0.01</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1349530190</v>
+        <v>1345716305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1010,35 +996,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.051</v>
+        <v>0.0171</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45448.6458705787</v>
       </c>
       <c r="G9" t="n">
-        <v>118.42</v>
+        <v>1184.19</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45464.64586949074</v>
+        <v>45452.49530114583</v>
       </c>
       <c r="I9" t="n">
-        <v>126.76</v>
+        <v>1184.19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>correction</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>6.04</v>
+        <v>20.25</v>
       </c>
       <c r="M9" t="n">
-        <v>6.46</v>
+        <v>20.25</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1053,22 +1039,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>NVDA.US split 10 for 1</t>
+          <t>STC Transfer Out</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1357737013</v>
+        <v>1393281432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1077,35 +1063,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0115</v>
+        <v>0.4033</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45460.68557657408</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G10" t="n">
-        <v>1797.13</v>
+        <v>5.981</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45464.65982668981</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I10" t="n">
-        <v>1686.26</v>
+        <v>5.98</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>20.67</v>
+        <v>2.41</v>
       </c>
       <c r="M10" t="n">
-        <v>19.39</v>
+        <v>2.41</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1120,18 +1106,18 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1362492338</v>
+        <v>1393281432</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1140,35 +1126,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2806</v>
+        <v>0.4201</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45464.66150739583</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G11" t="n">
-        <v>71.61</v>
+        <v>5.981</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45464.66725368056</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I11" t="n">
-        <v>70.95999999999999</v>
+        <v>5.98</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>20.09</v>
+        <v>2.51</v>
       </c>
       <c r="M11" t="n">
-        <v>19.91</v>
+        <v>2.51</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1183,18 +1169,18 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1342641165</v>
+        <v>1342063955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,19 +1189,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1322</v>
+        <v>0.4139</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45446.64586891203</v>
+        <v>45446.37534833333</v>
       </c>
       <c r="G12" t="n">
-        <v>155.59</v>
+        <v>33.545</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45478.65186430555</v>
+        <v>45453.66360037037</v>
       </c>
       <c r="I12" t="n">
-        <v>183.6</v>
+        <v>32.605</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1228,10 +1214,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>20.57</v>
+        <v>15.15</v>
       </c>
       <c r="M12" t="n">
-        <v>24.27</v>
+        <v>14.42</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1246,18 +1232,18 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>-0.73</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1347626622</v>
+        <v>1393281432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1266,35 +1252,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1488</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G13" t="n">
-        <v>67.2</v>
+        <v>5.981</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I13" t="n">
-        <v>69.65000000000001</v>
+        <v>6.186</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>5.98</v>
       </c>
       <c r="M13" t="n">
-        <v>10.36</v>
+        <v>6.19</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1309,18 +1295,18 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1362562387</v>
+        <v>1393281260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1329,35 +1315,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.202</v>
+        <v>1.4632</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G14" t="n">
-        <v>100.78</v>
+        <v>5.812</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I14" t="n">
-        <v>100.83</v>
+        <v>6.02</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>20.36</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>20.37</v>
+        <v>8.81</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1372,18 +1358,18 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1362488938</v>
+        <v>1393287040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1392,35 +1378,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2742</v>
+        <v>0.2503</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G15" t="n">
-        <v>72.93000000000001</v>
+        <v>5.811</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I15" t="n">
-        <v>72.29000000000001</v>
+        <v>6.02</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>19.82</v>
+        <v>1.51</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1435,18 +1421,18 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.18</v>
+        <v>0.06</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1375967973</v>
+        <v>1350877137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>US30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1455,19 +1441,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.109</v>
+        <v>0.01</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45453.90555224537</v>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>38900</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45453.90972410879</v>
       </c>
       <c r="I16" t="n">
-        <v>186.5</v>
+        <v>38869</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1476,18 +1462,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+          <t>pending(t/p|s/l)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>38874</v>
+      </c>
+      <c r="O16" t="n">
+        <v>38933</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9.73</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -1498,18 +1486,22 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>-1.55</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1375856858</v>
+        <v>1403180431</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1510,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1052</v>
+        <v>0.2773</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G17" t="n">
-        <v>188.48</v>
+        <v>5.84</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I17" t="n">
-        <v>189.21</v>
+        <v>6.02</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>19.83</v>
+        <v>1.62</v>
       </c>
       <c r="M17" t="n">
-        <v>19.9</v>
+        <v>1.67</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1553,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1357595824</v>
+        <v>1403180445</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1581,35 +1573,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.0092</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G18" t="n">
-        <v>22.89</v>
+        <v>5.836</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I18" t="n">
-        <v>18.62</v>
+        <v>6.02</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>22.89</v>
+        <v>0.05</v>
       </c>
       <c r="M18" t="n">
-        <v>18.62</v>
+        <v>0.06</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1616,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.27</v>
+        <v>0.01</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1375967973</v>
+        <v>1393735509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1636,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0014</v>
+        <v>0.0366</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>67.37</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I19" t="n">
-        <v>182.97</v>
+        <v>71.16</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.26</v>
+        <v>2.47</v>
       </c>
       <c r="M19" t="n">
-        <v>0.26</v>
+        <v>2.6</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1687,18 +1679,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1377834040</v>
+        <v>1395218355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,35 +1699,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1077</v>
+        <v>0.074</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G20" t="n">
-        <v>186.7</v>
+        <v>67.13</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I20" t="n">
-        <v>182.97</v>
+        <v>71.16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>20.11</v>
+        <v>4.97</v>
       </c>
       <c r="M20" t="n">
-        <v>19.71</v>
+        <v>5.27</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1742,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.39</v>
+        <v>0.3</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1377407433</v>
+        <v>1403166009</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1762,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0771</v>
+        <v>0.0362</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G21" t="n">
-        <v>129.48</v>
+        <v>68.05</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I21" t="n">
-        <v>130.75</v>
+        <v>71.16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.98</v>
+        <v>2.46</v>
       </c>
       <c r="M21" t="n">
-        <v>10.08</v>
+        <v>2.58</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1805,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1377407433</v>
+        <v>1403177543</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1825,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0001</v>
+        <v>0.0368</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G22" t="n">
-        <v>129.48</v>
+        <v>68.045</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I22" t="n">
-        <v>131.24</v>
+        <v>71.16</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01</v>
+        <v>2.62</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1868,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1377834040</v>
+        <v>1357581812</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,19 +1888,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0011</v>
+        <v>0.123</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45460.64587106481</v>
       </c>
       <c r="G23" t="n">
-        <v>186.7</v>
+        <v>1.65</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45460.73847521991</v>
       </c>
       <c r="I23" t="n">
-        <v>184.46</v>
+        <v>165.24</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1917,14 +1909,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2</v>
+        <v>20.32</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1931,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1362491459</v>
+        <v>1403180429</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,35 +1951,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.228</v>
+        <v>0.0733</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G24" t="n">
-        <v>88.67</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I24" t="n">
-        <v>87.81</v>
+        <v>71.16</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.22</v>
+        <v>4.99</v>
       </c>
       <c r="M24" t="n">
-        <v>20.02</v>
+        <v>5.22</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +1994,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2</v>
+        <v>0.23</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1362491459</v>
+        <v>1403180445</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2014,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0001</v>
+        <v>0.9908</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G25" t="n">
-        <v>88.67</v>
+        <v>5.836</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I25" t="n">
-        <v>87.81999999999999</v>
+        <v>6.027</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.01</v>
+        <v>5.78</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01</v>
+        <v>5.97</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2057,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1375856858</v>
+        <v>1393281432</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,35 +2077,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0026</v>
+        <v>0.1102</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G26" t="n">
-        <v>188.48</v>
+        <v>5.981</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I26" t="n">
-        <v>190.3</v>
+        <v>6.176</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="M26" t="n">
-        <v>0.49</v>
+        <v>0.68</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2128,18 +2120,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1377584836</v>
+        <v>1393301698</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,35 +2140,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4828</v>
+        <v>0.1401</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G27" t="n">
-        <v>41.87</v>
+        <v>5.99</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I27" t="n">
-        <v>42.35</v>
+        <v>6.176</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.21</v>
+        <v>0.84</v>
       </c>
       <c r="M27" t="n">
-        <v>20.45</v>
+        <v>0.87</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2183,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1377584836</v>
+        <v>1403180427</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,35 +2203,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0013</v>
+        <v>0.4203</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G28" t="n">
-        <v>41.87</v>
+        <v>5.989</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I28" t="n">
-        <v>42.35</v>
+        <v>6.176</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.05</v>
+        <v>2.52</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>2.6</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2246,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1350885655</v>
+        <v>1343394966</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,19 +2266,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0234</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45446.90410443287</v>
       </c>
       <c r="G29" t="n">
-        <v>427.17</v>
+        <v>13.37</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45460.88503490741</v>
       </c>
       <c r="I29" t="n">
-        <v>458.18</v>
+        <v>12.62</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2299,10 +2291,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>13.37</v>
       </c>
       <c r="M29" t="n">
-        <v>10.72</v>
+        <v>12.62</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2309,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1414374074</v>
+        <v>1349530190</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,23 +2329,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0481</v>
+        <v>0.12</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G30" t="n">
-        <v>311.85</v>
+        <v>118.42</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45464.64586856482</v>
       </c>
       <c r="I30" t="n">
-        <v>308</v>
+        <v>126.75</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2362,10 +2354,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>14.21</v>
       </c>
       <c r="M30" t="n">
-        <v>14.81</v>
+        <v>15.21</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2372,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="U30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1414372067</v>
+        <v>1343379129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,19 +2396,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0575</v>
+        <v>0.0975</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45446.89366082176</v>
       </c>
       <c r="G31" t="n">
-        <v>260.8</v>
+        <v>205.08</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45464.6458686574</v>
       </c>
       <c r="I31" t="n">
-        <v>290.19</v>
+        <v>211.24</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2421,14 +2417,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M31" t="n">
-        <v>16.69</v>
+        <v>20.6</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2439,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>0.6</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1377764546</v>
+        <v>1349530190</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,23 +2459,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G32" t="n">
-        <v>244.47</v>
+        <v>118.42</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45464.64586949074</v>
       </c>
       <c r="I32" t="n">
-        <v>196.86</v>
+        <v>126.76</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2488,10 +2484,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>19.02</v>
+        <v>6.04</v>
       </c>
       <c r="M32" t="n">
-        <v>15.32</v>
+        <v>6.46</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2502,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="U32" t="inlineStr"/>
+        <v>0.42</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1377764546</v>
+        <v>1357737013</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,19 +2526,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0051</v>
+        <v>0.0115</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45460.68557657408</v>
       </c>
       <c r="G33" t="n">
-        <v>244.47</v>
+        <v>1797.13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45464.65982668981</v>
       </c>
       <c r="I33" t="n">
-        <v>196.91</v>
+        <v>1686.26</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>20.67</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>19.39</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.25</v>
+        <v>-1.28</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1380259753</v>
+        <v>1362492338</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.131</v>
+        <v>0.2806</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45464.66150739583</v>
       </c>
       <c r="G34" t="n">
-        <v>190.71</v>
+        <v>71.61</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45464.66725368056</v>
       </c>
       <c r="I34" t="n">
-        <v>161.87</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>24.98</v>
+        <v>20.09</v>
       </c>
       <c r="M34" t="n">
-        <v>21.2</v>
+        <v>19.91</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,39 +2632,39 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-3.78</v>
+        <v>-0.18</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1509051251</v>
+        <v>1342641165</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.1322</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45446.64586891203</v>
       </c>
       <c r="G35" t="n">
-        <v>19.8731</v>
+        <v>155.59</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45478.65186430555</v>
       </c>
       <c r="I35" t="n">
-        <v>19.8835</v>
+        <v>183.6</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2676,13 +2676,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="M35" t="n">
+        <v>24.27</v>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2693,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1.05</v>
+        <v>3.7</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1508055372</v>
+        <v>1347626622</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2713,19 +2715,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.02</v>
+        <v>0.1488</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G36" t="n">
-        <v>19.8369</v>
+        <v>67.2</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I36" t="n">
-        <v>19.8761</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2737,13 +2739,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10.36</v>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -2754,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.94</v>
+        <v>0.36</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1512925323</v>
+        <v>1362562387</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2774,19 +2778,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>0.202</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G37" t="n">
-        <v>20.0663</v>
+        <v>100.78</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I37" t="n">
-        <v>20.1405</v>
+        <v>100.83</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2798,56 +2802,58 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20.37</v>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>5</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.68</v>
+        <v>0.01</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1514707570</v>
+        <v>1362488938</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01</v>
+        <v>0.2742</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45595.88186449074</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G38" t="n">
-        <v>20.1597</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45595.94583810185</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I38" t="n">
-        <v>20.1911</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2859,17 +2865,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="O38" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>5</v>
-      </c>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2880,43 +2884,39 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.18</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1516787001</v>
+        <v>1375967973</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01</v>
+        <v>0.109</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G39" t="n">
-        <v>2748.04</v>
+        <v>183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I39" t="n">
-        <v>2747.79</v>
+        <v>186.5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2928,13 +2928,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20.33</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -2945,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1516790032</v>
+        <v>1375856858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2965,19 +2967,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.01</v>
+        <v>0.1052</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45597.13541888889</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G40" t="n">
-        <v>2747.23</v>
+        <v>188.48</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45597.13874358797</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I40" t="n">
-        <v>2747.25</v>
+        <v>189.21</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2989,13 +2991,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="M40" t="n">
+        <v>19.9</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -3006,39 +3010,39 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1516793905</v>
+        <v>1357595824</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45597.14024802083</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G41" t="n">
-        <v>2747.11</v>
+        <v>22.89</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45597.14548700232</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I41" t="n">
-        <v>2747.77</v>
+        <v>18.62</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3050,13 +3054,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="M41" t="n">
+        <v>18.62</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -3067,18 +3073,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.66</v>
+        <v>-4.27</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1516796610</v>
+        <v>1375967973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3087,19 +3093,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>0.0014</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45597.14556364583</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G42" t="n">
-        <v>2748.12</v>
+        <v>183</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45597.14936810185</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I42" t="n">
-        <v>2746.29</v>
+        <v>182.97</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3111,13 +3117,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.26</v>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -3128,39 +3136,39 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1516798655</v>
+        <v>1377834040</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>0.1077</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45597.14949375</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G43" t="n">
-        <v>2746.13</v>
+        <v>186.7</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45597.15075293981</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I43" t="n">
-        <v>2747.4</v>
+        <v>182.97</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3172,13 +3180,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="M43" t="n">
+        <v>19.71</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>13.73</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -3189,18 +3199,18 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.27</v>
+        <v>-0.39</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1393281432</v>
+        <v>1377407433</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3209,35 +3219,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.632</v>
+        <v>0.0771</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G44" t="n">
-        <v>5.981</v>
+        <v>129.48</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I44" t="n">
-        <v>5.967</v>
+        <v>130.75</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.78</v>
+        <v>9.98</v>
       </c>
       <c r="M44" t="n">
-        <v>3.77</v>
+        <v>10.08</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3252,18 +3262,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1516805560</v>
+        <v>1377407433</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3272,37 +3282,39 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>45481.65801625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>129.48</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45482.91500505787</v>
+      </c>
+      <c r="I45" t="n">
+        <v>131.24</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
         <v>0.01</v>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>45597.16385188657</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2748.03</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>45597.16756914352</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2748.36</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0.01</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -3313,18 +3325,18 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1393281260</v>
+        <v>1377834040</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3333,35 +3345,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.5612</v>
+        <v>0.0011</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G46" t="n">
-        <v>5.812</v>
+        <v>186.7</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I46" t="n">
-        <v>5.81</v>
+        <v>184.46</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.26</v>
+        <v>0.21</v>
       </c>
       <c r="M46" t="n">
-        <v>3.26</v>
+        <v>0.2</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3376,18 +3388,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1516814771</v>
+        <v>1362491459</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3396,19 +3408,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0.228</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45597.18416002315</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G47" t="n">
-        <v>2749.48</v>
+        <v>88.67</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45597.18971934028</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I47" t="n">
-        <v>2749.54</v>
+        <v>87.81</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3420,13 +3432,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="M47" t="n">
+        <v>20.02</v>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>13.75</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
@@ -3437,18 +3451,18 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1393281260</v>
+        <v>1362491459</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3457,35 +3471,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.555</v>
+        <v>0.0001</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G48" t="n">
-        <v>5.812</v>
+        <v>88.67</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45483.77897271991</v>
       </c>
       <c r="I48" t="n">
-        <v>5.801</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.23</v>
+        <v>0.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>0.01</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -3500,18 +3514,18 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1393281432</v>
+        <v>1375856858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3520,35 +3534,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.4344</v>
+        <v>0.0026</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G49" t="n">
-        <v>5.981</v>
+        <v>188.48</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I49" t="n">
-        <v>5.968</v>
+        <v>190.3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.6</v>
+        <v>0.49</v>
       </c>
       <c r="M49" t="n">
-        <v>2.59</v>
+        <v>0.49</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3563,18 +3577,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1393281260</v>
+        <v>1377584836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3583,35 +3597,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.4828</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G50" t="n">
-        <v>5.812</v>
+        <v>41.87</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I50" t="n">
-        <v>5.814</v>
+        <v>42.35</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5.81</v>
+        <v>20.21</v>
       </c>
       <c r="M50" t="n">
-        <v>5.81</v>
+        <v>20.45</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -3626,18 +3640,18 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1393281432</v>
+        <v>1377584836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3646,35 +3660,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.0013</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G51" t="n">
-        <v>5.981</v>
+        <v>41.87</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I51" t="n">
-        <v>5.978</v>
+        <v>42.35</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>5.98</v>
+        <v>0.05</v>
       </c>
       <c r="M51" t="n">
-        <v>5.98</v>
+        <v>0.06</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3689,18 +3703,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1516838270</v>
+        <v>1350885655</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3709,19 +3723,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.01</v>
+        <v>0.0234</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45597.23811159722</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G52" t="n">
-        <v>2751.84</v>
+        <v>427.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45597.56254815972</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I52" t="n">
-        <v>2756.23</v>
+        <v>458.18</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3733,15 +3747,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>10.72</v>
+      </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>2754.07</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.76</v>
-      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
@@ -3752,22 +3766,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>[T/P]</t>
-        </is>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1393281260</v>
+        <v>1414374074</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3776,35 +3786,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.4206</v>
+        <v>0.0481</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G53" t="n">
-        <v>5.812</v>
+        <v>311.85</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I53" t="n">
-        <v>5.826</v>
+        <v>308</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.44</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>2.45</v>
+        <v>14.81</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -3819,18 +3829,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.01</v>
+        <v>-0.19</v>
       </c>
       <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1393281432</v>
+        <v>1414372067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3839,35 +3849,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4033</v>
+        <v>0.0575</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G54" t="n">
-        <v>5.981</v>
+        <v>260.8</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I54" t="n">
-        <v>5.98</v>
+        <v>290.19</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L54" t="n">
-        <v>2.41</v>
+        <v>15</v>
       </c>
       <c r="M54" t="n">
-        <v>2.41</v>
+        <v>16.69</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3882,18 +3892,18 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1515520253</v>
+        <v>1377764546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3902,19 +3912,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45596.55812129629</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G55" t="n">
-        <v>20.0901</v>
+        <v>244.47</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45597.73077199074</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I55" t="n">
-        <v>20.0775</v>
+        <v>196.86</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3926,35 +3936,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="M55" t="n">
+        <v>15.32</v>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>5</v>
-      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-0.63</v>
+        <v>-3.7</v>
       </c>
       <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1393281432</v>
+        <v>1377764546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3963,35 +3975,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.4201</v>
+        <v>0.0051</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G56" t="n">
-        <v>5.981</v>
+        <v>244.47</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I56" t="n">
-        <v>5.98</v>
+        <v>196.91</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.51</v>
+        <v>1.25</v>
       </c>
       <c r="M56" t="n">
-        <v>2.51</v>
+        <v>1</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4006,18 +4018,18 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1393281432</v>
+        <v>1380259753</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4026,35 +4038,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.131</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G57" t="n">
-        <v>5.981</v>
+        <v>190.71</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I57" t="n">
-        <v>6.186</v>
+        <v>161.87</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.98</v>
+        <v>24.98</v>
       </c>
       <c r="M57" t="n">
-        <v>6.19</v>
+        <v>21.2</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -4069,14 +4081,14 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.21</v>
+        <v>-3.78</v>
       </c>
       <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1517450167</v>
+        <v>1509051251</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4085,23 +4097,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45597.59638905092</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G58" t="n">
-        <v>19.9771</v>
+        <v>19.8731</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45597.73077270833</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I58" t="n">
-        <v>20.0775</v>
+        <v>19.8835</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4118,7 +4130,7 @@
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4130,18 +4142,18 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>5</v>
+        <v>-1.05</v>
       </c>
       <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1393281260</v>
+        <v>1508055372</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4150,39 +4162,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1.4632</v>
+        <v>0.02</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G59" t="n">
-        <v>5.812</v>
+        <v>19.8369</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I59" t="n">
-        <v>6.02</v>
+        <v>19.8761</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>8.81</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
@@ -4193,18 +4203,18 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.3</v>
+        <v>3.94</v>
       </c>
       <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1393287040</v>
+        <v>1512925323</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4213,57 +4223,55 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.2503</v>
+        <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G60" t="n">
-        <v>5.811</v>
+        <v>20.0663</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I60" t="n">
-        <v>6.02</v>
+        <v>20.1405</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1.51</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>5</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.06</v>
+        <v>3.68</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1517930572</v>
+        <v>1514707570</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4279,16 +4287,16 @@
         <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45597.73038726852</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G61" t="n">
-        <v>20.078</v>
+        <v>20.1597</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45597.73089077546</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I61" t="n">
-        <v>20.082</v>
+        <v>20.1911</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4302,8 +4310,12 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O61" t="n">
+        <v>20.12</v>
+      </c>
       <c r="P61" t="n">
         <v>5</v>
       </c>
@@ -4317,59 +4329,61 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1403180431</v>
+        <v>1516787001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2773</v>
+        <v>0.01</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G62" t="n">
-        <v>5.84</v>
+        <v>2748.04</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I62" t="n">
-        <v>6.02</v>
+        <v>2747.79</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1.67</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4380,18 +4394,18 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1403180445</v>
+        <v>1516790032</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4400,39 +4414,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.0092</v>
+        <v>0.01</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45597.13541888889</v>
       </c>
       <c r="G63" t="n">
-        <v>5.836</v>
+        <v>2747.23</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45597.13874358797</v>
       </c>
       <c r="I63" t="n">
-        <v>6.02</v>
+        <v>2747.25</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.06</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
@@ -4443,59 +4455,57 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1393735509</v>
+        <v>1516793905</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0366</v>
+        <v>0.01</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45597.14024802083</v>
       </c>
       <c r="G64" t="n">
-        <v>67.37</v>
+        <v>2747.11</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.14548700232</v>
       </c>
       <c r="I64" t="n">
-        <v>71.16</v>
+        <v>2747.77</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M64" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -4506,18 +4516,18 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0.13</v>
+        <v>-0.66</v>
       </c>
       <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1395218355</v>
+        <v>1516796610</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4526,39 +4536,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.074</v>
+        <v>0.01</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45597.14556364583</v>
       </c>
       <c r="G65" t="n">
-        <v>67.13</v>
+        <v>2748.12</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.14936810185</v>
       </c>
       <c r="I65" t="n">
-        <v>71.16</v>
+        <v>2746.29</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M65" t="n">
-        <v>5.27</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
@@ -4569,39 +4577,39 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0.3</v>
+        <v>-1.83</v>
       </c>
       <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1517879253</v>
+        <v>1516798655</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>0.01</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45597.7055271875</v>
+        <v>45597.14949375</v>
       </c>
       <c r="G66" t="n">
-        <v>20.08</v>
+        <v>2746.13</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45600.68392239583</v>
+        <v>45597.15075293981</v>
       </c>
       <c r="I66" t="n">
-        <v>19.63</v>
+        <v>2747.4</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4610,44 +4618,38 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>stop-out</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
-        <v>20.92</v>
-      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>12.05</v>
+        <v>13.73</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
-        </is>
-      </c>
+        <v>-1.27</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1403166009</v>
+        <v>1516805560</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4656,39 +4658,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0362</v>
+        <v>0.01</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45597.16385188657</v>
       </c>
       <c r="G67" t="n">
-        <v>68.05</v>
+        <v>2748.03</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.16756914352</v>
       </c>
       <c r="I67" t="n">
-        <v>71.16</v>
+        <v>2748.36</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="M67" t="n">
-        <v>2.58</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
@@ -4699,18 +4699,18 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1403177543</v>
+        <v>1516814771</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4719,39 +4719,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0368</v>
+        <v>0.01</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45597.18416002315</v>
       </c>
       <c r="G68" t="n">
-        <v>68.045</v>
+        <v>2749.48</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.18971934028</v>
       </c>
       <c r="I68" t="n">
-        <v>71.16</v>
+        <v>2749.54</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>2.62</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>13.75</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -4762,18 +4760,18 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1403180429</v>
+        <v>1516838270</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4782,39 +4780,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.0733</v>
+        <v>0.01</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45597.23811159722</v>
       </c>
       <c r="G69" t="n">
-        <v>68.01000000000001</v>
+        <v>2751.84</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45597.56254815972</v>
       </c>
       <c r="I69" t="n">
-        <v>71.16</v>
+        <v>2756.23</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M69" t="n">
-        <v>5.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>2754.07</v>
+      </c>
+      <c r="P69" t="n">
+        <v>13.76</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -4825,18 +4823,22 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="U69" t="inlineStr"/>
+        <v>4.39</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>[T/P]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1403180445</v>
+        <v>1515520253</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4845,61 +4847,59 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9908</v>
+        <v>0.01</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45596.55812129629</v>
       </c>
       <c r="G70" t="n">
-        <v>5.836</v>
+        <v>20.0901</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45597.73077199074</v>
       </c>
       <c r="I70" t="n">
-        <v>6.027</v>
+        <v>20.0775</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M70" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0.18</v>
+        <v>-0.63</v>
       </c>
       <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1379227659</v>
+        <v>1517450167</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4908,19 +4908,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.1521</v>
+        <v>0.01</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45482.9158127199</v>
+        <v>45597.59638905092</v>
       </c>
       <c r="G71" t="n">
-        <v>131.38</v>
+        <v>19.9771</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45603.87158311343</v>
+        <v>45597.73077270833</v>
       </c>
       <c r="I71" t="n">
-        <v>148.18</v>
+        <v>20.0775</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4932,15 +4932,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="M71" t="n">
-        <v>22.54</v>
-      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>5</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
@@ -4951,59 +4949,57 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1393281432</v>
+        <v>1517930572</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.1102</v>
+        <v>0.01</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45597.73038726852</v>
       </c>
       <c r="G72" t="n">
-        <v>5.981</v>
+        <v>20.078</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45597.73089077546</v>
       </c>
       <c r="I72" t="n">
-        <v>6.176</v>
+        <v>20.082</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0.68</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>5</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
@@ -5014,18 +5010,18 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1393301698</v>
+        <v>1517879253</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>^VIX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5034,61 +5030,65 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.1401</v>
+        <v>0.01</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45597.7055271875</v>
       </c>
       <c r="G73" t="n">
-        <v>5.99</v>
+        <v>20.08</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45600.68392239583</v>
       </c>
       <c r="I73" t="n">
-        <v>6.176</v>
+        <v>19.63</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.87</v>
-      </c>
+          <t>stop-out</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="P73" t="n">
+        <v>12.05</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U73" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>[S/O 29.63% 3.57 / 12.05 (USD)]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1403180427</v>
+        <v>1379227659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5097,35 +5097,35 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.4203</v>
+        <v>0.1521</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45482.9158127199</v>
       </c>
       <c r="G74" t="n">
-        <v>5.989</v>
+        <v>131.38</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45603.87158311343</v>
       </c>
       <c r="I74" t="n">
-        <v>6.176</v>
+        <v>148.18</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.52</v>
+        <v>19.98</v>
       </c>
       <c r="M74" t="n">
-        <v>2.6</v>
+        <v>22.54</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>0.08</v>
+        <v>2.56</v>
       </c>
       <c r="U74" t="inlineStr"/>
     </row>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U231"/>
+  <dimension ref="A1:U259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,11 +542,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1393281432</v>
+        <v>1345716305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,35 +555,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.632</v>
+        <v>0.0171</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45448.6458705787</v>
       </c>
       <c r="G2" t="n">
-        <v>5.981</v>
+        <v>1184.19</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45452.49530114583</v>
       </c>
       <c r="I2" t="n">
-        <v>5.967</v>
+        <v>1184.19</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.78</v>
+        <v>20.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.77</v>
+        <v>20.25</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -598,18 +598,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>STC Transfer Out</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1393281260</v>
+        <v>1342063955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,35 +622,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.5612</v>
+        <v>0.4139</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45446.37534833333</v>
       </c>
       <c r="G3" t="n">
-        <v>5.812</v>
+        <v>33.545</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45453.66360037037</v>
       </c>
       <c r="I3" t="n">
-        <v>5.81</v>
+        <v>32.605</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.26</v>
+        <v>15.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.26</v>
+        <v>14.42</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -661,18 +665,18 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1393281260</v>
+        <v>1350877137</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>US30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -681,39 +685,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.555</v>
+        <v>0.01</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45453.90555224537</v>
       </c>
       <c r="G4" t="n">
-        <v>5.812</v>
+        <v>38900</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45453.90972410879</v>
       </c>
       <c r="I4" t="n">
-        <v>5.801</v>
+        <v>38869</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+          <t>pending(t/p|s/l)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>38874</v>
+      </c>
+      <c r="O4" t="n">
+        <v>38933</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9.73</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -724,18 +730,22 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>-1.55</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1393281432</v>
+        <v>1357581812</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -744,35 +754,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4344</v>
+        <v>0.123</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45460.64587106481</v>
       </c>
       <c r="G5" t="n">
-        <v>5.981</v>
+        <v>1.65</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45460.73847521991</v>
       </c>
       <c r="I5" t="n">
-        <v>5.968</v>
+        <v>165.24</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.59</v>
+        <v>20.32</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -787,18 +797,18 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1393281260</v>
+        <v>1343394966</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -810,32 +820,32 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45446.90410443287</v>
       </c>
       <c r="G6" t="n">
-        <v>5.812</v>
+        <v>13.37</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45460.88503490741</v>
       </c>
       <c r="I6" t="n">
-        <v>5.814</v>
+        <v>12.62</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.81</v>
+        <v>13.37</v>
       </c>
       <c r="M6" t="n">
-        <v>5.81</v>
+        <v>12.62</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -850,18 +860,18 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1393281432</v>
+        <v>1349530190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -870,35 +880,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G7" t="n">
-        <v>5.981</v>
+        <v>118.42</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45464.64586856482</v>
       </c>
       <c r="I7" t="n">
-        <v>5.978</v>
+        <v>126.75</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.98</v>
+        <v>14.21</v>
       </c>
       <c r="M7" t="n">
-        <v>5.98</v>
+        <v>15.21</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -913,18 +923,22 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1393281260</v>
+        <v>1343379129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -933,35 +947,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4206</v>
+        <v>0.0975</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45446.89366082176</v>
       </c>
       <c r="G8" t="n">
-        <v>5.812</v>
+        <v>205.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45464.6458686574</v>
       </c>
       <c r="I8" t="n">
-        <v>5.826</v>
+        <v>211.24</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.44</v>
+        <v>20</v>
       </c>
       <c r="M8" t="n">
-        <v>2.45</v>
+        <v>20.6</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -976,14 +990,14 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01</v>
+        <v>0.6</v>
       </c>
       <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1345716305</v>
+        <v>1349530190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -996,35 +1010,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0171</v>
+        <v>0.051</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45448.6458705787</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G9" t="n">
-        <v>1184.19</v>
+        <v>118.42</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45452.49530114583</v>
+        <v>45464.64586949074</v>
       </c>
       <c r="I9" t="n">
-        <v>1184.19</v>
+        <v>126.76</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>20.25</v>
+        <v>6.04</v>
       </c>
       <c r="M9" t="n">
-        <v>20.25</v>
+        <v>6.46</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1039,22 +1053,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>STC Transfer Out</t>
+          <t>NVDA.US split 10 for 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1393281432</v>
+        <v>1357737013</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1063,35 +1077,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4033</v>
+        <v>0.0115</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45460.68557657408</v>
       </c>
       <c r="G10" t="n">
-        <v>5.981</v>
+        <v>1797.13</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45464.65982668981</v>
       </c>
       <c r="I10" t="n">
-        <v>5.98</v>
+        <v>1686.26</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.41</v>
+        <v>20.67</v>
       </c>
       <c r="M10" t="n">
-        <v>2.41</v>
+        <v>19.39</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1106,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="U10" t="inlineStr"/>
     </row>
@@ -1126,7 +1140,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4201</v>
+        <v>0.632</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>45496.37566553241</v>
@@ -1135,10 +1149,10 @@
         <v>5.981</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I11" t="n">
-        <v>5.98</v>
+        <v>5.967</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1151,10 +1165,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.51</v>
+        <v>3.78</v>
       </c>
       <c r="M11" t="n">
-        <v>2.51</v>
+        <v>3.77</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1169,18 +1183,18 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1342063955</v>
+        <v>1362492338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1189,19 +1203,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4139</v>
+        <v>0.2806</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45446.37534833333</v>
+        <v>45464.66150739583</v>
       </c>
       <c r="G12" t="n">
-        <v>33.545</v>
+        <v>71.61</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45453.66360037037</v>
+        <v>45464.66725368056</v>
       </c>
       <c r="I12" t="n">
-        <v>32.605</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1214,10 +1228,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>15.15</v>
+        <v>20.09</v>
       </c>
       <c r="M12" t="n">
-        <v>14.42</v>
+        <v>19.91</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1232,18 +1246,18 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.73</v>
+        <v>-0.18</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1393281432</v>
+        <v>1393281260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1252,19 +1266,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.5612</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G13" t="n">
-        <v>5.981</v>
+        <v>5.812</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I13" t="n">
-        <v>6.186</v>
+        <v>5.81</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1277,10 +1291,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.98</v>
+        <v>3.26</v>
       </c>
       <c r="M13" t="n">
-        <v>6.19</v>
+        <v>3.26</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1295,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
@@ -1315,7 +1329,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.4632</v>
+        <v>0.555</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>45496.37564016203</v>
@@ -1324,10 +1338,10 @@
         <v>5.812</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I14" t="n">
-        <v>6.02</v>
+        <v>5.801</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1340,10 +1354,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>3.23</v>
       </c>
       <c r="M14" t="n">
-        <v>8.81</v>
+        <v>3.22</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1358,18 +1372,18 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3</v>
+        <v>-0.01</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1393287040</v>
+        <v>1342641165</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1378,35 +1392,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2503</v>
+        <v>0.1322</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45446.64586891203</v>
       </c>
       <c r="G15" t="n">
-        <v>5.811</v>
+        <v>155.59</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45478.65186430555</v>
       </c>
       <c r="I15" t="n">
-        <v>6.02</v>
+        <v>183.6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>20.57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.51</v>
+        <v>24.27</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1421,18 +1435,18 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1350877137</v>
+        <v>1393281432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1441,41 +1455,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01</v>
+        <v>0.4344</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45453.90555224537</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G16" t="n">
-        <v>38900</v>
+        <v>5.981</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45453.90972410879</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I16" t="n">
-        <v>38869</v>
+        <v>5.968</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>pending(t/p|s/l)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>38874</v>
-      </c>
-      <c r="O16" t="n">
-        <v>38933</v>
-      </c>
-      <c r="P16" t="n">
-        <v>9.73</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -1486,18 +1498,14 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1403180431</v>
+        <v>1393281260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1510,19 +1518,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.2773</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G17" t="n">
-        <v>5.84</v>
+        <v>5.812</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I17" t="n">
-        <v>6.02</v>
+        <v>5.814</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1535,10 +1543,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>5.81</v>
       </c>
       <c r="M17" t="n">
-        <v>1.67</v>
+        <v>5.81</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1553,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1403180445</v>
+        <v>1393281432</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1573,19 +1581,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0092</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G18" t="n">
-        <v>5.836</v>
+        <v>5.981</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I18" t="n">
-        <v>6.02</v>
+        <v>5.978</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1598,10 +1606,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.05</v>
+        <v>5.98</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06</v>
+        <v>5.98</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1616,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1393735509</v>
+        <v>1393281260</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1636,19 +1644,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0366</v>
+        <v>0.4206</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G19" t="n">
-        <v>67.37</v>
+        <v>5.812</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I19" t="n">
-        <v>71.16</v>
+        <v>5.826</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1661,10 +1669,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1679,18 +1687,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1395218355</v>
+        <v>1347626622</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1699,35 +1707,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.074</v>
+        <v>0.1488</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G20" t="n">
-        <v>67.13</v>
+        <v>67.2</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I20" t="n">
-        <v>71.16</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.97</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>5.27</v>
+        <v>10.36</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1742,18 +1750,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1403166009</v>
+        <v>1393281432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1762,19 +1770,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0362</v>
+        <v>0.4033</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G21" t="n">
-        <v>68.05</v>
+        <v>5.981</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I21" t="n">
-        <v>71.16</v>
+        <v>5.98</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1787,10 +1795,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="M21" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1805,18 +1813,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1403177543</v>
+        <v>1393281432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1825,19 +1833,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0368</v>
+        <v>0.4201</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G22" t="n">
-        <v>68.045</v>
+        <v>5.981</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I22" t="n">
-        <v>71.16</v>
+        <v>5.98</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1850,10 +1858,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1868,18 +1876,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1357581812</v>
+        <v>1362562387</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1888,19 +1896,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.123</v>
+        <v>0.202</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45460.64587106481</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G23" t="n">
-        <v>1.65</v>
+        <v>100.78</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45460.73847521991</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I23" t="n">
-        <v>165.24</v>
+        <v>100.83</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1909,14 +1917,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
+        <v>20.36</v>
       </c>
       <c r="M23" t="n">
-        <v>20.32</v>
+        <v>20.37</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1931,18 +1939,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1403180429</v>
+        <v>1362488938</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1951,35 +1959,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0733</v>
+        <v>0.2742</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G24" t="n">
-        <v>68.01000000000001</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I24" t="n">
-        <v>71.16</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.99</v>
+        <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>5.22</v>
+        <v>19.82</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1994,18 +2002,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1403180445</v>
+        <v>1393281432</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2014,19 +2022,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G25" t="n">
-        <v>5.836</v>
+        <v>5.981</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I25" t="n">
-        <v>6.027</v>
+        <v>6.186</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2039,10 +2047,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.78</v>
+        <v>5.98</v>
       </c>
       <c r="M25" t="n">
-        <v>5.97</v>
+        <v>6.19</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2057,18 +2065,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1393281432</v>
+        <v>1393281260</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2077,19 +2085,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.1102</v>
+        <v>1.4632</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G26" t="n">
-        <v>5.981</v>
+        <v>5.812</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I26" t="n">
-        <v>6.176</v>
+        <v>6.02</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2102,10 +2110,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.66</v>
+        <v>8.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0.68</v>
+        <v>8.81</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2120,18 +2128,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1393301698</v>
+        <v>1393287040</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2140,19 +2148,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.1401</v>
+        <v>0.2503</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G27" t="n">
-        <v>5.99</v>
+        <v>5.811</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I27" t="n">
-        <v>6.176</v>
+        <v>6.02</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2165,10 +2173,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.84</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>0.87</v>
+        <v>1.51</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2183,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1403180427</v>
+        <v>1403180431</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2203,19 +2211,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.4203</v>
+        <v>0.2773</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G28" t="n">
-        <v>5.989</v>
+        <v>5.84</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I28" t="n">
-        <v>6.176</v>
+        <v>6.02</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2228,10 +2236,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.52</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2246,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1343394966</v>
+        <v>1403180445</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2266,35 +2274,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.0092</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45446.90410443287</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G29" t="n">
-        <v>13.37</v>
+        <v>5.836</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45460.88503490741</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I29" t="n">
-        <v>12.62</v>
+        <v>6.02</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>13.37</v>
+        <v>0.05</v>
       </c>
       <c r="M29" t="n">
-        <v>12.62</v>
+        <v>0.06</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2309,18 +2317,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.75</v>
+        <v>0.01</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1349530190</v>
+        <v>1375967973</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2329,23 +2337,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G30" t="n">
-        <v>118.42</v>
+        <v>183</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45464.64586856482</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I30" t="n">
-        <v>126.75</v>
+        <v>186.5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2354,10 +2362,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>14.21</v>
+        <v>19.95</v>
       </c>
       <c r="M30" t="n">
-        <v>15.21</v>
+        <v>20.33</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2372,22 +2380,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1343379129</v>
+        <v>1393735509</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2396,35 +2400,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0975</v>
+        <v>0.0366</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45446.89366082176</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G31" t="n">
-        <v>205.08</v>
+        <v>67.37</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45464.6458686574</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I31" t="n">
-        <v>211.24</v>
+        <v>71.16</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>20</v>
+        <v>2.47</v>
       </c>
       <c r="M31" t="n">
-        <v>20.6</v>
+        <v>2.6</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2439,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.6</v>
+        <v>0.13</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1349530190</v>
+        <v>1395218355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2459,35 +2463,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.051</v>
+        <v>0.074</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G32" t="n">
-        <v>118.42</v>
+        <v>67.13</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45464.64586949074</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I32" t="n">
-        <v>126.76</v>
+        <v>71.16</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.04</v>
+        <v>4.97</v>
       </c>
       <c r="M32" t="n">
-        <v>6.46</v>
+        <v>5.27</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2502,22 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1357737013</v>
+        <v>1403166009</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0115</v>
+        <v>0.0362</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45460.68557657408</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G33" t="n">
-        <v>1797.13</v>
+        <v>68.05</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45464.65982668981</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I33" t="n">
-        <v>1686.26</v>
+        <v>71.16</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>20.67</v>
+        <v>2.46</v>
       </c>
       <c r="M33" t="n">
-        <v>19.39</v>
+        <v>2.58</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-1.28</v>
+        <v>0.12</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1362492338</v>
+        <v>1403177543</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,35 +2589,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2806</v>
+        <v>0.0368</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45464.66150739583</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G34" t="n">
-        <v>71.61</v>
+        <v>68.045</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45464.66725368056</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I34" t="n">
-        <v>70.95999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>20.09</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>19.91</v>
+        <v>2.62</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,18 +2632,18 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.18</v>
+        <v>0.12</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1342641165</v>
+        <v>1403180429</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2652,35 +2652,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.1322</v>
+        <v>0.0733</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45446.64586891203</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G35" t="n">
-        <v>155.59</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45478.65186430555</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I35" t="n">
-        <v>183.6</v>
+        <v>71.16</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>20.57</v>
+        <v>4.99</v>
       </c>
       <c r="M35" t="n">
-        <v>24.27</v>
+        <v>5.22</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2695,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.7</v>
+        <v>0.23</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1347626622</v>
+        <v>1403180445</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2715,35 +2715,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1488</v>
+        <v>0.9908</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G36" t="n">
-        <v>67.2</v>
+        <v>5.836</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I36" t="n">
-        <v>69.65000000000001</v>
+        <v>6.027</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>10</v>
+        <v>5.78</v>
       </c>
       <c r="M36" t="n">
-        <v>10.36</v>
+        <v>5.97</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2758,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1362562387</v>
+        <v>1375856858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2778,19 +2778,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.202</v>
+        <v>0.1052</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G37" t="n">
-        <v>100.78</v>
+        <v>188.48</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I37" t="n">
-        <v>100.83</v>
+        <v>189.21</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>20.36</v>
+        <v>19.83</v>
       </c>
       <c r="M37" t="n">
-        <v>20.37</v>
+        <v>19.9</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2821,18 +2821,18 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1362488938</v>
+        <v>1357595824</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2742</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G38" t="n">
-        <v>72.93000000000001</v>
+        <v>22.89</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I38" t="n">
-        <v>72.29000000000001</v>
+        <v>18.62</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>22.89</v>
       </c>
       <c r="M38" t="n">
-        <v>19.82</v>
+        <v>18.62</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2884,18 +2884,18 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.18</v>
+        <v>-4.27</v>
       </c>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1375967973</v>
+        <v>1393281432</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2904,35 +2904,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.109</v>
+        <v>0.1102</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G39" t="n">
-        <v>183</v>
+        <v>5.981</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I39" t="n">
-        <v>186.5</v>
+        <v>6.176</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19.95</v>
+        <v>0.66</v>
       </c>
       <c r="M39" t="n">
-        <v>20.33</v>
+        <v>0.68</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2947,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.39</v>
+        <v>0.02</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1375856858</v>
+        <v>1393301698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2967,35 +2967,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.1052</v>
+        <v>0.1401</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G40" t="n">
-        <v>188.48</v>
+        <v>5.99</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I40" t="n">
-        <v>189.21</v>
+        <v>6.176</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>19.83</v>
+        <v>0.84</v>
       </c>
       <c r="M40" t="n">
-        <v>19.9</v>
+        <v>0.87</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3010,18 +3010,18 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1357595824</v>
+        <v>1403180427</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3030,35 +3030,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.4203</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G41" t="n">
-        <v>22.89</v>
+        <v>5.989</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I41" t="n">
-        <v>18.62</v>
+        <v>6.176</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>22.89</v>
+        <v>2.52</v>
       </c>
       <c r="M41" t="n">
-        <v>18.62</v>
+        <v>2.6</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-4.27</v>
+        <v>0.08</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
@@ -15120,22 +15120,50 @@
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+      <c r="B231" t="n">
+        <v>1729617775</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0.0546</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>45744.71339717592</v>
+      </c>
+      <c r="G231" t="n">
+        <v>165.35</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>45924.67898291667</v>
+      </c>
+      <c r="I231" t="n">
+        <v>278.82</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="M231" t="n">
+        <v>15.22</v>
+      </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
@@ -15143,15 +15171,1751 @@
         <v>0</v>
       </c>
       <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="U231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="n">
+        <v>1744879358</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>45751.73925931713</v>
+      </c>
+      <c r="G232" t="n">
+        <v>148.09</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>45924.67898291667</v>
+      </c>
+      <c r="I232" t="n">
+        <v>278.82</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="M232" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0</v>
+      </c>
+      <c r="T232" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="U232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="n">
+        <v>1599449649</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>45663.73562508102</v>
+      </c>
+      <c r="G233" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>45924.67923052084</v>
+      </c>
+      <c r="I233" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="n">
+        <v>1648735305</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>45695.85530658565</v>
+      </c>
+      <c r="G234" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="H234" s="2" t="n">
+        <v>45924.67923052084</v>
+      </c>
+      <c r="I234" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>10</v>
+      </c>
+      <c r="M234" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="n">
+        <v>1680994777</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>45716.85705359954</v>
+      </c>
+      <c r="G235" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>45924.67923052084</v>
+      </c>
+      <c r="I235" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="n">
+        <v>1680994777</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0.7231</v>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>45716.85705359954</v>
+      </c>
+      <c r="G236" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>45924.67923574074</v>
+      </c>
+      <c r="I236" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M236" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="n">
+        <v>1701100027</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>45727.87202054398</v>
+      </c>
+      <c r="G237" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>45924.67923574074</v>
+      </c>
+      <c r="I237" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="M237" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>0</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="n">
+        <v>1554741956</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>45623.74951929398</v>
+      </c>
+      <c r="G238" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>45924.69585796296</v>
+      </c>
+      <c r="I238" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="n">
+        <v>0</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="n">
+        <v>1666459175</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>45708.68165283565</v>
+      </c>
+      <c r="G239" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>45924.69585796296</v>
+      </c>
+      <c r="I239" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M239" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>0</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="n">
+        <v>1666459270</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>45708.68166240741</v>
+      </c>
+      <c r="G240" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>45924.69585796296</v>
+      </c>
+      <c r="I240" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M240" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="U240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="n">
+        <v>1817264187</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>45789.64859364583</v>
+      </c>
+      <c r="G241" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>45924.69607174768</v>
+      </c>
+      <c r="I241" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="M241" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="n">
+        <v>1817264187</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>45789.64859364583</v>
+      </c>
+      <c r="G242" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>45924.69624603009</v>
+      </c>
+      <c r="I242" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M242" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="n">
+        <v>1843470413</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>45804.66637241898</v>
+      </c>
+      <c r="G243" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>45924.69624603009</v>
+      </c>
+      <c r="I243" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M243" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="n">
+        <v>1666451221</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>45708.68022618056</v>
+      </c>
+      <c r="G244" t="n">
+        <v>43</v>
+      </c>
+      <c r="H244" s="2" t="n">
+        <v>45924.69906903935</v>
+      </c>
+      <c r="I244" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
+        <v>0</v>
+      </c>
+      <c r="U244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="n">
+        <v>1817256440</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>45789.64787097222</v>
+      </c>
+      <c r="G245" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H245" s="2" t="n">
+        <v>45924.69906903935</v>
+      </c>
+      <c r="I245" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>10</v>
+      </c>
+      <c r="M245" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="n">
+        <v>0</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0</v>
+      </c>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="n">
+        <v>1824477589</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>45792.64732965278</v>
+      </c>
+      <c r="G246" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="H246" s="2" t="n">
+        <v>45924.69906903935</v>
+      </c>
+      <c r="I246" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>10</v>
+      </c>
+      <c r="M246" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="n">
+        <v>0</v>
+      </c>
+      <c r="T246" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="U246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="n">
+        <v>1867195793</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>45818.80180447917</v>
+      </c>
+      <c r="G247" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="H247" s="2" t="n">
+        <v>45924.69906903935</v>
+      </c>
+      <c r="I247" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>10</v>
+      </c>
+      <c r="M247" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="n">
+        <v>0</v>
+      </c>
+      <c r="R247" t="n">
+        <v>0</v>
+      </c>
+      <c r="S247" t="n">
+        <v>0</v>
+      </c>
+      <c r="T247" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>1843468958</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>45804.66597129629</v>
+      </c>
+      <c r="G248" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>45924.70553350695</v>
+      </c>
+      <c r="I248" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="M248" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="n">
+        <v>0</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0</v>
+      </c>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="n">
+        <v>1993384302</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>45896.66850291667</v>
+      </c>
+      <c r="G249" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>45924.70553350695</v>
+      </c>
+      <c r="I249" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>10</v>
+      </c>
+      <c r="M249" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0</v>
+      </c>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="U249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="n">
+        <v>1995846726</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>45897.72549565972</v>
+      </c>
+      <c r="G250" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>45924.70553350695</v>
+      </c>
+      <c r="I250" t="n">
+        <v>72.97</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M250" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="n">
+        <v>0</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0</v>
+      </c>
+      <c r="U250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="n">
+        <v>1582735114</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>45645.90076787037</v>
+      </c>
+      <c r="G251" t="n">
+        <v>130.51</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>45926.83905096065</v>
+      </c>
+      <c r="I251" t="n">
+        <v>151.99</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>xStation Mobile Android</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="n">
+        <v>0</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0</v>
+      </c>
+      <c r="S251" t="n">
+        <v>0</v>
+      </c>
+      <c r="T251" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="n">
+        <v>1867195417</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>45818.80165216435</v>
+      </c>
+      <c r="G252" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>45926.83905096065</v>
+      </c>
+      <c r="I252" t="n">
+        <v>151.99</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="M252" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="n">
+        <v>0</v>
+      </c>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="n">
+        <v>1880445013</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>45825.89222704861</v>
+      </c>
+      <c r="G253" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>45926.83905096065</v>
+      </c>
+      <c r="I253" t="n">
+        <v>151.99</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M253" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="n">
+        <v>0</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0</v>
+      </c>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="U253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="n">
+        <v>1880445013</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>45825.89222704861</v>
+      </c>
+      <c r="G254" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>45929.6523715162</v>
+      </c>
+      <c r="I254" t="n">
+        <v>153.27</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="M254" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="n">
+        <v>0</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0</v>
+      </c>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="n">
+        <v>1882281884</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>45826.76478986111</v>
+      </c>
+      <c r="G255" t="n">
+        <v>138.84</v>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>45929.6523715162</v>
+      </c>
+      <c r="I255" t="n">
+        <v>153.27</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>10</v>
+      </c>
+      <c r="M255" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="n">
+        <v>0</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="U255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="n">
+        <v>1633116336</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>45686.83271512731</v>
+      </c>
+      <c r="G256" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>45932.89700041667</v>
+      </c>
+      <c r="I256" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="M256" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="U256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="n">
+        <v>1993443280</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>45896.67386782407</v>
+      </c>
+      <c r="G257" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>45932.90148762731</v>
+      </c>
+      <c r="I257" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="M257" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="n">
+        <v>1885700231</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>45828.65147913194</v>
+      </c>
+      <c r="G258" t="n">
+        <v>534.86</v>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>45932.90173462963</v>
+      </c>
+      <c r="I258" t="n">
+        <v>578.46</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M258" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S231" t="n">
-        <v>0</v>
-      </c>
-      <c r="T231" t="n">
-        <v>142.91</v>
-      </c>
-      <c r="U231" t="inlineStr"/>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>200.82</v>
+      </c>
+      <c r="U259" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U259"/>
+  <dimension ref="A1:U277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,11 +1127,11 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1393281432</v>
+        <v>1362492338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1140,35 +1140,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.632</v>
+        <v>0.2806</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66150739583</v>
       </c>
       <c r="G11" t="n">
-        <v>5.981</v>
+        <v>71.61</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45464.66725368056</v>
       </c>
       <c r="I11" t="n">
-        <v>5.967</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.78</v>
+        <v>20.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3.77</v>
+        <v>19.91</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1183,18 +1183,18 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1362492338</v>
+        <v>1342641165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2806</v>
+        <v>0.1322</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45464.66150739583</v>
+        <v>45446.64586891203</v>
       </c>
       <c r="G12" t="n">
-        <v>71.61</v>
+        <v>155.59</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45464.66725368056</v>
+        <v>45478.65186430555</v>
       </c>
       <c r="I12" t="n">
-        <v>70.95999999999999</v>
+        <v>183.6</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>20.09</v>
+        <v>20.57</v>
       </c>
       <c r="M12" t="n">
-        <v>19.91</v>
+        <v>24.27</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1246,18 +1246,18 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.18</v>
+        <v>3.7</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1393281260</v>
+        <v>1347626622</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1266,35 +1266,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5612</v>
+        <v>0.1488</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G13" t="n">
-        <v>5.812</v>
+        <v>67.2</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I13" t="n">
-        <v>5.81</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.26</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>3.26</v>
+        <v>10.36</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1309,18 +1309,18 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1393281260</v>
+        <v>1362562387</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1329,35 +1329,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.555</v>
+        <v>0.202</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G14" t="n">
-        <v>5.812</v>
+        <v>100.78</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I14" t="n">
-        <v>5.801</v>
+        <v>100.83</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.23</v>
+        <v>20.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.22</v>
+        <v>20.37</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1372,18 +1372,18 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1342641165</v>
+        <v>1362488938</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.1322</v>
+        <v>0.2742</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45446.64586891203</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G15" t="n">
-        <v>155.59</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45478.65186430555</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I15" t="n">
-        <v>183.6</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20.57</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>24.27</v>
+        <v>19.82</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1435,18 +1435,18 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7</v>
+        <v>-0.18</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1393281432</v>
+        <v>1375967973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1455,35 +1455,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4344</v>
+        <v>0.109</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G16" t="n">
-        <v>5.981</v>
+        <v>183</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I16" t="n">
-        <v>5.968</v>
+        <v>186.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>19.95</v>
       </c>
       <c r="M16" t="n">
-        <v>2.59</v>
+        <v>20.33</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1498,18 +1498,18 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01</v>
+        <v>0.39</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1393281260</v>
+        <v>1375856858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1518,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.1052</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G17" t="n">
-        <v>5.812</v>
+        <v>188.48</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I17" t="n">
-        <v>5.814</v>
+        <v>189.21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.81</v>
+        <v>19.83</v>
       </c>
       <c r="M17" t="n">
-        <v>5.81</v>
+        <v>19.9</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1393281432</v>
+        <v>1357595824</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1584,32 +1584,32 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G18" t="n">
-        <v>5.981</v>
+        <v>22.89</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I18" t="n">
-        <v>5.978</v>
+        <v>18.62</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.98</v>
+        <v>22.89</v>
       </c>
       <c r="M18" t="n">
-        <v>5.98</v>
+        <v>18.62</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-4.27</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1393281260</v>
+        <v>1375967973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1644,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4206</v>
+        <v>0.0014</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G19" t="n">
-        <v>5.812</v>
+        <v>183</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I19" t="n">
-        <v>5.826</v>
+        <v>182.97</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>0.26</v>
       </c>
       <c r="M19" t="n">
-        <v>2.45</v>
+        <v>0.26</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1687,18 +1687,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1347626622</v>
+        <v>1377834040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,19 +1707,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1488</v>
+        <v>0.1077</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G20" t="n">
-        <v>67.2</v>
+        <v>186.7</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I20" t="n">
-        <v>69.65000000000001</v>
+        <v>182.97</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>20.11</v>
       </c>
       <c r="M20" t="n">
-        <v>10.36</v>
+        <v>19.71</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1750,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1393281432</v>
+        <v>1377407433</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1770,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4033</v>
+        <v>0.0771</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G21" t="n">
-        <v>5.981</v>
+        <v>129.48</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I21" t="n">
-        <v>5.98</v>
+        <v>130.75</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.41</v>
+        <v>9.98</v>
       </c>
       <c r="M21" t="n">
-        <v>2.41</v>
+        <v>10.08</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1813,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1393281432</v>
+        <v>1377407433</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1833,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4201</v>
+        <v>0.0001</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G22" t="n">
-        <v>5.981</v>
+        <v>129.48</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45482.91500505787</v>
       </c>
       <c r="I22" t="n">
-        <v>5.98</v>
+        <v>131.24</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>0.01</v>
       </c>
       <c r="M22" t="n">
-        <v>2.51</v>
+        <v>0.01</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1883,11 +1883,11 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1362562387</v>
+        <v>1377834040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.202</v>
+        <v>0.0011</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G23" t="n">
-        <v>100.78</v>
+        <v>186.7</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I23" t="n">
-        <v>100.83</v>
+        <v>184.46</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>20.36</v>
+        <v>0.21</v>
       </c>
       <c r="M23" t="n">
-        <v>20.37</v>
+        <v>0.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1939,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1362488938</v>
+        <v>1362491459</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2742</v>
+        <v>0.228</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G24" t="n">
-        <v>72.93000000000001</v>
+        <v>88.67</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I24" t="n">
-        <v>72.29000000000001</v>
+        <v>87.81</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>20.22</v>
       </c>
       <c r="M24" t="n">
-        <v>19.82</v>
+        <v>20.02</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1393281432</v>
+        <v>1362491459</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.0001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G25" t="n">
-        <v>5.981</v>
+        <v>88.67</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45483.77897271991</v>
       </c>
       <c r="I25" t="n">
-        <v>6.186</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.98</v>
+        <v>0.01</v>
       </c>
       <c r="M25" t="n">
-        <v>6.19</v>
+        <v>0.01</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2065,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1393281260</v>
+        <v>1375856858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,35 +2085,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.4632</v>
+        <v>0.0026</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G26" t="n">
-        <v>5.812</v>
+        <v>188.48</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I26" t="n">
-        <v>6.02</v>
+        <v>190.3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8.5</v>
+        <v>0.49</v>
       </c>
       <c r="M26" t="n">
-        <v>8.81</v>
+        <v>0.49</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2128,18 +2128,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1393287040</v>
+        <v>1377584836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,35 +2148,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2503</v>
+        <v>0.4828</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G27" t="n">
-        <v>5.811</v>
+        <v>41.87</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I27" t="n">
-        <v>6.02</v>
+        <v>42.35</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>20.21</v>
       </c>
       <c r="M27" t="n">
-        <v>1.51</v>
+        <v>20.45</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1403180431</v>
+        <v>1377584836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,35 +2211,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2773</v>
+        <v>0.0013</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G28" t="n">
-        <v>5.84</v>
+        <v>41.87</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I28" t="n">
-        <v>6.02</v>
+        <v>42.35</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>0.05</v>
       </c>
       <c r="M28" t="n">
-        <v>1.67</v>
+        <v>0.06</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1403180445</v>
+        <v>1350885655</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,35 +2274,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0092</v>
+        <v>0.0234</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G29" t="n">
-        <v>5.836</v>
+        <v>427.17</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I29" t="n">
-        <v>6.02</v>
+        <v>458.18</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06</v>
+        <v>10.72</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2317,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.01</v>
+        <v>0.72</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1375967973</v>
+        <v>1414374074</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,19 +2337,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.109</v>
+        <v>0.0481</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G30" t="n">
-        <v>183</v>
+        <v>311.85</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I30" t="n">
-        <v>186.5</v>
+        <v>308</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>19.95</v>
+        <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>20.33</v>
+        <v>14.81</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1393735509</v>
+        <v>1414372067</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,35 +2400,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0366</v>
+        <v>0.0575</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G31" t="n">
-        <v>67.37</v>
+        <v>260.8</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I31" t="n">
-        <v>71.16</v>
+        <v>290.19</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L31" t="n">
-        <v>2.47</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>2.6</v>
+        <v>16.69</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.13</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1395218355</v>
+        <v>1377764546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,35 +2463,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.074</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G32" t="n">
-        <v>67.13</v>
+        <v>244.47</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I32" t="n">
-        <v>71.16</v>
+        <v>196.86</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.97</v>
+        <v>19.02</v>
       </c>
       <c r="M32" t="n">
-        <v>5.27</v>
+        <v>15.32</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3</v>
+        <v>-3.7</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1403166009</v>
+        <v>1377764546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0362</v>
+        <v>0.0051</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G33" t="n">
-        <v>68.05</v>
+        <v>244.47</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I33" t="n">
-        <v>71.16</v>
+        <v>196.91</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>2.58</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1403177543</v>
+        <v>1380259753</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,35 +2589,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0368</v>
+        <v>0.131</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G34" t="n">
-        <v>68.045</v>
+        <v>190.71</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I34" t="n">
-        <v>71.16</v>
+        <v>161.87</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>24.98</v>
       </c>
       <c r="M34" t="n">
-        <v>2.62</v>
+        <v>21.2</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,59 +2632,57 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.12</v>
+        <v>-3.78</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1403180429</v>
+        <v>1509051251</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0733</v>
+        <v>0.02</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G35" t="n">
-        <v>68.01000000000001</v>
+        <v>19.8731</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I35" t="n">
-        <v>71.16</v>
+        <v>19.8835</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5.22</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2695,18 +2693,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.23</v>
+        <v>-1.05</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1403180445</v>
+        <v>1393281432</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2715,19 +2713,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9908</v>
+        <v>0.632</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G36" t="n">
-        <v>5.836</v>
+        <v>5.981</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I36" t="n">
-        <v>6.027</v>
+        <v>5.967</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2740,10 +2738,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.78</v>
+        <v>3.78</v>
       </c>
       <c r="M36" t="n">
-        <v>5.97</v>
+        <v>3.77</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2758,18 +2756,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1375856858</v>
+        <v>1393281260</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2778,35 +2776,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1052</v>
+        <v>0.5612</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G37" t="n">
-        <v>188.48</v>
+        <v>5.812</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I37" t="n">
-        <v>189.21</v>
+        <v>5.81</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>19.83</v>
+        <v>3.26</v>
       </c>
       <c r="M37" t="n">
-        <v>19.9</v>
+        <v>3.26</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2821,18 +2819,18 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1357595824</v>
+        <v>1508055372</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2841,19 +2839,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G38" t="n">
-        <v>22.89</v>
+        <v>19.8369</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I38" t="n">
-        <v>18.62</v>
+        <v>19.8761</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2865,15 +2863,13 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="M38" t="n">
-        <v>18.62</v>
-      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2884,18 +2880,18 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-4.27</v>
+        <v>3.94</v>
       </c>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1393281432</v>
+        <v>1393281260</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2904,19 +2900,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1102</v>
+        <v>0.555</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G39" t="n">
-        <v>5.981</v>
+        <v>5.812</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I39" t="n">
-        <v>6.176</v>
+        <v>5.801</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2929,10 +2925,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.66</v>
+        <v>3.23</v>
       </c>
       <c r="M39" t="n">
-        <v>0.68</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2947,14 +2943,14 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1393301698</v>
+        <v>1393281432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2967,19 +2963,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.1401</v>
+        <v>0.4344</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G40" t="n">
-        <v>5.99</v>
+        <v>5.981</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I40" t="n">
-        <v>6.176</v>
+        <v>5.968</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.84</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0.87</v>
+        <v>2.59</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3010,18 +3006,18 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1403180427</v>
+        <v>1393281260</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3030,19 +3026,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.4203</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G41" t="n">
-        <v>5.989</v>
+        <v>5.812</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I41" t="n">
-        <v>6.176</v>
+        <v>5.814</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3055,10 +3051,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.52</v>
+        <v>5.81</v>
       </c>
       <c r="M41" t="n">
-        <v>2.6</v>
+        <v>5.81</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3073,18 +3069,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1375967973</v>
+        <v>1393281432</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3093,35 +3089,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.0014</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G42" t="n">
-        <v>183</v>
+        <v>5.981</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I42" t="n">
-        <v>182.97</v>
+        <v>5.978</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.26</v>
+        <v>5.98</v>
       </c>
       <c r="M42" t="n">
-        <v>0.26</v>
+        <v>5.98</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3143,11 +3139,11 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1377834040</v>
+        <v>1512925323</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3156,19 +3152,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.1077</v>
+        <v>0.01</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G43" t="n">
-        <v>186.7</v>
+        <v>20.0663</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I43" t="n">
-        <v>182.97</v>
+        <v>20.1405</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3180,37 +3176,35 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="M43" t="n">
-        <v>19.71</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>5</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.39</v>
+        <v>3.68</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1377407433</v>
+        <v>1393281260</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3219,35 +3213,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0771</v>
+        <v>0.4206</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G44" t="n">
-        <v>129.48</v>
+        <v>5.812</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I44" t="n">
-        <v>130.75</v>
+        <v>5.826</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9.98</v>
+        <v>2.44</v>
       </c>
       <c r="M44" t="n">
-        <v>10.08</v>
+        <v>2.45</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3262,18 +3256,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1377407433</v>
+        <v>1393281432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3282,35 +3276,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0001</v>
+        <v>0.4033</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G45" t="n">
-        <v>129.48</v>
+        <v>5.981</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I45" t="n">
-        <v>131.24</v>
+        <v>5.98</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0.01</v>
+        <v>2.41</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01</v>
+        <v>2.41</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -3332,11 +3326,11 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1377834040</v>
+        <v>1393281432</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3345,35 +3339,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0011</v>
+        <v>0.4201</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G46" t="n">
-        <v>186.7</v>
+        <v>5.981</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I46" t="n">
-        <v>184.46</v>
+        <v>5.98</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0.21</v>
+        <v>2.51</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2</v>
+        <v>2.51</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3388,18 +3382,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1362491459</v>
+        <v>1393281432</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3408,35 +3402,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.228</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G47" t="n">
-        <v>88.67</v>
+        <v>5.981</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I47" t="n">
-        <v>87.81</v>
+        <v>6.186</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>20.22</v>
+        <v>5.98</v>
       </c>
       <c r="M47" t="n">
-        <v>20.02</v>
+        <v>6.19</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3451,39 +3445,39 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-0.2</v>
+        <v>0.21</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1362491459</v>
+        <v>1514707570</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0001</v>
+        <v>0.01</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G48" t="n">
-        <v>88.67</v>
+        <v>20.1597</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I48" t="n">
-        <v>87.81999999999999</v>
+        <v>20.1911</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3495,15 +3489,17 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O48" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3514,18 +3510,22 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1375856858</v>
+        <v>1393281260</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3534,35 +3534,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0026</v>
+        <v>1.4632</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G49" t="n">
-        <v>188.48</v>
+        <v>5.812</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I49" t="n">
-        <v>190.3</v>
+        <v>6.02</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0.49</v>
+        <v>8.5</v>
       </c>
       <c r="M49" t="n">
-        <v>0.49</v>
+        <v>8.81</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3577,18 +3577,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1377584836</v>
+        <v>1393287040</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3597,35 +3597,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.4828</v>
+        <v>0.2503</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G50" t="n">
-        <v>41.87</v>
+        <v>5.811</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I50" t="n">
-        <v>42.35</v>
+        <v>6.02</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>20.21</v>
+        <v>1.45</v>
       </c>
       <c r="M50" t="n">
-        <v>20.45</v>
+        <v>1.51</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -3640,18 +3640,18 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1377584836</v>
+        <v>1403180431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3660,35 +3660,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0013</v>
+        <v>0.2773</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G51" t="n">
-        <v>41.87</v>
+        <v>5.84</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I51" t="n">
-        <v>42.35</v>
+        <v>6.02</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.05</v>
+        <v>1.62</v>
       </c>
       <c r="M51" t="n">
-        <v>0.06</v>
+        <v>1.67</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3703,18 +3703,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1350885655</v>
+        <v>1403180445</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3723,35 +3723,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0234</v>
+        <v>0.0092</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G52" t="n">
-        <v>427.17</v>
+        <v>5.836</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I52" t="n">
-        <v>458.18</v>
+        <v>6.02</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="M52" t="n">
-        <v>10.72</v>
+        <v>0.06</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -3766,18 +3766,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.72</v>
+        <v>0.01</v>
       </c>
       <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1414374074</v>
+        <v>1393735509</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3786,35 +3786,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0481</v>
+        <v>0.0366</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G53" t="n">
-        <v>311.85</v>
+        <v>67.37</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I53" t="n">
-        <v>308</v>
+        <v>71.16</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>15</v>
+        <v>2.47</v>
       </c>
       <c r="M53" t="n">
-        <v>14.81</v>
+        <v>2.6</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -3829,18 +3829,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1414372067</v>
+        <v>1395218355</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,23 +3849,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0575</v>
+        <v>0.074</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G54" t="n">
-        <v>260.8</v>
+        <v>67.13</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I54" t="n">
-        <v>290.19</v>
+        <v>71.16</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>15</v>
+        <v>4.97</v>
       </c>
       <c r="M54" t="n">
-        <v>16.69</v>
+        <v>5.27</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3892,18 +3892,18 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.69</v>
+        <v>0.3</v>
       </c>
       <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1377764546</v>
+        <v>1403166009</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3912,35 +3912,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0362</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G55" t="n">
-        <v>244.47</v>
+        <v>68.05</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I55" t="n">
-        <v>196.86</v>
+        <v>71.16</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>19.02</v>
+        <v>2.46</v>
       </c>
       <c r="M55" t="n">
-        <v>15.32</v>
+        <v>2.58</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -3955,18 +3955,18 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>-3.7</v>
+        <v>0.12</v>
       </c>
       <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1377764546</v>
+        <v>1403177543</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3975,35 +3975,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0051</v>
+        <v>0.0368</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G56" t="n">
-        <v>244.47</v>
+        <v>68.045</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I56" t="n">
-        <v>196.91</v>
+        <v>71.16</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>2.62</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4018,18 +4018,18 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.25</v>
+        <v>0.12</v>
       </c>
       <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1380259753</v>
+        <v>1403180429</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4038,35 +4038,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.131</v>
+        <v>0.0733</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G57" t="n">
-        <v>190.71</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I57" t="n">
-        <v>161.87</v>
+        <v>71.16</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>24.98</v>
+        <v>4.99</v>
       </c>
       <c r="M57" t="n">
-        <v>21.2</v>
+        <v>5.22</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -4081,57 +4081,59 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>-3.78</v>
+        <v>0.23</v>
       </c>
       <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1509051251</v>
+        <v>1403180445</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.02</v>
+        <v>0.9908</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G58" t="n">
-        <v>19.8731</v>
+        <v>5.836</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I58" t="n">
-        <v>19.8835</v>
+        <v>6.027</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5.97</v>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>10</v>
-      </c>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
@@ -4142,39 +4144,39 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>-1.05</v>
+        <v>0.18</v>
       </c>
       <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1508055372</v>
+        <v>1516787001</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G59" t="n">
-        <v>19.8369</v>
+        <v>2748.04</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I59" t="n">
-        <v>19.8761</v>
+        <v>2747.79</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4191,7 +4193,7 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>10</v>
+        <v>13.74</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4203,18 +4205,18 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.94</v>
+        <v>0.25</v>
       </c>
       <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1512925323</v>
+        <v>1393281432</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4223,102 +4225,102 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.1102</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G60" t="n">
-        <v>20.0663</v>
+        <v>5.981</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I60" t="n">
-        <v>20.1405</v>
+        <v>6.176</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.68</v>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>5</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3.68</v>
+        <v>0.02</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1514707570</v>
+        <v>1393301698</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>0.1401</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45595.88186449074</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G61" t="n">
-        <v>20.1597</v>
+        <v>5.99</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45595.94583810185</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I61" t="n">
-        <v>20.1911</v>
+        <v>6.176</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="O61" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P61" t="n">
-        <v>5</v>
-      </c>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
@@ -4329,61 +4331,59 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1516787001</v>
+        <v>1403180427</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>0.4203</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G62" t="n">
-        <v>2748.04</v>
+        <v>5.989</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I62" t="n">
-        <v>2747.79</v>
+        <v>6.176</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2.6</v>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>13.74</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="U62" t="inlineStr"/>
     </row>
@@ -16884,22 +16884,50 @@
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
+      <c r="B259" t="n">
+        <v>1995249699</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>45897.61086003472</v>
+      </c>
+      <c r="G259" t="n">
+        <v>87.16500000000001</v>
+      </c>
+      <c r="H259" s="2" t="n">
+        <v>45936.6094418287</v>
+      </c>
+      <c r="I259" t="n">
+        <v>95.56</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="M259" t="n">
+        <v>11.11</v>
+      </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
@@ -16907,15 +16935,1121 @@
         <v>0</v>
       </c>
       <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="n">
+        <v>1744879358</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>45751.73925931713</v>
+      </c>
+      <c r="G260" t="n">
+        <v>148.09</v>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>45936.64745715278</v>
+      </c>
+      <c r="I260" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="M260" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0</v>
+      </c>
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="U260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="n">
+        <v>1970057305</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>45881.70511153936</v>
+      </c>
+      <c r="G261" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>45938.67421793981</v>
+      </c>
+      <c r="I261" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M261" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0</v>
+      </c>
+      <c r="S261" t="n">
+        <v>0</v>
+      </c>
+      <c r="T261" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="n">
+        <v>2017847675</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>45910.65426619213</v>
+      </c>
+      <c r="G262" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>45938.67421793981</v>
+      </c>
+      <c r="I262" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L262" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M262" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0</v>
+      </c>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="n">
+        <v>2042867993</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>45924.680154375</v>
+      </c>
+      <c r="G263" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>45938.67421793981</v>
+      </c>
+      <c r="I263" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M263" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="n">
+        <v>2045990228</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>45925.79958339121</v>
+      </c>
+      <c r="G264" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>45938.67421793981</v>
+      </c>
+      <c r="I264" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="M264" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="U264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="n">
+        <v>1975988073</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>45884.65727951389</v>
+      </c>
+      <c r="G265" t="n">
+        <v>319.83</v>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>45939.75557090278</v>
+      </c>
+      <c r="I265" t="n">
+        <v>391</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="M265" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="n">
+        <v>0</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="n">
+        <v>1975988073</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>45884.65727951389</v>
+      </c>
+      <c r="G266" t="n">
+        <v>319.83</v>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>45939.75563726852</v>
+      </c>
+      <c r="I266" t="n">
+        <v>391</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="M266" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="n">
+        <v>1982267978</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>45889.64851528935</v>
+      </c>
+      <c r="G267" t="n">
+        <v>303.76</v>
+      </c>
+      <c r="H267" s="2" t="n">
+        <v>45939.75563726852</v>
+      </c>
+      <c r="I267" t="n">
+        <v>391</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M267" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="n">
+        <v>1843470413</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>45804.66637241898</v>
+      </c>
+      <c r="G268" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>45939.75800336806</v>
+      </c>
+      <c r="I268" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="M268" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="n">
+        <v>0</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="U268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="n">
+        <v>1867196288</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>45818.80209082176</v>
+      </c>
+      <c r="G269" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>45939.75800336806</v>
+      </c>
+      <c r="I269" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M269" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="U269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="n">
+        <v>1978489328</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>45887.66345528935</v>
+      </c>
+      <c r="G270" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>45940.67282796296</v>
+      </c>
+      <c r="I270" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="M270" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="U270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="n">
+        <v>1499061783</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>45582.73996877314</v>
+      </c>
+      <c r="G271" t="n">
+        <v>232.2</v>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>45940.88685980324</v>
+      </c>
+      <c r="I271" t="n">
+        <v>246.33</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>0</v>
+      </c>
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="n">
+        <v>1712850989</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>45734.85576756945</v>
+      </c>
+      <c r="G272" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>45940.88694511574</v>
+      </c>
+      <c r="I272" t="n">
+        <v>237.71</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="n">
+        <v>1648737122</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>45695.8561993287</v>
+      </c>
+      <c r="G273" t="n">
+        <v>408.33</v>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>45940.88702475694</v>
+      </c>
+      <c r="I273" t="n">
+        <v>514.08</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="n">
+        <v>1867461578</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>BAP</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>45818.90835054398</v>
+      </c>
+      <c r="G274" t="n">
+        <v>216.54</v>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>45940.8871543287</v>
+      </c>
+      <c r="I274" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L274" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="n">
+        <v>0</v>
+      </c>
+      <c r="T274" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="n">
+        <v>1744929368</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>45751.7450085301</v>
+      </c>
+      <c r="G275" t="n">
+        <v>324.48</v>
+      </c>
+      <c r="H275" s="2" t="n">
+        <v>45940.88746283565</v>
+      </c>
+      <c r="I275" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="M275" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="n">
+        <v>0</v>
+      </c>
+      <c r="T275" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="n">
+        <v>1882278057</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>45826.76262896991</v>
+      </c>
+      <c r="G276" t="n">
+        <v>346.61</v>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>45940.88746283565</v>
+      </c>
+      <c r="I276" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L276" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M276" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0</v>
+      </c>
+      <c r="S276" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S259" t="n">
-        <v>0</v>
-      </c>
-      <c r="T259" t="n">
-        <v>200.82</v>
-      </c>
-      <c r="U259" t="inlineStr"/>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>244</v>
+      </c>
+      <c r="U277" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -1253,11 +1253,11 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1347626622</v>
+        <v>1393281432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1266,35 +1266,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1488</v>
+        <v>0.632</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G13" t="n">
-        <v>67.2</v>
+        <v>5.981</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I13" t="n">
-        <v>69.65000000000001</v>
+        <v>5.967</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>3.78</v>
       </c>
       <c r="M13" t="n">
-        <v>10.36</v>
+        <v>3.77</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1309,18 +1309,18 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.36</v>
+        <v>-0.01</v>
       </c>
       <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1362562387</v>
+        <v>1393281260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1329,35 +1329,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.202</v>
+        <v>0.5612</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G14" t="n">
-        <v>100.78</v>
+        <v>5.812</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I14" t="n">
-        <v>100.83</v>
+        <v>5.81</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>20.36</v>
+        <v>3.26</v>
       </c>
       <c r="M14" t="n">
-        <v>20.37</v>
+        <v>3.26</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1372,18 +1372,18 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1362488938</v>
+        <v>1393281260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1392,35 +1392,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2742</v>
+        <v>0.555</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G15" t="n">
-        <v>72.93000000000001</v>
+        <v>5.812</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I15" t="n">
-        <v>72.29000000000001</v>
+        <v>5.801</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>3.23</v>
       </c>
       <c r="M15" t="n">
-        <v>19.82</v>
+        <v>3.22</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1435,18 +1435,18 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1375967973</v>
+        <v>1393281432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1455,35 +1455,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.109</v>
+        <v>0.4344</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>5.981</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I16" t="n">
-        <v>186.5</v>
+        <v>5.968</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>19.95</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>20.33</v>
+        <v>2.59</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1498,18 +1498,18 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.39</v>
+        <v>-0.01</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1375856858</v>
+        <v>1393281260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1518,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1052</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G17" t="n">
-        <v>188.48</v>
+        <v>5.812</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45481.82631694445</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I17" t="n">
-        <v>189.21</v>
+        <v>5.814</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>19.83</v>
+        <v>5.81</v>
       </c>
       <c r="M17" t="n">
-        <v>19.9</v>
+        <v>5.81</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1357595824</v>
+        <v>1393281432</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1584,32 +1584,32 @@
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45460.64611910879</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G18" t="n">
-        <v>22.89</v>
+        <v>5.981</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45482.71325359954</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I18" t="n">
-        <v>18.62</v>
+        <v>5.978</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>22.89</v>
+        <v>5.98</v>
       </c>
       <c r="M18" t="n">
-        <v>18.62</v>
+        <v>5.98</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.27</v>
+        <v>0</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1375967973</v>
+        <v>1393281260</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,35 +1644,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0014</v>
+        <v>0.4206</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>5.812</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I19" t="n">
-        <v>182.97</v>
+        <v>5.826</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.26</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>0.26</v>
+        <v>2.45</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1687,18 +1687,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1377834040</v>
+        <v>1393281432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,35 +1707,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1077</v>
+        <v>0.4033</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G20" t="n">
-        <v>186.7</v>
+        <v>5.981</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45482.72996420139</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I20" t="n">
-        <v>182.97</v>
+        <v>5.98</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>20.11</v>
+        <v>2.41</v>
       </c>
       <c r="M20" t="n">
-        <v>19.71</v>
+        <v>2.41</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,18 +1750,18 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1377407433</v>
+        <v>1393281432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1770,35 +1770,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0771</v>
+        <v>0.4201</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G21" t="n">
-        <v>129.48</v>
+        <v>5.981</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45482.86465565972</v>
+        <v>45504.64158128472</v>
       </c>
       <c r="I21" t="n">
-        <v>130.75</v>
+        <v>5.98</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9.98</v>
+        <v>2.51</v>
       </c>
       <c r="M21" t="n">
-        <v>10.08</v>
+        <v>2.51</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1813,18 +1813,18 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1377407433</v>
+        <v>1393281432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1833,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45481.65801625</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G22" t="n">
-        <v>129.48</v>
+        <v>5.981</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45482.91500505787</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I22" t="n">
-        <v>131.24</v>
+        <v>6.186</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>5.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01</v>
+        <v>6.19</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1876,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1377834040</v>
+        <v>1393281260</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,35 +1896,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0011</v>
+        <v>1.4632</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45481.83128234954</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G23" t="n">
-        <v>186.7</v>
+        <v>5.812</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45482.91506453704</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I23" t="n">
-        <v>184.46</v>
+        <v>6.02</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.21</v>
+        <v>8.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2</v>
+        <v>8.81</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,18 +1939,18 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01</v>
+        <v>0.3</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1362491459</v>
+        <v>1393287040</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1959,35 +1959,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.228</v>
+        <v>0.2503</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G24" t="n">
-        <v>88.67</v>
+        <v>5.811</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45483.778784375</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I24" t="n">
-        <v>87.81</v>
+        <v>6.02</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.22</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>20.02</v>
+        <v>1.51</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1362491459</v>
+        <v>1403180431</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0001</v>
+        <v>0.2773</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45464.66139070602</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G25" t="n">
-        <v>88.67</v>
+        <v>5.84</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45483.77897271991</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I25" t="n">
-        <v>87.81999999999999</v>
+        <v>6.02</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.01</v>
+        <v>1.62</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01</v>
+        <v>1.67</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,18 +2065,18 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1375856858</v>
+        <v>1403180445</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2085,35 +2085,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0026</v>
+        <v>0.0092</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45478.65581936343</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G26" t="n">
-        <v>188.48</v>
+        <v>5.836</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45483.77908715278</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I26" t="n">
-        <v>190.3</v>
+        <v>6.02</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>0.05</v>
       </c>
       <c r="M26" t="n">
-        <v>0.49</v>
+        <v>0.06</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2128,18 +2128,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1377584836</v>
+        <v>1393735509</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,35 +2148,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4828</v>
+        <v>0.0366</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G27" t="n">
-        <v>41.87</v>
+        <v>67.37</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45484.66768255787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I27" t="n">
-        <v>42.35</v>
+        <v>71.16</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20.21</v>
+        <v>2.47</v>
       </c>
       <c r="M27" t="n">
-        <v>20.45</v>
+        <v>2.6</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1377584836</v>
+        <v>1395218355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,35 +2211,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0013</v>
+        <v>0.074</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45481.71107186343</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G28" t="n">
-        <v>41.87</v>
+        <v>67.13</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45484.6678155787</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I28" t="n">
-        <v>42.35</v>
+        <v>71.16</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0.05</v>
+        <v>4.97</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>5.27</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,18 +2254,18 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1350885655</v>
+        <v>1403166009</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2274,35 +2274,35 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0234</v>
+        <v>0.0362</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45453.9133437037</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G29" t="n">
-        <v>427.17</v>
+        <v>68.05</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45484.67834626157</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I29" t="n">
-        <v>458.18</v>
+        <v>71.16</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>2.46</v>
       </c>
       <c r="M29" t="n">
-        <v>10.72</v>
+        <v>2.58</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,18 +2317,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1414374074</v>
+        <v>1403177543</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2337,35 +2337,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0481</v>
+        <v>0.0368</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45511.72337184028</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G30" t="n">
-        <v>311.85</v>
+        <v>68.045</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45511.85963359954</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I30" t="n">
-        <v>308</v>
+        <v>71.16</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>14.81</v>
+        <v>2.62</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,18 +2380,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.19</v>
+        <v>0.12</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1414372067</v>
+        <v>1403180429</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2400,23 +2400,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0575</v>
+        <v>0.0733</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45511.72271230324</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G31" t="n">
-        <v>260.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45551.90509481481</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I31" t="n">
-        <v>290.19</v>
+        <v>71.16</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>4.99</v>
       </c>
       <c r="M31" t="n">
-        <v>16.69</v>
+        <v>5.22</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>0.23</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1377764546</v>
+        <v>1403180445</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,35 +2463,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.9908</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G32" t="n">
-        <v>244.47</v>
+        <v>5.836</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45559.6505103125</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I32" t="n">
-        <v>196.86</v>
+        <v>6.027</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>19.02</v>
+        <v>5.78</v>
       </c>
       <c r="M32" t="n">
-        <v>15.32</v>
+        <v>5.97</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-3.7</v>
+        <v>0.18</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1377764546</v>
+        <v>1393281432</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0051</v>
+        <v>0.1102</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45481.77934608796</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G33" t="n">
-        <v>244.47</v>
+        <v>5.981</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45559.65105630787</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I33" t="n">
-        <v>196.91</v>
+        <v>6.176</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>0.66</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.25</v>
+        <v>0.02</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1380259753</v>
+        <v>1393301698</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,35 +2589,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.131</v>
+        <v>0.1401</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45483.78714761574</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G34" t="n">
-        <v>190.71</v>
+        <v>5.99</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45560.82029805556</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I34" t="n">
-        <v>161.87</v>
+        <v>6.176</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>24.98</v>
+        <v>0.84</v>
       </c>
       <c r="M34" t="n">
-        <v>21.2</v>
+        <v>0.87</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,57 +2632,59 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-3.78</v>
+        <v>0.03</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1509051251</v>
+        <v>1403180427</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.4203</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45590.72843084491</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G35" t="n">
-        <v>19.8731</v>
+        <v>5.989</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45590.7303809838</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I35" t="n">
-        <v>19.8835</v>
+        <v>6.176</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.6</v>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -2693,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1.05</v>
+        <v>0.08</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1393281432</v>
+        <v>1347626622</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2713,35 +2715,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.632</v>
+        <v>0.1488</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G36" t="n">
-        <v>5.981</v>
+        <v>67.2</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I36" t="n">
-        <v>5.967</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.78</v>
+        <v>10</v>
       </c>
       <c r="M36" t="n">
-        <v>3.77</v>
+        <v>10.36</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2756,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.01</v>
+        <v>0.36</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1393281260</v>
+        <v>1362562387</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2776,35 +2778,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5612</v>
+        <v>0.202</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G37" t="n">
-        <v>5.812</v>
+        <v>100.78</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I37" t="n">
-        <v>5.81</v>
+        <v>100.83</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.26</v>
+        <v>20.36</v>
       </c>
       <c r="M37" t="n">
-        <v>3.26</v>
+        <v>20.37</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2819,18 +2821,18 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1508055372</v>
+        <v>1362488938</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2839,19 +2841,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.02</v>
+        <v>0.2742</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45590.22327229167</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G38" t="n">
-        <v>19.8369</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45590.73070716435</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I38" t="n">
-        <v>19.8761</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2863,13 +2865,15 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19.82</v>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -2880,18 +2884,18 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.94</v>
+        <v>-0.18</v>
       </c>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1393281260</v>
+        <v>1375967973</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2900,35 +2904,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.555</v>
+        <v>0.109</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G39" t="n">
-        <v>5.812</v>
+        <v>183</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I39" t="n">
-        <v>5.801</v>
+        <v>186.5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.23</v>
+        <v>19.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>20.33</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2943,18 +2947,18 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.01</v>
+        <v>0.39</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1393281432</v>
+        <v>1375856858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2963,35 +2967,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.4344</v>
+        <v>0.1052</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G40" t="n">
-        <v>5.981</v>
+        <v>188.48</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45481.82631694445</v>
       </c>
       <c r="I40" t="n">
-        <v>5.968</v>
+        <v>189.21</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>19.83</v>
       </c>
       <c r="M40" t="n">
-        <v>2.59</v>
+        <v>19.9</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -3006,18 +3010,18 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1393281260</v>
+        <v>1357595824</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>LEVI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3029,32 +3033,32 @@
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45460.64611910879</v>
       </c>
       <c r="G41" t="n">
-        <v>5.812</v>
+        <v>22.89</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45482.71325359954</v>
       </c>
       <c r="I41" t="n">
-        <v>5.814</v>
+        <v>18.62</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.81</v>
+        <v>22.89</v>
       </c>
       <c r="M41" t="n">
-        <v>5.81</v>
+        <v>18.62</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3069,18 +3073,18 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>-4.27</v>
       </c>
       <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1393281432</v>
+        <v>1375967973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3089,35 +3093,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.0014</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G42" t="n">
-        <v>5.981</v>
+        <v>183</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I42" t="n">
-        <v>5.978</v>
+        <v>182.97</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.98</v>
+        <v>0.26</v>
       </c>
       <c r="M42" t="n">
-        <v>5.98</v>
+        <v>0.26</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3139,11 +3143,11 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1512925323</v>
+        <v>1377834040</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3152,19 +3156,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01</v>
+        <v>0.1077</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45594.79117905092</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G43" t="n">
-        <v>20.0663</v>
+        <v>186.7</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45595.55638846065</v>
+        <v>45482.72996420139</v>
       </c>
       <c r="I43" t="n">
-        <v>20.1405</v>
+        <v>182.97</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3176,35 +3180,37 @@
           <t>xStation Mobile iOS</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="M43" t="n">
+        <v>19.71</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="n">
-        <v>5</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.68</v>
+        <v>-0.39</v>
       </c>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1393281260</v>
+        <v>1377407433</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3213,35 +3219,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.4206</v>
+        <v>0.0771</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G44" t="n">
-        <v>5.812</v>
+        <v>129.48</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45482.86465565972</v>
       </c>
       <c r="I44" t="n">
-        <v>5.826</v>
+        <v>130.75</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.44</v>
+        <v>9.98</v>
       </c>
       <c r="M44" t="n">
-        <v>2.45</v>
+        <v>10.08</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3256,18 +3262,18 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1393281432</v>
+        <v>1377407433</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3276,35 +3282,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.4033</v>
+        <v>0.0001</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.65801625</v>
       </c>
       <c r="G45" t="n">
-        <v>5.981</v>
+        <v>129.48</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45482.91500505787</v>
       </c>
       <c r="I45" t="n">
-        <v>5.98</v>
+        <v>131.24</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.41</v>
+        <v>0.01</v>
       </c>
       <c r="M45" t="n">
-        <v>2.41</v>
+        <v>0.01</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -3326,11 +3332,11 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1393281432</v>
+        <v>1377834040</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3339,35 +3345,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.4201</v>
+        <v>0.0011</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45481.83128234954</v>
       </c>
       <c r="G46" t="n">
-        <v>5.981</v>
+        <v>186.7</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45504.64158128472</v>
+        <v>45482.91506453704</v>
       </c>
       <c r="I46" t="n">
-        <v>5.98</v>
+        <v>184.46</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.51</v>
+        <v>0.21</v>
       </c>
       <c r="M46" t="n">
-        <v>2.51</v>
+        <v>0.2</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3382,18 +3388,18 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1393281432</v>
+        <v>1362491459</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3402,35 +3408,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0.228</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66139070602</v>
       </c>
       <c r="G47" t="n">
-        <v>5.981</v>
+        <v>88.67</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45483.778784375</v>
       </c>
       <c r="I47" t="n">
-        <v>6.186</v>
+        <v>87.81</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5.98</v>
+        <v>20.22</v>
       </c>
       <c r="M47" t="n">
-        <v>6.19</v>
+        <v>20.02</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3445,61 +3451,59 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.21</v>
+        <v>-0.2</v>
       </c>
       <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1514707570</v>
+        <v>1362491459</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>45464.66139070602</v>
+      </c>
+      <c r="G48" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>45483.77897271991</v>
+      </c>
+      <c r="I48" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
         <v>0.01</v>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>45595.88186449074</v>
-      </c>
-      <c r="G48" t="n">
-        <v>20.1597</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>45595.94583810185</v>
-      </c>
-      <c r="I48" t="n">
-        <v>20.1911</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>xStation Mobile iOS</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="O48" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="P48" t="n">
-        <v>5</v>
-      </c>
+      <c r="M48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -3510,22 +3514,18 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>[S/L]</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1393281260</v>
+        <v>1375856858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3534,35 +3534,35 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.4632</v>
+        <v>0.0026</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45478.65581936343</v>
       </c>
       <c r="G49" t="n">
-        <v>5.812</v>
+        <v>188.48</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45483.77908715278</v>
       </c>
       <c r="I49" t="n">
-        <v>6.02</v>
+        <v>190.3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>8.5</v>
+        <v>0.49</v>
       </c>
       <c r="M49" t="n">
-        <v>8.81</v>
+        <v>0.49</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3577,18 +3577,18 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1393287040</v>
+        <v>1377584836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3597,35 +3597,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.2503</v>
+        <v>0.4828</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G50" t="n">
-        <v>5.811</v>
+        <v>41.87</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.66768255787</v>
       </c>
       <c r="I50" t="n">
-        <v>6.02</v>
+        <v>42.35</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.45</v>
+        <v>20.21</v>
       </c>
       <c r="M50" t="n">
-        <v>1.51</v>
+        <v>20.45</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -3640,18 +3640,18 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1403180431</v>
+        <v>1377584836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3660,35 +3660,35 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.2773</v>
+        <v>0.0013</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45481.71107186343</v>
       </c>
       <c r="G51" t="n">
-        <v>5.84</v>
+        <v>41.87</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.6678155787</v>
       </c>
       <c r="I51" t="n">
-        <v>6.02</v>
+        <v>42.35</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.62</v>
+        <v>0.05</v>
       </c>
       <c r="M51" t="n">
-        <v>1.67</v>
+        <v>0.06</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -3703,18 +3703,18 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1403180445</v>
+        <v>1350885655</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3723,35 +3723,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0092</v>
+        <v>0.0234</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45453.9133437037</v>
       </c>
       <c r="G52" t="n">
-        <v>5.836</v>
+        <v>427.17</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45484.67834626157</v>
       </c>
       <c r="I52" t="n">
-        <v>6.02</v>
+        <v>458.18</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="M52" t="n">
-        <v>0.06</v>
+        <v>10.72</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -3766,18 +3766,18 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.01</v>
+        <v>0.72</v>
       </c>
       <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1393735509</v>
+        <v>1414374074</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3786,35 +3786,35 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0366</v>
+        <v>0.0481</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45511.72337184028</v>
       </c>
       <c r="G53" t="n">
-        <v>67.37</v>
+        <v>311.85</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45511.85963359954</v>
       </c>
       <c r="I53" t="n">
-        <v>71.16</v>
+        <v>308</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.47</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>2.6</v>
+        <v>14.81</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -3829,18 +3829,18 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.13</v>
+        <v>-0.19</v>
       </c>
       <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1395218355</v>
+        <v>1414372067</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3849,35 +3849,35 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.074</v>
+        <v>0.0575</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45511.72271230324</v>
       </c>
       <c r="G54" t="n">
-        <v>67.13</v>
+        <v>260.8</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45551.90509481481</v>
       </c>
       <c r="I54" t="n">
-        <v>71.16</v>
+        <v>290.19</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>xStation 5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
       <c r="L54" t="n">
-        <v>4.97</v>
+        <v>15</v>
       </c>
       <c r="M54" t="n">
-        <v>5.27</v>
+        <v>16.69</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3892,18 +3892,18 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.3</v>
+        <v>1.69</v>
       </c>
       <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1403166009</v>
+        <v>1377764546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3912,35 +3912,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0362</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G55" t="n">
-        <v>68.05</v>
+        <v>244.47</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45559.6505103125</v>
       </c>
       <c r="I55" t="n">
-        <v>71.16</v>
+        <v>196.86</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.46</v>
+        <v>19.02</v>
       </c>
       <c r="M55" t="n">
-        <v>2.58</v>
+        <v>15.32</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -3955,18 +3955,18 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.12</v>
+        <v>-3.7</v>
       </c>
       <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1403177543</v>
+        <v>1377764546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3975,35 +3975,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0368</v>
+        <v>0.0051</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45481.77934608796</v>
       </c>
       <c r="G56" t="n">
-        <v>68.045</v>
+        <v>244.47</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45559.65105630787</v>
       </c>
       <c r="I56" t="n">
-        <v>71.16</v>
+        <v>196.91</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="M56" t="n">
-        <v>2.62</v>
+        <v>1</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
@@ -4018,18 +4018,18 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1403180429</v>
+        <v>1380259753</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4038,35 +4038,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0733</v>
+        <v>0.131</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45483.78714761574</v>
       </c>
       <c r="G57" t="n">
-        <v>68.01000000000001</v>
+        <v>190.71</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45560.82029805556</v>
       </c>
       <c r="I57" t="n">
-        <v>71.16</v>
+        <v>161.87</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.99</v>
+        <v>24.98</v>
       </c>
       <c r="M57" t="n">
-        <v>5.22</v>
+        <v>21.2</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -4081,59 +4081,57 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.23</v>
+        <v>-3.78</v>
       </c>
       <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1403180445</v>
+        <v>1509051251</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9908</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45590.72843084491</v>
       </c>
       <c r="G58" t="n">
-        <v>5.836</v>
+        <v>19.8731</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45590.7303809838</v>
       </c>
       <c r="I58" t="n">
-        <v>6.027</v>
+        <v>19.8835</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M58" t="n">
-        <v>5.97</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
@@ -4144,39 +4142,39 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.18</v>
+        <v>-1.05</v>
       </c>
       <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1516787001</v>
+        <v>1508055372</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45597.1323971875</v>
+        <v>45590.22327229167</v>
       </c>
       <c r="G59" t="n">
-        <v>2748.04</v>
+        <v>19.8369</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45597.13338680556</v>
+        <v>45590.73070716435</v>
       </c>
       <c r="I59" t="n">
-        <v>2747.79</v>
+        <v>19.8761</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4193,7 +4191,7 @@
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>13.74</v>
+        <v>10</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4205,18 +4203,18 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.25</v>
+        <v>3.94</v>
       </c>
       <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1393281432</v>
+        <v>1512925323</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4225,102 +4223,102 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.1102</v>
+        <v>0.01</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45594.79117905092</v>
       </c>
       <c r="G60" t="n">
-        <v>5.981</v>
+        <v>20.0663</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45595.55638846065</v>
       </c>
       <c r="I60" t="n">
-        <v>6.176</v>
+        <v>20.1405</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.68</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>5</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.02</v>
+        <v>3.68</v>
       </c>
       <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1393301698</v>
+        <v>1514707570</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.1401</v>
+        <v>0.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45595.88186449074</v>
       </c>
       <c r="G61" t="n">
-        <v>5.99</v>
+        <v>20.1597</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45595.94583810185</v>
       </c>
       <c r="I61" t="n">
-        <v>6.176</v>
+        <v>20.1911</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O61" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="P61" t="n">
+        <v>5</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
@@ -4331,59 +4329,61 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
+        <v>-1.56</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>[S/L]</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1403180427</v>
+        <v>1516787001</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>GC=F</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.4203</v>
+        <v>0.01</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45597.1323971875</v>
       </c>
       <c r="G62" t="n">
-        <v>5.989</v>
+        <v>2748.04</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45597.13338680556</v>
       </c>
       <c r="I62" t="n">
-        <v>6.176</v>
+        <v>2747.79</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>xStation 5</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M62" t="n">
-        <v>2.6</v>
-      </c>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>13.74</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="U62" t="inlineStr"/>
     </row>

--- a/Stock Selection/CLOSED POSITION HISTORY.xlsx
+++ b/Stock Selection/CLOSED POSITION HISTORY.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U277"/>
+  <dimension ref="A1:U366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,11 +997,11 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1349530190</v>
+        <v>1393281432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1010,35 +1010,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.051</v>
+        <v>0.632</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45452.64409975694</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G9" t="n">
-        <v>118.42</v>
+        <v>5.981</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45464.64586949074</v>
+        <v>45496.61775418981</v>
       </c>
       <c r="I9" t="n">
-        <v>126.76</v>
+        <v>5.967</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.04</v>
+        <v>3.78</v>
       </c>
       <c r="M9" t="n">
-        <v>6.46</v>
+        <v>3.77</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1053,22 +1053,18 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>NVDA.US split 10 for 1</t>
-        </is>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1357737013</v>
+        <v>1349530190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1077,23 +1073,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0115</v>
+        <v>0.051</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45460.68557657408</v>
+        <v>45452.64409975694</v>
       </c>
       <c r="G10" t="n">
-        <v>1797.13</v>
+        <v>118.42</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45464.65982668981</v>
+        <v>45464.64586949074</v>
       </c>
       <c r="I10" t="n">
-        <v>1686.26</v>
+        <v>126.76</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>correction</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1102,10 +1098,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>20.67</v>
+        <v>6.04</v>
       </c>
       <c r="M10" t="n">
-        <v>19.39</v>
+        <v>6.46</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1120,18 +1116,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>0.42</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NVDA.US split 10 for 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1362492338</v>
+        <v>1393281260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1140,35 +1140,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2806</v>
+        <v>0.5612</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45464.66150739583</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G11" t="n">
-        <v>71.61</v>
+        <v>5.812</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45464.66725368056</v>
+        <v>45496.61775451389</v>
       </c>
       <c r="I11" t="n">
-        <v>70.95999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>20.09</v>
+        <v>3.26</v>
       </c>
       <c r="M11" t="n">
-        <v>19.91</v>
+        <v>3.26</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1183,18 +1183,18 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1342641165</v>
+        <v>1357737013</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1203,19 +1203,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1322</v>
+        <v>0.0115</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45446.64586891203</v>
+        <v>45460.68557657408</v>
       </c>
       <c r="G12" t="n">
-        <v>155.59</v>
+        <v>1797.13</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45478.65186430555</v>
+        <v>45464.65982668981</v>
       </c>
       <c r="I12" t="n">
-        <v>183.6</v>
+        <v>1686.26</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>20.57</v>
+        <v>20.67</v>
       </c>
       <c r="M12" t="n">
-        <v>24.27</v>
+        <v>19.39</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1246,18 +1246,18 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>-1.28</v>
       </c>
       <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1393281432</v>
+        <v>1393281260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.632</v>
+        <v>0.555</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G13" t="n">
-        <v>5.981</v>
+        <v>5.812</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45496.61775418981</v>
+        <v>45497.65423505787</v>
       </c>
       <c r="I13" t="n">
-        <v>5.967</v>
+        <v>5.801</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.78</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.77</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1316,11 +1316,11 @@
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1393281260</v>
+        <v>1393281432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1329,19 +1329,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5612</v>
+        <v>0.4344</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G14" t="n">
-        <v>5.812</v>
+        <v>5.981</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45496.61775451389</v>
+        <v>45497.65423550926</v>
       </c>
       <c r="I14" t="n">
-        <v>5.81</v>
+        <v>5.968</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.26</v>
+        <v>2.59</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="U14" t="inlineStr"/>
     </row>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.555</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>45496.37564016203</v>
@@ -1401,10 +1401,10 @@
         <v>5.812</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45497.65423505787</v>
+        <v>45497.65424290509</v>
       </c>
       <c r="I15" t="n">
-        <v>5.801</v>
+        <v>5.814</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.23</v>
+        <v>5.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.22</v>
+        <v>5.81</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U15" t="inlineStr"/>
     </row>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4344</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>45496.37566553241</v>
@@ -1464,10 +1464,10 @@
         <v>5.981</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45497.65423550926</v>
+        <v>45497.65424459491</v>
       </c>
       <c r="I16" t="n">
-        <v>5.968</v>
+        <v>5.978</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>5.98</v>
       </c>
       <c r="M16" t="n">
-        <v>2.59</v>
+        <v>5.98</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1498,18 +1498,18 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1393281260</v>
+        <v>1362492338</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1518,35 +1518,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.2806</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45464.66150739583</v>
       </c>
       <c r="G17" t="n">
-        <v>5.812</v>
+        <v>71.61</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45497.65424290509</v>
+        <v>45464.66725368056</v>
       </c>
       <c r="I17" t="n">
-        <v>5.814</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.81</v>
+        <v>20.09</v>
       </c>
       <c r="M17" t="n">
-        <v>5.81</v>
+        <v>19.91</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1561,18 +1561,18 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1393281432</v>
+        <v>1393281260</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.4206</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G18" t="n">
-        <v>5.981</v>
+        <v>5.812</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45497.65424459491</v>
+        <v>45504.63556305556</v>
       </c>
       <c r="I18" t="n">
-        <v>5.978</v>
+        <v>5.826</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.98</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>5.98</v>
+        <v>2.45</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1393281260</v>
+        <v>1393281432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1644,19 +1644,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4206</v>
+        <v>0.4033</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G19" t="n">
-        <v>5.812</v>
+        <v>5.981</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45504.63556305556</v>
+        <v>45504.6355634375</v>
       </c>
       <c r="I19" t="n">
-        <v>5.826</v>
+        <v>5.98</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1687,18 +1687,18 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1393281432</v>
+        <v>1342641165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1707,35 +1707,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4033</v>
+        <v>0.1322</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45446.64586891203</v>
       </c>
       <c r="G20" t="n">
-        <v>5.981</v>
+        <v>155.59</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45504.6355634375</v>
+        <v>45478.65186430555</v>
       </c>
       <c r="I20" t="n">
-        <v>5.98</v>
+        <v>183.6</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.41</v>
+        <v>20.57</v>
       </c>
       <c r="M20" t="n">
-        <v>2.41</v>
+        <v>24.27</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="inlineStr"/>
     </row>
@@ -1820,11 +1820,11 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1393281432</v>
+        <v>1347626622</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1833,35 +1833,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.1488</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45449.86760850695</v>
       </c>
       <c r="G22" t="n">
-        <v>5.981</v>
+        <v>67.2</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45726.37522701389</v>
+        <v>45481.65772898148</v>
       </c>
       <c r="I22" t="n">
-        <v>6.186</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.98</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>6.19</v>
+        <v>10.36</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1876,18 +1876,18 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1393281260</v>
+        <v>1393281432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.4632</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45496.37564016203</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G23" t="n">
-        <v>5.812</v>
+        <v>5.981</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45726.37526289352</v>
+        <v>45726.37522701389</v>
       </c>
       <c r="I23" t="n">
-        <v>6.02</v>
+        <v>6.186</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8.5</v>
+        <v>5.98</v>
       </c>
       <c r="M23" t="n">
-        <v>8.81</v>
+        <v>6.19</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1939,14 +1939,14 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1393287040</v>
+        <v>1393281260</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2503</v>
+        <v>1.4632</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45496.37755140047</v>
+        <v>45496.37564016203</v>
       </c>
       <c r="G24" t="n">
-        <v>5.811</v>
+        <v>5.812</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>45726.37526289352</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>8.5</v>
       </c>
       <c r="M24" t="n">
-        <v>1.51</v>
+        <v>8.81</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2002,14 +2002,14 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1403180431</v>
+        <v>1393287040</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.2773</v>
+        <v>0.2503</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45504.64299350695</v>
+        <v>45496.37755140047</v>
       </c>
       <c r="G25" t="n">
-        <v>5.84</v>
+        <v>5.811</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>45726.37526289352</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2065,14 +2065,14 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1403180445</v>
+        <v>1403180431</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0092</v>
+        <v>0.2773</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45504.64299350695</v>
       </c>
       <c r="G26" t="n">
-        <v>5.836</v>
+        <v>5.84</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>45726.37526289352</v>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.05</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06</v>
+        <v>1.67</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2128,18 +2128,18 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1393735509</v>
+        <v>1403180445</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2148,19 +2148,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0366</v>
+        <v>0.0092</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45496.61777673611</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G27" t="n">
-        <v>67.37</v>
+        <v>5.836</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45726.37526289352</v>
       </c>
       <c r="I27" t="n">
-        <v>71.16</v>
+        <v>6.02</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.47</v>
+        <v>0.05</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6</v>
+        <v>0.06</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2191,18 +2191,18 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1395218355</v>
+        <v>1362562387</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,35 +2211,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.074</v>
+        <v>0.202</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45497.65423574074</v>
+        <v>45464.67381712963</v>
       </c>
       <c r="G28" t="n">
-        <v>67.13</v>
+        <v>100.78</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45726.37603653935</v>
+        <v>45481.67021972223</v>
       </c>
       <c r="I28" t="n">
-        <v>71.16</v>
+        <v>100.83</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.97</v>
+        <v>20.36</v>
       </c>
       <c r="M28" t="n">
-        <v>5.27</v>
+        <v>20.37</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2254,14 +2254,14 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1403166009</v>
+        <v>1393735509</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0362</v>
+        <v>0.0366</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45504.63556387732</v>
+        <v>45496.61777673611</v>
       </c>
       <c r="G29" t="n">
-        <v>68.05</v>
+        <v>67.37</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>45726.37603653935</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2317,14 +2317,14 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1403177543</v>
+        <v>1395218355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0368</v>
+        <v>0.074</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45504.64158137731</v>
+        <v>45497.65423574074</v>
       </c>
       <c r="G30" t="n">
-        <v>68.045</v>
+        <v>67.13</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>45726.37603653935</v>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>4.97</v>
       </c>
       <c r="M30" t="n">
-        <v>2.62</v>
+        <v>5.27</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2380,14 +2380,14 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1403180429</v>
+        <v>1403166009</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0733</v>
+        <v>0.0362</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45504.6429933912</v>
+        <v>45504.63556387732</v>
       </c>
       <c r="G31" t="n">
-        <v>68.01000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>45726.37603653935</v>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.99</v>
+        <v>2.46</v>
       </c>
       <c r="M31" t="n">
-        <v>5.22</v>
+        <v>2.58</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2443,18 +2443,18 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1403180445</v>
+        <v>1403177543</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2463,19 +2463,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9908</v>
+        <v>0.0368</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45504.64300175926</v>
+        <v>45504.64158137731</v>
       </c>
       <c r="G32" t="n">
-        <v>5.836</v>
+        <v>68.045</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45726.43231427083</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I32" t="n">
-        <v>6.027</v>
+        <v>71.16</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.78</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>5.97</v>
+        <v>2.62</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2506,18 +2506,18 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1393281432</v>
+        <v>1362488938</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2526,35 +2526,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1102</v>
+        <v>0.2742</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45496.37566553241</v>
+        <v>45464.66097233797</v>
       </c>
       <c r="G33" t="n">
-        <v>5.981</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45481.77903942129</v>
       </c>
       <c r="I33" t="n">
-        <v>6.176</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>xStation 5</t>
+          <t>xStation Mobile iOS</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.66</v>
+        <v>20</v>
       </c>
       <c r="M33" t="n">
-        <v>0.68</v>
+        <v>19.82</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2569,18 +2569,18 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1393301698</v>
+        <v>1403180429</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2589,19 +2589,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1401</v>
+        <v>0.0733</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45496.37886077546</v>
+        <v>45504.6429933912</v>
       </c>
       <c r="G34" t="n">
-        <v>5.99</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.37603653935</v>
       </c>
       <c r="I34" t="n">
-        <v>6.176</v>
+        <v>71.16</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0.84</v>
+        <v>4.99</v>
       </c>
       <c r="M34" t="n">
-        <v>0.87</v>
+        <v>5.22</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2632,18 +2632,18 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1403180427</v>
+        <v>1403180445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4203</v>
+        <v>0.9908</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45504.64299328704</v>
+        <v>45504.64300175926</v>
       </c>
       <c r="G35" t="n">
-        <v>5.989</v>
+        <v>5.836</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>45727.38638285879</v>
+        <v>45726.43231427083</v>
       </c>
       <c r="I35" t="n">
-        <v>6.176</v>
+        <v>6.027</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.52</v>
+        <v>5.78</v>
       </c>
       <c r="M35" t="n">
-        <v>2.6</v>
+        <v>5.97</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2695,18 +2695,18 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1347626622</v>
+        <v>1393281432</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2715,35 +2715,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1488</v>
+        <v>0.1102</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45449.86760850695</v>
+        <v>45496.37566553241</v>
       </c>
       <c r="G36" t="n">
-        <v>67.2</v>
+        <v>5.981</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45481.65772898148</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I36" t="n">
-        <v>69.65000000000001</v>
+        <v>6.176</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>10</v>
+        <v>0.66</v>
       </c>
       <c r="M36" t="n">
-        <v>10.36</v>
+        <v>0.68</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2758,18 +2758,18 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.36</v>
+        <v>0.02</v>
       </c>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1362562387</v>
+        <v>1393301698</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2778,35 +2778,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.202</v>
+        <v>0.1401</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45464.67381712963</v>
+        <v>45496.37886077546</v>
       </c>
       <c r="G37" t="n">
-        <v>100.78</v>
+        <v>5.99</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45481.67021972223</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I37" t="n">
-        <v>100.83</v>
+        <v>6.176</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>20.36</v>
+        <v>0.84</v>
       </c>
       <c r="M37" t="n">
-        <v>20.37</v>
+        <v>0.87</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2821,18 +2821,18 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1362488938</v>
+        <v>1375967973</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2742</v>
+        <v>0.109</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45464.66097233797</v>
+        <v>45478.67815513889</v>
       </c>
       <c r="G38" t="n">
-        <v>72.93000000000001</v>
+        <v>183</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45481.77903942129</v>
+        <v>45481.81205453704</v>
       </c>
       <c r="I38" t="n">
-        <v>72.29000000000001</v>
+        <v>186.5</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>19.95</v>
       </c>
       <c r="M38" t="n">
-        <v>19.82</v>
+        <v>20.33</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2884,18 +2884,18 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.18</v>
+        <v>0.39</v>
       </c>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1375967973</v>
+        <v>1403180427</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2904,35 +2904,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.109</v>
+        <v>0.4203</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45478.67815513889</v>
+        <v>45504.64299328704</v>
       </c>
       <c r="G39" t="n">
-        <v>183</v>
+        <v>5.989</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45481.81205453704</v>
+        <v>45727.38638285879</v>
       </c>
       <c r="I39" t="n">
-        <v>186.5</v>
+        <v>6.176</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>xStation Mobile iOS</t>
+          <t>xStation 5</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>19.95</v>
+        <v>2.52</v>
       </c>
       <c r="M39" t="n">
-        <v>20.33</v>
+        <v>2.6</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="U39" t="inlineStr"/>
     </row>
@@ -18018,22 +18018,50 @@
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
+      <c r="B277" t="n">
+        <v>1358151307</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>45460.88529037037</v>
+      </c>
+      <c r="G277" t="n">
+        <v>165.93</v>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I277" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="M277" t="n">
+        <v>16.54</v>
+      </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
@@ -18041,15 +18069,5594 @@
         <v>0</v>
       </c>
       <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="U277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="n">
+        <v>1517510856</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>45597.61014833333</v>
+      </c>
+      <c r="G278" t="n">
+        <v>166.03</v>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I278" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>10</v>
+      </c>
+      <c r="M278" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="U278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="n">
+        <v>1559803221</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>45628.85951909722</v>
+      </c>
+      <c r="G279" t="n">
+        <v>162.85</v>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I279" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="M279" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>0</v>
+      </c>
+      <c r="T279" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="n">
+        <v>1563288050</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0.0626</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>45630.85583420139</v>
+      </c>
+      <c r="G280" t="n">
+        <v>159.74</v>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I280" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>10</v>
+      </c>
+      <c r="M280" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="U280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="n">
+        <v>1599431096</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>45663.73014715278</v>
+      </c>
+      <c r="G281" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I281" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="M281" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="n">
+        <v>0</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="n">
+        <v>0</v>
+      </c>
+      <c r="T281" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="U281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="n">
+        <v>1644788775</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>45693.85093373842</v>
+      </c>
+      <c r="G282" t="n">
+        <v>144.94</v>
+      </c>
+      <c r="H282" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I282" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M282" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="n">
+        <v>0</v>
+      </c>
+      <c r="T282" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="U282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="n">
+        <v>1824476420</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>45792.64714130787</v>
+      </c>
+      <c r="G283" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="H283" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I283" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>20</v>
+      </c>
+      <c r="M283" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="n">
+        <v>0</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="n">
+        <v>0</v>
+      </c>
+      <c r="T283" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="U283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="n">
+        <v>1867197360</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>45818.80265565973</v>
+      </c>
+      <c r="G284" t="n">
+        <v>131.96</v>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I284" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="M284" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="n">
+        <v>0</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="n">
+        <v>1880446729</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>45825.89315046297</v>
+      </c>
+      <c r="G285" t="n">
+        <v>129.62</v>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>45950.6970040625</v>
+      </c>
+      <c r="I285" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M285" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="n">
+        <v>1727591551</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>45743.77388565972</v>
+      </c>
+      <c r="G286" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>45950.69745444445</v>
+      </c>
+      <c r="I286" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="M286" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="n">
+        <v>0</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="n">
+        <v>0</v>
+      </c>
+      <c r="T286" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="U286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="n">
+        <v>1727591551</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>45743.77388565972</v>
+      </c>
+      <c r="G287" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>45950.69746504629</v>
+      </c>
+      <c r="I287" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="M287" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="n">
+        <v>0</v>
+      </c>
+      <c r="T287" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="n">
+        <v>1744930699</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>45751.74534408565</v>
+      </c>
+      <c r="G288" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>45950.69746504629</v>
+      </c>
+      <c r="I288" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="M288" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="n">
+        <v>0</v>
+      </c>
+      <c r="T288" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="n">
+        <v>2072501999</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ASML.AS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>45938.6787378125</v>
+      </c>
+      <c r="G289" t="n">
+        <v>844.9</v>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>45951.58098621527</v>
+      </c>
+      <c r="I289" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="M289" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
+        <v>0</v>
+      </c>
+      <c r="T289" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="n">
+        <v>2045990228</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>45925.79958339121</v>
+      </c>
+      <c r="G290" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="H290" s="2" t="n">
+        <v>45951.8738377662</v>
+      </c>
+      <c r="I290" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M290" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="n">
+        <v>1796453499</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>45777.64668211806</v>
+      </c>
+      <c r="G291" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>45952.64808331019</v>
+      </c>
+      <c r="I291" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="M291" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="n">
+        <v>0</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>0</v>
+      </c>
+      <c r="T291" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="n">
+        <v>2091123728</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>45945.66748790509</v>
+      </c>
+      <c r="G292" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>45952.64975872685</v>
+      </c>
+      <c r="I292" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="M292" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>0</v>
+      </c>
+      <c r="T292" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="U292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="n">
+        <v>2095264263</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>45946.74280219907</v>
+      </c>
+      <c r="G293" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>45952.64975872685</v>
+      </c>
+      <c r="I293" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>10</v>
+      </c>
+      <c r="M293" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="n">
+        <v>0</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
+      <c r="T293" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="U293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="n">
+        <v>1830410729</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0.1091</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>45796.82476541667</v>
+      </c>
+      <c r="G294" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>45953.8342396875</v>
+      </c>
+      <c r="I294" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="M294" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="n">
+        <v>2042979139</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>45924.70564366898</v>
+      </c>
+      <c r="G295" t="n">
+        <v>32</v>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>45953.8342396875</v>
+      </c>
+      <c r="I295" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M295" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>0</v>
+      </c>
+      <c r="T295" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="n">
+        <v>2050940197</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>45929.65257806713</v>
+      </c>
+      <c r="G296" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>45953.8342396875</v>
+      </c>
+      <c r="I296" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M296" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="n">
+        <v>1843469729</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>45804.66615434028</v>
+      </c>
+      <c r="G297" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H297" s="2" t="n">
+        <v>45954.65744255787</v>
+      </c>
+      <c r="I297" t="n">
+        <v>239.38</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="M297" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="n">
+        <v>0</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="n">
+        <v>0</v>
+      </c>
+      <c r="T297" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="U297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="n">
+        <v>1880443947</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>45825.89169543982</v>
+      </c>
+      <c r="G298" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>45954.65744255787</v>
+      </c>
+      <c r="I298" t="n">
+        <v>239.38</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M298" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="n">
+        <v>0</v>
+      </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
+      <c r="T298" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="U298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="n">
+        <v>1984829391</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>45890.71798842592</v>
+      </c>
+      <c r="G299" t="n">
+        <v>195.52</v>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>45954.65744255787</v>
+      </c>
+      <c r="I299" t="n">
+        <v>239.38</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M299" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="n">
+        <v>0</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="n">
+        <v>0</v>
+      </c>
+      <c r="T299" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="n">
+        <v>1997498400</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>45898.65380726852</v>
+      </c>
+      <c r="G300" t="n">
+        <v>197.26</v>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>45954.65744255787</v>
+      </c>
+      <c r="I300" t="n">
+        <v>239.38</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L300" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="n">
+        <v>0</v>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>0</v>
+      </c>
+      <c r="T300" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="n">
+        <v>2020498366</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>45911.68944652778</v>
+      </c>
+      <c r="G301" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>45958.60418344908</v>
+      </c>
+      <c r="I301" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L301" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="M301" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="n">
+        <v>0</v>
+      </c>
+      <c r="T301" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="U301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="n">
+        <v>2047762508</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>45926.65279315972</v>
+      </c>
+      <c r="G302" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>45958.60418344908</v>
+      </c>
+      <c r="I302" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L302" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T302" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="n">
+        <v>2047762608</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>1</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>45926.65280347222</v>
+      </c>
+      <c r="G303" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>45958.60418344908</v>
+      </c>
+      <c r="I303" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="M303" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="n">
+        <v>0</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="n">
+        <v>0</v>
+      </c>
+      <c r="T303" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="U303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="n">
+        <v>2091099618</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>45945.66309912037</v>
+      </c>
+      <c r="G304" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>45958.60418344908</v>
+      </c>
+      <c r="I304" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L304" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="n">
+        <v>0</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="n">
+        <v>0</v>
+      </c>
+      <c r="T304" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="n">
+        <v>2091099733</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>1</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>45945.66310534722</v>
+      </c>
+      <c r="G305" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="H305" s="2" t="n">
+        <v>45958.60418344908</v>
+      </c>
+      <c r="I305" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L305" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M305" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="n">
+        <v>0</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="U305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="n">
+        <v>2020498366</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>45911.68944652778</v>
+      </c>
+      <c r="G306" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="H306" s="2" t="n">
+        <v>45958.60421048611</v>
+      </c>
+      <c r="I306" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L306" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="n">
+        <v>0</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="U306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="n">
+        <v>1993444707</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>45896.67433202546</v>
+      </c>
+      <c r="G307" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>45958.60421048611</v>
+      </c>
+      <c r="I307" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
+        <v>10</v>
+      </c>
+      <c r="M307" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="n">
+        <v>0</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="n">
+        <v>0</v>
+      </c>
+      <c r="T307" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="n">
+        <v>2020498309</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>BBAR</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>45911.68944172453</v>
+      </c>
+      <c r="G308" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>45958.60421048611</v>
+      </c>
+      <c r="I308" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L308" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M308" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="n">
+        <v>0</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T308" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="n">
+        <v>2109291993</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>UEC</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>45951.83087202546</v>
+      </c>
+      <c r="G309" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>45958.60680231482</v>
+      </c>
+      <c r="I309" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="M309" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="n">
+        <v>0</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0</v>
+      </c>
+      <c r="S309" t="n">
+        <v>0</v>
+      </c>
+      <c r="T309" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="n">
+        <v>2109291993</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>UEC</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>45951.83087202546</v>
+      </c>
+      <c r="G310" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>45958.60681138889</v>
+      </c>
+      <c r="I310" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L310" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M310" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="n">
+        <v>0</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="n">
+        <v>0</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="n">
+        <v>2112207310</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>UEC</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>45952.6496053125</v>
+      </c>
+      <c r="G311" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>45958.60681138889</v>
+      </c>
+      <c r="I311" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L311" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M311" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="n">
+        <v>0</v>
+      </c>
+      <c r="R311" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" t="n">
+        <v>0</v>
+      </c>
+      <c r="T311" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="n">
+        <v>1744930699</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>45751.74534408565</v>
+      </c>
+      <c r="G312" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="H312" s="2" t="n">
+        <v>45958.74670788195</v>
+      </c>
+      <c r="I312" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L312" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M312" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="n">
+        <v>0</v>
+      </c>
+      <c r="T312" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="n">
+        <v>2047814173</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>IAPD.AS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>45926.65929415509</v>
+      </c>
+      <c r="G313" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>45959.70013888889</v>
+      </c>
+      <c r="I313" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L313" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M313" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="n">
+        <v>0</v>
+      </c>
+      <c r="R313" t="n">
+        <v>0</v>
+      </c>
+      <c r="S313" t="n">
+        <v>0</v>
+      </c>
+      <c r="T313" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="n">
+        <v>2065642904</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>IAPD.AS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>45936.61247827546</v>
+      </c>
+      <c r="G314" t="n">
+        <v>22.935</v>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>45959.70013888889</v>
+      </c>
+      <c r="I314" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L314" t="n">
+        <v>15</v>
+      </c>
+      <c r="M314" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="n">
+        <v>0</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="n">
+        <v>0</v>
+      </c>
+      <c r="T314" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="n">
+        <v>2091105918</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>IAPD.AS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>45945.66408121528</v>
+      </c>
+      <c r="G315" t="n">
+        <v>23.185</v>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>45959.70013888889</v>
+      </c>
+      <c r="I315" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>15</v>
+      </c>
+      <c r="M315" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="n">
+        <v>0</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
+      <c r="S315" t="n">
+        <v>0</v>
+      </c>
+      <c r="T315" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="U315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="n">
+        <v>2107046686</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>IAPD.AS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0.7369</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>45951.50496479167</v>
+      </c>
+      <c r="G316" t="n">
+        <v>23.235</v>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>45959.70013888889</v>
+      </c>
+      <c r="I316" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L316" t="n">
+        <v>20</v>
+      </c>
+      <c r="M316" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="n">
+        <v>0</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="n">
+        <v>0</v>
+      </c>
+      <c r="T316" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="n">
+        <v>2047814173</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>IAPD.AS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>45926.65929415509</v>
+      </c>
+      <c r="G317" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>45959.7001415162</v>
+      </c>
+      <c r="I317" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L317" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="M317" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="n">
+        <v>0</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="n">
+        <v>0</v>
+      </c>
+      <c r="T317" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="n">
+        <v>1997498400</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>45898.65380726852</v>
+      </c>
+      <c r="G318" t="n">
+        <v>197.26</v>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>45961.60668196759</v>
+      </c>
+      <c r="I318" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L318" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="M318" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="n">
+        <v>0</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0</v>
+      </c>
+      <c r="S318" t="n">
+        <v>0</v>
+      </c>
+      <c r="T318" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="n">
+        <v>2002501482</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>45902.6558890625</v>
+      </c>
+      <c r="G319" t="n">
+        <v>190.17</v>
+      </c>
+      <c r="H319" s="2" t="n">
+        <v>45961.60668196759</v>
+      </c>
+      <c r="I319" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L319" t="n">
+        <v>10</v>
+      </c>
+      <c r="M319" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="n">
+        <v>0</v>
+      </c>
+      <c r="R319" t="n">
+        <v>0</v>
+      </c>
+      <c r="S319" t="n">
+        <v>0</v>
+      </c>
+      <c r="T319" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="U319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="n">
+        <v>2109287572</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>45951.82903048611</v>
+      </c>
+      <c r="G320" t="n">
+        <v>225.32</v>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>45961.60668196759</v>
+      </c>
+      <c r="I320" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L320" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="M320" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="n">
+        <v>0</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" t="n">
+        <v>0</v>
+      </c>
+      <c r="T320" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="n">
+        <v>2109287572</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>45951.82903048611</v>
+      </c>
+      <c r="G321" t="n">
+        <v>225.32</v>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>45961.60844064815</v>
+      </c>
+      <c r="I321" t="n">
+        <v>263.08</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L321" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M321" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="n">
+        <v>0</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="n">
+        <v>1989207013</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>45894.6535458912</v>
+      </c>
+      <c r="G322" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>45964.65422170139</v>
+      </c>
+      <c r="I322" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L322" t="n">
+        <v>10</v>
+      </c>
+      <c r="M322" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="U322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="n">
+        <v>1997500170</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>45898.65406584491</v>
+      </c>
+      <c r="G323" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>45964.65422170139</v>
+      </c>
+      <c r="I323" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L323" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="M323" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="n">
+        <v>0</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="n">
+        <v>0</v>
+      </c>
+      <c r="T323" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="n">
+        <v>2141395344</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SEDG</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>45964.79154650463</v>
+      </c>
+      <c r="G324" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>45966.71830077546</v>
+      </c>
+      <c r="I324" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L324" t="n">
+        <v>10</v>
+      </c>
+      <c r="M324" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="n">
+        <v>0</v>
+      </c>
+      <c r="R324" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" t="n">
+        <v>0</v>
+      </c>
+      <c r="T324" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="n">
+        <v>1997500170</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>45898.65406584491</v>
+      </c>
+      <c r="G325" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>45966.71850699074</v>
+      </c>
+      <c r="I325" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L325" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M325" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="n">
+        <v>0</v>
+      </c>
+      <c r="T325" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="U325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="n">
+        <v>2042867331</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>45924.67994315972</v>
+      </c>
+      <c r="G326" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>45966.71850699074</v>
+      </c>
+      <c r="I326" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L326" t="n">
+        <v>10</v>
+      </c>
+      <c r="M326" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="n">
+        <v>0</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="n">
+        <v>0</v>
+      </c>
+      <c r="T326" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="n">
+        <v>2048501554</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>45926.83927930555</v>
+      </c>
+      <c r="G327" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="H327" s="2" t="n">
+        <v>45966.71850699074</v>
+      </c>
+      <c r="I327" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L327" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M327" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="n">
+        <v>0</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" t="n">
+        <v>0</v>
+      </c>
+      <c r="T327" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="U327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="n">
+        <v>2048501554</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>45926.83927930555</v>
+      </c>
+      <c r="G328" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="H328" s="2" t="n">
+        <v>45966.7185150463</v>
+      </c>
+      <c r="I328" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L328" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="M328" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="n">
+        <v>0</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0</v>
+      </c>
+      <c r="S328" t="n">
+        <v>0</v>
+      </c>
+      <c r="T328" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="n">
+        <v>2065818035</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>45936.64826233796</v>
+      </c>
+      <c r="G329" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H329" s="2" t="n">
+        <v>45966.7185150463</v>
+      </c>
+      <c r="I329" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L329" t="n">
+        <v>10</v>
+      </c>
+      <c r="M329" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="n">
+        <v>0</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="n">
+        <v>2078838036</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>45940.66691290509</v>
+      </c>
+      <c r="G330" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="H330" s="2" t="n">
+        <v>45966.7185150463</v>
+      </c>
+      <c r="I330" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L330" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="M330" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="n">
+        <v>0</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="n">
+        <v>0</v>
+      </c>
+      <c r="T330" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="n">
+        <v>2080281129</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>45940.89117033565</v>
+      </c>
+      <c r="G331" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>45966.7185150463</v>
+      </c>
+      <c r="I331" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L331" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="M331" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="n">
+        <v>0</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="n">
+        <v>0</v>
+      </c>
+      <c r="T331" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="n">
+        <v>2133520390</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>45960.62467003473</v>
+      </c>
+      <c r="G332" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>45966.7185150463</v>
+      </c>
+      <c r="I332" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L332" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="M332" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="n">
+        <v>0</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="n">
+        <v>0</v>
+      </c>
+      <c r="T332" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="n">
+        <v>2156679020</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>HCA</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>45971.64796355324</v>
+      </c>
+      <c r="G333" t="n">
+        <v>449.55</v>
+      </c>
+      <c r="H333" s="2" t="n">
+        <v>45973.79502746528</v>
+      </c>
+      <c r="I333" t="n">
+        <v>478.21</v>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L333" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M333" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="n">
+        <v>0</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="n">
+        <v>0</v>
+      </c>
+      <c r="T333" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="n">
+        <v>2123893596</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>45957.77249494213</v>
+      </c>
+      <c r="G334" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>45974.65359165509</v>
+      </c>
+      <c r="I334" t="n">
+        <v>114.73</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L334" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M334" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="n">
+        <v>0</v>
+      </c>
+      <c r="T334" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="n">
+        <v>1986476926</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>45891.66488920139</v>
+      </c>
+      <c r="G335" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="H335" s="2" t="n">
+        <v>45974.66803109954</v>
+      </c>
+      <c r="I335" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L335" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="M335" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="n">
+        <v>0</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="n">
+        <v>0</v>
+      </c>
+      <c r="T335" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="U335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="n">
+        <v>1845429956</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>45805.66180795139</v>
+      </c>
+      <c r="G336" t="n">
+        <v>13.275</v>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>45974.66881899306</v>
+      </c>
+      <c r="I336" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L336" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="M336" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="n">
+        <v>0</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="n">
+        <v>0</v>
+      </c>
+      <c r="T336" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="U336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="n">
+        <v>1845429980</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F337" s="2" t="n">
+        <v>45805.66181158565</v>
+      </c>
+      <c r="G337" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="H337" s="2" t="n">
+        <v>45974.66881899306</v>
+      </c>
+      <c r="I337" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L337" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="M337" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="n">
+        <v>0</v>
+      </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="n">
+        <v>0</v>
+      </c>
+      <c r="T337" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="n">
+        <v>1845429980</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="F338" s="2" t="n">
+        <v>45805.66181158565</v>
+      </c>
+      <c r="G338" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>45974.66882324074</v>
+      </c>
+      <c r="I338" t="n">
+        <v>18.985</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L338" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="M338" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>0</v>
+      </c>
+      <c r="S338" t="n">
+        <v>0</v>
+      </c>
+      <c r="T338" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="U338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="n">
+        <v>1869077157</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>45819.67426199074</v>
+      </c>
+      <c r="G339" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>45974.66882324074</v>
+      </c>
+      <c r="I339" t="n">
+        <v>18.985</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L339" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="M339" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
+      <c r="P339" t="inlineStr"/>
+      <c r="Q339" t="n">
+        <v>0</v>
+      </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="n">
+        <v>0</v>
+      </c>
+      <c r="T339" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="n">
+        <v>2160487534</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CSIQ</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>45972.87629090278</v>
+      </c>
+      <c r="G340" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>45975.71181398148</v>
+      </c>
+      <c r="I340" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="L340" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="M340" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="n">
+        <v>0</v>
+      </c>
+      <c r="R340" t="n">
+        <v>0</v>
+      </c>
+      <c r="S340" t="n">
+        <v>0</v>
+      </c>
+      <c r="T340" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="n">
+        <v>1599455288</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>45663.73750246528</v>
+      </c>
+      <c r="G341" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>45975.82115320602</v>
+      </c>
+      <c r="I341" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L341" t="n">
+        <v>10</v>
+      </c>
+      <c r="M341" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
+      <c r="P341" t="inlineStr"/>
+      <c r="Q341" t="n">
+        <v>0</v>
+      </c>
+      <c r="R341" t="n">
+        <v>0</v>
+      </c>
+      <c r="S341" t="n">
+        <v>0</v>
+      </c>
+      <c r="T341" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="U341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="n">
+        <v>1621495187</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>45678.83178153935</v>
+      </c>
+      <c r="G342" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="H342" s="2" t="n">
+        <v>45975.82115320602</v>
+      </c>
+      <c r="I342" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L342" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M342" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr"/>
+      <c r="P342" t="inlineStr"/>
+      <c r="Q342" t="n">
+        <v>0</v>
+      </c>
+      <c r="R342" t="n">
+        <v>0</v>
+      </c>
+      <c r="S342" t="n">
+        <v>0</v>
+      </c>
+      <c r="T342" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="U342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="n">
+        <v>1631475148</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>45685.83625184028</v>
+      </c>
+      <c r="G343" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="H343" s="2" t="n">
+        <v>45975.82115320602</v>
+      </c>
+      <c r="I343" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L343" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M343" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
+      <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="n">
+        <v>0</v>
+      </c>
+      <c r="R343" t="n">
+        <v>0</v>
+      </c>
+      <c r="S343" t="n">
+        <v>0</v>
+      </c>
+      <c r="T343" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="n">
+        <v>1631475148</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>45685.83625184028</v>
+      </c>
+      <c r="G344" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="H344" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I344" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L344" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="M344" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
+      <c r="P344" t="inlineStr"/>
+      <c r="Q344" t="n">
+        <v>0</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0</v>
+      </c>
+      <c r="S344" t="n">
+        <v>0</v>
+      </c>
+      <c r="T344" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="n">
+        <v>1635194117</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>45687.85228475695</v>
+      </c>
+      <c r="G345" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="H345" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I345" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L345" t="n">
+        <v>10</v>
+      </c>
+      <c r="M345" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr"/>
+      <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="n">
+        <v>0</v>
+      </c>
+      <c r="T345" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="U345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="n">
+        <v>1653137218</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>45699.85152174769</v>
+      </c>
+      <c r="G346" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="H346" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I346" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L346" t="n">
+        <v>10</v>
+      </c>
+      <c r="M346" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0</v>
+      </c>
+      <c r="S346" t="n">
+        <v>0</v>
+      </c>
+      <c r="T346" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="U346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="n">
+        <v>1666461140</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>45708.68207077546</v>
+      </c>
+      <c r="G347" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H347" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I347" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L347" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M347" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="n">
+        <v>0</v>
+      </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="n">
+        <v>0</v>
+      </c>
+      <c r="T347" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="U347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="n">
+        <v>1754302454</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>45755.88025306713</v>
+      </c>
+      <c r="G348" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="H348" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I348" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L348" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M348" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr"/>
+      <c r="P348" t="inlineStr"/>
+      <c r="Q348" t="n">
+        <v>0</v>
+      </c>
+      <c r="R348" t="n">
+        <v>0</v>
+      </c>
+      <c r="S348" t="n">
+        <v>0</v>
+      </c>
+      <c r="T348" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="U348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="n">
+        <v>1806977521</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>45783.8305749537</v>
+      </c>
+      <c r="G349" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H349" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I349" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L349" t="n">
+        <v>10</v>
+      </c>
+      <c r="M349" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="n">
+        <v>0</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="n">
+        <v>0</v>
+      </c>
+      <c r="T349" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="n">
+        <v>1888686062</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>45831.64964783565</v>
+      </c>
+      <c r="G350" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="H350" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I350" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L350" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M350" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="n">
+        <v>0</v>
+      </c>
+      <c r="T350" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="n">
+        <v>1895465445</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>45834.65394833333</v>
+      </c>
+      <c r="G351" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="H351" s="2" t="n">
+        <v>45975.82115746527</v>
+      </c>
+      <c r="I351" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L351" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M351" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="n">
+        <v>0</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="n">
+        <v>2152867309</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>45968.66867929398</v>
+      </c>
+      <c r="G352" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="H352" s="2" t="n">
+        <v>45978.67588634259</v>
+      </c>
+      <c r="I352" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L352" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M352" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="n">
+        <v>0</v>
+      </c>
+      <c r="R352" t="n">
+        <v>0</v>
+      </c>
+      <c r="S352" t="n">
+        <v>0</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="n">
+        <v>2165806168</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>45974.65783918981</v>
+      </c>
+      <c r="G353" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="H353" s="2" t="n">
+        <v>45978.67588634259</v>
+      </c>
+      <c r="I353" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L353" t="n">
+        <v>10</v>
+      </c>
+      <c r="M353" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr"/>
+      <c r="Q353" t="n">
+        <v>0</v>
+      </c>
+      <c r="R353" t="n">
+        <v>0</v>
+      </c>
+      <c r="S353" t="n">
+        <v>0</v>
+      </c>
+      <c r="T353" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="n">
+        <v>1744879358</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>45751.73925931713</v>
+      </c>
+      <c r="G354" t="n">
+        <v>148.09</v>
+      </c>
+      <c r="H354" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I354" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>xStation 5</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L354" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="M354" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" t="inlineStr"/>
+      <c r="Q354" t="n">
+        <v>0</v>
+      </c>
+      <c r="R354" t="n">
+        <v>0</v>
+      </c>
+      <c r="S354" t="n">
+        <v>0</v>
+      </c>
+      <c r="T354" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="n">
+        <v>1981010841</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>45888.84617726852</v>
+      </c>
+      <c r="G355" t="n">
+        <v>235.53</v>
+      </c>
+      <c r="H355" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I355" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L355" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M355" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0</v>
+      </c>
+      <c r="S355" t="n">
+        <v>0</v>
+      </c>
+      <c r="T355" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="n">
+        <v>1982273555</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>45889.64957435185</v>
+      </c>
+      <c r="G356" t="n">
+        <v>228</v>
+      </c>
+      <c r="H356" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I356" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L356" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M356" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="n">
+        <v>0</v>
+      </c>
+      <c r="T356" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="n">
+        <v>1997552824</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>45898.6562727662</v>
+      </c>
+      <c r="G357" t="n">
+        <v>233.17</v>
+      </c>
+      <c r="H357" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I357" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
+        <v>10</v>
+      </c>
+      <c r="M357" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0</v>
+      </c>
+      <c r="S357" t="n">
+        <v>0</v>
+      </c>
+      <c r="T357" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="n">
+        <v>2002503461</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>45902.65623501157</v>
+      </c>
+      <c r="G358" t="n">
+        <v>227.95</v>
+      </c>
+      <c r="H358" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I358" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L358" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M358" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="n">
+        <v>0</v>
+      </c>
+      <c r="T358" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="n">
+        <v>2047758738</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>45926.65183600695</v>
+      </c>
+      <c r="G359" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="H359" s="2" t="n">
+        <v>45978.88263240741</v>
+      </c>
+      <c r="I359" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L359" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M359" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="n">
+        <v>0</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="n">
+        <v>0</v>
+      </c>
+      <c r="T359" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="n">
+        <v>2029950407</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>45917.66293971065</v>
+      </c>
+      <c r="G360" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="H360" s="2" t="n">
+        <v>45982.57895226852</v>
+      </c>
+      <c r="I360" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L360" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="M360" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="n">
+        <v>0</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="n">
+        <v>0</v>
+      </c>
+      <c r="T360" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="U360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="n">
+        <v>2035164705</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>45919.66704454861</v>
+      </c>
+      <c r="G361" t="n">
+        <v>252.81</v>
+      </c>
+      <c r="H361" s="2" t="n">
+        <v>45982.57895226852</v>
+      </c>
+      <c r="I361" t="n">
+        <v>288.8</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L361" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M361" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="n">
+        <v>0</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" t="n">
+        <v>0</v>
+      </c>
+      <c r="T361" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="n">
+        <v>1869077157</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F362" s="2" t="n">
+        <v>45819.67426199074</v>
+      </c>
+      <c r="G362" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H362" s="2" t="n">
+        <v>45982.58014435185</v>
+      </c>
+      <c r="I362" t="n">
+        <v>17.665</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L362" t="n">
+        <v>0</v>
+      </c>
+      <c r="M362" t="n">
+        <v>0</v>
+      </c>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="n">
+        <v>0</v>
+      </c>
+      <c r="T362" t="n">
+        <v>0</v>
+      </c>
+      <c r="U362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="n">
+        <v>1869077178</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>45819.67426688658</v>
+      </c>
+      <c r="G363" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H363" s="2" t="n">
+        <v>45982.58014435185</v>
+      </c>
+      <c r="I363" t="n">
+        <v>17.665</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L363" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="M363" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
+      <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="n">
+        <v>0</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="n">
+        <v>0</v>
+      </c>
+      <c r="T363" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="U363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="n">
+        <v>1867196288</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>45818.80209082176</v>
+      </c>
+      <c r="G364" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="H364" s="2" t="n">
+        <v>45982.64775597222</v>
+      </c>
+      <c r="I364" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L364" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="M364" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="n">
+        <v>0</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="n">
+        <v>0</v>
+      </c>
+      <c r="T364" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="U364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="n">
+        <v>1923271589</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>45853.65794842593</v>
+      </c>
+      <c r="G365" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="H365" s="2" t="n">
+        <v>45982.64775597222</v>
+      </c>
+      <c r="I365" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L365" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="M365" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="n">
+        <v>0</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0</v>
+      </c>
+      <c r="S365" t="n">
+        <v>0</v>
+      </c>
+      <c r="T365" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="U365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="n">
+        <v>0</v>
+      </c>
+      <c r="R366" t="n">
         <v>-2.32</v>
       </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>244</v>
-      </c>
-      <c r="U277" t="inlineStr"/>
+      <c r="S366" t="n">
+        <v>0</v>
+      </c>
+      <c r="T366" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="U366" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
